--- a/output/stores_complete.xlsx
+++ b/output/stores_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A7A2B0-41DA-431E-ADBA-9F669AFC20CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8671124A-D54A-4D9A-9ED9-28E90EE65F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15706,7 +15706,7 @@
         <v>20</v>
       </c>
       <c r="I283" t="s">
-        <v>994</v>
+        <v>21</v>
       </c>
       <c r="J283">
         <v>87.37</v>

--- a/output/stores_complete.xlsx
+++ b/output/stores_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27036B97-3E65-4851-951A-D563C11A3651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F135B14D-2F0B-440D-A6B9-9DC7DE339368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3819,6 +3819,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3848,11 +3851,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8024,10 +8028,10 @@
         <v>18333333</v>
       </c>
       <c r="M88">
-        <v>-7.3658149999999996</v>
-      </c>
-      <c r="N88">
-        <v>111.367045</v>
+        <v>-3.0362812899999998</v>
+      </c>
+      <c r="N88" s="2">
+        <v>104.79204900000001</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">

--- a/output/stores_complete.xlsx
+++ b/output/stores_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F135B14D-2F0B-440D-A6B9-9DC7DE339368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8950074D-3367-44F8-9745-0A76A8EA0073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4162,6 +4162,7 @@
   <dimension ref="A1:N343"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4247,10 +4248,10 @@
         <v>73231900</v>
       </c>
       <c r="M2">
-        <v>-6.1587563000000003</v>
+        <v>-6.1574260000000001</v>
       </c>
       <c r="N2">
-        <v>106.90824259999999</v>
+        <v>106.90817</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -4291,10 +4292,10 @@
         <v>181353600</v>
       </c>
       <c r="M3">
-        <v>-6.2260106000000004</v>
+        <v>-6.226127</v>
       </c>
       <c r="N3">
-        <v>107.0010614</v>
+        <v>107.001076</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -4335,10 +4336,10 @@
         <v>36588430</v>
       </c>
       <c r="M4">
-        <v>-6.4842060000000004</v>
+        <v>-6.4816789999999997</v>
       </c>
       <c r="N4">
-        <v>106.842326</v>
+        <v>106.82447999999999</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -4379,10 +4380,10 @@
         <v>45805840</v>
       </c>
       <c r="M5">
-        <v>-6.1773182000000002</v>
+        <v>-6.1777129999999998</v>
       </c>
       <c r="N5">
-        <v>106.7914969</v>
+        <v>106.791349</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -4423,10 +4424,10 @@
         <v>42741000</v>
       </c>
       <c r="M6">
-        <v>-6.2407190000000003</v>
+        <v>-6.238105</v>
       </c>
       <c r="N6">
-        <v>106.628665</v>
+        <v>106.630724</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -4467,10 +4468,10 @@
         <v>67950738</v>
       </c>
       <c r="M7">
-        <v>-6.1823398999999997</v>
+        <v>-6.1961649999999997</v>
       </c>
       <c r="N7">
-        <v>106.8428715</v>
+        <v>106.821789</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -4511,10 +4512,10 @@
         <v>51003000</v>
       </c>
       <c r="M8">
-        <v>-6.9090600000000002</v>
+        <v>-6.9093</v>
       </c>
       <c r="N8">
-        <v>107.60883200000001</v>
+        <v>107.608763</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -4555,10 +4556,10 @@
         <v>40450688</v>
       </c>
       <c r="M9">
-        <v>-6.6013419000000004</v>
+        <v>-6.5921820000000002</v>
       </c>
       <c r="N9">
-        <v>106.8073342</v>
+        <v>106.80481</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -4599,10 +4600,10 @@
         <v>22322500</v>
       </c>
       <c r="M10">
-        <v>-7.2890600000000001</v>
+        <v>-7.2902480000000001</v>
       </c>
       <c r="N10">
-        <v>112.67560779999999</v>
+        <v>112.67453399999999</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -4643,10 +4644,10 @@
         <v>29166667</v>
       </c>
       <c r="M11">
-        <v>-5.1580674999999996</v>
+        <v>-5.1555590000000002</v>
       </c>
       <c r="N11">
-        <v>119.4466383</v>
+        <v>119.441374</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -4687,10 +4688,10 @@
         <v>31240000</v>
       </c>
       <c r="M12">
-        <v>-7.2622939999999998</v>
+        <v>-7.2620490000000002</v>
       </c>
       <c r="N12">
-        <v>112.737272</v>
+        <v>112.738867</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -4731,10 +4732,10 @@
         <v>22370956</v>
       </c>
       <c r="M13">
-        <v>-7.7821651000000003</v>
+        <v>-7.7836689999999997</v>
       </c>
       <c r="N13">
-        <v>110.40134449999999</v>
+        <v>110.392461</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -4775,10 +4776,10 @@
         <v>37500000</v>
       </c>
       <c r="M14">
-        <v>-6.4195932000000004</v>
+        <v>-6.387581</v>
       </c>
       <c r="N14">
-        <v>106.8284048</v>
+        <v>106.82740099999999</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -4819,10 +4820,10 @@
         <v>41052700</v>
       </c>
       <c r="M15">
-        <v>-6.2853849999999998</v>
+        <v>-6.2851499999999998</v>
       </c>
       <c r="N15">
-        <v>106.728295</v>
+        <v>106.72765</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -4863,10 +4864,10 @@
         <v>31715600</v>
       </c>
       <c r="M16">
-        <v>-6.1275785999999997</v>
+        <v>-6.1270759999999997</v>
       </c>
       <c r="N16">
-        <v>106.790964</v>
+        <v>106.79073</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -4907,10 +4908,10 @@
         <v>46800000</v>
       </c>
       <c r="M17">
-        <v>-6.2442757000000002</v>
+        <v>-6.2439629999999999</v>
       </c>
       <c r="N17">
-        <v>106.78348630000001</v>
+        <v>106.783115</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -4951,10 +4952,10 @@
         <v>14082250</v>
       </c>
       <c r="M18">
-        <v>-6.188015</v>
+        <v>-6.1883109999999997</v>
       </c>
       <c r="N18">
-        <v>106.739346</v>
+        <v>106.73880699999999</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -4995,10 +4996,10 @@
         <v>12446900</v>
       </c>
       <c r="M19">
-        <v>-5.1532849000000001</v>
+        <v>-5.1533389999999999</v>
       </c>
       <c r="N19">
-        <v>119.41730800000001</v>
+        <v>119.417417</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -5039,10 +5040,10 @@
         <v>48547570</v>
       </c>
       <c r="M20">
-        <v>-6.2712899999999996</v>
+        <v>-6.3307479999999998</v>
       </c>
       <c r="N20">
-        <v>106.86823800000001</v>
+        <v>107.13300099999999</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -5083,10 +5084,10 @@
         <v>51750000</v>
       </c>
       <c r="M21">
-        <v>-7.2764017000000001</v>
+        <v>-7.2759</v>
       </c>
       <c r="N21">
-        <v>112.7804951</v>
+        <v>112.77826899999999</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -5127,10 +5128,10 @@
         <v>38100000</v>
       </c>
       <c r="M22">
-        <v>-7.9769597000000001</v>
+        <v>-7.9773259999999997</v>
       </c>
       <c r="N22">
-        <v>112.6238701</v>
+        <v>112.62235699999999</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -5171,10 +5172,10 @@
         <v>14457352</v>
       </c>
       <c r="M23">
-        <v>1.4714045</v>
+        <v>1.466243</v>
       </c>
       <c r="N23">
-        <v>124.83123620000001</v>
+        <v>124.835188</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -5215,10 +5216,10 @@
         <v>38610000</v>
       </c>
       <c r="M24">
-        <v>-6.9139999999999997</v>
+        <v>-6.9150179999999999</v>
       </c>
       <c r="N24">
-        <v>107.60899000000001</v>
+        <v>107.591256</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -5259,10 +5260,10 @@
         <v>63250000</v>
       </c>
       <c r="M25">
-        <v>3.5894617000000002</v>
+        <v>3.5944389999999999</v>
       </c>
       <c r="N25">
-        <v>98.674162300000006</v>
+        <v>98.674274999999994</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -5303,10 +5304,10 @@
         <v>61710894</v>
       </c>
       <c r="M26">
-        <v>-6.9142580000000002</v>
+        <v>-6.9258920000000002</v>
       </c>
       <c r="N26">
-        <v>107.6021243</v>
+        <v>107.636404</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -5347,10 +5348,10 @@
         <v>112578000</v>
       </c>
       <c r="M27">
-        <v>-6.1882573000000001</v>
+        <v>-6.188707</v>
       </c>
       <c r="N27">
-        <v>106.7338886</v>
+        <v>106.73313899999999</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -5391,10 +5392,10 @@
         <v>25649400</v>
       </c>
       <c r="M28">
-        <v>-6.5673310000000003</v>
+        <v>-6.3958510000000004</v>
       </c>
       <c r="N28">
-        <v>106.843645</v>
+        <v>106.979793</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -5435,10 +5436,10 @@
         <v>18878400</v>
       </c>
       <c r="M29">
-        <v>-0.52562799999999998</v>
+        <v>-0.52501200000000003</v>
       </c>
       <c r="N29">
-        <v>117.116337</v>
+        <v>117.115939</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -5479,10 +5480,10 @@
         <v>26640000</v>
       </c>
       <c r="M30">
-        <v>3.5917222999999998</v>
+        <v>3.5951949999999999</v>
       </c>
       <c r="N30">
-        <v>98.6809899</v>
+        <v>98.672222000000005</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -5523,10 +5524,10 @@
         <v>55160000</v>
       </c>
       <c r="M31">
-        <v>-6.3044979999999997</v>
+        <v>-6.3044219999999997</v>
       </c>
       <c r="N31">
-        <v>106.642678</v>
+        <v>106.64401700000001</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -5567,10 +5568,10 @@
         <v>29250000</v>
       </c>
       <c r="M32">
-        <v>-6.9889510000000001</v>
+        <v>-6.9882949999999999</v>
       </c>
       <c r="N32">
-        <v>110.423849</v>
+        <v>110.423447</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -5611,10 +5612,10 @@
         <v>26161800</v>
       </c>
       <c r="M33">
-        <v>1.484108</v>
+        <v>1.4888520000000001</v>
       </c>
       <c r="N33">
-        <v>124.834057</v>
+        <v>124.837932</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -5655,10 +5656,10 @@
         <v>164780000</v>
       </c>
       <c r="M34">
-        <v>-6.3013310000000002</v>
+        <v>-6.3021589999999996</v>
       </c>
       <c r="N34">
-        <v>107.278344</v>
+        <v>107.27939499999999</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -5699,10 +5700,10 @@
         <v>17262760</v>
       </c>
       <c r="M35">
-        <v>-6.1451585</v>
+        <v>-6.1456350000000004</v>
       </c>
       <c r="N35">
-        <v>106.8914384</v>
+        <v>106.89216500000001</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -5743,10 +5744,10 @@
         <v>62800000</v>
       </c>
       <c r="M36">
-        <v>-7.7582388</v>
+        <v>-7.7622929999999997</v>
       </c>
       <c r="N36">
-        <v>110.39948099999999</v>
+        <v>110.39756800000001</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -5787,10 +5788,10 @@
         <v>31768000</v>
       </c>
       <c r="M37">
-        <v>-6.3746767999999996</v>
+        <v>-6.3756700000000004</v>
       </c>
       <c r="N37">
-        <v>106.9023871</v>
+        <v>106.901945</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -5831,10 +5832,10 @@
         <v>25575000</v>
       </c>
       <c r="M38">
-        <v>-6.0240691000000002</v>
+        <v>-6.0220909999999996</v>
       </c>
       <c r="N38">
-        <v>106.070026</v>
+        <v>106.0642</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -5875,10 +5876,10 @@
         <v>37149300</v>
       </c>
       <c r="M39">
-        <v>-6.7188340000000002</v>
+        <v>-6.7134119999999999</v>
       </c>
       <c r="N39">
-        <v>108.56875700000001</v>
+        <v>108.552183</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -5919,10 +5920,10 @@
         <v>22977920</v>
       </c>
       <c r="M40">
-        <v>-6.1719834000000002</v>
+        <v>-6.2250129999999997</v>
       </c>
       <c r="N40">
-        <v>106.9528486</v>
+        <v>106.900447</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -5963,10 +5964,10 @@
         <v>30937586</v>
       </c>
       <c r="M41">
-        <v>-8.5934965999999999</v>
+        <v>-8.5946560000000005</v>
       </c>
       <c r="N41">
-        <v>116.1046795</v>
+        <v>116.10522</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -6007,10 +6008,10 @@
         <v>17341198</v>
       </c>
       <c r="M42">
-        <v>-6.9793377000000003</v>
+        <v>-6.9790559999999999</v>
       </c>
       <c r="N42">
-        <v>110.4159578</v>
+        <v>110.41570900000001</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -6051,10 +6052,10 @@
         <v>37003356</v>
       </c>
       <c r="M43">
-        <v>-6.2448107999999998</v>
+        <v>-6.2443869999999997</v>
       </c>
       <c r="N43">
-        <v>106.653052</v>
+        <v>106.653631</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -6092,10 +6093,10 @@
         <v>87</v>
       </c>
       <c r="M44">
-        <v>-6.2628908000000001</v>
+        <v>-6.2783110000000004</v>
       </c>
       <c r="N44">
-        <v>106.8822289</v>
+        <v>106.869567</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -6136,10 +6137,10 @@
         <v>10416667</v>
       </c>
       <c r="M45">
-        <v>-8.6653348999999995</v>
+        <v>-8.6620819999999998</v>
       </c>
       <c r="N45">
-        <v>115.21761909999999</v>
+        <v>115.21697</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -6180,10 +6181,10 @@
         <v>20833333</v>
       </c>
       <c r="M46">
-        <v>-6.9833201000000003</v>
+        <v>-6.9835240000000001</v>
       </c>
       <c r="N46">
-        <v>110.4127632</v>
+        <v>110.41233699999999</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -6224,10 +6225,10 @@
         <v>29853000</v>
       </c>
       <c r="M47">
-        <v>-6.3763809</v>
+        <v>-6.3761739999999998</v>
       </c>
       <c r="N47">
-        <v>106.74451070000001</v>
+        <v>106.74499400000001</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -6268,10 +6269,10 @@
         <v>60645000</v>
       </c>
       <c r="M48">
-        <v>-5.1630200000000001E-2</v>
+        <v>-5.1243999999999998E-2</v>
       </c>
       <c r="N48">
-        <v>109.34505660000001</v>
+        <v>109.345662</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -6312,10 +6313,10 @@
         <v>20700000</v>
       </c>
       <c r="M49">
-        <v>-2.9785784999999998</v>
+        <v>-2.9781879999999998</v>
       </c>
       <c r="N49">
-        <v>104.7457881</v>
+        <v>104.741816</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -6356,10 +6357,10 @@
         <v>32888900</v>
       </c>
       <c r="M50">
-        <v>-8.6343876999999996</v>
+        <v>-8.6356599999999997</v>
       </c>
       <c r="N50">
-        <v>115.2321053</v>
+        <v>115.230413</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -6400,10 +6401,10 @@
         <v>20500000</v>
       </c>
       <c r="M51">
-        <v>-7.3091349000000001</v>
+        <v>-7.3088139999999999</v>
       </c>
       <c r="N51">
-        <v>112.7342835</v>
+        <v>112.734624</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -6444,10 +6445,10 @@
         <v>27370000</v>
       </c>
       <c r="M52">
-        <v>-7.4254864999999999</v>
+        <v>-7.4271469999999997</v>
       </c>
       <c r="N52">
-        <v>109.23041480000001</v>
+        <v>109.23649500000001</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -6488,10 +6489,10 @@
         <v>39468500</v>
       </c>
       <c r="M53">
-        <v>-6.9550866999999998</v>
+        <v>-6.9552670000000001</v>
       </c>
       <c r="N53">
-        <v>107.69801390000001</v>
+        <v>107.69852</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
@@ -6532,10 +6533,10 @@
         <v>80144000</v>
       </c>
       <c r="M54">
-        <v>-6.1189391000000004</v>
+        <v>-6.1190540000000002</v>
       </c>
       <c r="N54">
-        <v>106.1822008</v>
+        <v>106.18141300000001</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
@@ -6576,10 +6577,10 @@
         <v>22176000</v>
       </c>
       <c r="M55">
-        <v>-7.5624618000000003</v>
+        <v>-7.5625400000000003</v>
       </c>
       <c r="N55">
-        <v>110.80999660000001</v>
+        <v>110.809951</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -6620,10 +6621,10 @@
         <v>26388889</v>
       </c>
       <c r="M56">
-        <v>-6.2230740000000004</v>
+        <v>-6.2241400000000002</v>
       </c>
       <c r="N56">
-        <v>106.8338184</v>
+        <v>106.82659</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
@@ -6664,10 +6665,10 @@
         <v>22032000</v>
       </c>
       <c r="M57">
-        <v>-3.3224969999999998</v>
+        <v>-3.3233969999999999</v>
       </c>
       <c r="N57">
-        <v>114.603432</v>
+        <v>114.600335</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -6708,10 +6709,10 @@
         <v>46999960</v>
       </c>
       <c r="M58">
-        <v>-6.9578680000000004</v>
+        <v>-6.9085580000000002</v>
       </c>
       <c r="N58">
-        <v>107.676039</v>
+        <v>107.610801</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
@@ -6752,10 +6753,10 @@
         <v>39256400</v>
       </c>
       <c r="M59">
-        <v>-6.7137044000000001</v>
+        <v>-6.7181610000000003</v>
       </c>
       <c r="N59">
-        <v>108.5608483</v>
+        <v>108.55003499999999</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -6796,10 +6797,10 @@
         <v>13461140</v>
       </c>
       <c r="M60">
-        <v>-6.181705</v>
+        <v>-6.2609360000000001</v>
       </c>
       <c r="N60">
-        <v>106.643551</v>
+        <v>106.52486500000001</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
@@ -6840,10 +6841,10 @@
         <v>28800000</v>
       </c>
       <c r="M61">
-        <v>-6.2838694000000004</v>
+        <v>-6.3056089999999996</v>
       </c>
       <c r="N61">
-        <v>106.8048297</v>
+        <v>106.839957</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
@@ -6884,10 +6885,10 @@
         <v>18840000</v>
       </c>
       <c r="M62">
-        <v>-7.753431</v>
+        <v>-7.7477749999999999</v>
       </c>
       <c r="N62">
-        <v>110.36062699999999</v>
+        <v>110.362371</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
@@ -6928,10 +6929,10 @@
         <v>50535079</v>
       </c>
       <c r="M63">
-        <v>-6.2725017000000003</v>
+        <v>-6.2728590000000004</v>
       </c>
       <c r="N63">
-        <v>106.74228960000001</v>
+        <v>106.74262899999999</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
@@ -6972,10 +6973,10 @@
         <v>31666667</v>
       </c>
       <c r="M64">
-        <v>-5.4164399999999997</v>
+        <v>-5.4167810000000003</v>
       </c>
       <c r="N64">
-        <v>105.25317099999999</v>
+        <v>105.253226</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -7016,10 +7017,10 @@
         <v>25000000</v>
       </c>
       <c r="M65">
-        <v>5.5528455000000001</v>
+        <v>5.5368449999999996</v>
       </c>
       <c r="N65">
-        <v>95.319290800000005</v>
+        <v>95.306488999999999</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
@@ -7060,10 +7061,10 @@
         <v>19666667</v>
       </c>
       <c r="M66">
-        <v>0.49958989999999998</v>
+        <v>0.49909100000000001</v>
       </c>
       <c r="N66">
-        <v>101.41810030000001</v>
+        <v>101.41777</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
@@ -7104,10 +7105,10 @@
         <v>32920000</v>
       </c>
       <c r="M67">
-        <v>-6.1783745000000003</v>
+        <v>-6.178293</v>
       </c>
       <c r="N67">
-        <v>106.7922761</v>
+        <v>106.792402</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -7148,10 +7149,10 @@
         <v>50000000</v>
       </c>
       <c r="M68">
-        <v>-6.3725670000000001</v>
+        <v>-7.5040659999999999</v>
       </c>
       <c r="N68">
-        <v>106.831988</v>
+        <v>110.224767</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
@@ -7192,10 +7193,10 @@
         <v>19200000</v>
       </c>
       <c r="M69">
-        <v>-0.92475870000000004</v>
+        <v>-0.949766</v>
       </c>
       <c r="N69">
-        <v>100.3632561</v>
+        <v>100.35557900000001</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
@@ -7236,10 +7237,10 @@
         <v>84888240</v>
       </c>
       <c r="M70">
-        <v>-7.8122986000000001</v>
+        <v>-7.8129059999999999</v>
       </c>
       <c r="N70">
-        <v>112.0158066</v>
+        <v>112.01577899999999</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
@@ -7280,10 +7281,10 @@
         <v>10947000</v>
       </c>
       <c r="M71">
-        <v>-7.3262483999999999</v>
+        <v>-7.3412009999999999</v>
       </c>
       <c r="N71">
-        <v>108.2201154</v>
+        <v>108.21763300000001</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
@@ -7324,10 +7325,10 @@
         <v>9200100</v>
       </c>
       <c r="M72">
-        <v>-7.4458662000000002</v>
+        <v>-7.4462229999999998</v>
       </c>
       <c r="N72">
-        <v>112.6982142</v>
+        <v>112.69844399999999</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
@@ -7368,10 +7369,10 @@
         <v>40043298</v>
       </c>
       <c r="M73">
-        <v>-1.2398711</v>
+        <v>-1.2724899999999999</v>
       </c>
       <c r="N73">
-        <v>116.8593379</v>
+        <v>116.858486</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
@@ -7412,10 +7413,10 @@
         <v>41756715</v>
       </c>
       <c r="M74">
-        <v>-8.7019672000000003</v>
+        <v>-8.7018079999999998</v>
       </c>
       <c r="N74">
-        <v>115.1831846</v>
+        <v>115.182802</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
@@ -7456,10 +7457,10 @@
         <v>28800000</v>
       </c>
       <c r="M75">
-        <v>-8.1834330000000008</v>
+        <v>-8.1857070000000007</v>
       </c>
       <c r="N75">
-        <v>113.663138</v>
+        <v>113.66279</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
@@ -7500,10 +7501,10 @@
         <v>3472222</v>
       </c>
       <c r="M76">
-        <v>-6.5653670000000002</v>
+        <v>-6.5665880000000003</v>
       </c>
       <c r="N76">
-        <v>106.856397</v>
+        <v>106.84590300000001</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
@@ -7544,10 +7545,10 @@
         <v>37043800</v>
       </c>
       <c r="M77">
-        <v>-6.2707863000000001</v>
+        <v>-6.2706</v>
       </c>
       <c r="N77">
-        <v>106.97221829999999</v>
+        <v>106.9717</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
@@ -7588,10 +7589,10 @@
         <v>24793333</v>
       </c>
       <c r="M78">
-        <v>-6.3276409999999998</v>
+        <v>-6.3210550000000003</v>
       </c>
       <c r="N78">
-        <v>107.29277500000001</v>
+        <v>107.292214</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
@@ -7632,10 +7633,10 @@
         <v>58750000</v>
       </c>
       <c r="M79">
-        <v>-6.2838694000000004</v>
+        <v>-6.2236890000000002</v>
       </c>
       <c r="N79">
-        <v>106.8048297</v>
+        <v>106.82342</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
@@ -7676,10 +7677,10 @@
         <v>61102350</v>
       </c>
       <c r="M80">
-        <v>-7.1578739999999996</v>
+        <v>-7.166042</v>
       </c>
       <c r="N80">
-        <v>112.616338</v>
+        <v>112.601688</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
@@ -7720,10 +7721,10 @@
         <v>16641900</v>
       </c>
       <c r="M81">
-        <v>-6.942126</v>
+        <v>-6.9296959999999999</v>
       </c>
       <c r="N81">
-        <v>107.659192</v>
+        <v>107.586242</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
@@ -7764,10 +7765,10 @@
         <v>20833333</v>
       </c>
       <c r="M82">
-        <v>-3.8118946999999999</v>
+        <v>-3.8072189999999999</v>
       </c>
       <c r="N82">
-        <v>102.26820360000001</v>
+        <v>102.267369</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
@@ -7808,10 +7809,10 @@
         <v>12408270</v>
       </c>
       <c r="M83">
-        <v>-3.670445</v>
+        <v>-3.6722190000000001</v>
       </c>
       <c r="N83">
-        <v>128.197926</v>
+        <v>128.198103</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
@@ -7852,10 +7853,10 @@
         <v>9900000</v>
       </c>
       <c r="M84">
-        <v>-5.0504790000000002</v>
+        <v>-5.0489430000000004</v>
       </c>
       <c r="N84">
-        <v>119.553631</v>
+        <v>119.554146</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
@@ -7896,10 +7897,10 @@
         <v>18564000</v>
       </c>
       <c r="M85">
-        <v>-6.1941557999999999</v>
+        <v>-6.1935880000000001</v>
       </c>
       <c r="N85">
-        <v>106.8904553</v>
+        <v>106.88909200000001</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
@@ -7940,10 +7941,10 @@
         <v>33000000</v>
       </c>
       <c r="M86">
-        <v>-7.0514700000000001</v>
+        <v>-7.0061809999999998</v>
       </c>
       <c r="N86">
-        <v>110.41928299999999</v>
+        <v>110.432253</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
@@ -7984,10 +7985,10 @@
         <v>42255758</v>
       </c>
       <c r="M87">
-        <v>-6.1608046999999999</v>
+        <v>-6.1608390000000002</v>
       </c>
       <c r="N87">
-        <v>106.8181441</v>
+        <v>106.818022</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
@@ -8028,10 +8029,10 @@
         <v>18333333</v>
       </c>
       <c r="M88">
-        <v>-3.0362812899999998</v>
+        <v>-3.0361400000000001</v>
       </c>
       <c r="N88" s="2">
-        <v>104.79204900000001</v>
+        <v>104.79156399999999</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
@@ -8072,10 +8073,10 @@
         <v>13888600</v>
       </c>
       <c r="M89">
-        <v>-0.50353179999999997</v>
+        <v>-0.50346100000000005</v>
       </c>
       <c r="N89">
-        <v>117.1550694</v>
+        <v>117.154967</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
@@ -8116,10 +8117,10 @@
         <v>21336000</v>
       </c>
       <c r="M90">
-        <v>-6.2483075000000001</v>
+        <v>-6.2480589999999996</v>
       </c>
       <c r="N90">
-        <v>106.9896214</v>
+        <v>106.982479</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
@@ -8160,10 +8161,10 @@
         <v>41650000</v>
       </c>
       <c r="M91">
-        <v>3.5910470000000001</v>
+        <v>3.5908869999999999</v>
       </c>
       <c r="N91">
-        <v>98.626666</v>
+        <v>98.626718999999994</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
@@ -8204,10 +8205,10 @@
         <v>35000000</v>
       </c>
       <c r="M92">
-        <v>3.5928673999999998</v>
+        <v>3.5922139999999998</v>
       </c>
       <c r="N92">
-        <v>98.663744399999999</v>
+        <v>98.663635999999997</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
@@ -8248,10 +8249,10 @@
         <v>25087500</v>
       </c>
       <c r="M93">
-        <v>-6.2497771000000002</v>
+        <v>-6.2494930000000002</v>
       </c>
       <c r="N93">
-        <v>106.99327700000001</v>
+        <v>106.993112</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
@@ -8292,10 +8293,10 @@
         <v>5042750</v>
       </c>
       <c r="M94">
-        <v>-7.4714619000000004</v>
+        <v>-7.4717019999999996</v>
       </c>
       <c r="N94">
-        <v>112.4432958</v>
+        <v>112.443512</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
@@ -8336,10 +8337,10 @@
         <v>95341440</v>
       </c>
       <c r="M95">
-        <v>-6.2560840000000004</v>
+        <v>-6.2565999999999997</v>
       </c>
       <c r="N95">
-        <v>106.989225</v>
+        <v>106.989428</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
@@ -8380,10 +8381,10 @@
         <v>26422891</v>
       </c>
       <c r="M96">
-        <v>-6.8162263000000003</v>
+        <v>-6.8148470000000003</v>
       </c>
       <c r="N96">
-        <v>107.1306977</v>
+        <v>107.13134599999999</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
@@ -8424,10 +8425,10 @@
         <v>35700000</v>
       </c>
       <c r="M97">
-        <v>-7.6009450000000003</v>
+        <v>-7.5988319999999998</v>
       </c>
       <c r="N97">
-        <v>110.8148386</v>
+        <v>110.816699</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
@@ -8468,10 +8469,10 @@
         <v>13856000</v>
       </c>
       <c r="M98">
-        <v>-7.2462835999999999</v>
+        <v>-7.2619680000000004</v>
       </c>
       <c r="N98">
-        <v>112.7377674</v>
+        <v>112.749994</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
@@ -8512,10 +8513,10 @@
         <v>76000000</v>
       </c>
       <c r="M99">
-        <v>-5.1292429999999998</v>
+        <v>-5.1390219999999998</v>
       </c>
       <c r="N99">
-        <v>119.414501</v>
+        <v>119.450033</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
@@ -8556,10 +8557,10 @@
         <v>28900000</v>
       </c>
       <c r="M100">
-        <v>-7.3386391</v>
+        <v>-7.3389150000000001</v>
       </c>
       <c r="N100">
-        <v>112.7283467</v>
+        <v>112.72849100000001</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
@@ -8600,10 +8601,10 @@
         <v>22345942</v>
       </c>
       <c r="M101">
-        <v>-7.1106781000000003</v>
+        <v>-8.7232230000000008</v>
       </c>
       <c r="N101">
-        <v>113.3721692</v>
+        <v>115.18433899999999</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
@@ -8644,10 +8645,10 @@
         <v>20924850</v>
       </c>
       <c r="M102">
-        <v>-7.1718549999999999</v>
+        <v>-7.1574780000000002</v>
       </c>
       <c r="N102">
-        <v>112.645869</v>
+        <v>112.616159</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
@@ -8688,10 +8689,10 @@
         <v>20910560</v>
       </c>
       <c r="M103">
-        <v>-3.4392100000000001</v>
+        <v>-3.4418470000000001</v>
       </c>
       <c r="N103">
-        <v>114.84948</v>
+        <v>114.84831</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
@@ -8732,10 +8733,10 @@
         <v>39500000</v>
       </c>
       <c r="M104">
-        <v>-2.9761723</v>
+        <v>-2.9711639999999999</v>
       </c>
       <c r="N104">
-        <v>104.74187310000001</v>
+        <v>104.738058</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
@@ -8776,10 +8777,10 @@
         <v>22500000</v>
       </c>
       <c r="M105">
-        <v>-2.9510100000000001</v>
+        <v>-2.9516450000000001</v>
       </c>
       <c r="N105">
-        <v>104.76089399999999</v>
+        <v>104.76113599999999</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
@@ -8820,10 +8821,10 @@
         <v>22916667</v>
       </c>
       <c r="M106">
-        <v>-3.9831370000000001</v>
+        <v>-3.9773320000000001</v>
       </c>
       <c r="N106">
-        <v>122.519705</v>
+        <v>122.524231</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
@@ -8864,10 +8865,10 @@
         <v>41691510</v>
       </c>
       <c r="M107">
-        <v>-7.2756970000000001</v>
+        <v>-7.276923</v>
       </c>
       <c r="N107">
-        <v>112.805992</v>
+        <v>112.81139400000001</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
@@ -8908,10 +8909,10 @@
         <v>25435180</v>
       </c>
       <c r="M108">
-        <v>-3.9922135000000001</v>
+        <v>-3.9924469999999999</v>
       </c>
       <c r="N108">
-        <v>122.51207770000001</v>
+        <v>122.512057</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
@@ -8952,10 +8953,10 @@
         <v>22400000</v>
       </c>
       <c r="M109">
-        <v>-7.2650189999999997</v>
+        <v>-7.3159840000000003</v>
       </c>
       <c r="N109">
-        <v>112.74805600000001</v>
+        <v>112.74863499999999</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
@@ -8996,10 +8997,10 @@
         <v>47470000</v>
       </c>
       <c r="M110">
-        <v>-6.1896994000000003</v>
+        <v>-6.1900170000000001</v>
       </c>
       <c r="N110">
-        <v>106.8742939</v>
+        <v>106.874185</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
@@ -9040,10 +9041,10 @@
         <v>41612500</v>
       </c>
       <c r="M111">
-        <v>-6.5797109999999996</v>
+        <v>-6.5793990000000004</v>
       </c>
       <c r="N111">
-        <v>106.800371</v>
+        <v>106.79934799999999</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
@@ -9084,10 +9085,10 @@
         <v>27000000</v>
       </c>
       <c r="M112">
-        <v>3.5928949999999999</v>
+        <v>3.6004529999999999</v>
       </c>
       <c r="N112">
-        <v>98.663415000000001</v>
+        <v>98.644181000000003</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
@@ -9128,10 +9129,10 @@
         <v>29760000</v>
       </c>
       <c r="M113">
-        <v>-6.2846967999999999</v>
+        <v>-6.2841100000000001</v>
       </c>
       <c r="N113">
-        <v>106.911506</v>
+        <v>106.911119</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
@@ -9172,10 +9173,10 @@
         <v>40000000</v>
       </c>
       <c r="M114">
-        <v>-6.1390775</v>
+        <v>-6.138852</v>
       </c>
       <c r="N114">
-        <v>106.7286378</v>
+        <v>106.72872099999999</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
@@ -9216,10 +9217,10 @@
         <v>26806500</v>
       </c>
       <c r="M115">
-        <v>-6.5963564000000003</v>
+        <v>-6.6216350000000004</v>
       </c>
       <c r="N115">
-        <v>106.7973188</v>
+        <v>106.817064</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
@@ -9260,10 +9261,10 @@
         <v>60000000</v>
       </c>
       <c r="M116">
-        <v>1.4900447000000001</v>
+        <v>1.4888520000000001</v>
       </c>
       <c r="N116">
-        <v>124.8407673</v>
+        <v>124.837932</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
@@ -9304,10 +9305,10 @@
         <v>29944438</v>
       </c>
       <c r="M117">
-        <v>-6.070398</v>
+        <v>-6.2264239999999997</v>
       </c>
       <c r="N117">
-        <v>106.70609</v>
+        <v>106.606495</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
@@ -9348,10 +9349,10 @@
         <v>60365600</v>
       </c>
       <c r="M118">
-        <v>-6.1771760000000002</v>
+        <v>-6.1540689999999998</v>
       </c>
       <c r="N118">
-        <v>106.790081</v>
+        <v>106.843892</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
@@ -9392,10 +9393,10 @@
         <v>43184926</v>
       </c>
       <c r="M119">
-        <v>-6.1939612000000004</v>
+        <v>-6.1939399999999996</v>
       </c>
       <c r="N119">
-        <v>106.63390870000001</v>
+        <v>106.634049</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
@@ -9436,10 +9437,10 @@
         <v>17542000</v>
       </c>
       <c r="M120">
-        <v>-7.2650189999999997</v>
+        <v>-7.2645379999999999</v>
       </c>
       <c r="N120">
-        <v>112.74805600000001</v>
+        <v>112.74751999999999</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
@@ -9480,10 +9481,10 @@
         <v>14455800</v>
       </c>
       <c r="M121">
-        <v>-6.1615690000000001</v>
+        <v>-6.1547710000000002</v>
       </c>
       <c r="N121">
-        <v>106.74389050000001</v>
+        <v>106.69411700000001</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
@@ -9524,10 +9525,10 @@
         <v>21120000</v>
       </c>
       <c r="M122">
-        <v>0.5376727</v>
+        <v>0.537717</v>
       </c>
       <c r="N122">
-        <v>123.06260210000001</v>
+        <v>123.062073</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
@@ -9568,10 +9569,10 @@
         <v>25928000</v>
       </c>
       <c r="M123">
-        <v>-6.9131830000000001</v>
+        <v>-6.9097790000000003</v>
       </c>
       <c r="N123">
-        <v>112.079464</v>
+        <v>112.076255</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.3">
@@ -9612,10 +9613,10 @@
         <v>38665000</v>
       </c>
       <c r="M124">
-        <v>-2.2477621999999999</v>
+        <v>-2.2492450000000002</v>
       </c>
       <c r="N124">
-        <v>113.9230786</v>
+        <v>113.924392</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
@@ -9656,10 +9657,10 @@
         <v>28083333</v>
       </c>
       <c r="M125">
-        <v>-0.89577929999999995</v>
+        <v>-0.88347100000000001</v>
       </c>
       <c r="N125">
-        <v>119.86799739999999</v>
+        <v>119.8426</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
@@ -9700,10 +9701,10 @@
         <v>41660833</v>
       </c>
       <c r="M126">
-        <v>-6.3701600000000003</v>
+        <v>-6.3686030000000002</v>
       </c>
       <c r="N126">
-        <v>106.959008</v>
+        <v>106.959187</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.3">
@@ -9744,10 +9745,10 @@
         <v>23000000</v>
       </c>
       <c r="M127">
-        <v>2.9592269999999998</v>
+        <v>2.961843</v>
       </c>
       <c r="N127">
-        <v>99.062831599999996</v>
+        <v>99.072187999999997</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
@@ -9788,10 +9789,10 @@
         <v>23400000</v>
       </c>
       <c r="M128">
-        <v>-6.2749433000000003</v>
+        <v>-6.3415929999999996</v>
       </c>
       <c r="N128">
-        <v>107.9719908</v>
+        <v>108.33702</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
@@ -9832,10 +9833,10 @@
         <v>36844000</v>
       </c>
       <c r="M129">
-        <v>-6.3823382000000004</v>
+        <v>-6.3833359999999999</v>
       </c>
       <c r="N129">
-        <v>106.92613</v>
+        <v>106.925792</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
@@ -9876,10 +9877,10 @@
         <v>10000000</v>
       </c>
       <c r="M130">
-        <v>-0.90219550000000004</v>
+        <v>-0.91611799999999999</v>
       </c>
       <c r="N130">
-        <v>100.3510308</v>
+        <v>100.397521</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
@@ -9920,10 +9921,10 @@
         <v>55962600</v>
       </c>
       <c r="M131">
-        <v>-7.0238500000000004</v>
+        <v>-6.9537820000000004</v>
       </c>
       <c r="N131">
-        <v>110.40374199999999</v>
+        <v>110.381372</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.3">
@@ -9964,10 +9965,10 @@
         <v>40619733</v>
       </c>
       <c r="M132">
-        <v>-6.9218457000000004</v>
+        <v>-6.9082530000000002</v>
       </c>
       <c r="N132">
-        <v>107.6070833</v>
+        <v>107.608931</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
@@ -10008,10 +10009,10 @@
         <v>65000000</v>
       </c>
       <c r="M133">
-        <v>-6.2838694000000004</v>
+        <v>-6.2240349999999998</v>
       </c>
       <c r="N133">
-        <v>106.8048297</v>
+        <v>106.842597</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.3">
@@ -10052,10 +10053,10 @@
         <v>125035000</v>
       </c>
       <c r="M134">
-        <v>-6.4842630000000003</v>
+        <v>-6.4843510000000002</v>
       </c>
       <c r="N134">
-        <v>106.84105700000001</v>
+        <v>106.840907</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
@@ -10093,10 +10094,10 @@
         <v>90</v>
       </c>
       <c r="M135">
-        <v>-5.1597144000000004</v>
+        <v>-5.1611140000000004</v>
       </c>
       <c r="N135">
-        <v>119.3944814</v>
+        <v>119.39393099999999</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.3">
@@ -10137,10 +10138,10 @@
         <v>38400000</v>
       </c>
       <c r="M136">
-        <v>-6.9724694999999999</v>
+        <v>-6.9728789999999998</v>
       </c>
       <c r="N136">
-        <v>110.4204458</v>
+        <v>110.420416</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.3">
@@ -10181,10 +10182,10 @@
         <v>69285833</v>
       </c>
       <c r="M137">
-        <v>-6.2612119000000002</v>
+        <v>-6.2612569999999996</v>
       </c>
       <c r="N137">
-        <v>106.8126979</v>
+        <v>106.81286</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.3">
@@ -10225,10 +10226,10 @@
         <v>30000000</v>
       </c>
       <c r="M138">
-        <v>-6.1725830000000004</v>
+        <v>-6.3519399999999999</v>
       </c>
       <c r="N138">
-        <v>106.952257</v>
+        <v>107.195449</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
@@ -10269,10 +10270,10 @@
         <v>19999999</v>
       </c>
       <c r="M139">
-        <v>-6.1615690000000001</v>
+        <v>-6.1683899999999996</v>
       </c>
       <c r="N139">
-        <v>106.74389050000001</v>
+        <v>106.786618</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
@@ -10310,10 +10311,10 @@
         <v>110.79</v>
       </c>
       <c r="M140">
-        <v>-6.1771760000000002</v>
+        <v>-6.1514540000000002</v>
       </c>
       <c r="N140">
-        <v>106.790081</v>
+        <v>106.89189399999999</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.3">
@@ -10354,10 +10355,10 @@
         <v>35000000</v>
       </c>
       <c r="M141">
-        <v>-2.9849492</v>
+        <v>-2.9844550000000001</v>
       </c>
       <c r="N141">
-        <v>104.75357339999999</v>
+        <v>104.753834</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.3">
@@ -10398,10 +10399,10 @@
         <v>21090000</v>
       </c>
       <c r="M142">
-        <v>-7.6879000000000003E-2</v>
+        <v>-7.6410000000000006E-2</v>
       </c>
       <c r="N142">
-        <v>109.368804</v>
+        <v>109.369536</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
@@ -10442,10 +10443,10 @@
         <v>26527500</v>
       </c>
       <c r="M143">
-        <v>-7.2807599999999999</v>
+        <v>-7.2929649999999997</v>
       </c>
       <c r="N143">
-        <v>112.63458900000001</v>
+        <v>112.720054</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
@@ -10486,10 +10487,10 @@
         <v>10416667</v>
       </c>
       <c r="M144">
-        <v>-8.6683240000000001</v>
+        <v>-8.6738839999999993</v>
       </c>
       <c r="N144">
-        <v>115.220027</v>
+        <v>115.208021</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
@@ -10530,10 +10531,10 @@
         <v>33333333</v>
       </c>
       <c r="M145">
-        <v>-7.4598345000000004</v>
+        <v>-7.4557479999999998</v>
       </c>
       <c r="N145">
-        <v>112.71753649999999</v>
+        <v>112.717679</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
@@ -10574,10 +10575,10 @@
         <v>10416667</v>
       </c>
       <c r="M146">
-        <v>-7.2643344000000001</v>
+        <v>-7.2635680000000002</v>
       </c>
       <c r="N146">
-        <v>112.6618462</v>
+        <v>112.666859</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
@@ -10618,10 +10619,10 @@
         <v>6500000</v>
       </c>
       <c r="M147">
-        <v>-3.3489620000000002</v>
+        <v>-3.3982749999999999</v>
       </c>
       <c r="N147">
-        <v>114.6260528</v>
+        <v>114.87306700000001</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
@@ -10662,10 +10663,10 @@
         <v>8333333</v>
       </c>
       <c r="M148">
-        <v>3.6069621999999999</v>
+        <v>3.6070169999999999</v>
       </c>
       <c r="N148">
-        <v>98.678657400000006</v>
+        <v>98.678877999999997</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
@@ -10706,10 +10707,10 @@
         <v>34166667</v>
       </c>
       <c r="M149">
-        <v>-7.2784529999999998</v>
+        <v>-7.3187189999999998</v>
       </c>
       <c r="N149">
-        <v>112.725723</v>
+        <v>112.780812</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
@@ -10750,10 +10751,10 @@
         <v>7500000</v>
       </c>
       <c r="M150">
-        <v>-6.8898324000000004</v>
+        <v>-6.8900139999999999</v>
       </c>
       <c r="N150">
-        <v>109.65211770000001</v>
+        <v>109.651066</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
@@ -10794,10 +10795,10 @@
         <v>8333334</v>
       </c>
       <c r="M151">
-        <v>-8.1951769999999993</v>
+        <v>-8.1712240000000005</v>
       </c>
       <c r="N151">
-        <v>113.680859</v>
+        <v>113.722081</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
@@ -10838,10 +10839,10 @@
         <v>8333333</v>
       </c>
       <c r="M152">
-        <v>-0.30940000000000001</v>
+        <v>-0.29566199999999998</v>
       </c>
       <c r="N152">
-        <v>100.382971</v>
+        <v>100.396214</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
@@ -10882,10 +10883,10 @@
         <v>5500000</v>
       </c>
       <c r="M153">
-        <v>-0.93762420000000002</v>
+        <v>-0.93937999999999999</v>
       </c>
       <c r="N153">
-        <v>100.35451279999999</v>
+        <v>100.354747</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
@@ -10926,10 +10927,10 @@
         <v>6250000</v>
       </c>
       <c r="M154">
-        <v>-1.2397847</v>
+        <v>-1.2745550000000001</v>
       </c>
       <c r="N154">
-        <v>116.8398483</v>
+        <v>116.844972</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
@@ -10970,10 +10971,10 @@
         <v>5000000</v>
       </c>
       <c r="M155">
-        <v>0.90486599999999995</v>
+        <v>0.91313299999999997</v>
       </c>
       <c r="N155">
-        <v>108.983664</v>
+        <v>108.981435</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
@@ -11014,10 +11015,10 @@
         <v>9166600</v>
       </c>
       <c r="M156">
-        <v>-5.6963699999999999E-2</v>
+        <v>-6.0687999999999999E-2</v>
       </c>
       <c r="N156">
-        <v>109.3101808</v>
+        <v>109.306162</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
@@ -11058,10 +11059,10 @@
         <v>9166815</v>
       </c>
       <c r="M157">
-        <v>-8.0634432999999994</v>
+        <v>-8.065804</v>
       </c>
       <c r="N157">
-        <v>111.8983588</v>
+        <v>111.898601</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
@@ -11102,10 +11103,10 @@
         <v>8333360</v>
       </c>
       <c r="M158">
-        <v>-7.8333089999999999</v>
+        <v>-7.8229240000000004</v>
       </c>
       <c r="N158">
-        <v>112.016654</v>
+        <v>112.01836400000001</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
@@ -11146,10 +11147,10 @@
         <v>11250000</v>
       </c>
       <c r="M159">
-        <v>-0.89052699999999996</v>
+        <v>-0.89712700000000001</v>
       </c>
       <c r="N159">
-        <v>119.885875</v>
+        <v>119.887102</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
@@ -11190,10 +11191,10 @@
         <v>7500000</v>
       </c>
       <c r="M160">
-        <v>-2.9769380000000001</v>
+        <v>-2.9783520000000001</v>
       </c>
       <c r="N160">
-        <v>104.734354</v>
+        <v>104.76451400000001</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
@@ -11234,10 +11235,10 @@
         <v>8333333</v>
       </c>
       <c r="M161">
-        <v>3.5700835999999998</v>
+        <v>3.5817860000000001</v>
       </c>
       <c r="N161">
-        <v>98.717172000000005</v>
+        <v>98.708527000000004</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.3">
@@ -11278,10 +11279,10 @@
         <v>8333333</v>
       </c>
       <c r="M162">
-        <v>-1.611362</v>
+        <v>-1.6100620000000001</v>
       </c>
       <c r="N162">
-        <v>103.59601859999999</v>
+        <v>103.59678</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.3">
@@ -11322,10 +11323,10 @@
         <v>8333333</v>
       </c>
       <c r="M163">
-        <v>5.5528455000000001</v>
+        <v>5.5361459999999996</v>
       </c>
       <c r="N163">
-        <v>95.319290800000005</v>
+        <v>95.330163999999996</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.3">
@@ -11366,10 +11367,10 @@
         <v>17799700</v>
       </c>
       <c r="M164">
-        <v>-5.0726681999999998</v>
+        <v>-5.1559670000000004</v>
       </c>
       <c r="N164">
-        <v>119.49744389999999</v>
+        <v>119.443811</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.3">
@@ -11410,10 +11411,10 @@
         <v>4902430</v>
       </c>
       <c r="M165">
-        <v>-6.9315696999999998</v>
+        <v>-6.9315530000000001</v>
       </c>
       <c r="N165">
-        <v>107.62382409999999</v>
+        <v>107.623908</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
@@ -11454,10 +11455,10 @@
         <v>4166000</v>
       </c>
       <c r="M166">
-        <v>-7.5324396</v>
+        <v>-7.5249050000000004</v>
       </c>
       <c r="N166">
-        <v>110.601225</v>
+        <v>110.60007299999999</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
@@ -11498,10 +11499,10 @@
         <v>2085000</v>
       </c>
       <c r="M167">
-        <v>-7.0801809999999996</v>
+        <v>-7.0972799999999996</v>
       </c>
       <c r="N167">
-        <v>110.90931</v>
+        <v>110.91150399999999</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
@@ -11542,10 +11543,10 @@
         <v>2085000</v>
       </c>
       <c r="M168">
-        <v>-7.3292279999999996</v>
+        <v>-7.3291539999999999</v>
       </c>
       <c r="N168">
-        <v>110.50312529999999</v>
+        <v>110.503196</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
@@ -11586,10 +11587,10 @@
         <v>7500000</v>
       </c>
       <c r="M169">
-        <v>-8.4473160000000007</v>
+        <v>-8.5410009999999996</v>
       </c>
       <c r="N169">
-        <v>115.28354</v>
+        <v>115.321116</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
@@ -11630,10 +11631,10 @@
         <v>6666667</v>
       </c>
       <c r="M170">
-        <v>-7.8756740000000001</v>
+        <v>-7.8716520000000001</v>
       </c>
       <c r="N170">
-        <v>111.46925299999999</v>
+        <v>111.469902</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
@@ -11674,10 +11675,10 @@
         <v>8333334</v>
       </c>
       <c r="M171">
-        <v>-7.6251787999999996</v>
+        <v>-7.6251769999999999</v>
       </c>
       <c r="N171">
-        <v>111.5220192</v>
+        <v>111.521343</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
@@ -11718,10 +11719,10 @@
         <v>10833333</v>
       </c>
       <c r="M172">
-        <v>0.50815679999999996</v>
+        <v>0.498946</v>
       </c>
       <c r="N172">
-        <v>117.5355673</v>
+        <v>117.530023</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.3">
@@ -11762,10 +11763,10 @@
         <v>5833333</v>
       </c>
       <c r="M173">
-        <v>0.12970599999999999</v>
+        <v>0.13455900000000001</v>
       </c>
       <c r="N173">
-        <v>117.47153</v>
+        <v>117.491473</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.3">
@@ -11806,10 +11807,10 @@
         <v>5000000</v>
       </c>
       <c r="M174">
-        <v>-6.8991569999999998</v>
+        <v>-6.8956030000000004</v>
       </c>
       <c r="N174">
-        <v>109.41875400000001</v>
+        <v>109.387243</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.3">
@@ -11850,10 +11851,10 @@
         <v>9166667</v>
       </c>
       <c r="M175">
-        <v>-7.9510703999999999</v>
+        <v>-7.9577470000000003</v>
       </c>
       <c r="N175">
-        <v>112.6028931</v>
+        <v>112.608926</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
@@ -11894,10 +11895,10 @@
         <v>8333333</v>
       </c>
       <c r="M176">
-        <v>-5.4024549999999998</v>
+        <v>-5.4216350000000002</v>
       </c>
       <c r="N176">
-        <v>105.257957</v>
+        <v>105.247274</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
@@ -11938,10 +11939,10 @@
         <v>7166667</v>
       </c>
       <c r="M177">
-        <v>3.430768</v>
+        <v>3.628933</v>
       </c>
       <c r="N177">
-        <v>98.902634000000006</v>
+        <v>98.703643999999997</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
@@ -11982,10 +11983,10 @@
         <v>20833000</v>
       </c>
       <c r="M178">
-        <v>-8.6693800000000003</v>
+        <v>-8.6693519999999999</v>
       </c>
       <c r="N178">
-        <v>115.2128768</v>
+        <v>115.211603</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.3">
@@ -12026,10 +12027,10 @@
         <v>7500000</v>
       </c>
       <c r="M179">
-        <v>-2.3824000000000001E-2</v>
+        <v>-3.6639999999999999E-2</v>
       </c>
       <c r="N179">
-        <v>109.330603</v>
+        <v>109.331602</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.3">
@@ -12070,10 +12071,10 @@
         <v>4240000</v>
       </c>
       <c r="M180">
-        <v>-7.9763221</v>
+        <v>-8.1320820000000005</v>
       </c>
       <c r="N180">
-        <v>112.6355325</v>
+        <v>112.570826</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.3">
@@ -12114,10 +12115,10 @@
         <v>33333333</v>
       </c>
       <c r="M181">
-        <v>-5.1394941999999997</v>
+        <v>-5.1385170000000002</v>
       </c>
       <c r="N181">
-        <v>119.41002949999999</v>
+        <v>119.40918000000001</v>
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.3">
@@ -12158,10 +12159,10 @@
         <v>16666666</v>
       </c>
       <c r="M182">
-        <v>1.4869509999999999</v>
+        <v>1.487269</v>
       </c>
       <c r="N182">
-        <v>124.85534800000001</v>
+        <v>124.861063</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.3">
@@ -12202,10 +12203,10 @@
         <v>16666666</v>
       </c>
       <c r="M183">
-        <v>5.1813481000000001</v>
+        <v>5.1791830000000001</v>
       </c>
       <c r="N183">
-        <v>97.142187899999996</v>
+        <v>97.144687000000005</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
@@ -12246,10 +12247,10 @@
         <v>9749249</v>
       </c>
       <c r="M184">
-        <v>-7.7320495999999999</v>
+        <v>-7.7322600000000001</v>
       </c>
       <c r="N184">
-        <v>109.009491</v>
+        <v>109.009351</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.3">
@@ -12290,10 +12291,10 @@
         <v>14583333</v>
       </c>
       <c r="M185">
-        <v>-5.1383150000000004</v>
+        <v>-5.1412389999999997</v>
       </c>
       <c r="N185">
-        <v>119.458405</v>
+        <v>119.48123200000001</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.3">
@@ -12334,10 +12335,10 @@
         <v>4000000</v>
       </c>
       <c r="M186">
-        <v>-7.4286352999999998</v>
+        <v>-7.42502</v>
       </c>
       <c r="N186">
-        <v>111.01531110000001</v>
+        <v>111.029685</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
@@ -12378,10 +12379,10 @@
         <v>7000000</v>
       </c>
       <c r="M187">
-        <v>3.628504</v>
+        <v>3.6296300000000001</v>
       </c>
       <c r="N187">
-        <v>98.669447399999996</v>
+        <v>98.682354000000004</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.3">
@@ -12422,10 +12423,10 @@
         <v>8333333</v>
       </c>
       <c r="M188">
-        <v>-7.6112650999999998</v>
+        <v>-7.6182920000000003</v>
       </c>
       <c r="N188">
-        <v>111.8989133</v>
+        <v>111.898078</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.3">
@@ -12466,10 +12467,10 @@
         <v>4162500</v>
       </c>
       <c r="M189">
-        <v>-3.4609320000000001</v>
+        <v>-3.420115</v>
       </c>
       <c r="N189">
-        <v>115.9977612</v>
+        <v>116.00132600000001</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.3">
@@ -12510,10 +12511,10 @@
         <v>12718750</v>
       </c>
       <c r="M190">
-        <v>-1.235994</v>
+        <v>-1.2756130000000001</v>
       </c>
       <c r="N190">
-        <v>116.846166</v>
+        <v>116.846875</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.3">
@@ -12554,10 +12555,10 @@
         <v>4583333</v>
       </c>
       <c r="M191">
-        <v>-3.3097476000000001</v>
+        <v>-3.3064930000000001</v>
       </c>
       <c r="N191">
-        <v>114.5874989</v>
+        <v>114.578221</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.3">
@@ -12598,10 +12599,10 @@
         <v>16666667</v>
       </c>
       <c r="M192">
-        <v>-6.1379910000000004</v>
+        <v>-6.1227039999999997</v>
       </c>
       <c r="N192">
-        <v>106.89971199999999</v>
+        <v>106.9164</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.3">
@@ -12642,10 +12643,10 @@
         <v>9083333</v>
       </c>
       <c r="M193">
-        <v>-3.331502</v>
+        <v>-3.3233480000000002</v>
       </c>
       <c r="N193">
-        <v>114.59299</v>
+        <v>114.602159</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.3">
@@ -12686,10 +12687,10 @@
         <v>22916598</v>
       </c>
       <c r="M194">
-        <v>-7.5793780999999996</v>
+        <v>-7.5750659999999996</v>
       </c>
       <c r="N194">
-        <v>110.8187169</v>
+        <v>110.82023700000001</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.3">
@@ -12730,10 +12731,10 @@
         <v>12500000</v>
       </c>
       <c r="M195">
-        <v>-7.9339861999999997</v>
+        <v>-7.9379549999999997</v>
       </c>
       <c r="N195">
-        <v>112.6175197</v>
+        <v>112.628643</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.3">
@@ -12774,10 +12775,10 @@
         <v>30850000</v>
       </c>
       <c r="M196">
-        <v>-7.1106781000000003</v>
+        <v>-8.6440300000000008</v>
       </c>
       <c r="N196">
-        <v>113.3721692</v>
+        <v>115.157217</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.3">
@@ -12818,10 +12819,10 @@
         <v>5000000</v>
       </c>
       <c r="M197">
-        <v>-6.3083260000000001</v>
+        <v>-6.3089370000000002</v>
       </c>
       <c r="N197">
-        <v>107.30654</v>
+        <v>107.301137</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.3">
@@ -12862,10 +12863,10 @@
         <v>6250000</v>
       </c>
       <c r="M198">
-        <v>-7.3338634999999996</v>
+        <v>-7.3337479999999999</v>
       </c>
       <c r="N198">
-        <v>108.2170473</v>
+        <v>108.21779100000001</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.3">
@@ -12906,10 +12907,10 @@
         <v>7950000</v>
       </c>
       <c r="M199">
-        <v>-3.4477030000000002</v>
+        <v>-3.4385379999999999</v>
       </c>
       <c r="N199">
-        <v>114.78778800000001</v>
+        <v>114.848354</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.3">
@@ -12950,10 +12951,10 @@
         <v>12500000</v>
       </c>
       <c r="M200">
-        <v>-7.2487629</v>
+        <v>-7.2494100000000001</v>
       </c>
       <c r="N200">
-        <v>112.75812430000001</v>
+        <v>112.76169899999999</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.3">
@@ -12994,10 +12995,10 @@
         <v>4200000</v>
       </c>
       <c r="M201">
-        <v>-6.904801</v>
+        <v>-6.9608350000000003</v>
       </c>
       <c r="N201">
-        <v>109.67203000000001</v>
+        <v>109.63630000000001</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.3">
@@ -13038,10 +13039,10 @@
         <v>4200000</v>
       </c>
       <c r="M202">
-        <v>-7.5026133000000002</v>
+        <v>-7.4901650000000002</v>
       </c>
       <c r="N202">
-        <v>110.2236791</v>
+        <v>110.221926</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.3">
@@ -13082,10 +13083,10 @@
         <v>4316667</v>
       </c>
       <c r="M203">
-        <v>-2.0437919999999998</v>
+        <v>-2.5479449999999999</v>
       </c>
       <c r="N203">
-        <v>112.73477200000001</v>
+        <v>112.941255</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.3">
@@ -13126,10 +13127,10 @@
         <v>10000000</v>
       </c>
       <c r="M204">
-        <v>-7.689279</v>
+        <v>-7.7702980000000004</v>
       </c>
       <c r="N204">
-        <v>110.35131800000001</v>
+        <v>110.304295</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.3">
@@ -13170,10 +13171,10 @@
         <v>25000000</v>
       </c>
       <c r="M205">
-        <v>-8.6391790000000004</v>
+        <v>-8.6362269999999999</v>
       </c>
       <c r="N205">
-        <v>115.20496110000001</v>
+        <v>115.242654</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.3">
@@ -13214,10 +13215,10 @@
         <v>10000000</v>
       </c>
       <c r="M206">
-        <v>-2.4575300000000001E-2</v>
+        <v>-3.8670000000000003E-2</v>
       </c>
       <c r="N206">
-        <v>109.3186158</v>
+        <v>109.34725400000001</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.3">
@@ -13258,10 +13259,10 @@
         <v>6666667</v>
       </c>
       <c r="M207">
-        <v>-3.9692818000000001</v>
+        <v>-3.969452</v>
       </c>
       <c r="N207">
-        <v>122.52216060000001</v>
+        <v>122.52200000000001</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.3">
@@ -13302,10 +13303,10 @@
         <v>900000</v>
       </c>
       <c r="M208">
-        <v>-3.8078618</v>
+        <v>-3.9235540000000002</v>
       </c>
       <c r="N208">
-        <v>120.0450189</v>
+        <v>119.79543</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.3">
@@ -13346,10 +13347,10 @@
         <v>10000000</v>
       </c>
       <c r="M209">
-        <v>-5.4131552999999997</v>
+        <v>-5.413672</v>
       </c>
       <c r="N209">
-        <v>105.2570573</v>
+        <v>105.257171</v>
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.3">
@@ -13390,10 +13391,10 @@
         <v>9583333</v>
       </c>
       <c r="M210">
-        <v>-0.95239580000000001</v>
+        <v>-0.95484800000000003</v>
       </c>
       <c r="N210">
-        <v>100.3626759</v>
+        <v>100.361576</v>
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.3">
@@ -13434,10 +13435,10 @@
         <v>15000000</v>
       </c>
       <c r="M211">
-        <v>0.552261</v>
+        <v>0.53605599999999998</v>
       </c>
       <c r="N211">
-        <v>101.467032</v>
+        <v>101.447146</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.3">
@@ -13478,10 +13479,10 @@
         <v>4200000</v>
       </c>
       <c r="M212">
-        <v>-7.9934070000000004</v>
+        <v>-7.9921639999999998</v>
       </c>
       <c r="N212">
-        <v>112.6198562</v>
+        <v>112.621184</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.3">
@@ -13522,10 +13523,10 @@
         <v>15000000</v>
       </c>
       <c r="M213">
-        <v>-6.9018547999999997</v>
+        <v>-6.9186120000000004</v>
       </c>
       <c r="N213">
-        <v>107.5637941</v>
+        <v>107.583369</v>
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.3">
@@ -13566,10 +13567,10 @@
         <v>13888889</v>
       </c>
       <c r="M214">
-        <v>-7.6532210000000003</v>
+        <v>-7.6551679999999998</v>
       </c>
       <c r="N214">
-        <v>112.90248699999999</v>
+        <v>112.897693</v>
       </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.3">
@@ -13610,10 +13611,10 @@
         <v>12500000</v>
       </c>
       <c r="M215">
-        <v>-2.9759251</v>
+        <v>-2.9757009999999999</v>
       </c>
       <c r="N215">
-        <v>104.75598669999999</v>
+        <v>104.768023</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.3">
@@ -13654,10 +13655,10 @@
         <v>8333333</v>
       </c>
       <c r="M216">
-        <v>3.6106725000000002</v>
+        <v>3.616177</v>
       </c>
       <c r="N216">
-        <v>98.676816599999995</v>
+        <v>98.676056000000003</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.3">
@@ -13698,10 +13699,10 @@
         <v>8333333</v>
       </c>
       <c r="M217">
-        <v>-6.3595081000000002</v>
+        <v>-6.3554430000000002</v>
       </c>
       <c r="N217">
-        <v>106.8485524</v>
+        <v>106.853514</v>
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.3">
@@ -13742,10 +13743,10 @@
         <v>12500000</v>
       </c>
       <c r="M218">
-        <v>-6.7120088999999998</v>
+        <v>-6.7112959999999999</v>
       </c>
       <c r="N218">
-        <v>108.54961900000001</v>
+        <v>108.542145</v>
       </c>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.3">
@@ -13786,10 +13787,10 @@
         <v>9540000</v>
       </c>
       <c r="M219">
-        <v>-6.9098002999999997</v>
+        <v>-6.9641609999999998</v>
       </c>
       <c r="N219">
-        <v>109.6615702</v>
+        <v>109.65213900000001</v>
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.3">
@@ -13830,10 +13831,10 @@
         <v>5416667</v>
       </c>
       <c r="M220">
-        <v>-2.4226519999999998</v>
+        <v>-2.6649129999999999</v>
       </c>
       <c r="N220">
-        <v>111.73237399999999</v>
+        <v>111.674758</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.3">
@@ -13874,10 +13875,10 @@
         <v>10185185</v>
       </c>
       <c r="M221">
-        <v>-3.0646293</v>
+        <v>-3.0090159999999999</v>
       </c>
       <c r="N221">
-        <v>104.7246372</v>
+        <v>104.76015</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.3">
@@ -13918,10 +13919,10 @@
         <v>12500000</v>
       </c>
       <c r="M222">
-        <v>0.54738120000000001</v>
+        <v>0.54761499999999996</v>
       </c>
       <c r="N222">
-        <v>123.06238260000001</v>
+        <v>123.062428</v>
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.3">
@@ -13962,10 +13963,10 @@
         <v>9259259</v>
       </c>
       <c r="M223">
-        <v>-2.9254574999999998</v>
+        <v>-2.9141189999999999</v>
       </c>
       <c r="N223">
-        <v>104.78532920000001</v>
+        <v>104.791476</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.3">
@@ -14006,10 +14007,10 @@
         <v>7407407</v>
       </c>
       <c r="M224">
-        <v>1.44228</v>
+        <v>1.4478660000000001</v>
       </c>
       <c r="N224">
-        <v>125.14478800000001</v>
+        <v>125.127532</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.3">
@@ -14050,10 +14051,10 @@
         <v>13875000</v>
       </c>
       <c r="M225">
-        <v>-7.1541274000000001</v>
+        <v>-7.1570840000000002</v>
       </c>
       <c r="N225">
-        <v>111.8824067</v>
+        <v>111.882268</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.3">
@@ -14094,10 +14095,10 @@
         <v>8400000</v>
       </c>
       <c r="M226">
-        <v>-7.856382</v>
+        <v>-7.8957519999999999</v>
       </c>
       <c r="N226">
-        <v>112.39558599999999</v>
+        <v>112.665565</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.3">
@@ -14138,10 +14139,10 @@
         <v>8333333</v>
       </c>
       <c r="M227">
-        <v>-4.9865839999999997</v>
+        <v>-4.9391360000000004</v>
       </c>
       <c r="N227">
-        <v>105.188557</v>
+        <v>105.21337800000001</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.3">
@@ -14182,10 +14183,10 @@
         <v>6250000</v>
       </c>
       <c r="M228">
-        <v>-5.5494219999999999</v>
+        <v>-5.5425389999999997</v>
       </c>
       <c r="N228">
-        <v>120.190731</v>
+        <v>120.192222</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.3">
@@ -14226,10 +14227,10 @@
         <v>8000000</v>
       </c>
       <c r="M229">
-        <v>-7.5603191000000001</v>
+        <v>-7.5604019999999998</v>
       </c>
       <c r="N229">
-        <v>110.8197569</v>
+        <v>110.819518</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.3">
@@ -14270,10 +14271,10 @@
         <v>4600000</v>
       </c>
       <c r="M230">
-        <v>-8.1067225000000001</v>
+        <v>-8.1048380000000009</v>
       </c>
       <c r="N230">
-        <v>112.1674022</v>
+        <v>112.167683</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.3">
@@ -14314,10 +14315,10 @@
         <v>7400000</v>
       </c>
       <c r="M231">
-        <v>0.13130600000000001</v>
+        <v>-4.5404590000000002</v>
       </c>
       <c r="N231">
-        <v>117.48639300000001</v>
+        <v>120.314673</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.3">
@@ -14358,10 +14359,10 @@
         <v>21666667</v>
       </c>
       <c r="M232">
-        <v>-6.2688170000000003</v>
+        <v>-6.3122319999999998</v>
       </c>
       <c r="N232">
-        <v>106.97681300000001</v>
+        <v>107.164843</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.3">
@@ -14402,10 +14403,10 @@
         <v>10000000</v>
       </c>
       <c r="M233">
-        <v>-7.4338290000000002</v>
+        <v>-7.3469170000000004</v>
       </c>
       <c r="N233">
-        <v>112.673362</v>
+        <v>112.767736</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.3">
@@ -14446,10 +14447,10 @@
         <v>8350000</v>
       </c>
       <c r="M234">
-        <v>-7.2858523000000002</v>
+        <v>-7.2854359999999998</v>
       </c>
       <c r="N234">
-        <v>112.6551111</v>
+        <v>112.652907</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.3">
@@ -14490,10 +14491,10 @@
         <v>8500000</v>
       </c>
       <c r="M235">
-        <v>-6.9684239000000003</v>
+        <v>-6.9817429999999998</v>
       </c>
       <c r="N235">
-        <v>110.386961</v>
+        <v>110.39166400000001</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.3">
@@ -14534,10 +14535,10 @@
         <v>14814815</v>
       </c>
       <c r="M236">
-        <v>-0.49953799999999998</v>
+        <v>-0.46177000000000001</v>
       </c>
       <c r="N236">
-        <v>117.166201</v>
+        <v>117.13990099999999</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.3">
@@ -14578,10 +14579,10 @@
         <v>9259259</v>
       </c>
       <c r="M237">
-        <v>-2.1931314999999998</v>
+        <v>-2.184895</v>
       </c>
       <c r="N237">
-        <v>113.8865437</v>
+        <v>113.885851</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.3">
@@ -14622,10 +14623,10 @@
         <v>6666667</v>
       </c>
       <c r="M238">
-        <v>-3.5148499999999999E-2</v>
+        <v>-3.8565000000000002E-2</v>
       </c>
       <c r="N238">
-        <v>109.34646600000001</v>
+        <v>109.347481</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.3">
@@ -14666,10 +14667,10 @@
         <v>8333333</v>
       </c>
       <c r="M239">
-        <v>-6.9116350000000004</v>
+        <v>-6.9224300000000003</v>
       </c>
       <c r="N239">
-        <v>106.92764200000001</v>
+        <v>106.930753</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.3">
@@ -14710,10 +14711,10 @@
         <v>10000000</v>
       </c>
       <c r="M240">
-        <v>-8.5895630000000001</v>
+        <v>-8.5888279999999995</v>
       </c>
       <c r="N240">
-        <v>116.1271814</v>
+        <v>116.117907</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.3">
@@ -14754,10 +14755,10 @@
         <v>11111111</v>
       </c>
       <c r="M241">
-        <v>-6.8899492999999996</v>
+        <v>-6.8919540000000001</v>
       </c>
       <c r="N241">
-        <v>112.0507356</v>
+        <v>112.04934900000001</v>
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.3">
@@ -14798,10 +14799,10 @@
         <v>6666667</v>
       </c>
       <c r="M242">
-        <v>-3.5148499999999999E-2</v>
+        <v>-3.8565000000000002E-2</v>
       </c>
       <c r="N242">
-        <v>109.34646600000001</v>
+        <v>109.347481</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.3">
@@ -14842,10 +14843,10 @@
         <v>11574074</v>
       </c>
       <c r="M243">
-        <v>-7.5568429999999998</v>
+        <v>-7.5387729999999999</v>
       </c>
       <c r="N243">
-        <v>112.24809</v>
+        <v>112.24469000000001</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.3">
@@ -14886,10 +14887,10 @@
         <v>6000000</v>
       </c>
       <c r="M244">
-        <v>-7.4338290000000002</v>
+        <v>-7.4069630000000002</v>
       </c>
       <c r="N244">
-        <v>112.673362</v>
+        <v>112.67265999999999</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.3">
@@ -14930,10 +14931,10 @@
         <v>5000000</v>
       </c>
       <c r="M245">
-        <v>3.3000169000000001</v>
+        <v>3.310654</v>
       </c>
       <c r="N245">
-        <v>117.6330159</v>
+        <v>117.587605</v>
       </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.3">
@@ -14974,10 +14975,10 @@
         <v>9166666</v>
       </c>
       <c r="M246">
-        <v>-7.2157039999999997</v>
+        <v>-7.2157859999999996</v>
       </c>
       <c r="N246">
-        <v>107.90136200000001</v>
+        <v>107.908772</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.3">
@@ -15018,10 +15019,10 @@
         <v>6666667</v>
       </c>
       <c r="M247">
-        <v>-6.8343790000000002</v>
+        <v>-6.8353599999999997</v>
       </c>
       <c r="N247">
-        <v>108.251267</v>
+        <v>108.23177200000001</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.3">
@@ -15062,10 +15063,10 @@
         <v>21666667</v>
       </c>
       <c r="M248">
-        <v>-6.1761923999999997</v>
+        <v>-6.2714759999999998</v>
       </c>
       <c r="N248">
-        <v>106.63821609999999</v>
+        <v>106.630234</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.3">
@@ -15106,10 +15107,10 @@
         <v>8350000</v>
       </c>
       <c r="M249">
-        <v>-7.1588839999999996</v>
+        <v>-7.1389820000000004</v>
       </c>
       <c r="N249">
-        <v>112.621172</v>
+        <v>112.61539500000001</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.3">
@@ -15150,10 +15151,10 @@
         <v>3750000</v>
       </c>
       <c r="M250">
-        <v>-8.5495269999999994</v>
+        <v>-8.5289029999999997</v>
       </c>
       <c r="N250">
-        <v>115.41203400000001</v>
+        <v>115.39859800000001</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.3">
@@ -15194,10 +15195,10 @@
         <v>8333333</v>
       </c>
       <c r="M251">
-        <v>-2.2083599</v>
+        <v>-2.208793</v>
       </c>
       <c r="N251">
-        <v>113.933357</v>
+        <v>113.933882</v>
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.3">
@@ -15238,10 +15239,10 @@
         <v>6666667</v>
       </c>
       <c r="M252">
-        <v>-6.2998320999999997</v>
+        <v>-6.3044529999999996</v>
       </c>
       <c r="N252">
-        <v>107.28991550000001</v>
+        <v>107.292559</v>
       </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.3">
@@ -15282,10 +15283,10 @@
         <v>18208333</v>
       </c>
       <c r="M253">
-        <v>-6.181705</v>
+        <v>-6.225727</v>
       </c>
       <c r="N253">
-        <v>106.643551</v>
+        <v>106.720572</v>
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.3">
@@ -15326,10 +15327,10 @@
         <v>4590000</v>
       </c>
       <c r="M254">
-        <v>-7.4347190000000003</v>
+        <v>-7.4092409999999997</v>
       </c>
       <c r="N254">
-        <v>111.414176</v>
+        <v>111.439922</v>
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.3">
@@ -15370,10 +15371,10 @@
         <v>5583333</v>
       </c>
       <c r="M255">
-        <v>-7.6704274000000003</v>
+        <v>-7.670452</v>
       </c>
       <c r="N255">
-        <v>109.6576482</v>
+        <v>109.65588700000001</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.3">
@@ -15414,10 +15415,10 @@
         <v>6666667</v>
       </c>
       <c r="M256">
-        <v>-6.3021906000000003</v>
+        <v>-6.1563939999999997</v>
       </c>
       <c r="N256">
-        <v>107.3046116</v>
+        <v>107.29899399999999</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.3">
@@ -15458,10 +15459,10 @@
         <v>25000000</v>
       </c>
       <c r="M257">
-        <v>-10.192152999999999</v>
+        <v>-10.171537000000001</v>
       </c>
       <c r="N257">
-        <v>123.608271</v>
+        <v>123.590211</v>
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.3">
@@ -15502,10 +15503,10 @@
         <v>7291667</v>
       </c>
       <c r="M258">
-        <v>-0.857209</v>
+        <v>-0.91914099999999999</v>
       </c>
       <c r="N258">
-        <v>119.942661</v>
+        <v>119.883326</v>
       </c>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.3">
@@ -15546,10 +15547,10 @@
         <v>10416666</v>
       </c>
       <c r="M259">
-        <v>-6.5647481000000001</v>
+        <v>-6.563993</v>
       </c>
       <c r="N259">
-        <v>107.76587429999999</v>
+        <v>107.766926</v>
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.3">
@@ -15590,10 +15591,10 @@
         <v>5833333</v>
       </c>
       <c r="M260">
-        <v>-6.1855998999999997</v>
+        <v>-6.1804439999999996</v>
       </c>
       <c r="N260">
-        <v>106.61695709999999</v>
+        <v>106.621224</v>
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.3">
@@ -15634,10 +15635,10 @@
         <v>6666667</v>
       </c>
       <c r="M261">
-        <v>4.1606860000000001</v>
+        <v>4.1403439999999998</v>
       </c>
       <c r="N261">
-        <v>96.131044000000003</v>
+        <v>96.126309000000006</v>
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.3">
@@ -15678,10 +15679,10 @@
         <v>5000000</v>
       </c>
       <c r="M262">
-        <v>-8.1981819999999992</v>
+        <v>-8.1955089999999995</v>
       </c>
       <c r="N262">
-        <v>111.112962</v>
+        <v>111.112225</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.3">
@@ -15722,10 +15723,10 @@
         <v>4600000</v>
       </c>
       <c r="M263">
-        <v>-7.8333089999999999</v>
+        <v>-7.807658</v>
       </c>
       <c r="N263">
-        <v>112.016654</v>
+        <v>112.038389</v>
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.3">
@@ -15766,10 +15767,10 @@
         <v>4792000</v>
       </c>
       <c r="M264">
-        <v>-7.4811190999999999</v>
+        <v>-7.4753160000000003</v>
       </c>
       <c r="N264">
-        <v>112.4303542</v>
+        <v>112.432158</v>
       </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.3">
@@ -15810,10 +15811,10 @@
         <v>6250000</v>
       </c>
       <c r="M265">
-        <v>-6.8222975999999997</v>
+        <v>-6.8228970000000002</v>
       </c>
       <c r="N265">
-        <v>107.1414267</v>
+        <v>107.140998</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.3">
@@ -15854,10 +15855,10 @@
         <v>47291090</v>
       </c>
       <c r="M266">
-        <v>-6.1823398999999997</v>
+        <v>-6.1771760000000002</v>
       </c>
       <c r="N266">
-        <v>106.8428715</v>
+        <v>106.841382</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.3">
@@ -15898,10 +15899,10 @@
         <v>30000000</v>
       </c>
       <c r="M267">
-        <v>-6.2180109999999997</v>
+        <v>-6.2177490000000004</v>
       </c>
       <c r="N267">
-        <v>106.9241761</v>
+        <v>106.92419200000001</v>
       </c>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.3">
@@ -15942,10 +15943,10 @@
         <v>24821852</v>
       </c>
       <c r="M268">
-        <v>-6.8893810000000002</v>
+        <v>-6.889564</v>
       </c>
       <c r="N268">
-        <v>107.596457</v>
+        <v>107.596006</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.3">
@@ -15986,10 +15987,10 @@
         <v>42203400</v>
       </c>
       <c r="M269">
-        <v>0.500135</v>
+        <v>0.49989</v>
       </c>
       <c r="N269">
-        <v>101.42028500000001</v>
+        <v>101.41874799999999</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.3">
@@ -16030,10 +16031,10 @@
         <v>20000000</v>
       </c>
       <c r="M270">
-        <v>0.50887499999999997</v>
+        <v>0.52919799999999995</v>
       </c>
       <c r="N270">
-        <v>101.46202099999999</v>
+        <v>101.446726</v>
       </c>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.3">
@@ -16074,10 +16075,10 @@
         <v>26342500</v>
       </c>
       <c r="M271">
-        <v>-7.5692488999999998</v>
+        <v>-7.5989630000000004</v>
       </c>
       <c r="N271">
-        <v>110.82844799999999</v>
+        <v>110.81621699999999</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.3">
@@ -16118,10 +16119,10 @@
         <v>57884756</v>
       </c>
       <c r="M272">
-        <v>-6.3457790000000003</v>
+        <v>-6.2126200000000003</v>
       </c>
       <c r="N272">
-        <v>106.87584</v>
+        <v>106.94340800000001</v>
       </c>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.3">
@@ -16162,10 +16163,10 @@
         <v>24646800</v>
       </c>
       <c r="M273">
-        <v>-6.8701059999999998</v>
+        <v>-6.8699839999999996</v>
       </c>
       <c r="N273">
-        <v>109.129098</v>
+        <v>109.128843</v>
       </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.3">
@@ -16206,10 +16207,10 @@
         <v>37050000</v>
       </c>
       <c r="M274">
-        <v>-7.2462835999999999</v>
+        <v>-7.2627389999999998</v>
       </c>
       <c r="N274">
-        <v>112.7377674</v>
+        <v>112.748824</v>
       </c>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.3">
@@ -16250,10 +16251,10 @@
         <v>23490000</v>
       </c>
       <c r="M275">
-        <v>-5.4432611</v>
+        <v>-5.4437540000000002</v>
       </c>
       <c r="N275">
-        <v>105.280197</v>
+        <v>105.280238</v>
       </c>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.3">
@@ -16294,10 +16295,10 @@
         <v>24474483</v>
       </c>
       <c r="M276">
-        <v>3.6075124999999999</v>
+        <v>3.606017</v>
       </c>
       <c r="N276">
-        <v>98.496608699999996</v>
+        <v>98.488361999999995</v>
       </c>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.3">
@@ -16338,10 +16339,10 @@
         <v>40047344</v>
       </c>
       <c r="M277">
-        <v>-6.2553976999999996</v>
+        <v>-6.2559889999999996</v>
       </c>
       <c r="N277">
-        <v>106.8453236</v>
+        <v>106.854455</v>
       </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.3">
@@ -16382,10 +16383,10 @@
         <v>31213000</v>
       </c>
       <c r="M278">
-        <v>-6.2349857999999996</v>
+        <v>-6.2993129999999997</v>
       </c>
       <c r="N278">
-        <v>106.9945444</v>
+        <v>107.149914</v>
       </c>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.3">
@@ -16426,10 +16427,10 @@
         <v>39944650</v>
       </c>
       <c r="M279">
-        <v>-6.2238680000000004</v>
+        <v>-6.2126200000000003</v>
       </c>
       <c r="N279">
-        <v>106.878175</v>
+        <v>106.94340800000001</v>
       </c>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.3">
@@ -16470,10 +16471,10 @@
         <v>28800000</v>
       </c>
       <c r="M280">
-        <v>-7.6843820000000003</v>
+        <v>-7.6921270000000002</v>
       </c>
       <c r="N280">
-        <v>109.09414700000001</v>
+        <v>109.02432</v>
       </c>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.3">
@@ -16514,10 +16515,10 @@
         <v>0</v>
       </c>
       <c r="M281">
-        <v>-1.2398711</v>
+        <v>-1.24302</v>
       </c>
       <c r="N281">
-        <v>116.8593379</v>
+        <v>116.897696</v>
       </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.3">
@@ -16558,10 +16559,10 @@
         <v>37758000</v>
       </c>
       <c r="M282">
-        <v>-5.4460712999999998</v>
+        <v>-5.4174049999999996</v>
       </c>
       <c r="N282">
-        <v>105.26437420000001</v>
+        <v>105.257766</v>
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.3">
@@ -16602,10 +16603,10 @@
         <v>26211000</v>
       </c>
       <c r="M283">
-        <v>0.89852220000000005</v>
+        <v>0.89840799999999998</v>
       </c>
       <c r="N283">
-        <v>108.9693142</v>
+        <v>108.969689</v>
       </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.3">
@@ -16646,10 +16647,10 @@
         <v>20400000</v>
       </c>
       <c r="M284">
-        <v>-7.7067842999999998</v>
+        <v>-7.7001949999999999</v>
       </c>
       <c r="N284">
-        <v>114.0054142</v>
+        <v>114.02211</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.3">
@@ -16690,10 +16691,10 @@
         <v>16000000</v>
       </c>
       <c r="M285">
-        <v>-2.6747475999999999</v>
+        <v>-2.6689020000000001</v>
       </c>
       <c r="N285">
-        <v>118.8862879</v>
+        <v>118.89269899999999</v>
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.3">
@@ -16734,10 +16735,10 @@
         <v>6250000</v>
       </c>
       <c r="M286">
-        <v>-7.5451755</v>
+        <v>-7.5450090000000003</v>
       </c>
       <c r="N286">
-        <v>112.24117819999999</v>
+        <v>112.240522</v>
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.3">
@@ -16778,10 +16779,10 @@
         <v>0</v>
       </c>
       <c r="M287">
-        <v>-7.5968159000000002</v>
+        <v>-7.7553270000000003</v>
       </c>
       <c r="N287">
-        <v>110.42538949999999</v>
+        <v>110.383214</v>
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.3">
@@ -16822,10 +16823,10 @@
         <v>8333333</v>
       </c>
       <c r="M288">
-        <v>-7.1584823999999996</v>
+        <v>-7.1567030000000003</v>
       </c>
       <c r="N288">
-        <v>112.6480668</v>
+        <v>112.64920600000001</v>
       </c>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.3">
@@ -16866,10 +16867,10 @@
         <v>5833333</v>
       </c>
       <c r="M289">
-        <v>-7.4682040000000001</v>
+        <v>-7.4694510000000003</v>
       </c>
       <c r="N289">
-        <v>112.4396254</v>
+        <v>112.43944</v>
       </c>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.3">
@@ -16954,10 +16955,10 @@
         <v>12962963</v>
       </c>
       <c r="M291">
-        <v>-7.9803252000000002</v>
+        <v>-7.9807319999999997</v>
       </c>
       <c r="N291">
-        <v>112.6525918</v>
+        <v>112.653008</v>
       </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.3">
@@ -16998,10 +16999,10 @@
         <v>6250000</v>
       </c>
       <c r="M292">
-        <v>-2.8324790000000002</v>
+        <v>-3.3983210000000001</v>
       </c>
       <c r="N292">
-        <v>102.96142399999999</v>
+        <v>119.212132</v>
       </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.3">
@@ -17086,10 +17087,10 @@
         <v>9259377</v>
       </c>
       <c r="M294">
-        <v>-1.8383581</v>
+        <v>-1.839747</v>
       </c>
       <c r="N294">
-        <v>109.9676656</v>
+        <v>109.96825800000001</v>
       </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.3">
@@ -17130,10 +17131,10 @@
         <v>8750000</v>
       </c>
       <c r="M295">
-        <v>-1.6155337000000001</v>
+        <v>-1.6180950000000001</v>
       </c>
       <c r="N295">
-        <v>103.6271038</v>
+        <v>103.628708</v>
       </c>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.3">
@@ -17174,10 +17175,10 @@
         <v>9166666</v>
       </c>
       <c r="M296">
-        <v>0.49220969999999997</v>
+        <v>0.49174099999999998</v>
       </c>
       <c r="N296">
-        <v>101.4383242</v>
+        <v>101.438861</v>
       </c>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.3">
@@ -17218,10 +17219,10 @@
         <v>8333333</v>
       </c>
       <c r="M297">
-        <v>0.50539369999999995</v>
+        <v>0.50585800000000003</v>
       </c>
       <c r="N297">
-        <v>101.43439600000001</v>
+        <v>101.435382</v>
       </c>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.3">
@@ -17262,10 +17263,10 @@
         <v>8000000</v>
       </c>
       <c r="M298">
-        <v>-7.5692488999999998</v>
+        <v>-7.574052</v>
       </c>
       <c r="N298">
-        <v>110.82844799999999</v>
+        <v>110.81626900000001</v>
       </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.3">
@@ -17306,10 +17307,10 @@
         <v>15740741</v>
       </c>
       <c r="M299">
-        <v>-10.1580706</v>
+        <v>-10.162362999999999</v>
       </c>
       <c r="N299">
-        <v>123.6285707</v>
+        <v>123.63088999999999</v>
       </c>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.3">
@@ -17350,10 +17351,10 @@
         <v>7500000</v>
       </c>
       <c r="M300">
-        <v>-6.993023</v>
+        <v>-6.983949</v>
       </c>
       <c r="N300">
-        <v>110.458387</v>
+        <v>110.459352</v>
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.3">
@@ -17394,10 +17395,10 @@
         <v>8083333</v>
       </c>
       <c r="M301">
-        <v>-6.882701</v>
+        <v>-6.8724860000000003</v>
       </c>
       <c r="N301">
-        <v>109.051416</v>
+        <v>109.04513900000001</v>
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.3">
@@ -17438,10 +17439,10 @@
         <v>10000000</v>
       </c>
       <c r="M302">
-        <v>3.572702</v>
+        <v>0.73313300000000003</v>
       </c>
       <c r="N302">
-        <v>98.673415000000006</v>
+        <v>124.303524</v>
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.3">
@@ -17482,10 +17483,10 @@
         <v>7000000</v>
       </c>
       <c r="M303">
-        <v>-2.9769380000000001</v>
+        <v>-2.9746980000000001</v>
       </c>
       <c r="N303">
-        <v>104.734354</v>
+        <v>104.782999</v>
       </c>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.3">
@@ -17526,10 +17527,10 @@
         <v>10833333</v>
       </c>
       <c r="M304">
-        <v>-6.2448724999999996</v>
+        <v>-6.2404950000000001</v>
       </c>
       <c r="N304">
-        <v>106.6727918</v>
+        <v>106.676568</v>
       </c>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.3">
@@ -17570,10 +17571,10 @@
         <v>8333333</v>
       </c>
       <c r="M305">
-        <v>3.68201</v>
+        <v>3.70608</v>
       </c>
       <c r="N305">
-        <v>98.656091000000004</v>
+        <v>98.659222</v>
       </c>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.3">
@@ -17614,10 +17615,10 @@
         <v>15833333</v>
       </c>
       <c r="M306">
-        <v>-6.1892019999999999</v>
+        <v>-6.1842810000000004</v>
       </c>
       <c r="N306">
-        <v>106.70365099999999</v>
+        <v>106.708175</v>
       </c>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.3">
@@ -17658,10 +17659,10 @@
         <v>11250000</v>
       </c>
       <c r="M307">
-        <v>-6.1736674000000002</v>
+        <v>-6.1760729999999997</v>
       </c>
       <c r="N307">
-        <v>106.6871931</v>
+        <v>106.688096</v>
       </c>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.3">
@@ -17702,10 +17703,10 @@
         <v>7916667</v>
       </c>
       <c r="M308">
-        <v>-5.4024549999999998</v>
+        <v>-5.1139070000000002</v>
       </c>
       <c r="N308">
-        <v>105.257957</v>
+        <v>105.302295</v>
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.3">
@@ -17746,10 +17747,10 @@
         <v>10083333</v>
       </c>
       <c r="M309">
-        <v>-6.9259269999999997</v>
+        <v>-6.9802999999999997</v>
       </c>
       <c r="N309">
-        <v>107.626976</v>
+        <v>107.6343</v>
       </c>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.3">
@@ -17790,10 +17791,10 @@
         <v>4166667</v>
       </c>
       <c r="M310">
-        <v>-4.0605397999999999</v>
+        <v>-4.016038</v>
       </c>
       <c r="N310">
-        <v>119.6234068</v>
+        <v>119.62249</v>
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.3">
@@ -17834,10 +17835,10 @@
         <v>10000000</v>
       </c>
       <c r="M311">
-        <v>-6.1508596000000004</v>
+        <v>-6.1542909999999997</v>
       </c>
       <c r="N311">
-        <v>106.5639019</v>
+        <v>106.574645</v>
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.3">
@@ -17878,10 +17879,10 @@
         <v>4583333</v>
       </c>
       <c r="M312">
-        <v>0.46412039999999999</v>
+        <v>0.45553300000000002</v>
       </c>
       <c r="N312">
-        <v>101.3939475</v>
+        <v>101.402602</v>
       </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.3">
@@ -17922,10 +17923,10 @@
         <v>8000000</v>
       </c>
       <c r="M313">
-        <v>-7.8199059999999996</v>
+        <v>-7.8111189999999997</v>
       </c>
       <c r="N313">
-        <v>111.00273</v>
+        <v>110.924075</v>
       </c>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.3">
@@ -17966,10 +17967,10 @@
         <v>11666667</v>
       </c>
       <c r="M314">
-        <v>3.3307540000000002</v>
+        <v>3.3329149999999998</v>
       </c>
       <c r="N314">
-        <v>99.139320999999995</v>
+        <v>99.160880000000006</v>
       </c>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.3">
@@ -18010,10 +18011,10 @@
         <v>8333333</v>
       </c>
       <c r="M315">
-        <v>3.2983180999999999</v>
+        <v>3.2988089999999999</v>
       </c>
       <c r="N315">
-        <v>117.58627610000001</v>
+        <v>117.58619299999999</v>
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.3">
@@ -18054,10 +18055,10 @@
         <v>11666667</v>
       </c>
       <c r="M316">
-        <v>-6.2660819999999999</v>
+        <v>-6.2599150000000003</v>
       </c>
       <c r="N316">
-        <v>106.9749858</v>
+        <v>106.968514</v>
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.3">
@@ -18098,10 +18099,10 @@
         <v>10000000</v>
       </c>
       <c r="M317">
-        <v>-6.2688170000000003</v>
+        <v>-6.1679380000000004</v>
       </c>
       <c r="N317">
-        <v>106.97681300000001</v>
+        <v>106.975098</v>
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.3">
@@ -18142,10 +18143,10 @@
         <v>11666667</v>
       </c>
       <c r="M318">
-        <v>6.1650999999999997E-2</v>
+        <v>6.4342999999999997E-2</v>
       </c>
       <c r="N318">
-        <v>111.4828467</v>
+        <v>111.491871</v>
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.3">
@@ -18186,10 +18187,10 @@
         <v>16083333</v>
       </c>
       <c r="M319">
-        <v>-8.7069039999999998</v>
+        <v>-8.6455909999999996</v>
       </c>
       <c r="N319">
-        <v>116.56244700000001</v>
+        <v>116.519181</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.3">
@@ -18230,10 +18231,10 @@
         <v>12500000</v>
       </c>
       <c r="M320">
-        <v>-7.2036036000000001</v>
+        <v>-7.2081359999999997</v>
       </c>
       <c r="N320">
-        <v>107.89017219999999</v>
+        <v>107.897812</v>
       </c>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.3">
@@ -18274,10 +18275,10 @@
         <v>11666667</v>
       </c>
       <c r="M321">
-        <v>-5.4844539000000001</v>
+        <v>2.985357</v>
       </c>
       <c r="N321">
-        <v>105.7128867</v>
+        <v>99.628338999999997</v>
       </c>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.3">
@@ -18318,10 +18319,10 @@
         <v>12000000</v>
       </c>
       <c r="M322">
-        <v>-6.5376349999999999</v>
+        <v>-6.5375579999999998</v>
       </c>
       <c r="N322">
-        <v>107.429947</v>
+        <v>107.445504</v>
       </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.3">
@@ -18362,10 +18363,10 @@
         <v>14166667</v>
       </c>
       <c r="M323">
-        <v>-6.3901301000000004</v>
+        <v>-6.3960699999999999</v>
       </c>
       <c r="N323">
-        <v>106.7520225</v>
+        <v>106.74329400000001</v>
       </c>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.3">
@@ -18406,10 +18407,10 @@
         <v>10000000</v>
       </c>
       <c r="M324">
-        <v>-8.1166619999999998</v>
+        <v>-8.1172970000000007</v>
       </c>
       <c r="N324">
-        <v>115.13952999999999</v>
+        <v>115.08147200000001</v>
       </c>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.3">
@@ -18450,10 +18451,10 @@
         <v>7916667</v>
       </c>
       <c r="M325">
-        <v>-5.4024549999999998</v>
+        <v>-5.3900579999999998</v>
       </c>
       <c r="N325">
-        <v>105.257957</v>
+        <v>105.261799</v>
       </c>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.3">
@@ -18494,10 +18495,10 @@
         <v>12500000</v>
       </c>
       <c r="M326">
-        <v>-2.9684680000000001</v>
+        <v>-0.91443799999999997</v>
       </c>
       <c r="N326">
-        <v>119.898115</v>
+        <v>119.876328</v>
       </c>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.3">
@@ -18538,10 +18539,10 @@
         <v>12500000</v>
       </c>
       <c r="M327">
-        <v>-2.838803</v>
+        <v>-3.3913329999999999</v>
       </c>
       <c r="N327">
-        <v>120.206909</v>
+        <v>120.369246</v>
       </c>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.3">
@@ -18582,10 +18583,10 @@
         <v>16666667</v>
       </c>
       <c r="M328">
-        <v>-8.2228110000000001</v>
+        <v>-8.2039419999999996</v>
       </c>
       <c r="N328">
-        <v>114.35442999999999</v>
+        <v>114.37392699999999</v>
       </c>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.3">
@@ -18626,10 +18627,10 @@
         <v>10000000</v>
       </c>
       <c r="M329">
-        <v>-6.7137044000000001</v>
+        <v>-6.906695</v>
       </c>
       <c r="N329">
-        <v>108.5608483</v>
+        <v>108.747607</v>
       </c>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.3">
@@ -18670,10 +18671,10 @@
         <v>14166667</v>
       </c>
       <c r="M330">
-        <v>-2.1221809999999999</v>
+        <v>-2.142941</v>
       </c>
       <c r="N330">
-        <v>106.138741</v>
+        <v>106.150015</v>
       </c>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.3">
@@ -18714,10 +18715,10 @@
         <v>10416667</v>
       </c>
       <c r="M331">
-        <v>-6.8119484000000003</v>
+        <v>-6.8113070000000002</v>
       </c>
       <c r="N331">
-        <v>107.14296109999999</v>
+        <v>107.145921</v>
       </c>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.3">
@@ -18758,10 +18759,10 @@
         <v>12083333</v>
       </c>
       <c r="M332">
-        <v>-2.9996306000000001</v>
+        <v>-2.9934639999999999</v>
       </c>
       <c r="N332">
-        <v>120.1920679</v>
+        <v>120.193006</v>
       </c>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.3">
@@ -18802,10 +18803,10 @@
         <v>8333333</v>
       </c>
       <c r="M333">
-        <v>-6.839391</v>
+        <v>-6.8605150000000004</v>
       </c>
       <c r="N333">
-        <v>107.922</v>
+        <v>107.918882</v>
       </c>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.3">
@@ -18846,10 +18847,10 @@
         <v>4583333</v>
       </c>
       <c r="M334">
-        <v>3.5941255999999999</v>
+        <v>3.6130209999999998</v>
       </c>
       <c r="N334">
-        <v>98.714712599999999</v>
+        <v>98.741460000000004</v>
       </c>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.3">
@@ -18890,10 +18891,10 @@
         <v>5000000</v>
       </c>
       <c r="M335">
-        <v>3.757225</v>
+        <v>3.7631670000000002</v>
       </c>
       <c r="N335">
-        <v>98.452220999999994</v>
+        <v>98.449181999999993</v>
       </c>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.3">
@@ -18934,10 +18935,10 @@
         <v>6166667</v>
       </c>
       <c r="M336">
-        <v>-6.8982435000000004</v>
+        <v>-6.8986369999999999</v>
       </c>
       <c r="N336">
-        <v>107.560517</v>
+        <v>107.55388499999999</v>
       </c>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.3">
@@ -18978,10 +18979,10 @@
         <v>19166667</v>
       </c>
       <c r="M337">
-        <v>-6.3341000000000003</v>
+        <v>-6.3316720000000002</v>
       </c>
       <c r="N337">
-        <v>106.8214</v>
+        <v>106.828756</v>
       </c>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.3">
@@ -19022,10 +19023,10 @@
         <v>12500000</v>
       </c>
       <c r="M338">
-        <v>2.0594929999999998</v>
+        <v>2.0918670000000001</v>
       </c>
       <c r="N338">
-        <v>100.011591</v>
+        <v>99.838648000000006</v>
       </c>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.3">
@@ -19066,10 +19067,10 @@
         <v>6666667</v>
       </c>
       <c r="M339">
-        <v>3.5674967999999998</v>
+        <v>3.5676420000000002</v>
       </c>
       <c r="N339">
-        <v>98.647352400000003</v>
+        <v>98.650711999999999</v>
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.3">
@@ -19110,10 +19111,10 @@
         <v>7500000</v>
       </c>
       <c r="M340">
-        <v>-4.3585022999999996</v>
+        <v>-4.3561820000000004</v>
       </c>
       <c r="N340">
-        <v>119.8892383</v>
+        <v>119.888642</v>
       </c>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.3">
@@ -19154,10 +19155,10 @@
         <v>11350000</v>
       </c>
       <c r="M341">
-        <v>-6.9201487000000004</v>
+        <v>-6.919638</v>
       </c>
       <c r="N341">
-        <v>107.5694383</v>
+        <v>107.569948</v>
       </c>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.3">
@@ -19198,10 +19199,10 @@
         <v>16666667</v>
       </c>
       <c r="M342">
-        <v>-0.49953799999999998</v>
+        <v>-0.49393900000000002</v>
       </c>
       <c r="N342">
-        <v>117.166201</v>
+        <v>117.15514</v>
       </c>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.3">

--- a/output/stores_complete.xlsx
+++ b/output/stores_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8950074D-3367-44F8-9745-0A76A8EA0073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2B4802-FCF3-4FF3-8512-A20BE0989BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3305" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4335" uniqueCount="1616">
   <si>
     <t>Store ID</t>
   </si>
@@ -3813,16 +3813,1096 @@
   </si>
   <si>
     <t>D</t>
+  </si>
+  <si>
+    <t>Google Maps Link</t>
+  </si>
+  <si>
+    <t>POPULATION</t>
+  </si>
+  <si>
+    <t>Daily Traffic (Est)</t>
+  </si>
+  <si>
+    <t>Monthly Traffic (Est)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Kelapa%20Gading%20Jakarta%20Indonesia%20Jl.%20Boulevar%20Kelapa%20Gading%20Blok%20M%2C%20Jakarta%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014240%2C%20Lt.%201%20Unit%20F%20No.%20286%2C%20288%20%26%20294</t>
+  </si>
+  <si>
+    <t>18,000-28,000</t>
+  </si>
+  <si>
+    <t>540,000-840,000</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Summarecon%20Mall%20Bekasi%20Indonesia%20Jl.%20Boulevard%20Ahmad%20Yani%20Blok%20M%2C%20Sentra%20Summarecon%20Bekasi%2C%20Kota%20Bks%2C%20Jawa%20Barat%2017142%2C%20GF%20-%20121A</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Cibinong%20City%20Mall%20Cibinong%20Indonesia%20CIBINONG%20CITY%20MALL%20Jl.Tegar%20Beriman%20No.1%20Pakansari%2C%20Cibinong%2C%20Bogor%2C%20Jawa%20Barat%2016914%2C%20Lantai%20LG%2C%2019</t>
+  </si>
+  <si>
+    <t>25,000-40,000</t>
+  </si>
+  <si>
+    <t>750,000-1,200,000</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Central%20Park%20Mall%20Jakarta%20Indonesia%20Letjen%20S.%20Parman%20St%20No.Kav.%2028%2C%20South%20Tanjung%20Duren%2C%20Grogol%20petamburan%2C%20West%20Jakarta%20City%2C%20Jakarta%2011470</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Summarecon%20Mall%20Serpong%20Tangerang%20Indonesia%20Jalan%20Gading%20Serpong%20Boulevard%20GF%2002%2C%20Pakulonan%20Bar.%2C%20Kec.%20Klp.%20Dua%2C%20Kabupaten%20Tangerang%2C%20Banten%2015810</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Grand%20Indonesia%20Mall%20Jakarta%20Indonesia%20%20EAST%20MALL%2C%20Mall%20Grand%20Indonesia%20East%20Mall%20Lt.3A%2030%2C%20Jl.%20M.H.%20Thamrin%20No.1%2C%20Kec.%20Menteng%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010230</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Istana%20BEC%20Bandung%20Indonesia%20Jl%20Purnawarman%20No.5-17%2C%20Babakan%20Ciamis%2C%20Sumur%20Bandung%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040117%2C%20UG%20AA008%20%26%20AA09</t>
+  </si>
+  <si>
+    <t>6,000-9,000</t>
+  </si>
+  <si>
+    <t>180,000-270,000</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Botani%20Square%20Mall%20Bogor%20Indonesia%20Jl.%20Raya%20Pajajaran%2C%20Tegallega%2C%20Bogor%20Tengah%2C%20Kota%20Bogor%2C%20Jawa%20Barat%2016127%2C%20L1%20Area%20EX%20IT%20Center%20B%20%28Samping%20ibox%29</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Pakuwon%20Mall%20Surabaya%20Indonesia%20Level%202%2C%20Pakuwon%20Mall%20Jl.%20Puncak%20Indah%20Lontar.%202%20Babatan%20Kecamatan%20Wiyung%20Lt.2-%2030%2C%20East%20Java%2060216</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Panakkukang%20Makassar%20Indonesia%20Mall%20Panakukkang%20Makasar%20Lt.%20Dasar%20Gedung%20D%20Unit%20D1/01%20Jl.%20Boulevard%20No.3%2C%20Masale%2C%20Kec.%20Panakkukang%2C%20Kota%20Makassar%2C%20Sulawesi%20Selatan%2090231</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Tunjungan%20Plaza%204%20Surabaya%20Indonesia%20Jl.%20Basuki%20Rahmat%20No.8012%2C%20Kedungdoro%2C%20Kec.%20Tegalsari%2C%20Surabaya%2C%20Jawa%20Timur%2060261</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Ambarrukmo%20Plaza%20Yogyakarta%20Indonesia%20Plaza%20Ambarukmo%20Jl.%20Laksda%20Adisucipto%20No.80%2C%20Caturtunggal%2C%20Kec.%20Depok%2C%20Kota%20Yogyakarta%2C%20Daerah%20Istimewa%20Yogyakarta%2055281%2C%20LG%20Unit%20B%203%20-%204</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Margo%20City%20Depok%20Indonesia%20Margo%20City%20Depok%20Lt.2%20Unit%202-70%20Jl.%20Margonda%20Raya%20No.358%20Kemiri%20Muka%20Kecamatan%20Beji%20Kota%20Depok%20Jawa%20Barat%2016423</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Bintaro%20Jaya%20Xchange%20Mall%201%20Tangerang%20Selatan%20Indonesia%20Jl.%20Lkr.%20Jaya%20No.24%2C%20Pd.%20Jaya%2C%20Kec.%20Pd.%20Aren%2C%20Tangerang%2C%20Banten%2015227</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Emporium%20Pluit%20Mall%20Jakarta%20Indonesia%20Jl.%20Pluit%20Selatan%20Raya%2C%20RT.23/RW.8%2C%20Penjaringan%2C%20Kota%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014440%2C%20Lt.%202%20No.%2037</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Gandaria%20City%20Jakarta%20Indonesia%20Jl.%20Sultan%20Iskandar%20Muda%2C%20Gandaria%2C%20Kec.%20Kby.%20Lama%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2012240</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lippo%20Mall%20ST%20Moritz%20Jakarta%20Indonesia%20Jl.%20Puri%20Indah%20Raya%20Blok%20U%201%2C%20Puri%20Indah%20CBD%2C%20Kembangan%2C%20Jakarta%20Barat-11610%2C%20Lt.1%20No.%2087</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Ratu%20Indah%20Makassar%20Indonesia%20Mall%20Ratu%20Indah%20Lt.2%20Unit%20221-223%20Jl.%20Dr%20Ratulangi%20No.35%2C%20Mamajang%20Luar%2C%20Kec.%20Mamajang%20Kota%20Makassar</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lippo%20Mall%20Cikarang%20Indonesia%20Jl.%20MH.%20Thamrin%2C%20Cibatu%2C%20Cikarang%20Sel.%2C%20Kabupaten%20Bekasi%2C%20Jawa%20Barat%2017530%2C%20Indonesia</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Galaxy%20Mall%203%20Surabaya%20Indonesia%20Jl.%20Dharmahusada%20Indah%20XVI%20Blok%20J%20No.12%2C%20Mulyorejo%2C%20Kec.%20Mulyorejo%2C%20Kota%20SBY%2C%20Jawa%20Timur%2060115%2C%20Lt.%203%20Unit%203-304-305</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Olympic%20Garden%20Malang%20Indonesia%20Jl.%20Kawi%20No.%2024%2C%20Kauman%2C%20Klojen%2C%20Kota%20Malang%2C%20Jawa%20Timur%2065116%2C%20Lt.2%20SF%2084%20-%2086</t>
+  </si>
+  <si>
+    <t>10,000-18,000</t>
+  </si>
+  <si>
+    <t>300,000-540,000</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Manado%20Town%20Square%20Manado%20Indonesia%20Jl.%20Pierre%20Tendean%2C%20Sario%20Utara%2C%20Sario%2C%20Manado%2C%20Sulawesi%20Utara%2095114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%2023%20Paskal%20Bandung%20indonesia%20Paskal%20Hyper%20Square%2C%20Jl.%20Pasir%20Kaliki%20No.25-27%20Lantai%203%20depan%20CGV%2C%20Ciroyom%2C%20Kec.%20Andir%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040171</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Deli%20Park%20Mall%20Medan%20Indonesia%20Deli%20Park%20Medan%2C%20Lantai%20LM%2C%20Jl.%20Putri%20Hijau%20No.1%2C%20Kesawan%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20TSM%20Bandung%20Indonesia%20Trans%20Studio%20Mall%20Lantai%201%20Unit%20B178%2C%20Jl.%20Gatot%20Subroto%20No.290%20%2C%20Binong%2C%20Kec.%20Batununggal%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040275</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Puri%20Indah%20Mall%20Jakarta%20Indonesia%20Jl.%20Puri%20Agung%20No.1%2C%20Kembangan%20Sel.%2C%20Kec.%20Kembangan%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011610</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Metropolitan%20Mall%20Cileungsi%20Bogor%20Indonesia%20Jl.%20Metland%20No.4-15%2C%20Cileungsi%2C%20Bogor%2C%20Jawa%20Barat%2016820%2C%20Lt.1%20No.%2023-24</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Big%20Mall%20Samarinda%20Indonesia%20JL.%20Untung%20Suropati%20NO.8%20Karang%20Asam%20Ulu%2C%20Kec.%20Sungai%20Kunjang%2C%2075126%20Lt.2%20No%2018%2C%20Kec.%20Sungai%20Kunjang%2C%20Kota%20Samarinda%2C%20Kalimantan%20Timur%2075243</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Centre%20Point%20Mall%20Medan%20Indonesia%20Jl.%20Timor%20/%20jawa%20No.%201%20-%20Medan%2C%20Sumatera%20Utara%20-%20Indonesia%2C%20LG%20No.%2016</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20AEON%20Mall%20BSD%20City%20Tangerang%20Indonesia%20Jl.%20BSD%20Raya%20Utama%20No.LT%203%2C%20Pagedangan%2C%20Kec.%20Pagedangan%2C%20Kabupaten%20Tangerang%2C%20Banten%2015345</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Ciputra%20Semarang%20Indonesia%20Jl.%20Simpang%20Lima%20No.1%2C%20Pekunden%2C%20Kec.%20Semarang%20Tengah%2C%20Kota%20Semarang%2C%20Jawa%20Tengah%2050125</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Megamall%20Manado%20Indonesia%20Mega%20Mall%20Manado%20Lt.%20UG-49%20Kawasan%20Megamas%20Jl.%20Pierre%20Tendean%20Wenang%20Selatan%2C%20Wenang%2C%20Manado%20Sulawesi%20Utara</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Resinda%20Park%20Mall%20Karawang%20Indonesia%20Jl.%20Akses%20Tol%20Karawang%20Bar%2C%20Purwadana%2C%20Telukjambe%20Timur%20Kabupaten%20Karawang%2C%20Jawa%20Barat%2041361%2C%20Lt%2C%20GF40%2C%20Karawang%2C%20Jawa%20Barat%2041361</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Artha%20Gading%20Jakarta%20Indonesia%20Mall%20Artha%20Gading%20Mall%20artha%20gading%20GF/A6/016%20%2CJl.%20Artha%20Gading%20Sel.%20No.1%2C%20Klp.%20Gading%20Bar.%2C%20Kec.%20Klp.%20Gading%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014240</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Pakuwon%20Mall%20Jogja%20Yogyakarta%20Indonesia%20Pakuwon%20Mall%20Lantai.1%2C%20Kaliwaru%2C%20Condong%20Catur%2C%20Depok%2C%20Sleman%20Regency%2C%20Special%20Region%20of%20Yogyakarta%2055281</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Trans%20Studio%20Mall%20Cibubur%20Depok%20Indonesia%20jl.alternatif%20cibubur%2C%20trans%20studio%20mall%20cibubur%20no.230%20Lt.2%20unit%2056%2Charjamukti%2Ckec.cimanggis%20kota%20depok</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Cilegon%20Center%20Mall%20Cilegon%20Indonesia%20Cilegon%20Center%20Mall%20%20Lt.%201%20Unit%20No.%2012%2C%20Jl.%20Ahmad%20Yani%2C%20Sukmajaya%2C%20Kec.%20Jombang%2C%20Kota%20Cilegon%2C%20Banten%2042416%2C</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Grage%20Mall%20Cirebon%20Indonesia%20Jl%20Tentara%20Pelajar%20No%201%2C%20Kejaksan%2C%20Kota%20Cirebon%2C%20Jawa%20Barat%2045123%2C%20Lt.1%20Unit%20BA%20005</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20AEON%20Mall%20Jakarta%20Garden%20City%20Jakarta%20Indonesia%20Jl.%20Jakarta%20Garden%20City%2C%20RT.1/RW.6%2C%20Cakung%20Timur%2C%20Kota%20Jakarta%20Timur%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2013910%2C%20Lt.%20GF%20Unit%20G%20-%20G32</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lombok%20Epicentrum%20Mall%20Mataram%20Indonesia%20Jl.%20Sriwijaya%20No.333%2C%20Punia%2C%20Kec.%20Mataram%2C%20Kota%20Mataram%2C%20Nusa%20Tenggara%20Bar.%2083127</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Pollux%20Mall%20Paragon%20Semarang%20Indonesia%20Pollux%20Mall%20Paragon%20Lt.%203%20Unit%20L3-03%20Jl.%20Pemuda%20No.118%2C%20Sekayu%2C%20Semarang%20Tengah%2C%20Kota%20Semarang%2C%20Jawa%20Tengah%2050132%2C</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Living%20World%20Alam%20Sutera%20Tangerang%20Selatan%20Indonesia%20Jl.%20Alam%20Sutera%20Boulevard%20No.Kav.%2021%2C%20Pakulonan%2C%20Kec.%20Serpong%20Utara%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%2015325</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lippo%20Plaza%20Kramat%20Jati%20Jakarta%20Timur%20Indonesia%20Lippo%20Plaza%20Jl.%20Raya%20Jakarta-Bogor%20No.Km%2019%2C%20RT.14/RW.6%2C%20Kramat%20Jati%2C%20Kec.%20Kramat%20jati%2C%20Kota%20Jakarta%20Timur%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2013510</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Udayana%20Dewata%20Denpasar%20Indonesia%20Jl.%20Mayjen%20Sutoyo%20No.55%2C%20Dauh%20Puri%2C%20Kec.%20Denpasar%20Bar.%2C%20Kota%20Denpasar%2C%20Bali%2080112</t>
+  </si>
+  <si>
+    <t>5,000-7,000</t>
+  </si>
+  <si>
+    <t>150,000-210,000</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20DP%20Mall%20Semarang%20Indonesia%20DP%20Mall%20Semarang%2C%20Jl.%20Pemuda%20No.150%20lantai%201%2C%20Sekayu%2C%20Semarang%20Tengah%2C%20Semarang%20City%2C%20Central%20Java%2050132</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20The%20Park%20Sawangan%20Depok%20Indonesia%20The%20Park%20Mall%20Sawangan%20Lt.2%20Unit%200060%2C%20Jl.%20Serua%20Kec.%20Bojongsari%20Sawangan%20Kota%20Depok%20Jawa%20Barat%2016517</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Ayani%20Mega%20Mall%20Pontianak%20Indonesia%20Ayani%20Mega%20Mall%2C%20Jl.%20Jenderal%20Ahmad%20Yani%2C%20Parit%20Tokaya%2C%20South%20Pontianak%2C%20Pontianak%2C%20West%20Kalimantan%2078113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Icon%20Mall%20Palembang%20Indonesia%20Palembang%20icon%20Jl.%20POM%20IX%2C%20Lorok%20Pakjo%2C%20Kec.%20Ilir%20Bar.%20I%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030137%20%281%20Floor-%2036%29</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Living%20World%20Denpasar%20Indonesia%20Jl.%20Gatot%20Subroto%20Tim.%2C%20Tonja%2C%20Kec.%20Denpasar%20Utara%2C%20Kota%20Denpasar%2C%20Bali%2080235</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Royal%20Plaza%20Surabaya%20Indonesia%20Royal%20Plaza%2C%20Jl.%20Ahmad%20Yani%20No.16-18%20lt%202%20unit%20K1%20no%209-11%2C%20Ketintang%2C%20Kec.%20Gayungan%2C%20Surabaya%2C%20Jawa%20Timur%2060231</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Rita%20Supermall%20Purwokerto%20Banyumas%20Indonesia%20Jl.%20Jend.%20Sudirman%20No.296%2C%20Pereng%2C%20Sokanegara%2C%20Kec.%20Purwokerto%20Tim.%2C%20Kabupaten%20Banyumas%2C%20Jawa%20Tengah%2053116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Summarecon%20Mall%20Bandung%20Indonesia%20Jl.%20Grand%20Bulevar%20No.1%2C%20Cisaranten%20Kidul%2C%20Kec.%20Gedebage%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040295</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20of%20Serang%20Banten%20Indonesia%20Jl.%20Akses%20Tol%20Serang%20Tim.%2C%20Panancangan%2C%20Kec.%20Cipocok%20Jaya%2C%20Kota%20Serang%2C%20Banten%2042124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Solo%20Paragon%20Mall%20Surakarta%20Indonesia%20Solo%20Paragon%2C%20Jl.%20Yosodipuro%20No.133%2C%20Mangkubumen%2C%20Kec.%20Banjarsari%2C%20Kota%20Surakarta%2C%20Jawa%20Tengah%2057139</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Ambassador%20Jakarta%20Indonesia%20Mall%20Ambasador%20Lantai%20Dasar%2C%20Jl.%20Prof.%20DR.%20Satrio%20No.8%20Ground%20Floor%2C%20Kuningan%2C%20Karet%20Kuningan%2C%20Kecamatan%20Setiabudi%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2012940</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Duta%20Mall%20Banjarmasin%20Indonesia%20Jl.%20Ahmad%20Yani%20Km.%202%20No.%2098%2C%20Banjarmasin%2C%20Kalimantan%20Selatan%2070232%2C%20Lt.%201%20Blok%20H%20No.006</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Bandung%20Indah%20Plaza%20Bandung%20Indonesia%20XIAOMI%20STORE%20BIP%2C%20Jl.%20Merdeka%20No.56%20LT.%20GF-55%2C%20Citarum%2C%20Kec.%20Bandung%20Wetan%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040115</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Cirebon%20Super%20Block%20Mall%20Indonesia%20Komp.%20Chelsea%20Blue%20Ruko%209%20-%2010%2C%20Jl.%20DR.%20Cipto%20Mangunkusumo%20No.26%2C%20Pekiringan%2C%20Kec.%20Kesambi%2C%20Kota%20Cirebon%2C%20Jawa%20Barat%2045131</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Ciputra%20Tangerang%20Indonesia%20Mall%20Ciputra%20Tanggerang%2C%20Jl.%20Citra%20Raya%20Boulevard%20Lt.%20GF%20No.%20C03%2C%20Ciakar%2C%20Kec.%20Panongan%2C%20Kabupaten%20Tangerang%2C%20Banten%2015710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20AEON%20Mall%20Tanjung%20Barat%20Jakarta%20Indonesia%20Jl.%20Raya%20Tj.%20Barat%20No.163%2C%20RT.12/RW.4%2C%20Tj.%20Bar.%2C%20Kec.%20Jagakarsa%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2012530</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Jogja%20City%20Mall%20Yogyakarta%20Indonesia%20Jogja%20City%20Mall%20Lt.1%20Unit%2023%20Jl.%20Magelang%2018%20N0.6%20Kutu%20Patran%2C%20Sinduadi%20Kec.%20Mlati%20Kab.%20Sleman%20DIY%2055284</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Bintaro%20Plaza%20Tangerang%20Indonesia%20Jl.%20Bintaro%20Utama%203A%20No.81%2C%20Pd.%20Karya%2C%20Kec.%20Pd.%20Aren%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%2015225</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Kartini%20Lampung%20Indonesia%20Jl.%20RA%20Kartini%20No.49%2C%20Palapa%2C%20Tanjung%20Karang%20Pusat%2C%20Palapa%2C%20Kota%20Bandar%20Lampung-%2035116%2C%20Lt.%201%20Blok%20A13-A15</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Suzuya%20Mall%20Banda%20Aceh%20Indonesia%20Jl.%20Teuku%20Umar%2C%20Lamtemen%20Tim.%2C%20Kec.%20Jaya%20Baru%2C%20Kota%20Banda%20Aceh%2C%20Aceh%2023232</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20MAll%20SKA%20Pekanbaru%20Indonesia%20Jl.%20Delima%2C%20Tampan%2C%20Kota%20Pekanbaru%2C%20Riau%2028292%2C%20Lt.2%20-72</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Taman%20Anggrek%20Jakarta%20Indonesia%20Jl.%20Letjen%20S.%20Parman%2C%20RT.12/RW.1%2C%20Tj.%20Duren%20Sel.%2C%20Kec.%20Grogol%20petamburan%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011470</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Armada%20Town%20Square%20Magelang%20Indonesia%20Jl.%20Mayjen%20Bambang%20Soegeng%20No.1%2C%20Kedungdowo%2C%20Mertoyudan%2C%20Kec.%20Mertoyudan%2C%20Kabupaten%20Magelang%2C%20Jawa%20Tengah%2056172</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Plaza%20Andalaz%20Padang%20Indonesia%20Plaza%20Andalas%20Lt.%202%2C%20Jl.%20Belakang%20Lintas%20No.2F%20Unit%20L2%20unit%20L2-B001%2C%20Olo%2C%20Kec.%20Padang%20Bar.%2C%20Kota%20Padang%2C%20Sumatera%20Barat%2025117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Kediri%20Town%20Square%20Kediri%20Indonesia%20Kediri%20Town%20Square%20Lt.%20Dasar%20Jl.%20Hasanudin%20No.2%2C%20Balowerti%2C%20Kec.%20Kota%2C%20Kota%20Kediri%2C%20Jawa%20Timur%2064129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Plaza%20Asia%20Tasikmalaya%20Indonesia%20Jl.%20HZ.%20Mustofa%20No.326%2C%20Tugujaya%2C%20Kec.%20Cihideung%2C%20Kab.%20Tasikmalaya%2C%20Jawa%20Barat%2046125</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lippo%20Plaza%20Sidoarjo%20Indonesia%20Lippo%20Plaza%20Sidoarjo%2C%20Jl.%20Jati%20Raya%20No.1%20Ground%20Floor%2C%20GF-39%2C%20Jati%2C%20Kec.%20Sidoarjo%2C%20Kabupaten%20Sidoarjo%2C%20Jawa%C2%A0Timur%C2%A061226</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Pentacity%20Mall%20Balikpapan%20Indonesia%20Pentacity%20Mall%20Balikpapan%2C%20Jl.%20Jenderal%20Sudirman%20No.47%2C%20Gunung%20Bahagia%2C%20Balikpapan%20Selatan%2C%20Balikpapan%20City%2C%20East%20Kalimantan%2076114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Trans%20Studio%20Mall%20Bali%20Indonesia%20Jl.%20Imam%20Bonjol%20No.440%2C%20Pemecutan%20Klod%2C%20Kec.%20Denpasar%20Bar.%2C%20Kota%20Denpasar%2C%20Bali%2080361</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Jember%20Roxy%20Square%20Jember%20Indonesia%20Jember%20Roxy%20Square%20Lt.%20GF%20Unit%20GF1B1%20Jl.%20Hayam%20Wuruk%20No.50-58%2C%20Gerdu%2C%20Sempusari%2C%20Kec.%20Kaliwates%2C%20Kabupaten%20Jember%2C%20Jawa%20Timur%2068131</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20AEON%20Mall%20Sentul%20City%20Indonesia%20AEON%20Mall%20Sentul%20City%2C%20Lt2%20Unit%2028A%20%26%2028B%2C%20Jl.%20MH.%20Thamrin%2C%20Citaringgul%2C%20Kec.%20Babakan%20Madang%2C%20Kabupaten%20Bogor%2C%20Jawa%20Barat%2016810</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Grand%20Galaxy%20Park%20Bekasi%20Indonesia%20Grand%20Galaxy%20Park%20Lt%201%20Unit%201-D8%2CJl.%20Pulo%20Sirih%20Utama%20No.1%2C%20RT.003/RW.017%2C%20Jaka%20Setia%2C%20Kec.%20Bekasi%20Sel.%2C%20Kota%20Bks%2C%20Jawa%20Barat%2017147</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Karawang%20Central%20Plaza%20Indonesia%20Karawang%20Central%20Plaza%20Lt.1%20Blok%20C2%2C%20Jl.%20Galuh%20Mas%20Raya%2C%20Sukaharja%2C%20Kec.%20Telukjambe%20Timur%2C%20Karawang%2C%20Jawa%20Barat%2C%2041361</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lotte%20Avenue%20Ciputra%20World%20Mall%20Jakarta%20Selatan%20Indonesia%20Jl.%20Prof.%20DR.%20Satrio%20No.Kav.%203-5%2C%20RT.17/RW.4%2C%20Kuningan%2C%20Karet%20Kuningan%2C%20Kecamatan%20Setiabudi%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2012940</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Icon%20Mall%20Gresik%20Indonesia%20Icon%20Mall%20Gresik%20Lt.%20LG%20Unit%2019-20%2C%20Jl.%20Dr.%20Wahidin%20S.H.%20No.788%2C%20Kembangan%2C%20Kebomas%2C%20Kabupaten%20Gresik%2C%20Jawa%20Timur%2061124%2C</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Festival%20Citylink%20Bandung%20Indonesia%20Mall%20Festival%20Citylink%20Lantai%20GF%20No.%2041%20Jl.%20Peta%20No.241%2C%20Suka%20Asih%2C%20Kec.%20Bojongloa%20Kaler%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040232</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Bencoolen%20Mall%20Bengkulu%20Indonesia%20Jl.%20Putri%20Gading%20Cempaka%2C%20Penurunan%2C%20Ratu%20Samban%2C%20Kota%20Bengkulu%2C%20GF%20Blok%20A%20No.%202%2C3%20%265</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Maluku%20City%20Mall%20Ambon%20Indonesia%20Jl.%20Jenderal%20Sudirman%20No.1%2C%20Hative%20Kecil%2C%20Kec.%20Sirimau%2C%20Kota%20Ambon%2C%20Maluku</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Grand%20Mall%20Maros%20Indonesia%20Jl.%20Poros%20Makassar%20-%20Maros%20No.53%2C%20Bontoa%2C%20Kec.%20Mandai%2C%20Kabupaten%20Maros%2C%20Sulawesi%20Selatan%2090552</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Arion%20Mall%20Jakarta%20Timur%20Indonesia%20Arion%20Mall%20Jl.%20Pemuda%20No.Kavling%203-4%2C%20RT.2/RW.7%2C%20Rawamangun%2C%20Kec.%20Pulo%20Gadung%2C%20Kota%20Jakarta%20Timur%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2013220</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Java%20Mall%20Semarang%20Indonesia%20Java%20Mall%20Semarang%2C%20Lt%201%2C%20No%20102%2C%20Jl.%20MT.%20Haryono%2C%20Lamper%20Kidul%2C%20Kec.%20Semarang%20Sel.%2C%20Kota%20Semarang%2C%20Jawa%20Tengah%2050257</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Gajah%20Mada%20Plaza%20Jakarta%20Indonesia%20Jl.%20Gajah%20Mada%20No.19%2026%2C%20RT.2/RW.1%2C%20North%20Petojo%2C%20Gambir%2C%20Central%20Jakarta%20City%2C%20Jakarta%2010130</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Opi%20Mall%20Palembang%20Indonesia%20Opi%20mall%20Jakabaring%20Sport%20City%2C%20Jl.%20Gubernur%20H.%20A%20Bastari%2C%20Sungai%20Kedukan%2C%20Kec.%20Rambutan%2C%20Kab.%20Banyuasin%2C%20Sumatera%20Selatan%2030257</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Samarinda%20Central%20Plaza%20Samarinda%20Indonesia%20Jl.%20P.%20Irian%20No.1%2C%20Karang%20Mumus%2C%20Kec.%20Samarinda%20Kota%2C%20Kota%20Samarinda%2C%20Kalimantan%20Timur%2075113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Grand%20Metropolitan%20Mall%20Bekasi%20Indonesia%20Jl.%20KH.%20Noer%20Ali%2C%20RT.007/RW.003%2C%20Pekayon%20Jaya%2C%20Kec.%20Bekasi%20Sel.%2C%20Kota%20Bks%2C%20Jawa%20Barat%2017148</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Manhattan%20Time%20Square%20Medan%20Indonesia%20Manhattan%20Medan%20GF-13%2C%20Jl.%20Gatot%20Subroto%20No.217%2C%20Sei%20Sikambing%20B%2C%20Kec.%20Medan%20Sunggal%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020123</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Plaza%20Medan%20Fair%20Medan%20Indonesia%20Plaza%20Medan%20Fair%20Lt.%204%20Unit%205%20Jl.%20Gatot%20Subroto%20No.30%2C%20Sekip%2C%20Kec.%20Medan%20Petisah%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mega%20Bekasi%20Hypermall%20Bekasi%20Indonesia%20Mega%20Bekasi%20Hypermall%20Lt.%201%20-%20Jl.Jenderal%20Ahmad%20Yani%20No.%201%2C%20Marga%20Jaya%2C%20Bekasi%20Selatan%2C%20Kota%20Bekasi%2C%20Jawa%20Barat%2017141</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Sunrise%20Mall%20Mojokerto%20Indonesia%20Jl.%20Benteng%20Pancasila%20No.9%2C%20Mergelo%2C%20Balongsari%20Kec.%20Magersari%20Kota%20Mojokerto%20Jawa%20Timur%2061314%2C%20Lt%20G%20No.%20DF%2005</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Pakuwon%20Mall%20Bekasi%20Indonesia%20Pakuwon%20Mall%20Bekasi%20L2%20-%2046%20Jl.%20Raya%20Pekayon%20No.002%2C%20Pekayon%20Jaya%2C%20Kec.%20Bekasi%20Sel.%2C%20Kota%20Bks%2C%20Jawa%20Barat%2017148</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Citimall%20Cianjur%20Indonesia%20Jl.%20KH%20Abdullah%20Bin%20Nuh%20No.2B%2C%20Pamoyanan%2C%20Kec.%20Cianjur%2C%20Kabupaten%20Cianjur%2C%20Jawa%20Barat%2043211</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Pakuwon%20Mall%20Solo%20Indonesia%20PAKUWON%20MALL%20SOLO%20FIRST%20FLOOR%20/L1%20-%2025%20Jl.%20Ir.%20Soekarno%2C%20Dusun%20II%2C%20Madegondo%2C%20Kec.%20Grogol%2C%20Kabupaten%20Sukoharjo%2C%20Jawa%20Tengah%2057552</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Grand%20City%20Surabaya%20Indonesia%20Grand%20City%20Mall%20Lt%20No.G/32%2C%20Ketabang%2C%20Jl.%20Walikota%20Mustajab%20%2C%20Surabaya%2C%20Jawa%20Timur%2060272</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Nipah%20Mall%20Makassar%20Indonesia%20Jl.%20Urip%20Sumoharjo%20No.23c%2C%20Maccini%2C%20Kec.%20Panakkukang%2C%20Kota%20Makassar%2C%20Sulawesi%20Selatan%2090144</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Trans%20Icon%20Mall%20Surabaya%20Indonesia%20Jl.%20Ahmad%20Yani%20No.260%2C%20Menanggal%2C%20Kec.%20Gayungan%2C%20Surabaya%2C%20Jawa%20Timur%2060235</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mal%20Bali%20Galeria%20Bali%20Indonesia%20Mal%20Bali%20Galleria%2C%202%20Floor%2C%202C-79%2C%20Jl.%20Bypass%20Ngurah%20Rai%2C%20Kuta%2C%20Kec.%20Kuta%2C%20Kabupaten%20Badung%2C%20Bali%2080361</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Gressmall%20Gresik%20Indonesia%20Jl.%20Sumatra%20No.1-5%2C%20RT.07/RW.08%2C%20Gn.%20Malang%2C%20Randuagung%2C%20Kec.%20Kebomas%2C%20Kabupaten%20Gresik%2C%20Jawa%20Timur%2061121</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Q%20Mall%20Banjarmasin%20Indonesia%20Jalan%20Ahmad%20Yani%20Km.%2036%2C8%20No.1%2C%20Komet%2C%20Kec.%20Banjarbaru%20Utara%2C%20Kota%20Banjar%20Baru%2C%20Kalimantan%20Selatan%2070714</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Palembang%20Square%20Palembang%20Indonesia%20L1%2C%20Jl.%20Angkatan%2045%20unit%20A-18%2C%20Lorok%20Pakjo%2C%20Ilir%20Barat%20I%2C%20Palembang%20City%2C%20South%20Sumatra%2030121</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Palembang%20Trade%20Center%20Palembang%20Indonesia%20Palembang%20Trade%20Center%20Lt.%20UG%20Unit%2027%20Jl.%20R.%20Sukamto%20No.8A%2C%208%20Ilir%2C%20Kec.%20Ilir%20Tim.%20II%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20The%20Park%20Kendari%20Mall%20Sulawesi%20Indonesia%20The%20Park%2C%20Jl.%20Brigjen%20M.%20Yoenoes%201-0080%2C%20Bende%2C%20Kec.%20Kadia%2C%20Kota%20Kendari%2C%20Sulawesi%20Tenggara%2093461</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Pakuwon%20City%20Mall%203%20Surabaya%20Indonesia%20Jl.%20Raya%20Laguna%20KJW%20Putih%20Tambak%20No.2%2C%20Kejawaan%20Putih%20Tamba%2C%20Kec.%20Mulyorejo%2C%20Surabaya%2C%20Jawa%20Timur%2060112</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lippo%20Plaza%20Kendari%20Indonesia%20Lippo%20Plaza%20Kendari%20UG.02%20%2CJl.%20Jenderal%20M.t.%20Haryono%20No.61%20-%2063%2C%20Bende%2C%20Kec.%20Kadia%2C%20Kota%20Kendari%2C%20Sulawesi%20Tenggara%2093117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Plaza%20Marina%20Surabaya%20Indonesia%20Jl.%20Margorejo%20Indah%20Utara%20No.97-99%2C%20Sidosermo%2C%20Kec.%20Wonocolo%2C%20Surabaya%2C%20Jawa%20Timur%2060238</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Green%20Pramuka%20Square%20Mall%20Jakarta%20Indonesia%20Jl.%20Rw.%20Jaya%20No.49%2C%20Rawasari%2C%20Kec.%20Cemp.%20Putih%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010570%2C%20Indonesia</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Plaza%20Jambu%202%20Bogor%20indonesia%20Plaza%20Jambu%20Dua%2C%20Lt.%201%2C%20Blok.%20A2%20No.%2004%2C%20Jl.%20A.%20Yani%20No.1%2C%20Bantarjati%2C%20Kec.%20Kota%20Bogor%20Utara%2C%20Kota%20Bogor%2C%20Jawa%20Barat%2016153</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Plaza%20Millenium%20Medan%20Indonesia%20Jl.%20Kapten%20Muslim%20No.111%2C%20Dwi%20Kora%2C%20Kec.%20Medan%20Helvetia%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020118</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Plaza%20Pondok%20Gede%20Bekasi%20Indonesia%20Jl.%20Raya%20Pd.%20Gede%2C%20RT.001/RW.001%2C%20Jatiwaringin%2C%20Kec.%20Pd.%20Gede%2C%20Kota%20Bks%2C%20Jawa%20Barat%2017411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Green%20Sedayu%20Mall%20Jakarta%20Indonesia%20Green%20Sedayu%20Mall%20Lt%201%20No.16%2C%20Jl.%20Taman%20Palem%20Lestari%20No%202%20RT%2007%20/%20RW%2013%20Cengkareng%20Barat%2C%20Kecamatan%20Cengkareng%2C%20Kota%20Jakarta%20Barat%20DKI%20Jakarta%2011730</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lippo%20Plaza%20Ekalokasari%20Bogor%20Indonesia%20Lippo%20Plaza%20Ekalokasari%20%E2%80%93%20Jl.%20Siliwangi%20No.%20123%2C%20Sukasari%2C%20Bogor%20Timur%2C%20Bogor%2C%20Jawa%20Barat%2016142</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mantos%20Handphone%20Center%20Manado%20Indonesia%20Jl.%20Pierre%20Tendean%2C%20Sario%20Utara%2C%20Sario%2C%20Manado%2095114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20E-Center%20Supermall%20Karawaci%20Indonesia%20Jl.%20Boulevard%20Diponegoro%20No.105%2C%20Bencongan%2C%20Kec.%20Klp.%20Dua%2C%20Kabupaten%20Tangerang%2C%20Banten%2015810</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Jakarta%20Tower%20Kemayoran%20Jakarta%20Pusat%20Indonesia%20Menara%20Jakarta%20Lt.1%20%2CJl.%20Kota%20Baru%20Bandar%20Kemayoran%20No.C-8%2C%20Gunung%20Sahari%20Selatan%2C%20Kemayoran%2C%20Jakarta%20Pusat%2C%20Jakarta%2010610</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Tangerang%20City%20Mall%20Tangerang%20Indonesia%20Tangcity%20Mall%20Lantai%20LG%20Blok%20B%20No.%2063-64%20%2CJl.%20Jenderal%20Sudirman%20No.1%2C%20Cikokol%2C%20Kec.%20Tangerang%2C%20Kota%20Tangerang%2C%20Banten%2015117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20WTC%20Surabaya%20Indonesia%20Jl.%20Pemuda%20No.27-31%2C%20Embong%20Kaliasin%2C%20Kec.%20Genteng%2C%20Surabaya%2C%20Jawa%20Timur%2060263</t>
+  </si>
+  <si>
+    <t>8,000-12,000</t>
+  </si>
+  <si>
+    <t>240,000-360,000</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Matahari%20Jakarta%20Barat%20Indonesia%201%20Floor%20No.33/34%20Jl.%20Daan%20Mogot%2C%20RT.8/RW.12%2C%20Kalideres%2C%20Kec.%20Kalideres%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011820</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Citimall%20Gorontalo%20Indonesia%20Jl.%20Sultan%20Botutihe%20No.68%2C%20Heledulaa%20Sel.%2C%20Kec.%20Kota%20Tim.%2C%20Kota%20Gorontalo%2C%20Gorontalo%2096134</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Citimall%20Tuban%20Indonesia%20GF%20Jl.%20Pahlawan%2C%20Dondong%2C%20Gedongombo%2C%20Kec.%20Semanding%2C%20Kabupaten%20Tuban%2C%20Jawa%20Timur%2062312</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Duta%20Mall%20Palangkaraya%20Indonesia%20Jl.%20Adonis%20Samad%2C%20Langkai%2C%20Kec.%20Pahandut%2C%20Palangka%20Raya%20City%2C%20Central%20Kalimantan%2074874.</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Grand%20Mall%20Palu%20Indonesia%20Grand%20Mall%20Lantai%201%2C%20Jl.%20Cumi-Cumi%20No.77%20LT.%20GF%20UNIT%20G%20-%200150%2C%20BUMI%20BAHARI%2C%20Kec.%20Palu%20Bar.%2C%20Kota%20Palu%2C%20Sulawesi%20Tengah%2094221</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Living%20World%20Cibubur%20Indonesia%20Living%20World%20Kota%20Wisata%20Lt.%202%20Jl.%20Boulevard%20Kota%20Wisata%2C%20Ciangsana%2C%20Kec.%20Gn.%20Putri%2C%20Kabupaten%20Bogor%2C%20Jawa%20Barat%2016968</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Suzuya%20Siantar%20Indonesia%20Jl.Merdeka%20No.12%20Pardomuan%2C%20kec%20siantar%20timur%2C%20kota%20pematang%20siantar%20sumatera%20Utara%2021136</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Indramayu%20Indoneisa%20Jl.%20Gatot%20Subroto%2C%20Karanganyar%2C%20Kec.%20Indramayu%2C%20Kabupaten%20Indramayu%2C%20Jawa%20Barat%2045213</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mal%20Ciputra%20Cibubur%20Indonesia%20Jl.%20Alternatif%20Cibubur%20No.KM%2C%20RT.005/RW.04%2C%20Jatikarya%2C%20Kec.%20Jatisampurna%2C%20Kota%20Bks%2C%20Jawa%20Barat%2017435</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Basko%20City%20Padang%20Indonesia%20Basko%20City%20Mall%20Lt.2%20-%20Jl.%20Manunggal%203%2C%20Kalumbuk%2C%20Kec.%20Kuranji%2C%20Kota%20Padang%2C%20Sumatera%20Barat%2025171</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%2023%20Arkana%20Semarang%20Indonesia%2023%20Arkana%20Semarang%2C%20Lt.%20LG%20Tambak%20Harjo%2C%20Kec.%20Semarang%20Barat%2C%20kota%20semarang%2C%20Jawa%20Tengah%2050144</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Istana%20BEC%202%20Bandung%20Indonesia%20Jl%20Purnawarman%2013-15%2C%20Babakan%20Ciamis%2C%20Kec%20Sumur%20Bandung%20Istana%20Bec2%20Lantai%20LG%20Blok%20R06%20-%2008%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Mall%20of%20Kota%20Kasablanka%20Jakarta%20Indonesia%20Xiaomi%20Store%20Kota%20Kasablanka%20Jl.%20Casablanca%20No.88%20Mall%20Kota%20Kasablanka%20Ltd.2%20No.263</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Cibinong%20City%20Mall%202%20Bogor%20Indonesia%20Jl.%20Tegar%20Beriman%20No.1%2C%20Pakansari%2C%20Kec.%20Cibinong%2C%20Kabupaten%20Bogor%2C%20Jawa%20Barat%2016914</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Trans%20Studio%20Mall%20Makassar%20Indonesia%20Jl.%20Metro%20Tj.%20Bunga%2C%20Maccini%20Sombala%2C%20Kec.%20Tamalate%2C%20Kota%20Makassar%2C%20Sulawesi%20Selatan%2090224</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Queen%20City%20Mall%20Semarang%20Indonesia%20Jl.%20Pemuda%20No.27-31%2C%20%2C%20Pandansari%2C%20Kec.%20Semarang%20Tengah%2050139%20Semarang</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Lippo%20Mall%20Kemang%20Jakarta%20Indonesia%20Lippo%20Mall%20Kemang%20lt.2%20Jl.%20Pangeran%20Antasari%20No.36%2C%20RT.11/RW.5%2C%20Bangka%2C%20Kec.%20Mampang%20Prpt.%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2012150</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20AEON%20Mall%20Deltamas%20Bekasi%20Indonesia%20AEON%20Mall%20Deltamas%2C%20Floor%20GF%20Unit%20G-062%2C%20Jl.%20Ganesha%20Boulevard%2C%20Pasirranji%2C%20Cikarang%20Pusat%2C%20Bekasi%2C%20Jawa%20Barat%2C%2017530</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Mall%20of%20Ciputra%20Jakarta%20Indonesia%20Xiaomi%20Store%20Ciputra%20Mall%20Jl.%20Daan%20Mogot%20Mal%20Ciputra%20Jakarta%20-%20Citraland%20Mall%20Lt.1%20No.44-45</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Mall%20Of%20Indonesia%20Jakarta%20Indonesia%20Xiaomi%20Store%20Mall%20Of%20Indonesia%20Jl.%20Boulevard%20Bar.%20Raya%20No.12%EF%BC%8C%2014240</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Palembang%20Indah%20Mall%20Palembang%20Indonesia%20Jl.%20Letkol%20Iskandar%20No.18%2C%2024%20Ilir%2C%20Kec.%20Bukit%20Kecil%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030134</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Gaia%20Bumi%20Raya%20Mall%20Pontianak%20Indonesia%20Gaia%20Bumi%20Raya%20City%20Mall%20%2CLt%202%20Jl.%20Arteri%20Supadio%2C%20Sungai%20Raya%2C%20Kec.%20Sungai%20Raya%2C%20Kabupaten%20Kubu%20Raya%2C%20Kalimantan%20Barat%2078391</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Store%20Mall%20Ciputra%20World%20Surabaya%20Indonesia%20%20Jl.%20Mayjen%20Sungkono%20No.89%2C%20Gn.%20Sari%2C%20Kec.%20Dukuhpakis%2C%20Surabaya%2C%20Jawa%20Timur%2060225</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Teuku%20Umar%20Denpasar%20Bali%20Indonesia%20Jl.%20Teuku%20Umar%20No.99%2C%20Dauh%20Puri%20Klod%2C%20Denpasar%2C%20Bali-%2080113%2C</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Gajah%20Mada%20Sidoarjo%20Indonesia%20Jl.%20Gajah%20Mada%20No.83%2C%20Daleman%2C%20Pekauman%2C%20Kec.%20Sidoarjo%2C%20Kabupaten%20Sidoarjo%2C%20Jawa%20Timur%2061212</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Manukan%20Tengah%20Surabaya%20Indonesia%20Jl.%20Manukan%20Tama%20No.2H%2C%20RW.13%2C%20Manukan%20Kulon%2C%20Kec.%20Tandes%2C%20Surabaya%2C%20Jawa%20Timur%2060185</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ahmad%20Yani%20Martapura%20Indonesia%20Jl.%20Ahmad%20Yani%20KM.%2039%20No.%2027%20RT.02%20RW.05%20Kelurahan%20Jawa%2C%20Kota%2C%20Martapura%2C%20Banjar%20Regency%2C%20South%20Kalimantan%2070614</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Bambu%20II%20Medan%20Indonesia%20Jl.%20Bambu%20II%20No.22%2C%20Durian%2C%20Kec.%20Medan%20Tim.%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020235</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20MERR%20Surabaya%20Indonesia%20Jl.%20Dr.%20Ir.%20H.%20Soekarno%20No.374-374A%2C%20Kedung%20Baruk%2C%20Kec.%20Rungkut%2C%20Surabaya%2C%20Jawa%20Timur%2060298</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Gajah%20Mada%20Pekalongan%20Indonesia%20Jl.%20Gajah%20Mada%20No.25%2C%20Bendan%2C%20Kec.%20Pekalongan%20Bar.%2C%20Kota%20Pekalongan%2C%20Jawa%20Tengah%2051118</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Karimata%20Jember%20Indonesia%20Jl.%20Karimata%20No.98%2C%20Tegal%20Boto%20Lor%2C%20Sumbersari%2C%20Kec.%20Sumbersari%2C%20Kabupaten%20Jember%2C%20Jawa%20Timur%2068121</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Soekarno%20Hatta%20Bukittinggi%20Indonesia%20Jl.%20Soekarno%20-%20Hatta%20No.17%2CGaregeh%2C%20Kec.%20Mandiangin%20Koto%20Selayan%2C%20Kota%20Bukittinggi%2C%20Sumatera%20Barat%2026117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Veteran%20Padang%20Indonesia%20Jl.%20Veteran%20No.24a%2C%20Padang%20Pasir%2C%20Kec.%20Padang%20Bar.%2C%20Kota%20Padang%2C%20Sumatera%20Barat%2025115</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Soekarno%20Hatta%20Balikpapan%20Indonesia%20Km%204%2C%20No%20Jl.%20Soekarno%20Hatta%2C%20Batu%20Ampar%2C%20Kec.%20Balikpapan%20Utara%2C%20Kota%20Balikpapan%2C%20Kalimantan%20Timur%2076136</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Alianyang%20Singkawang%20Indonesia%20Jl.%20Alianyang%20No.20-19%2C%20Melayu%2C%20Kec.%20Singkawang%20Bar.%2C%20Kota%20Singkawang%2C%20Kalimantan%20Barat%2079113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Prof.%20M.%20Yamin%20No.24%20Pontianak%20Indonesia%20Jl.%20Prof.%20M.Yamin%20No.24%2C%20Sungai%20Bangkong%2C%20Kec.%20Pontianak%20Kota%2C%20Kota%20Pontianak%2C%20Kalimantan%20Barat%2078114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Teuku%20Umar%20No.12%20Tulungagung%20Indonesia%20Jl.%20Teuku%20Umar%20No.12%2C%20Hutan%2C%20Kauman%2C%20Kec.%20Tulungagung%2C%20Kabupaten%20Tulungagung%2C%20Jawa%20Timur%2066219</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kilisuci%20No.2%20Kediri%20Indonesia%20Jl.%20Kilisuci%20No.2%2C%20Setono%20Pande%2C%20Kec.%20Kota%2C%20Kabupaten%20Kediri%2C%20Jawa%20Timur%2064129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sisingamangaraja%20Palu%20Indonesia%20Jl.%20Sisingamangaraja%20No.60%2C%20Lolu%20Utara%2C%20Kec.%20Palu%20Sel.%2C%20Kota%20Palu%2C%20Sulawesi%20Tengah%2094111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Mayor%20HM.%20Rasyad%20Nawawi%20Palembang%20Indonesia%20Jl.%20Mayor%20HM.%20Rasyad%20Nawawi%20No.254%2C%209%20Ilir%2C%20Kec.%20Ilir%20Tim.%20II%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Denai%20No.14%20Medan%20Indonesia%20Jl.%20Denai%20no%2014%20ABC%2C%20Tegal%20Sari%20Mandala%20I%2C%20Kec.%20Medan%20Denai%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020227</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Prof%20Dr%20Sumantri%20Brojonegoro%20Jambi%20Indonesia%20Jl.%20Soemantri%20Brojonegoro%2C%20Sungai%20Putri%2C%20Kec.%20Telanaipura%2C%20Kota%20Jambi%2C%20Jambi%2036124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Moh%20Hasan%20Batoh%20Banda%20Aceh%20Indonesia%20Jl.%20Dr.%20Mr.%20Mohd%20Hasan%20No.21-22%2C%20Batoh%2C%20Kec.%20Lueng%20Bata%2C%20Kota%20Banda%20Aceh%2C%20Aceh%2023123</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Boulevard%20Makassar%20Indonesia%20Jl.%20Boulevard%20Ruko%20Jesper%20II%20No.36%20%26%2037%2C%20Panakukang%2C%20Kota%20Makasar%2C%20Ruko%20Jasper%20II%20No.%2036-37</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Lodaya%20Bandung%20Indonesia%20Jl.%20Lodaya%20No.99%2C%20Lkr.%20Sel.%2C%20Kec.%20Lengkong%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040263</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Pandanaran%20Boyolali%20Indonesia%20Jl.%20Pandanaran%20No.256%2C%20Sidoharjo%2C%20Banaran%2C%20Kec.%20Boyolali%2C%20Kabupaten%20Boyolali%2C%20Jawa%20Tengah%2057313</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Diponegoro%20Purwodadi%20Indonesia%20Jl.Gajah%20Mada%204c%20Bundaran%20Simpang%20Lima%20blok%20Barat%2C%20Purwodadi%2C%20Purwodadi%2C%20Grobogan%20Regency%2C%20Central%20Java%2058111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Pemotongan%20Salatiga%20Indonesia%20Jl.%20Pemotongan%20No.28%2C%20Kalicacing%2C%20Kec.%20Sidomukti%2C%20Kota%20Salatiga%2C%20Jawa%20Tengah%2050724</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Dharma%20Giri%20Gianyar%20Indonesia%20Jl.%20Dharma%20Giri%20No.8%2C%20Gianyar%2C%20Kec.%20Gianyar%2C%20Kabupaten%20Gianyar%2C%20Bali%2080511</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend%20Sudirman%20Ponorogo%20Indonesia%20Jl.%20Jendral%20Sudirman%20No.%2079%2C%20Ponorogo%2C%20Mangkujayan%2C%20Kec.%20Ponorogo%2C%20Kabupaten%20Ponorogo%2C%20Jawa%20Timur%2063413</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Perintis%20Kemerdekaan%20Madiun%20Indonesia%20Jl.%20Perintis%20Kemerdekaan%20No.39%20-%2041%2C%20Kartoharjo%2C%20Kec.%20Kartoharjo%2C%20Kota%20Madiun%2C%20Jawa%20Timur%2063117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Yos%20Sudarso%20II%20Kutai%20TImur%20Indonesia%20Jl.%20Yos%20Sudarso%20II%20Gg.%20Mawar%20No.Samping%2C%20Sangatta%20Utara%2C%20Kec.%20Sangatta%20Utara%2C%20Kabupaten%20Kutai%20Timur%2C%20Kalimantan%20Timur%2075611</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20R.%20Suprapto%20Bontang%20Indonesia%20Jl.%20R.%20Suprapto%20No.81%2C%20Api-Api%2C%20Kec.%20Bontang%20Utara%2C%20Kota%20Bontang%2C%20Kalimantan%20Timur%2075313</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Veteran%20Pemalang%20Indonesia%20Jl.%20Veteran%20ruko%20PJKA%20No.2%20%28sebelah%20timur%20stasiun%2C%20Mulyoharjo%2C%20Kec.%20Pemalang%2C%20Kabupaten%20Pemalang%2C%20Jawa%20Tengah%2052313</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sigura%20Gura%20Malang%20Indonesia%20Jl.%20Sigura%20-%20Gura%20No.25D%2C%20Sumbersari%2C%20Kec.%20Lowokwaru%2C%20Kota%20Malang%2C%20Jawa%20Timur%2065145</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Brigjen%20Katamsi%20Lampung%20Indonesia%20Jalan%20Brigjen%20Katamso%2C%20Kelurahan%20Durian%20Payung%2C%20Kecamatan%20Tanjung%20Karang%20Pusat%2C%20memiliki%20kode%20pos%2035116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Cemara%20Medan%20Indonesia%20Komplek%20Grand%20Cemara%20Asri%2C%20Grand%20cemara%20asri%20No88CD%2C%20Jl.%20Cemara%2C%20Sumatera%20Utara%2020221</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Teuku%20Umar%2014A%20Denpasar%20Indonesia%20Jl.%20Teuku%20Umar%20No.14A%2C%20Dauh%20Puri%2C%20Kec.%20Denpasar%20Bar.%2C%20Kota%20Denpasar%2C%20Bali%2080232</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sultan%20Abdurrahman%20Pontianak%20Indonesia%20Jl.%20Slt.%20Abdurrahman%20No.38B%2C%20Akcaya%2C%20Kec.%20Pontianak%20Sel.%2C%20Kota%20Pontianak%2C%20Kalimantan%20Barat%2078113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sultan%20Agung%20No.39%20Kepanjen%20Malang%20Indonesia%20Jl.%20Sultan%20Agung%20No.39%2C%20Kepanjen%2C%20Kec.%20Kepanjen%2C%20Kabupaten%20Malang%2C%20Jawa%20Timur%2065163</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sultan%20Hasanuddin%20Makassar%20Indonesia%20%20Jl.%20Sultan%20Hasanuddin%20No.20%20Kel%20Baru%2C%20Kec%20Ujung%20Pandang%2C%20Makassar%2C%20Sulawesi%20Selatan%20Kode%20Pos%2090111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20RE%20Martadinata%20Manado%20Indonesia%20Komplek%20Ruko%20Ochard%20No.21%20Jl.%20Yos%20Sudarso%2C%20Paal%20Dua%20Kota%20Manado%2C%20Sulawesi%20Utara%2C%20Kode%20Poss%2095129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Merdeka%20No.5%20%266%20Lhokseumawe%20Indonesia%20Jl.%20Merdeka%20No.5%20%26%206%2C%20Simpang%20Empat%2C%20Kec.%20Banda%20Sakti%2C%20Kota%20Lhokseumawe%2C%20Aceh</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend.%20Ahmad%20Yani%20No.73%20Cilacap%20Indonesia%20Jl.%20Jend.%20Ahmad%20Yani%20No.73%2C%20RW.009%2C%20Manggisan%2C%20Tambakreja%2C%20Kec.%20Cilacap%20Sel.%2C%20Kabupaten%20Cilacap%2C%20Jawa%20Tengah%2053254</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Printis%20Kemerdekaan%20KM%209%20Makassar%20Indonesia%20Jl.%20Perintis%20Kemerdekaan%20No.KM%209%2C%20Tamalanrea%20Jaya%2C%20Kec.%20Tamalanrea%2C%20Kota%20Makassar%2C%20Sulawesi%20Selatan%2090245</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sukowati%20Sragen%20Indonesia%20Jl.%20Sukowati%20No.337%2C%20Dusun%20Kebayanan%20Widodo%201%2C%20Sragen%20Wetan%2C%20Kec.%20Sragen%2C%20Kabupaten%20Sragen%2C%20Jawa%20Tengah%2057214%2C%20Indonesia</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Cemara%20No.26%20Medan%20Indonesia%20Jalan%20Cemara%20No.26%2C%20Ruko%20The%20Great%20Arcade%2C%20Komplek%20Cemara%20Asri%2C%20Medan%20Estate%2C%20Percut%20Sei%20Tuan%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2C%2020221</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ahmad%20Yani%20Nganjuk%20Indonesia%20Jl.%20Raya%20Kediri%20-%20Nganjuk%20No.404Winong%2C%20Ploso%2C%20Kec.%20Nganjuk%2C%20Kabupaten%20Nganjuk%2C%20Jawa%20Timur%2064417</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Raya%20Batu%20Licin%20Tanah%20Bumbu%20Indonesia%20Jl.%20Raya%20Batulicin%2C%20kp.%20Baru%2C%20Kecamatan%20Batulicin%2C%20Kabupaten%20Tanah%20Bumbu%2C%20Kalimantan%20Selatan%2072273</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend%20Sudirman%20Balikpapan%20Indonesia%20Jalan%20Sudirman.16%20%28Depan%20Samsat%20Markoni%29%2C%20Kota%20Balikpapan%2C%20Kalimantan%2C%20Timur%2C%20Jl.%20Jenderal%20Sudirman%20No.16%2C%20RW.2%2C%20Klandasan%20Ilir%2C%20Kec.%20Balikpapan%20Kota%2C%20Kota%20Balikpapan%2C%20Kalimantan%20Timur%2076113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Belitung%20Laut%20Banjarmasin%20Indonesia%20Jl.%20Belitung%20Darat%20No.12%2C%20Belitung%20Sel.%2C%20Kec.%20Banjarmasin%20Bar.%2C%20Kota%20Banjarmasin%2C%20Kalimantan%20Selatan%2070116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Semper%20Av.%20Kramat%20Jaya%20Jakarta%20Indonesia%20Jl.%20Kramat%20Jaya%20Raya%20No.29%2C%20RT.002/RW.017%2C%20Tugu%20Utara%2C%20Kec.%20Koja%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014270</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20A%20Yani%20No.2%20Banjarmasin%20Indonesia%20Jalan.%20A%20Yani%20Km.%202%2C5%20No.%202%2C%20Sungai%20Baru%2C%20Kec.%20Banjarmasin%20Tengah%2C%20Kota%20Banjarmasin%2C%20Kalimantan%20Selatan%2070233</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Gatot%20Subroto%20Surakarta%20Indonesia%20Jl.%20Gatot%20Subroto%20No.146%2C%20Jayengan%2C%20Kec.%20Serengan%2C%20Kota%20Surakarta%2C%20Jawa%20Tengah%2057152</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Soekarno%20Hatta%20Malang%20Indonesia%20Ruko%20BorobudurJl.%20Soekarno%20Hatta%20No.16%2C%20Mojolangu%2C%20Kec.%20Lowokwaru%2C%20Kota%20Malang%2C%20Jawa%20Timur%2065141</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Raya%20Canggu%20No.60%20Bali%20Indonesia%20Jl.%20Raya%20Canggu%20No.60%2C%20Tibubeneng%2C%20Kec.%20Kuta%20Utara%2C%20Kabupaten%20Badung%2C%20Bali%2080361</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Tuparev%20No.267%20Karawang%20Indonesia%20Jl.%20Tuparev%20No.267%2C%20Nagasari%2C%20Kec.%20Karawang%20Bar.%2C%20Karawang%2C%20Jawa%20Barat%2041312</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Nagarawangi%20No.16%20Tasikmalaya%20Indonesia%20Jl.%20Nagarawangi%20No.16%2C%20Nagarawangi%2C%20Kec.%20Cihideung%2C%20Kab.%20Tasikmalaya%2C%20Jawa%20Barat%2046124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Jl.%20Ahmad%20Yani%20KM%2037%20Banjarbaru%20Indonesia%20Jl.%20Ahmad%20Yani%20KM%2037%2C%20Kelurahan%20Komet%20Kecamatan%20Banjarbaru%20Utara%20Kota%20Banjar%20Baru%2C%20Kalimantan%20Selatan%2070714</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kapas%20Krampung%20Surabaya%20Indonesia%20Jl.%20Kapas%20Krampung%20No.%2067E%2C%20Kel.%20Rangkah%2C%20Kec.%20Tambaksari%2C%20Surabaya%2060133</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Raya%20Kedungwuni%20Pekalongan%20Indonesia%20Jalan%20Raya%20No.2A%2C%20Kedungwuni%2C%20Karangdowo%2C%20Kec.%20Kedungwuni%2C%20Kabupaten%20Pekalongan%2C%20Jawa%20Tengah%2051173</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.Jenderal%20Sudirman%20Magelang%20Indonesia%20Jl.%20Ikhlas%20%2CMagersari%2C%20Kec.%20Magelang%20Sel.%2C%20Kota%20Magelang%2C%20Jawa%20Tengah%2059214</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Pelita%20Kotawaringin%20Timur%20Indonesia%20Jl.%20Pelita%2C%20Mentawa%20Baru%20Hilir%2C%20Kec.%20Mentawa%20Baru%20Ketapang%2C%20Kabupaten%20Kotawaringin%20Timur%2C%20Kalimantan%20Tengah%2074321</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Godean%202%20Sleman%20Indonesia%20Jl.%20Godean%20No.KM%209%2C%20Area%20Sawah%2C%20Sidoagung%2C%20Kec.%20Godean%2C%20Kabupaten%20Sleman%2C%20Daerah%20Istimewa%20Yogyakarta%2055564</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Gatot%20Subroto%20Bali%20Indonesia%20Jl.%20Gatot%20Subroto%20Tim.%20Nomor%2017%2C%20Tonja%2C%20Kec.%20Denpasar%20Utara%2C%20Kota%20Denpasar%2C%20Bali%2080235</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Gusti%20Hamzah%20Pontianak%20Indonesia%20Jl.%20Gusti%20Hamzah%20No.%203%20Sungai%20Jawi%2C%20Kec.%20Pontianak%20Kota%2C%20Kota%20Pontianak%2C%20Kalimantan%20Barat%2078244</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Syech%20Yusuf%20Kendari%20Indonesia%20Jl.%20Syech%20Yusuf%20No.10%2C%20Korumba%2C%20Kec.%20Mandonga%2C%20Kota%20Kendari%2C%20Sulawesi%20Tenggara%2093111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend%20Sudirman%20Sidrap%20Sulawesi%20Indonesia%20Jl%20Jendral%20Sudirman%20No%20189%20Poros%20Pare%20Kel%20Lakessi%2C%20Kec%20Maritengngae%20Kab%20Sidrap%2C%20Sulawesi%20Selatan%2091611</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Brigjend%20Katamso%20No.27%20Lampung%20Indonesia%20Jl.%20Brigjend%20katamso%20No%2027%20Simpur%20Kelurahan%20Palapa%20Kec.%20Tanjung%20Karang%20Pusat%20bandar%20Lampung%2035111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Imam%20Bonjol%20Padang%20Indonesia%20Jl.%20Imam%20Bonjol%20No.%2017%20AB%2C%20Belakang%20Pd.%2C%20Kec.%20Padang%20Sel.%2C%20Kota%20Padang%2C%20Sumatera%20Barat%2025133</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Juanda%20Pekanbaru%20Indonesia%20Jl.%20Ir.%20H.%20Juanda%20No.12%2C%20Sago%2C%20Kec.%20Senapelan%2C%20Kota%20Pekanbaru%2C%20Riau%2C%2028155</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sukun%20Malang%20Indonesia%20%20Jl.%20S.%20Supriadi%20No.59%2C%20Sukun%2C%20Kec.%20Sukun%2C%20Kota%20Malang%2C%20Jawa%20Timur%2065147</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend%20H.%20Amir%20Machmud%20Cimahi%20Indonesia%20Jl.%20Jend.%20H.%20Amir%20Machmud%20No.650%2C%20Setiamanah%2C%20Kec.%20Cimahi%20Tengah%2C%20Setiamanah%2C%20Kota%2C%20Kota%20Cimahi%2C%20Jawa%20Barat%2040524</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Panglima%20Sudirman%20Pasuruan%20Indonesia%20Jl.%20Panglima%20Sudirman%20No.90%2C%20Purworejo%2C%20Kec.%20Purworejo%2C%20Kota%20Pasuruan%2C%20Jawa%20Timur%2067116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Veteran%20Palembang%20Indonesia%20Jl.%20Veteran%20No.77%2C%20Kuto%20Batu%2C%20Kec.%20Ilir%20Tim.%20II%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kapten%20Muchtar%20Basri%20Medan%20Indonesia%20Jl.%20Kapten%20Muchtar%20Basri%20No.126%2C%20Glugur%20Darat%20II%2C%20Kec.%20Medan%20Tim.%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020238</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kelapa%20Dua%20Depok%20Indonesia%20Jl.%20Akses%20UI%20No.2%2C%20Tugu%2C%20Kec.%20Cimanggis%2C%20Kota%20Depok%2C%20Jawa%20Barat%2016451</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Tuparev%20Cirebon%20Indonesia%20Jl.%20Tuparev%20No.85F%2C%20Sutawinangun%2C%20Kec.%20Kedawung%2C%20Kabupaten%20Cirebon%2C%20Jawa%20Barat%2045153</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Urip%20Sumoharjo%20Pekalongan%20Indonesia%20Seblah%20utara%20perempatan%20podo%2C%20Jl.%20Raya%20Podo%20No.rt%2008/02%2C%20Kec.%20Kedungwuni%2C%20Kabupaten%20Pekalongan%2C%20Jawa%20Tengah%2051173</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20A%20Yani%20Pangkalanbun%20Kotawaringin%20Indonesia%20Jl.%20Ahmad%20Yani%20Kel.%20Baru%2C%20Kec.%20Arut%20Sel.%2C%20Kabupaten%20Kotawaringin%20Barat%2C%20Kalimantan%20Tengah%2074113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kertapati%20Palembang%20Indonesia%20Jl.%20KH%20Wahid%20Hasyim%2C%203-4%20Ulu%2C%20Kecamatan%20Seberang%20Ulu%20I%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030258</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Nani%20Wartabone%20Gorontalo%20Indonesia%20Jl.%20Nani%20Wartabone%2C%20Limba%20U%20I%2C%20Kota%20Sel.%2C%20Kota%20Gorontalo%2C%20Gorontalo%2096111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Siaran%20Sako%20Palembang%20Indonesia%20Jl.%20Siaran%2C%20Sako%20Baru%2C%20Kec.%20Sako%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030961</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20DR%20Girian%20Bitung%20Indonesia%20l.%20Dahlia%20Raya%2C%20Girian%20Bawah%2C%20Kec.%20Madidir%2C%20Kota%20Bitung%2C%20Sulawesi%20Utara%2095511</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Diponegoro%20Bojonegoro%20Indonesia%20Jl.%20Diponegoro%20No.40%2C%20Sukorejo%20Lor%2C%20Sumbang%2C%20Kec.%20Bojonegoro%2C%20Kabupaten%20Bojonegoro%2C%20Jawa%20Timur%2062115</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Raya%20Singosari%20Malang%20Indonesia%20Jl.%20raya%20singosari%20no%20125%20%20pangetan%2C%20kec%20singosari%2C%20kab%20malang%2C%20jawa%20timur%2065153</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Bandar%20Jaya%20Lampung%20Indonesia%20Jl.%20Proklamator%20Raya%20No.130%2C%20Bandar%20Jaya%20Tim.%2C%20Kec.%20Terbanggi%20Besar%2C%20Kabupaten%20Lampung%20Tengah%2C%20Lampung%2034163</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sam%20Ratulangi%20Bulukumba%20Indonesia%20Jl.%20Sam%20Ratulangi%2C%20Caile%2C%20Kec.%20Ujung%20Bulu%2C%20Kabupaten%20Bulukumba%2C%20Sulawesi%20Selatan%2092561</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av%20Gajah%20Mada%20Surakarta%20Indonesia%20Jl.%20Gajahmada%20No.123A%2C%20Punggawan%2C%20Kec.%20Banjarsari%2C%20Kota%20Surakarta%2C%20Jawa%20Tengah%2057132</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Veteran%20Blitar%20Indonesia%20Jl.%20Veteran%20No.1%2C%20Kepanjen%20Kidul%2C%20Kec.%20Kepanjenkidul%2C%20Kota%20Blitar%2C%20Jawa%20Timur%2066117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend%20A%20Yani%20Bone%20Indonesia%20Jl.%20Jend.%20Ahmad%20Yani%20No.178%2C%20Macanang%2C%20Kec.%20Tanete%20Riattang%20Bar.%2C%20Kabupaten%20Bone%2C%20Sulawesi%20Selatan%2092711</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Tarum%20Barat%20Bekasi%20Indonesia%20Jl.%20Tapir%20VI%20No.1%2C%20Jayamukti%2C%20Kec.%20Cikarang%20Pusat%2C%20Kabupaten%20Bekasi%2C%20Jawa%20Barat%2017530</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Wadungasri%20Sidoarjo%20Indonesia%20Jl.%20Raya%20Wadung%20Asri%20No.68%2C%20Wadungasri%2C%20Kec.%20Waru%2C%20Kabupaten%20Sidoarjo%2C%20Jawa%20Timur%2061256</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Citraland%20Surabaya%20Indonesia%20Jl.%20Sentra%20Taman%20Gapura%20No.168%2C%20Sambikerep%2C%20Kec.%20Sambikerep%2C%20Surabaya%2C%20Jawa%20Timur%2060217</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Puri%20Anjasmoro%20Semarang%20Indonesia%20Jl.%20Anjasmoro%20Raya%20No.1A/%202%201A/%202%2C%20RT.3/RW/RW.RT.3%2C%20Tawangmas%2C%20Semarang%20Barat%2C%20Semarang%20City%2C%20Central%20Java%2050142</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20AW%20Syahranie%20Samarinda%20Indonesia%20Jl.%20A.%20Wahab%20Syahranie%20No.102%2C%20Sempaja%20Sel.%2C%20Kec.%20Samarinda%20Ulu%2C%20Kota%20Samarinda%2C%20Kalimantan%20Timur%2075243</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Rajawali%20Palangkaraya%20Indonesia%20Jalan%20Rajawali%20Km%204%2C%20Jl.%20Manjuhan%20No.Sebelah%205%2C%20Bukit%20Tunggal%2C%20Kec.%20Jekan%20Raya%2C%20Kota%20Palangka%20Raya%2C%20Kalimantan%20Tengah%2074874</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Tanjung%20Pura%20No.463%20Pontianak%20Indonesia%20Jl.%20Tanjung%20Pura%20No.463%2C%20Benua%20Melayu%20Darat%2C%20Kec.%20Pontianak%20Sel.%2C%20Kota%20Pontianak%2C%20Kalimantan%20Barat%2078243</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ahmad%20Yani%20Sukabumi%20Indonesia%20Jl.%20A.%20Yani%20No.191%2C%20Gunungparang%2C%20Kec.%20Cikole%2C%20Kota%20Sukabumi%2C%20Jawa%20Barat%2043111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Panca%20Usaha%20Mataram%20Indonesia%20Jl.%20Panca%20Usaha%20%2C%20cilinaya%2Ckec.%20cakranegara%2C%20kota%20mataram%2C%20Nusa%20tenggara%20Barat%2C28983</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Diponegoro%20Tuban%20Indonesia%20Jl.%20Diponegoro%20No.56%2C%20Latsari%2C%20Kec.%20Tuban%2C%20Kabupaten%20Tuban%2C%20Jawa%20Timur%2062314</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Gus%20Dur%20Jombang%20Indonesia%20Jl.%20Gus%20Dur%20No.110%2C%20Candi%20Mulyo%2C%20Kec.%20Jombang%2C%20Kabupaten%20Jombang%2C%20Jawa%20Timur%2061419</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Karangnongko%20Sidoarjo%20Indonesia%20Jl.%20Karangnongko%20No.21%2C%20Karangnongko%2C%20Pekarungan%2C%20Kec.%20Sukodono%2C%20Kabupaten%20Sidoarjo%2C%20Jawa%20Timur%2061258Jl.%20Karangnongko%20No.21%2C%20Karangnongko%2C%20Pekarungan%2C%20Kec.%20Sukodono%2C%20Kabupaten%20Sidoarjo%2C%20Jawa%20Timur%2061258</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend%20Sudirman%20Tarakan%20Indonesia%20Jl.%20Jend.%20Sudirman%20No.10%2C%20Karang%20Anyar%2C%20Kec.%20Tarakan%20Bar.%2C%20Kota%20Tarakan%2C%20Kalimantan%20Utara%2077111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ahmad%20Yani%20Garut%20Indonesia%20Jl.%20Ahmad%20Yani%20No.167%2C%20Ciwalen%2C%20Kec.%20Garut%20Kota%2C%20Kabupaten%20Garut%2C%20Jawa%20Barat%2044115</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Raya%20KH%20Abdul%20Hakim%20Majalengka%20Indonesia%20Jl.%20Raya%20K%20H%20Abdul%20Halim%20No.298%2C%20Majalengka%20Wetan%2C%20Kec.%20Majalengka%2C%20Kabupaten%20Majalengka%2C%20Jawa%20Barat%2045411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Paramount%20Gading%20Serpong%20Tangerang%20Indonesia%20Paramount%20Gading%20Serpong%20Ruko%20Madison%20Grande%2C%20J%20No.52%2C%20Medang%2C%20Pagedangan%2C%20Tangerang%20Regency%2C%20Banten%2015334</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kalimantan%20Gresik%20Indonesia%20Jl.%20Kalimantan%20No.115%2C%20Wonorejo%2C%20Yosowilangun%2C%20Kec.%20Gresik%2C%20Kabupaten%20Gresik%2C%20Jawa%20Timur%2061151</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ngurah%20Rai%20Klungkung%20Bali%20Indonesia%20Jl.%20Ngurah%20Rai%2C%20Semarapura%20Tengah%2C%20Kec.%20Klungkung%2C%20Kabupaten%20Klungkung%2C%20Bali%2080716</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Irian%20Palangkaraya%20Indonesia%20Jl.%20Irian%20No.1%2C%20Pahandut%2C%20Kec.%20Pahandut%2C%20Kota%20Palangka%20Raya%2C%20Kalimantan%20Tengah%2073112</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kertabumi%20Karawang%20Indonesia%20Jl.%20Kertabumi%20No.42%2C%20Karawang%20Kulon%2C%20Kec.%20Karawang%20Bar.%2C%20Karawang%2C%20Jawa%20Barat%2041311</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Dr%20Soetomo%20Ciledug%20Tangerang%20Indonesia%20Jl.%20Dr.%20Soetomo%20No.17%2C%20RT.002/RW.009%2C%20Karang%20Tim.%2C%20Kec.%20Ciledug%2C%20Kota%20Tangerang%2C%20Banten%2015151</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jendral%20Sudirman%20Ngawi%20Indonesia%20%20Jl.%20PB.%20Sudirman%20No.35%20B%2C%20Kerek%2C%20Margomulyo%2C%20kec%20Ngawi%2C%20Kab%20Ngawi%20Jawa%20Timur%2063217</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Pahlawan%20Kebumen%20Indonesia%20Jl.%20Pahlawan%20No.133%2C%20Keposan%2C%20Kebumen%2C%20Kec.%20Kebumen%2C%20Kabupaten%20Kebumen%2C%20Jawa%20Tengah%2054311</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Rengasdenglok%20Karawang%20Indonesia%20Jl.%20Raya%20R.Dengklok%20No.94%2C%20R.Dengklok%20Sel.%2C%20Kec.%20R.Dengklok%2C%20Karawang%2C%20Jawa%20Barat%2041352</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jendral%20sudirman%20Kupang%20Indonesia%20Jl.%20Jenderal%20Sudirman%20%20No.%2060%20%2C%20Kuanino%2C%20kec.%20Kota%20Raja%2C%20Kota%20kupang%2C%20Nusa%20Tenggar%20Timur%2C%2085119</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend%20Basuki%20Rahmat%20Palu%20Indonesia%20Jl.%20Jenderal%20Basuki%20Rahmat%20No.74%2C%20Tatura%20Sel.%2C%20Kec.%20Palu%20Sel.%2C%20Kota%20Palu%2C%20Sulawesi%20Tengah%2094236</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Otto%20Iskandardinata%20Subang%20Indonesia%20Jl.%20Otto%20Iskandardinata%20No.102%2C%20Karanganyar%2C%20Kec.%20Subang%2C%20Kabupaten%20Subang%2C%20Jawa%20Barat%2041211</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av%20Merdeka%20Cimone%20Tangerang%20Indonesia%20Jl.Ruko%20Merdeka%20Cimone%2C%20Jl.%20Raya%20Merdeka%20No.101%20ABC%2C%20RT.002/RW.001%2C%20Cimone%20Jaya%2C%20Kec.%20Karawaci%2C%20Kota%20Tangerang%2C%20Banten%2015114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Teuku%20Umar%20Meulaboh%20Indonesia%20Jl.%20Teuku%20Umar%2C%20Ujung%20Kalak%2C%20Kec.%20Johan%20Pahlawan%2C%20Kabupaten%20Aceh%20Barat%2C%20Aceh%2023681</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20KA%20Posong%20Pacitan%20Indonesia%20Jl.%20KA.%20Posong%2C%20Gemulung%2C%20Tanjungsari%2C%20Kec.%20Pacitan%2C%20Kabupaten%20Pacitan%2C%20Jawa%20Timur%2063518</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sokarno%20Hatta%20Kediri%20Indonesia%20%20Jl.%20Soekarno%20Hatta%20No.33%2C%20Tepus%2C%20Sukorejo%2C%20Kec.%20Ngasem%2C%20Kabupaten%20Kediri%2C%20Jawa%20Timur%2064182</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Mojopahit%20Mojokerto%20Indonesia%20%20Jl.%20Mojopahit%20No.271%2C%20Mergelo%2C%20Kranggan%2C%20Kec.%20Prajurit%20Kulon%2C%20Kota%20Mojokerto%2C%20Jawa%20Timur%2061322</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Mangunsarkoro%202%20Cianjur%20Indonesia%20Jl.%20Mangunsarkoro%20No.102%2C%20Pamoyanan%2C%20Kec.%20Cianjur%2C%20Kabupaten%20Cianjur%2C%20Jawa%20Barat%2043211</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mal%20Atrium%20Senen%20Jakarta%20Indonesia%20Mall%20Atrium%20Senen%20Lt.GF%20Unit%20G-24%2C%20Jl.%20Senen%20Raya%20No.135%2C%20Senen%2C%20Kec.%20Senen%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010410</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Plaza%20Buaran%20Jakarta%20Indonesia%20%20Plaza%20Buaran%20Lt.GF%20Jl.%20Radin%20Inten%20II%20No.1%2C%20RT.8/RW.14%2C%20Klender%2C%20Kec.%20Duren%20Sawit%2C%20Kota%20Jakarta%20Timur%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2013470</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Paris%20Van%20Java%20Bandung%20Indonesia%20Paris%20Van%20Java%20Lt.%20GL-C-26B%2C%20Jl.%20Sukajadi%20No.131-139%2C%20Cipedes%2C%20Kec.%20Sukajadi%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040162</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Living%20World%20Pekanbaru%20Riau%20Indonesia%20Living%20World%20Pekan%20Baru%20Lt.2-15%2C%20Jl.%20Soekarno-Hatta%2C%20Tengkerang%20Bar.%2C%20Kec.%20Marpoyan%20Damai%2C%20Kota%20Pekanbaru%2C%20Riau%2028292</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Pekanbaru%20Mall%20Indonesia%20Pekanbaru%20Mall%20Lt%20GF%2C%20Jl.%20Jend.%20Sudirman%20No.123%2C%20Kota%20Tinggi%2C%20Kec.%20Pekanbaru%20Kota%2C%20Kota%20Pekanbaru%2C%20Riau%2028155</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20The%20Park%20Solo%20Indonesia%20The%20Park%20Solo%20Lt%202.%20Jl.Ir.%20Soekarno%2C%20Dusun%20II%2C%20Madegondo%2C%20Kec.%20Grogol%2C%20Kabupaten%20Sukoharjo%2C%20Jawa%20Tengah%2057552</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Cibubur%20Junction%20Indonesia%20Cibubur%20Junction%20L1-AE16B%2C%20Jl.%20Jambore%20No.1%2C%20RT.8/RW.7%2C%20Cibubur%2C%20Kec.%20Ciracas%2C%20Kota%20Jakarta%20Timur%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2013720</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Pacific%20Mall%20Tegal%20Indonesia%20Pacific%20Mall%20Tegal%2C%20Lt%201%20Unit%20FF%2015-16%2C%20Jl.%20Mayjend%20Sutoyo%20No.35%2C%20Pekauman%2C%20Kec.%20Tegal%20Bar.%2C%20Kota%20Tegal%2C%20Jawa%20Tengah%2052131</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Plaza%20Surabaya%20Indonesia%20Plaza%20Surabaya%20Lt%201%2C%20Mall%20Jl.%20Pemuda%20No.33-37%20Lt.%201%20No.%206-7%2C%20Embong%20Kaliasin%2C%20Genteng%2C%20Surabaya%2C%20East%20Java%2060273</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lampung%20City%20Mall%20Indonesia%20Lampung%20City%20Mall%2C%20Lt%20GF%20unit%20GF-08%2C%20Jl.%20Yos%20Sudarso%20No.80%2C%20Bumi%20Waras%2C%20Kec.%20Bumi%20Waras%2C%20Kota%20Bandar%20Lampung%2C%20Lampung%2035225</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Binjai%20Mall%20Indonesia%20Binjai%20Mall%20Lt.%201F%2C%20Tanah%20Tinggi%2C%20Binjai%20Timur%2C%20Binjai%20City%2C%20North%20Sumatra%2020742</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Kalibata%20City%20Jakarta%20Indonesia%20Kalibata%20City%20Square%20unit%20G-4100%20lt%20GF%2C%20Jl.%20Raya%20Kalibata%20No.1%2C%20RT.9/RW.4%2C%20Rawajati%2C%20Kec.%20Pancoran%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2012750</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Living%20Plaza%20Jababeka%20Bekasi%20Indonesia%20Living%20Plaza%20Jababeka%2C%20Jl.%20Niaga%20Raya%20LANTAI%20GF%2C%20Mekarmukti%2C%20Kec.%20Cikarang%20Utara%2C%20Kabupaten%20Bekasi%2C%20Jawa%20Barat%2017550</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Mall%20Bassura%20Jakarta%20Indonesia%20Mall%20Bassura%20Lt.%20GF%20Unit%20RE/10%20Jl.%20Jenderal%20Basuki%20Rachmat%20No.1A%2C%20RT.8/RW.10%2C%20Cipinang%20Besar%20Sel.%2C%20Kecamatan%20Jatinegara%2C%20Kota%20Jakarta%20Timur%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2013410</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Citimall%20Cilacap%20Indonesia%20Jl.%20Ir.%20H.%20Juanda%2C%20Gunungsimping%2C%20Kec.%20Cilacap%20Tengah%2C%20Kabupaten%20Cilacap%2C%20Jawa%20Tengah%2053224</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Central%20Park%20Borneo%20%20Balikpapan%20Indonesia%20Klandasan%20Ilir%2C%20Balikpapan%20Selatan%2C%20Balikpapan%20City%2C%20East%20Kalimantan</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Lippo%20Grand%20Mall%20Lampung%20Indonesia%20Lippo%20Grand%20Mall%20Lt.2%20Jl.%20Raden%20Intan%20No.88%2C%20Pelita%2C%20Engal%2C%20Kota%20Bandar%20Lampung%2C%20Lampung%2035117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Singkawang%20Grand%20Mall%20Indonesia%20Singkawang%20Grand%20Mall%20Lt.%202%20unit%202B%263%2C%20Jl.%20Alianyang%2C%20Pasiran%2C%20Kec.%20Singkawang%20Bar.%2C%20Kota%20Singkawang%2C%20Kalimantan%20Barat%2079123</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Roxy%20Square%20Situbondo%20Indonesia%20Roxy%20Square%20Situbondo%20Lt.%20GF%20016%2C%20Jl.%20Basuki%20Rahmat%20No.11%2C%20Mimbaan%20Utara%2C%20Mimbaan%2C%20Kec.%20Panji%2C%20Kabupaten%20Situbondo%2C%20Jawa%20Timur%2068323</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Maleo%20Town%20Square%20Mamuju%20Indonesia%20Maleo%20Town%20Square%20Lt.%20GF%2C%20Jl.%20Yos%20Sudarso%2C%20Binanga%2C%20Kec.%20Mamuju%2C%20Kabupaten%20Mamuju%2C%20Sulawesi%20Barat%2091511</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Pahlawan%20Jombang%20Indonesia%20Jl.Pahlawan%20jombang%20No.%2057%2CJombang%20jawa%20timur%2061411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorize%20Store%20Av.%20Kaliurang%20Sleman%20Indonesia%20Jl.%20Kaliurang%20No.KM.%2030%2C%20Manggung%2C%20Caturtunggal%2C%20Kec.%20Depok%2C%20Kabupaten%20Sleman%2C%20Daerah%20Istimewa%20Yogyakarta%2055281</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Usman%20Sadar%20No.87A%20Gresik%20Indonesia%20%20Jl.%20Usman%20Sadar%20No.87A%2C%20Sukorame%2C%20Kemuteran%2C%20Kec.%20Gresik%2C%20Kabupaten%20Gresik%2C%20Jawa%20Timur%2061118</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Gajah%20Mada%20Mojokerto%20Indonesia%20Jl.%20Gajah%20Mada%20No.%20106%2C%20Kec.%20Magersari%2C%20Mojokerto%2061314</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20PB%20Sudirman%20Pare%20Kediri%20Indonesia%20Jl.%20Pb.%20Sudirman%20No.116%2C%20Plongko%2C%20Pare%2C%20Kec.%20Pare%2C%20Kabupaten%20Kediri%2C%20Jawa%20Timur%2064211</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ranugrati%20Sawojajar%20Malang%20Indonesia%20Jl.%20Ranugrati%20No.78b%2C%20Sawojajar%2C%20Kec.%20Kedungkandang%2C%20Kota%20Malang%2C%20Jawa%20Timur%2065139</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend%20Sudirman%20Polewali%20Mandar%20Indonesia%20Jl.%20Jend.%20Sudirman%20No.21-23%2C%20Sidodadi%2C%20Kec.%20Wonomulyo%2C%20Kabupaten%20Polewali%20Mandar%2C%20Sulawesi%20Barat%2091342</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Perintis%20Kemerdekaan%20Purwokerto%20Indonesia%20Jl.%20Perintis%20Kemerdekaan%20No.87a%2C%20Penisian%2C%20Purwokerto%20Kulon%2C%20Kec.%20Purwokerto%20Sel.%2C%20Kabupaten%20Banyumas%2C%20Jawa%20Tengah%2053141</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Suprapto%20Ketapang%20Indonesia%20Jl.%20R.%20Suprapto%20No.88A%2C%20Sampit%2C%20Kec.%20Delta%20Pawan%2C%20Kabupaten%20Ketapang%2C%20Kalimantan%20Barat%2078811</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sudirman%20Jambi%20Indonesia%20Jl.%20Jend.%20Sudirman%20No.24%2C%20RW.25%2C%20The%20Hok%2C%20Kec.%20Jambi%20Sel.%2C%20Kota%20Jambi%2C%20Jambi%2036138</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Paus%20Pekanbaru%20Indonesia%20Jl.%20Paus%20No.12-13%2C%20Tangkerang%20Tengah%2C%20Kec.%20Marpoyan%20Damai%2C%20Kota%20Pekanbaru%2C%20Riau%2028124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Tuanku%20Tambusai%20Kampung%20Melayu%20Pekanbaru%20Indonesia%20Jl.Tuanku%20Tambusai%2C%20Kp.%20Melayu%20No.134%2C%20Kec.%20Sukajadi%2C%20Kota%20Pekanbaru%2C%20Riau%2028122</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Hanggowongso%20Surakarta%20Indonesia%20Jl.%20Honggowongso%20No.83%2C%20Jayengan%2C%20Kec.%20Serengan%2C%20Kota%20Surakarta%2C%20Jawa%20Tengah%2057149</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20TDM%20Kupang%20Indonesia%20Jl.%20Bund.%20PU%2C%20Tuak%20Daun%20Merah%2C%20Kec.%20Oebobo%2C%20Kota%20Kupang%2C%20Nusa%20Tenggara%20Tim.%2085119</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Tlogosari%20Semarang%20Indonesia%20Jl.%20Tlogosari%20Raya%2C%20Tlogosari%20Kulon%2C%20Kec.%20Pedurungan%2C%20Kota%20Semarang%2C%20Jawa%20Tengah%2050196</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20A%20Yani%20Brebes%20Indonesia%20Jl.%20Jenderal%20A.%20Yani%20No.109%2C%20Kaumanpasar%2C%20Brebes%2C%20Kec.%20Brebes%2C%20Kabupaten%20Brebes%2C%20Jawa%20Tengah%2052212</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Adampe%20Dolot%20Kotamobagu%20Indonesia%20Mogolaing%2C%20Kec.%20Kotamobagu%20Bar.%2C%20Kota%20Kotamobagu%2C%20Sulawesi%20Utara%20%2095716</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Lemabang%20Palembang%20Indonesia%20Jl.%20Laksamana%20Yos%20Sudarso%2C%20Ilir%2C%20Kec.%20Ilir%20Tim.%20II%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Graha%20Raya%20Tangerang%20Selatan%20Indonesia%20Jl.%20Boulevard%20Graha%20Raya%20No.7B%20Blok%20A8%20No%2021A%2C%20Paku%20Jaya%2C%20Kec.%20Serpong%20Utara%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%2015220</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Marelan%20Medan%20Indonesia%20Jl.%20Marelan%20Raya%20Ps.%20IV%20No.97%2C%20Rengas%20Pulau%2C%20Kec.%20Medan%20Marelan%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020255</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Green%20Lake%20City%20Tangerang%20Indonesia%20Jl.%20Green%20Lake%20City%20Boulevard%20No.58%2C%20RT.003/RW.009%2C%20Petir%2C%20Kec.%20Cipondoh%2C%20Kota%20Tangerang%2C%20Banten%2015147</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Poris%20Tangerang%20Indonesia%20Jl.%20Poris%20Indah%2C%20RT.003/RW.003%2C%20Poris%20Gaga%2C%20Kec.%20Batuceper%2C%20Kota%20Tangerang%2C%20Banten%2015122</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Metro%20Lampung%20Indonesia%20Jl.%20Jendral%20Sudirman%20No.872%2C%20Imopuro%2C%20Kec.%20Metro%20Pusat%2C%20Kota%20Metro%2C%20Lampung%2034111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Bojongsoang%20Bandung%20Indonesia%20Jl.%20Raya%20Bojongsoang%20No.85A%2C%20Bojongsoang%2C%20Kec.%20Bojongsoang%2C%20Kabupaten%20Bandung%2C%20Jawa%20Barat%2040288</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Bau%20Massepe%20Parepare%20Indonesia%20Jl.%20Bau%20Massepe%2C%20Labukkang%2C%20Kec.%20Ujung%2C%20Kota%20Parepare%2C%20Sulawesi%20Selatan%2091111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kutabumi%20Tangerang%20Indonesia%20Jl.%20Raya%20Kutabumi%20No.5%2C%20RW.6%2C%20Kuta%20Baru%2C%20Kec.%20Ps.%20Kemis%2C%20Kabupaten%20Tangerang%2C%20Banten%2015560</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Panam%20Pekanbaru%20Indonesia%20Jalan%20HR%20Soebrantas%20KM%2010%2C5%20Simpang%2C%20Jl.%20Purwodadi%20No.Kelurahan%2C%20Sidomulyo%20Bar.%2C%20Kec.%20Tampan%2C%20Kota%20Pekanbaru%2C%20Riau%2028294</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ahmad%20Yani%20Wonogiri%20Indonesia%20Jl.%20Jenderal%20Ahmad%20Yani%20No.172%2C%20Salak%2C%20Wonokarto%2C%20Kec.%20Wonogiri%2C%20Kabupaten%20Wonogiri%2C%20Jawa%20Tengah%2057612</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jend%20Sudirman%20Tebing%20Tinggi%20Indonesia%20Jl.%20Jend.%20Sudirman%20No.253-255%2C%20Badak%20Bejuang%2C%20Kec.%20Tebing%20Tinggi%20Kota%2C%20Kota%20Tebing%20Tinggi%2C%20Sumatera%20Utara%2020998</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Yos%20Sudarso%20Tarakan%20Indonesia%20Jl.%20Yos%20Sudarso%2C%20Selumit%20Pantai%2C%20Kec.%20Tarakan%20Tengah%2C%20Kota%20Tarakan%2C%20Kalimantan%20Utara%2077113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Taman%20Galaxy%20Bekasi%20Indonesia%20Jl.%20Taman%20Galaxy%20Raya%20No.9%20blok%20h%2C%20RT.004/RW.014%2C%20Jaka%20Setia%2C%20Bekasi%20Selatan%2C%20Bekasi%2C%20West%20Java%2017147</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Harapan%20Indah%20Bekasi%20Indonesia%20Ruko%20Commercial%20Park%2C%20Jl.%20Taman%20Harapan%20Indah%20No.16%202.1%2C%20Pusaka%20Rakyat%2C%20Kec.%20Tarumajaya%2C%20Kabupaten%20Bekasi%2C%20Jawa%20Barat%2017214</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Lintas%20Melawi%20Sintang%20Indonesia%20Jl.%20Lintas%20Melawi%20No.31%20RT03%2C%20RW.01%2C%20Ladang%2C%20Kec.%20Sintang%2C%20Kabupaten%20Sintang%2C%20Kalimantan%20Barat%2078612</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Selong%20Lombok%20Timur%20Indonesia%20Jl.%20TGH.%20Zainuddin%20Abdul%20Majid%20No.22%2C%20Pancor%2C%20Kec.%20Selong%2C%20Kabupaten%20Lombok%20Timur%2C%20Nusa%20Tenggara%20Bar.%2083652</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Cimanuk%20Garut%20Indonesia%20Jl.%20Cimanuk%20No.182%2C%20Jayawaras%2C%20Kec.%20Tarogong%20Kidul%2C%20Kabupaten%20Garut%2C%20Jawa%20Barat%2044151</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kisaran%20Asahan%20Indonesia%20Jl.%20Cokro%20Aminoto%2C%20Kisaran%20Kota%2C%20Kec.%20Kota%20Kisaran%20Barat%2C%20Kabupaten%20Asahan%2C%20Sumatera%20Utara%2021211</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Veteran%20Purwakarta%20Indonesia%20Jl.%20Veteran%20No.5%2C%20RT.66/RW.2%2C%20Nagri%20Kaler%2C%20Kec.%20Purwakarta%2C%20Kabupaten%20Purwakarta%2C%20Jawa%20Barat%2041115</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sawangan%20Depok%20Indonesia%20Jl.%20Raya%20Bojongsari%20No.34%2C%20Bojongsari%20Lama%2C%20Kec.%20Bojongsari%2C%20Kota%20Depok%2C%20Jawa%20Barat%2016516</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Sudirman%20Buleleng%20Singaraja%20Indonesia%20Jl.%20Sudirman%20No.55%2C%20Banyuasri%2C%20Kec.%20Buleleng%2C%20Kabupaten%20Buleleng%2C%20Bali%2081116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Teuku%20Umar%20Bandar%20Lampung%20Indonesia%20Jl.%20Teuku%20Umar%20No.82%2C%20Sidodadi%2C%20Kec.%20Kedaton%2C%20Kota%20Bandar%20Lampung%2C%20Lampung%2035123</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Emmy%20Saelan%20Palu%20Indonesia%20Jl.%20Emmy%20Saelan%2C%20Tatura%20Sel.%2C%20Kec.%20Palu%20Tim.%2C%20Kota%20Palu%2C%20Sulawesi%20Tengah%2094236</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Belopa%20Luwu%20Indonesia%20Jl.%20Poros%2C%20Tampumia%20Radda%2C%20Kec.%20Belopa%2C%20Kabupaten%20Luwu%2C%20Sulawesi%20Selatan%2091994</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Basuki%20Rahmat%20Banyuwangi%20Indonesia%20Jl.%20Basuki%20Rahmat%20No.43%2C%20RT.1%2C%20Singotrunan%2C%20Kec.%20Banyuwangi%2C%20Kabupaten%20Banyuwangi%2C%20Jawa%20Timur%2068414</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ciledug%20Cirebon%20Indonesia%20Jl.%20Merdeka%20Barat%20No.76%2C%20Ciledug%20Kulon%2C%20Kec.%20Ciledug%2C%20Kabupaten%20Cirebon%2C%20Jawa%20Barat%2045188</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Semabung%20Pangkal%20Pinang%20Indonesia%20Jl.%20Depati%20Hamzah%20No.88%2C%20Semabung%20Baru%2C%20Kec.%20Girimaya%2C%20Kota%20Pangkal%20Pinang%2C%20Kepulauan%20Bangka%20Belitung%2033684</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Dr%20Muwardi%20Cianjur%20Indonesia%20Jl.%20Dr.%20Muwardi%20No.37%2C%20Muka%2C%20Kec.%20Cianjur%2C%20Kabupaten%20Cianjur%2C%20Jawa%20Barat%2043215</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Manennungeng%20Palopo%20Indonesia%20Jl.%20Manennungeng%2C%20Batupasi%2C%20Kec.%20Wara%20Utara%2C%20Kota%20Palopo%2C%20Sulawesi%20Selatan%2091913</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Prabu%20Geusan%20Ulun%20Sumedang%20Indonesia%20Jl.%20Prabu%20Geusan%20Ulun%2C%20Regol%20Wetan%2C%20Kec.%20Sumedang%20Sel.%2C%20Kabupaten%20Sumedang%2C%20Jawa%20Barat%2045311</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Tembung%20Medan%20Indonesia%20Jl.%20Besar%20Tembung%2C%20Hutan%2C%20Kec.%20Percut%20Sei%20Tuan%2C%20Kabupaten%20Deli%20Serdang%2C%20Sumatera%20Utara%2020371</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20KH.%20Zainal%20Arifin%20Stabat%20Langkat%20Indonesia%20Jl.%20KH.%20Zainal%20Arifin%20No.772%2C%20Stabat%20Baru%2C%20Kec.%20Stabat%2C%20Kabupaten%20Langkat%2C%20Sumatera%20Utara%2020851</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Cimindi%20Cimahi%20Indonesia%20Jl.%20Mahar%20Martanegara%20No.22%2C%20Cigugur%20Tengah%2C%20Kec.%20Cimahi%20Tengah%2C%20Kota%20Cimahi%2C%20Jawa%20Barat%2040522</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jeruk%20Raya%20Jagakarsa%20Jakarta%20Indonesia%20Jl.%20Jeruk%20Raya%20No.164%2C%20RT.13/RW.1%2C%20Jagakarsa%2C%20Kec.%20Jagakarsa%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2012620</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20A%20Yani%20Rantau%20Prapat%20Indonesia%20Jl.%20Jend.%20Ahmad%20Yani%20No.50D%2C%20Bakaran%20Batu%2C%20Kec.%20Rantau%20Sel.%2C%20Kab.%20Labuhanbatu%2C%20Sumatera%20Utara%2021411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Dr%20Mansyur%20Medan%20Indonesia%20Jl.%20Dr.%20Mansyur%20No.84%20AA%2C%20Padang%20Bulan%20Selayang%20I%2C%20Kec.%20Medan%20Selayang%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020153</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Kemakmuran%20Soppeng%20Indonesia%20Jl.%20Kemakmuran%20No.66%2C%20Lemba%2C%20Kec.%20Lalabata%2C%20Kabupaten%20Soppeng%2C%20Sulawesi%20Selatan%2090811</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Cijerah%20Bandung%20Indonesia%20Jl.%20Raya%20Cijerah%20No.86%2C%20Cibuntu%2C%20Kec.%20Bandung%20Kulon%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040213</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ahmad%20Dahlan%20Samarinda%20Indonesia%20Jl.%20Kyai%20Haji%20Ahmad%20Dahlan%2C%20Sungai%20Pinang%20Luar%2C%20Kec.%20Samarinda%20Kota%2C%20Kota%20Samarinda%2C%20Kalimantan%20Timur%2075242</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Paniki%20Manado%20Indonesia%20Jl.%20A.A.%20Maramis%20No.141%2C%20Paniki%20Bawah%2C%20Kec.%20Mapanget%2C%20Kota%20Manado%2C%20Sulawesi%20Utara%2095370</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3831,12 +4911,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3848,17 +4934,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4159,14 +5249,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N343"/>
+  <dimension ref="A1:R343"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4209,8 +5301,20 @@
       <c r="N1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4253,8 +5357,20 @@
       <c r="N2">
         <v>106.90817</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="P2" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -4297,8 +5413,20 @@
       <c r="N3">
         <v>107.001076</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R3" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -4341,8 +5469,20 @@
       <c r="N4">
         <v>106.82447999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="P4" s="4">
+        <v>5495373</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R4" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -4385,8 +5525,20 @@
       <c r="N5">
         <v>106.791349</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R5" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -4429,8 +5581,20 @@
       <c r="N6">
         <v>106.630724</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="P6" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R6" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -4473,8 +5637,20 @@
       <c r="N7">
         <v>106.821789</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R7" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -4517,8 +5693,20 @@
       <c r="N8">
         <v>107.608763</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="P8" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R8" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -4561,8 +5749,20 @@
       <c r="N9">
         <v>106.80481</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="P9" s="4">
+        <v>1122771</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R9" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -4605,8 +5805,20 @@
       <c r="N10">
         <v>112.67453399999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="P10" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R10" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -4649,8 +5861,20 @@
       <c r="N11">
         <v>119.441374</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="P11" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R11" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -4693,8 +5917,20 @@
       <c r="N12">
         <v>112.738867</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="P12" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R12" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -4737,8 +5973,20 @@
       <c r="N13">
         <v>110.392461</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="P13" s="4">
+        <v>1105415</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R13" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -4781,8 +6029,20 @@
       <c r="N14">
         <v>106.82740099999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="P14" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R14" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>77</v>
       </c>
@@ -4825,8 +6085,20 @@
       <c r="N15">
         <v>106.72765</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="P15" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R15" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -4869,8 +6141,20 @@
       <c r="N16">
         <v>106.79073</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="P16" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R16" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -4913,8 +6197,20 @@
       <c r="N17">
         <v>106.783115</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="P17" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R17" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -4957,8 +6253,20 @@
       <c r="N18">
         <v>106.73880699999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P18" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R18" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -5001,8 +6309,20 @@
       <c r="N19">
         <v>119.417417</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="P19" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R19" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -5045,8 +6365,20 @@
       <c r="N20">
         <v>107.13300099999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="P20" s="4">
+        <v>3172831</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R20" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -5089,8 +6421,20 @@
       <c r="N21">
         <v>112.77826899999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="P21" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R21" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -5133,8 +6477,20 @@
       <c r="N22">
         <v>112.62235699999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O22" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="P22" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R22" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>106</v>
       </c>
@@ -5177,8 +6533,20 @@
       <c r="N23">
         <v>124.835188</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O23" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="P23" s="4">
+        <v>478194</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R23" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -5221,8 +6589,20 @@
       <c r="N24">
         <v>107.591256</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O24" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P24" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R24" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>115</v>
       </c>
@@ -5265,8 +6645,20 @@
       <c r="N25">
         <v>98.674274999999994</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O25" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="P25" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R25" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -5309,8 +6701,20 @@
       <c r="N26">
         <v>107.636404</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P26" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R26" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>124</v>
       </c>
@@ -5353,8 +6757,20 @@
       <c r="N27">
         <v>106.73313899999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="P27" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R27" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>128</v>
       </c>
@@ -5397,8 +6813,20 @@
       <c r="N28">
         <v>106.979793</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O28" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="P28" s="4">
+        <v>5495373</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R28" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>131</v>
       </c>
@@ -5441,8 +6869,20 @@
       <c r="N29">
         <v>117.115939</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O29" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="P29" s="4">
+        <v>856361</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R29" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>136</v>
       </c>
@@ -5485,8 +6925,20 @@
       <c r="N30">
         <v>98.672222000000005</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O30" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="P30" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R30" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -5529,8 +6981,20 @@
       <c r="N31">
         <v>106.64401700000001</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O31" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="P31" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R31" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>142</v>
       </c>
@@ -5573,8 +7037,20 @@
       <c r="N32">
         <v>110.423447</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O32" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="P32" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R32" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>147</v>
       </c>
@@ -5617,8 +7093,20 @@
       <c r="N33">
         <v>124.837932</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P33" s="4">
+        <v>478194</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R33" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>150</v>
       </c>
@@ -5661,8 +7149,20 @@
       <c r="N34">
         <v>107.27939499999999</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="P34" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R34" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>154</v>
       </c>
@@ -5705,8 +7205,20 @@
       <c r="N35">
         <v>106.89216500000001</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O35" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="P35" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R35" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -5749,8 +7261,20 @@
       <c r="N36">
         <v>110.39756800000001</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="P36" s="4">
+        <v>1105415</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R36" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>160</v>
       </c>
@@ -5793,8 +7317,20 @@
       <c r="N37">
         <v>106.901945</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O37" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="P37" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R37" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>163</v>
       </c>
@@ -5837,8 +7373,20 @@
       <c r="N38">
         <v>106.0642</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O38" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="P38" s="4">
+        <v>464716</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R38" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>167</v>
       </c>
@@ -5881,8 +7429,20 @@
       <c r="N39">
         <v>108.552183</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O39" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="P39" s="4">
+        <v>348911</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R39" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>171</v>
       </c>
@@ -5925,8 +7485,20 @@
       <c r="N40">
         <v>106.900447</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="P40" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R40" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>175</v>
       </c>
@@ -5969,8 +7541,20 @@
       <c r="N41">
         <v>116.10522</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O41" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="P41" s="4">
+        <v>452812</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R41" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>180</v>
       </c>
@@ -6013,8 +7597,20 @@
       <c r="N42">
         <v>110.41570900000001</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O42" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P42" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R42" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>183</v>
       </c>
@@ -6057,8 +7653,20 @@
       <c r="N43">
         <v>106.653631</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O43" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="P43" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R43" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>186</v>
       </c>
@@ -6098,8 +7706,20 @@
       <c r="N44">
         <v>106.869567</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O44" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="P44" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R44" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>189</v>
       </c>
@@ -6142,8 +7762,20 @@
       <c r="N45">
         <v>115.21697</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O45" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="P45" s="4">
+        <v>660984</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R45" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>194</v>
       </c>
@@ -6186,8 +7818,20 @@
       <c r="N46">
         <v>110.41233699999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O46" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="P46" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R46" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>197</v>
       </c>
@@ -6230,8 +7874,20 @@
       <c r="N47">
         <v>106.74499400000001</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O47" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="P47" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R47" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>200</v>
       </c>
@@ -6274,8 +7930,20 @@
       <c r="N48">
         <v>109.345662</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O48" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="P48" s="4">
+        <v>676096</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R48" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>205</v>
       </c>
@@ -6318,8 +7986,20 @@
       <c r="N49">
         <v>104.741816</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O49" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="P49" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R49" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>210</v>
       </c>
@@ -6362,8 +8042,20 @@
       <c r="N50">
         <v>115.230413</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O50" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="P50" s="4">
+        <v>660984</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R50" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>213</v>
       </c>
@@ -6406,8 +8098,20 @@
       <c r="N51">
         <v>112.734624</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O51" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="P51" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R51" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>216</v>
       </c>
@@ -6450,8 +8154,20 @@
       <c r="N52">
         <v>109.23649500000001</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O52" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="P52" s="4">
+        <v>1849956</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R52" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>220</v>
       </c>
@@ -6494,8 +8210,20 @@
       <c r="N53">
         <v>107.69852</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O53" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="P53" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R53" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>223</v>
       </c>
@@ -6538,8 +8266,20 @@
       <c r="N54">
         <v>106.18141300000001</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O54" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="P54" s="4">
+        <v>730530</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R54" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>228</v>
       </c>
@@ -6582,8 +8322,20 @@
       <c r="N55">
         <v>110.809951</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O55" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="P55" s="4">
+        <v>586166</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R55" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>232</v>
       </c>
@@ -6626,8 +8378,20 @@
       <c r="N56">
         <v>106.82659</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O56" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="P56" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R56" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>235</v>
       </c>
@@ -6670,8 +8434,20 @@
       <c r="N57">
         <v>114.600335</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O57" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="P57" s="4">
+        <v>675916</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R57" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>240</v>
       </c>
@@ -6714,8 +8490,20 @@
       <c r="N58">
         <v>107.610801</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O58" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="P58" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R58" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>244</v>
       </c>
@@ -6758,8 +8546,20 @@
       <c r="N59">
         <v>108.55003499999999</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O59" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="P59" s="4">
+        <v>348911</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R59" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>247</v>
       </c>
@@ -6802,8 +8602,20 @@
       <c r="N60">
         <v>106.52486500000001</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O60" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="P60" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R60" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>250</v>
       </c>
@@ -6846,8 +8658,20 @@
       <c r="N61">
         <v>106.839957</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O61" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="P61" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R61" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>253</v>
       </c>
@@ -6890,8 +8714,20 @@
       <c r="N62">
         <v>110.362371</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O62" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="P62" s="4">
+        <v>1105415</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R62" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>256</v>
       </c>
@@ -6934,8 +8770,20 @@
       <c r="N63">
         <v>106.74262899999999</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O63" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="P63" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R63" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>259</v>
       </c>
@@ -6978,8 +8826,20 @@
       <c r="N64">
         <v>105.253226</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O64" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="P64" s="4">
+        <v>1096935</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R64" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>264</v>
       </c>
@@ -7022,8 +8882,20 @@
       <c r="N65">
         <v>95.306488999999999</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O65" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="P65" s="4">
+        <v>257315</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R65" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>269</v>
       </c>
@@ -7066,8 +8938,20 @@
       <c r="N66">
         <v>101.41777</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O66" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="P66" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R66" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>274</v>
       </c>
@@ -7110,8 +8994,20 @@
       <c r="N67">
         <v>106.792402</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O67" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="P67" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R67" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>278</v>
       </c>
@@ -7154,8 +9050,20 @@
       <c r="N68">
         <v>110.224767</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O68" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="P68" s="4">
+        <v>1324756</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R68" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>282</v>
       </c>
@@ -7198,8 +9106,20 @@
       <c r="N69">
         <v>100.35557900000001</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O69" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="P69" s="4">
+        <v>928539</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R69" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>287</v>
       </c>
@@ -7242,8 +9162,20 @@
       <c r="N70">
         <v>112.01577899999999</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O70" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="P70" s="4">
+        <v>296792</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R70" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>291</v>
       </c>
@@ -7286,8 +9218,20 @@
       <c r="N71">
         <v>108.21763300000001</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O71" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="P71" s="4">
+        <v>752545</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R71" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>295</v>
       </c>
@@ -7330,8 +9274,20 @@
       <c r="N72">
         <v>112.69844399999999</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O72" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="P72" s="4">
+        <v>1982939</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R72" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>299</v>
       </c>
@@ -7374,8 +9330,20 @@
       <c r="N73">
         <v>116.858486</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O73" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="P73" s="4">
+        <v>733397</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R73" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>303</v>
       </c>
@@ -7418,8 +9386,20 @@
       <c r="N74">
         <v>115.182802</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O74" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="P74" s="4">
+        <v>660984</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R74" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>307</v>
       </c>
@@ -7462,8 +9442,20 @@
       <c r="N75">
         <v>113.66279</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O75" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="P75" s="4">
+        <v>2590289</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R75" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>311</v>
       </c>
@@ -7506,8 +9498,20 @@
       <c r="N76">
         <v>106.84590300000001</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O76" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="P76" s="4">
+        <v>5495373</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R76" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>314</v>
       </c>
@@ -7550,8 +9554,20 @@
       <c r="N77">
         <v>106.9717</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O77" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="P77" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R77" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>317</v>
       </c>
@@ -7594,8 +9610,20 @@
       <c r="N78">
         <v>107.292214</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O78" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="P78" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R78" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>321</v>
       </c>
@@ -7638,8 +9666,20 @@
       <c r="N79">
         <v>106.82342</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O79" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="P79" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R79" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>324</v>
       </c>
@@ -7682,8 +9722,20 @@
       <c r="N80">
         <v>112.601688</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O80" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="P80" s="4">
+        <v>1296688</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R80" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>328</v>
       </c>
@@ -7726,8 +9778,20 @@
       <c r="N81">
         <v>107.586242</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O81" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="P81" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R81" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>331</v>
       </c>
@@ -7770,8 +9834,20 @@
       <c r="N82">
         <v>102.267369</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O82" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="P82" s="4">
+        <v>385511</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R82" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>336</v>
       </c>
@@ -7814,8 +9890,20 @@
       <c r="N83">
         <v>128.198103</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O83" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="P83" s="4">
+        <v>354052</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R83" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>341</v>
       </c>
@@ -7858,8 +9946,20 @@
       <c r="N84">
         <v>119.554146</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O84" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="P84" s="4">
+        <v>394615</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R84" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>345</v>
       </c>
@@ -7902,8 +10002,20 @@
       <c r="N85">
         <v>106.88909200000001</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O85" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="P85" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R85" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>348</v>
       </c>
@@ -7946,8 +10058,20 @@
       <c r="N86">
         <v>110.432253</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O86" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="P86" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R86" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>351</v>
       </c>
@@ -7990,8 +10114,20 @@
       <c r="N87">
         <v>106.818022</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O87" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="P87" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R87" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>354</v>
       </c>
@@ -8034,8 +10170,20 @@
       <c r="N88" s="2">
         <v>104.79156399999999</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O88" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="P88" s="4">
+        <v>844108</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R88" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>359</v>
       </c>
@@ -8078,8 +10226,20 @@
       <c r="N89">
         <v>117.154967</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O89" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="P89" s="4">
+        <v>856361</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R89" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>362</v>
       </c>
@@ -8122,8 +10282,20 @@
       <c r="N90">
         <v>106.982479</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O90" s="3" t="s">
+        <v>1361</v>
+      </c>
+      <c r="P90" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R90" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>365</v>
       </c>
@@ -8166,8 +10338,20 @@
       <c r="N91">
         <v>98.626718999999994</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O91" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="P91" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R91" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>368</v>
       </c>
@@ -8210,8 +10394,20 @@
       <c r="N92">
         <v>98.663635999999997</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O92" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="P92" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R92" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>371</v>
       </c>
@@ -8254,8 +10450,20 @@
       <c r="N93">
         <v>106.993112</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O93" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="P93" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R93" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>375</v>
       </c>
@@ -8298,8 +10506,20 @@
       <c r="N94">
         <v>112.443512</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O94" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="P94" s="4">
+        <v>141335</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R94" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>379</v>
       </c>
@@ -8342,8 +10562,20 @@
       <c r="N95">
         <v>106.989428</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O95" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="P95" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R95" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>382</v>
       </c>
@@ -8386,8 +10618,20 @@
       <c r="N96">
         <v>107.13134599999999</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O96" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="P96" s="4">
+        <v>2516417</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R96" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>386</v>
       </c>
@@ -8430,8 +10674,20 @@
       <c r="N97">
         <v>110.816699</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O97" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="P97" s="4">
+        <v>908228</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R97" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>390</v>
       </c>
@@ -8474,8 +10730,20 @@
       <c r="N98">
         <v>112.749994</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O98" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="P98" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R98" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>393</v>
       </c>
@@ -8518,8 +10786,20 @@
       <c r="N99">
         <v>119.450033</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O99" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="P99" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R99" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>396</v>
       </c>
@@ -8562,8 +10842,20 @@
       <c r="N100">
         <v>112.72849100000001</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O100" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="P100" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R100" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>399</v>
       </c>
@@ -8606,8 +10898,20 @@
       <c r="N101">
         <v>115.18433899999999</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O101" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="P101" s="4">
+        <v>526029</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R101" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>403</v>
       </c>
@@ -8650,8 +10954,20 @@
       <c r="N102">
         <v>112.616159</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O102" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="P102" s="4">
+        <v>1296688</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R102" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>406</v>
       </c>
@@ -8694,8 +11010,20 @@
       <c r="N103">
         <v>114.84831</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O103" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="P103" s="4">
+        <v>270346</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R103" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>410</v>
       </c>
@@ -8738,8 +11066,20 @@
       <c r="N104">
         <v>104.738058</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O104" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="P104" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R104" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>413</v>
       </c>
@@ -8782,8 +11122,20 @@
       <c r="N105">
         <v>104.76113599999999</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O105" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="P105" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R105" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>416</v>
       </c>
@@ -8826,8 +11178,20 @@
       <c r="N106">
         <v>122.524231</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O106" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="P106" s="4">
+        <v>347380</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R106" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>421</v>
       </c>
@@ -8870,8 +11234,20 @@
       <c r="N107">
         <v>112.81139400000001</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O107" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="P107" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R107" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>424</v>
       </c>
@@ -8914,8 +11290,20 @@
       <c r="N108">
         <v>122.512057</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O108" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="P108" s="4">
+        <v>347380</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R108" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>427</v>
       </c>
@@ -8958,8 +11346,20 @@
       <c r="N109">
         <v>112.74863499999999</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O109" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="P109" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R109" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>430</v>
       </c>
@@ -9002,8 +11402,20 @@
       <c r="N110">
         <v>106.874185</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O110" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="P110" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R110" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>433</v>
       </c>
@@ -9046,8 +11458,20 @@
       <c r="N111">
         <v>106.79934799999999</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O111" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="P111" s="4">
+        <v>1122771</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R111" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>436</v>
       </c>
@@ -9090,8 +11514,20 @@
       <c r="N112">
         <v>98.644181000000003</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O112" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="P112" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R112" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>440</v>
       </c>
@@ -9134,8 +11570,20 @@
       <c r="N113">
         <v>106.911119</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O113" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="P113" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R113" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>443</v>
       </c>
@@ -9178,8 +11626,20 @@
       <c r="N114">
         <v>106.72872099999999</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O114" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P114" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R114" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>446</v>
       </c>
@@ -9222,8 +11682,20 @@
       <c r="N115">
         <v>106.817064</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O115" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="P115" s="4">
+        <v>1122771</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R115" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>449</v>
       </c>
@@ -9266,8 +11738,20 @@
       <c r="N116">
         <v>124.837932</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O116" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="P116" s="4">
+        <v>478194</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R116" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>453</v>
       </c>
@@ -9310,8 +11794,20 @@
       <c r="N117">
         <v>106.606495</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O117" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="P117" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R117" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>456</v>
       </c>
@@ -9354,8 +11850,20 @@
       <c r="N118">
         <v>106.843892</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O118" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="P118" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R118" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>459</v>
       </c>
@@ -9398,8 +11906,20 @@
       <c r="N119">
         <v>106.634049</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O119" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="P119" s="4">
+        <v>1899515</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R119" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>463</v>
       </c>
@@ -9442,8 +11962,20 @@
       <c r="N120">
         <v>112.74751999999999</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O120" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="P120" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R120" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>466</v>
       </c>
@@ -9486,8 +12018,20 @@
       <c r="N121">
         <v>106.69411700000001</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O121" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="P121" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R121" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>469</v>
       </c>
@@ -9530,8 +12074,20 @@
       <c r="N122">
         <v>123.062073</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O122" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="P122" s="4">
+        <v>203205</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R122" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>474</v>
       </c>
@@ -9574,8 +12130,20 @@
       <c r="N123">
         <v>112.076255</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O123" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="P123" s="4">
+        <v>1249619</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R123" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>478</v>
       </c>
@@ -9618,8 +12186,20 @@
       <c r="N124">
         <v>113.924392</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O124" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="P124" s="4">
+        <v>302311</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R124" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>483</v>
       </c>
@@ -9662,8 +12242,20 @@
       <c r="N125">
         <v>119.8426</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O125" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="P125" s="4">
+        <v>382017</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R125" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>488</v>
       </c>
@@ -9706,8 +12298,20 @@
       <c r="N126">
         <v>106.959187</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O126" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="P126" s="4">
+        <v>5495373</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R126" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>491</v>
       </c>
@@ -9750,8 +12354,20 @@
       <c r="N127">
         <v>99.072187999999997</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O127" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="P127" s="4">
+        <v>275189</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R127" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>495</v>
       </c>
@@ -9794,8 +12410,20 @@
       <c r="N128">
         <v>108.33702</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O128" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="P128" s="4">
+        <v>947166</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R128" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>499</v>
       </c>
@@ -9838,8 +12466,20 @@
       <c r="N129">
         <v>106.925792</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O129" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="P129" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R129" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>502</v>
       </c>
@@ -9882,8 +12522,20 @@
       <c r="N130">
         <v>100.397521</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O130" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="P130" s="4">
+        <v>928539</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R130" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>505</v>
       </c>
@@ -9926,8 +12578,20 @@
       <c r="N131">
         <v>110.381372</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O131" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="P131" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R131" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>508</v>
       </c>
@@ -9970,8 +12634,20 @@
       <c r="N132">
         <v>107.608931</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O132" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="P132" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R132" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>511</v>
       </c>
@@ -10014,8 +12690,20 @@
       <c r="N133">
         <v>106.842597</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O133" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="P133" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R133" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>515</v>
       </c>
@@ -10058,8 +12746,20 @@
       <c r="N134">
         <v>106.840907</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O134" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="P134" s="4">
+        <v>5495373</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R134" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>518</v>
       </c>
@@ -10099,8 +12799,20 @@
       <c r="N135">
         <v>119.39393099999999</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O135" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="P135" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R135" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>521</v>
       </c>
@@ -10143,8 +12855,20 @@
       <c r="N136">
         <v>110.420416</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O136" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="P136" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R136" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>524</v>
       </c>
@@ -10187,8 +12911,20 @@
       <c r="N137">
         <v>106.81286</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O137" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="P137" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R137" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>527</v>
       </c>
@@ -10231,8 +12967,20 @@
       <c r="N138">
         <v>107.195449</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O138" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="P138" s="4">
+        <v>3172831</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R138" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>530</v>
       </c>
@@ -10275,8 +13023,20 @@
       <c r="N139">
         <v>106.786618</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O139" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="P139" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R139" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>533</v>
       </c>
@@ -10316,8 +13076,20 @@
       <c r="N140">
         <v>106.89189399999999</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O140" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="P140" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R140" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>536</v>
       </c>
@@ -10360,8 +13132,20 @@
       <c r="N141">
         <v>104.753834</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O141" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="P141" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R141" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>539</v>
       </c>
@@ -10404,8 +13188,20 @@
       <c r="N142">
         <v>109.369536</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O142" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="P142" s="4">
+        <v>291750</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R142" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>543</v>
       </c>
@@ -10448,8 +13244,20 @@
       <c r="N143">
         <v>112.720054</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O143" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="P143" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R143" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>546</v>
       </c>
@@ -10492,8 +13300,20 @@
       <c r="N144">
         <v>115.208021</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O144" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="P144" s="4">
+        <v>660984</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R144" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>550</v>
       </c>
@@ -10536,8 +13356,20 @@
       <c r="N145">
         <v>112.717679</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O145" s="3" t="s">
+        <v>1418</v>
+      </c>
+      <c r="P145" s="4">
+        <v>1982939</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R145" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>553</v>
       </c>
@@ -10580,8 +13412,20 @@
       <c r="N146">
         <v>112.666859</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O146" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="P146" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R146" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>557</v>
       </c>
@@ -10624,8 +13468,20 @@
       <c r="N147">
         <v>114.87306700000001</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O147" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="P147" s="4">
+        <v>575113</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R147" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>562</v>
       </c>
@@ -10668,8 +13524,20 @@
       <c r="N148">
         <v>98.678877999999997</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O148" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="P148" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R148" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>565</v>
       </c>
@@ -10712,8 +13580,20 @@
       <c r="N149">
         <v>112.780812</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O149" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="P149" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R149" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>568</v>
       </c>
@@ -10756,8 +13636,20 @@
       <c r="N150">
         <v>109.651066</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O150" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="P150" s="4">
+        <v>317534</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R150" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>573</v>
       </c>
@@ -10800,8 +13692,20 @@
       <c r="N151">
         <v>113.722081</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O151" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="P151" s="4">
+        <v>2590289</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R151" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>577</v>
       </c>
@@ -10844,8 +13748,20 @@
       <c r="N152">
         <v>100.396214</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O152" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="P152" s="4">
+        <v>135489</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R152" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>582</v>
       </c>
@@ -10888,8 +13804,20 @@
       <c r="N153">
         <v>100.354747</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O153" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="P153" s="4">
+        <v>928539</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R153" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>586</v>
       </c>
@@ -10932,8 +13860,20 @@
       <c r="N154">
         <v>116.844972</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O154" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="P154" s="4">
+        <v>733397</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R154" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>590</v>
       </c>
@@ -10976,8 +13916,20 @@
       <c r="N155">
         <v>108.981435</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O155" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="P155" s="4">
+        <v>242146</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R155" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>595</v>
       </c>
@@ -11020,8 +13972,20 @@
       <c r="N156">
         <v>109.306162</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O156" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="P156" s="4">
+        <v>676096</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R156" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>598</v>
       </c>
@@ -11064,8 +14028,20 @@
       <c r="N157">
         <v>111.898601</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O157" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="P157" s="4">
+        <v>1132146</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R157" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>602</v>
       </c>
@@ -11108,8 +14084,20 @@
       <c r="N158">
         <v>112.01836400000001</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O158" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="P158" s="4">
+        <v>296792</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R158" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>605</v>
       </c>
@@ -11152,8 +14140,20 @@
       <c r="N159">
         <v>119.887102</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O159" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="P159" s="4">
+        <v>382017</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R159" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>608</v>
       </c>
@@ -11196,8 +14196,20 @@
       <c r="N160">
         <v>104.76451400000001</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O160" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="P160" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R160" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>611</v>
       </c>
@@ -11240,8 +14252,20 @@
       <c r="N161">
         <v>98.708527000000004</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O161" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="P161" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R161" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>614</v>
       </c>
@@ -11284,8 +14308,20 @@
       <c r="N162">
         <v>103.59678</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O162" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="P162" s="4">
+        <v>633649</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R162" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>619</v>
       </c>
@@ -11328,8 +14364,20 @@
       <c r="N163">
         <v>95.330163999999996</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O163" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="P163" s="4">
+        <v>257315</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R163" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>623</v>
       </c>
@@ -11372,8 +14420,20 @@
       <c r="N164">
         <v>119.443811</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O164" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="P164" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R164" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>626</v>
       </c>
@@ -11416,8 +14476,20 @@
       <c r="N165">
         <v>107.623908</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O165" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="P165" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R165" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>629</v>
       </c>
@@ -11460,8 +14532,20 @@
       <c r="N166">
         <v>110.60007299999999</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O166" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="P166" s="4">
+        <v>1099682</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R166" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>634</v>
       </c>
@@ -11504,8 +14588,20 @@
       <c r="N167">
         <v>110.91150399999999</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O167" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="P167" s="4">
+        <v>1507156</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R167" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>638</v>
       </c>
@@ -11548,8 +14644,20 @@
       <c r="N168">
         <v>110.503196</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O168" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="P168" s="4">
+        <v>200738</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R168" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>642</v>
       </c>
@@ -11592,8 +14700,20 @@
       <c r="N169">
         <v>115.321116</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O169" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="P169" s="4">
+        <v>503546</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R169" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>647</v>
       </c>
@@ -11636,8 +14756,20 @@
       <c r="N170">
         <v>111.469902</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O170" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="P170" s="4">
+        <v>973269</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R170" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>652</v>
       </c>
@@ -11680,8 +14812,20 @@
       <c r="N171">
         <v>111.521343</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O171" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="P171" s="4">
+        <v>201992</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R171" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>656</v>
       </c>
@@ -11724,8 +14868,20 @@
       <c r="N172">
         <v>117.530023</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O172" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="P172" s="4">
+        <v>427492</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R172" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>661</v>
       </c>
@@ -11768,8 +14924,20 @@
       <c r="N173">
         <v>117.491473</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O173" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="P173" s="4">
+        <v>187446</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R173" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>665</v>
       </c>
@@ -11812,8 +14980,20 @@
       <c r="N174">
         <v>109.387243</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O174" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="P174" s="4">
+        <v>1567045</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R174" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>670</v>
       </c>
@@ -11856,8 +15036,20 @@
       <c r="N175">
         <v>112.608926</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O175" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="P175" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R175" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>674</v>
       </c>
@@ -11900,8 +15092,20 @@
       <c r="N176">
         <v>105.247274</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O176" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="P176" s="4">
+        <v>1096935</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R176" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>677</v>
       </c>
@@ -11944,8 +15148,20 @@
       <c r="N177">
         <v>98.703643999999997</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O177" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="P177" s="4">
+        <v>2016906</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R177" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>681</v>
       </c>
@@ -11988,8 +15204,20 @@
       <c r="N178">
         <v>115.211603</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O178" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="P178" s="4">
+        <v>660984</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R178" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>685</v>
       </c>
@@ -12032,8 +15260,20 @@
       <c r="N179">
         <v>109.331602</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O179" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="P179" s="4">
+        <v>676096</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R179" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>688</v>
       </c>
@@ -12076,8 +15316,20 @@
       <c r="N180">
         <v>112.570826</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O180" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="P180" s="4">
+        <v>2692261</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R180" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>693</v>
       </c>
@@ -12120,8 +15372,20 @@
       <c r="N181">
         <v>119.40918000000001</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O181" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="P181" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R181" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>697</v>
       </c>
@@ -12164,8 +15428,20 @@
       <c r="N182">
         <v>124.861063</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O182" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="P182" s="4">
+        <v>478194</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R182" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>700</v>
       </c>
@@ -12208,8 +15484,20 @@
       <c r="N183">
         <v>97.144687000000005</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O183" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="P183" s="4">
+        <v>193950</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R183" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>704</v>
       </c>
@@ -12252,8 +15540,20 @@
       <c r="N184">
         <v>109.009351</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O184" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="P184" s="4">
+        <v>2022808</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R184" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>708</v>
       </c>
@@ -12296,8 +15596,20 @@
       <c r="N185">
         <v>119.48123200000001</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O185" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="P185" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R185" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>711</v>
       </c>
@@ -12340,8 +15652,20 @@
       <c r="N186">
         <v>111.029685</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O186" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="P186" s="4">
+        <v>1012493</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R186" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>716</v>
       </c>
@@ -12384,8 +15708,20 @@
       <c r="N187">
         <v>98.682354000000004</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O187" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="P187" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R187" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>719</v>
       </c>
@@ -12428,8 +15764,20 @@
       <c r="N188">
         <v>111.898078</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O188" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="P188" s="4">
+        <v>1139616</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R188" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>723</v>
       </c>
@@ -12472,8 +15820,20 @@
       <c r="N189">
         <v>116.00132600000001</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O189" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="P189" s="4">
+        <v>343740</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R189" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>727</v>
       </c>
@@ -12516,8 +15876,20 @@
       <c r="N190">
         <v>116.846875</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O190" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="P190" s="4">
+        <v>733397</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R190" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>730</v>
       </c>
@@ -12560,8 +15932,20 @@
       <c r="N191">
         <v>114.578221</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O191" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="P191" s="4">
+        <v>675916</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R191" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>733</v>
       </c>
@@ -12604,8 +15988,20 @@
       <c r="N192">
         <v>106.9164</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O192" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="P192" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R192" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>736</v>
       </c>
@@ -12648,8 +16044,20 @@
       <c r="N193">
         <v>114.602159</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O193" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="P193" s="4">
+        <v>675916</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R193" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>739</v>
       </c>
@@ -12692,8 +16100,20 @@
       <c r="N194">
         <v>110.82023700000001</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O194" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="P194" s="4">
+        <v>586166</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R194" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>742</v>
       </c>
@@ -12736,8 +16156,20 @@
       <c r="N195">
         <v>112.628643</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O195" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="P195" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R195" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>745</v>
       </c>
@@ -12780,8 +16212,20 @@
       <c r="N196">
         <v>115.157217</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O196" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="P196" s="4">
+        <v>526029</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R196" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>748</v>
       </c>
@@ -12824,8 +16268,20 @@
       <c r="N197">
         <v>107.301137</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O197" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="P197" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R197" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>751</v>
       </c>
@@ -12868,8 +16324,20 @@
       <c r="N198">
         <v>108.21779100000001</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O198" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="P198" s="4">
+        <v>752545</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R198" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>754</v>
       </c>
@@ -12912,8 +16380,20 @@
       <c r="N199">
         <v>114.848354</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O199" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="P199" s="4">
+        <v>270346</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R199" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>757</v>
       </c>
@@ -12956,8 +16436,20 @@
       <c r="N200">
         <v>112.76169899999999</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O200" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="P200" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R200" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>760</v>
       </c>
@@ -13000,8 +16492,20 @@
       <c r="N201">
         <v>109.63630000000001</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O201" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="P201" s="4">
+        <v>1008689</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R201" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>764</v>
       </c>
@@ -13044,8 +16548,20 @@
       <c r="N202">
         <v>110.221926</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O202" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="P202" s="4">
+        <v>128152</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R202" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>769</v>
       </c>
@@ -13088,8 +16604,20 @@
       <c r="N203">
         <v>112.941255</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O203" s="3" t="s">
+        <v>1476</v>
+      </c>
+      <c r="P203" s="4">
+        <v>433678</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R203" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>773</v>
       </c>
@@ -13132,8 +16660,20 @@
       <c r="N204">
         <v>110.304295</v>
       </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O204" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="P204" s="4">
+        <v>1105415</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R204" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>776</v>
       </c>
@@ -13176,8 +16716,20 @@
       <c r="N205">
         <v>115.242654</v>
       </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O205" s="3" t="s">
+        <v>1478</v>
+      </c>
+      <c r="P205" s="4">
+        <v>660984</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R205" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>779</v>
       </c>
@@ -13220,8 +16772,20 @@
       <c r="N206">
         <v>109.34725400000001</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O206" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="P206" s="4">
+        <v>676096</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R206" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>782</v>
       </c>
@@ -13264,8 +16828,20 @@
       <c r="N207">
         <v>122.52200000000001</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O207" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="P207" s="4">
+        <v>347380</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R207" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>785</v>
       </c>
@@ -13308,8 +16884,20 @@
       <c r="N208">
         <v>119.79543</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O208" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="P208" s="4">
+        <v>323430</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R208" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>790</v>
       </c>
@@ -13352,8 +16940,20 @@
       <c r="N209">
         <v>105.257171</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O209" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="P209" s="4">
+        <v>1096935</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R209" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>793</v>
       </c>
@@ -13396,8 +16996,20 @@
       <c r="N210">
         <v>100.361576</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O210" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="P210" s="4">
+        <v>928539</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R210" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>796</v>
       </c>
@@ -13440,8 +17052,20 @@
       <c r="N211">
         <v>101.447146</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O211" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="P211" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R211" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>799</v>
       </c>
@@ -13484,8 +17108,20 @@
       <c r="N212">
         <v>112.621184</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O212" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="P212" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R212" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>802</v>
       </c>
@@ -13528,8 +17164,20 @@
       <c r="N213">
         <v>107.583369</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O213" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="P213" s="4">
+        <v>570829</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R213" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>806</v>
       </c>
@@ -13572,8 +17220,20 @@
       <c r="N214">
         <v>112.897693</v>
       </c>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O214" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="P214" s="4">
+        <v>212403</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R214" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>810</v>
       </c>
@@ -13616,8 +17276,20 @@
       <c r="N215">
         <v>104.768023</v>
       </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O215" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="P215" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R215" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>813</v>
       </c>
@@ -13660,8 +17332,20 @@
       <c r="N216">
         <v>98.676056000000003</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O216" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="P216" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R216" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>816</v>
       </c>
@@ -13704,8 +17388,20 @@
       <c r="N217">
         <v>106.853514</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O217" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="P217" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R217" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>819</v>
       </c>
@@ -13748,8 +17444,20 @@
       <c r="N218">
         <v>108.542145</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O218" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="P218" s="4">
+        <v>2420956</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R218" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>823</v>
       </c>
@@ -13792,8 +17500,20 @@
       <c r="N219">
         <v>109.65213900000001</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O219" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="P219" s="4">
+        <v>1008689</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R219" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>826</v>
       </c>
@@ -13836,8 +17556,20 @@
       <c r="N220">
         <v>111.674758</v>
       </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O220" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="P220" s="4">
+        <v>282660</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R220" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>830</v>
       </c>
@@ -13880,8 +17612,20 @@
       <c r="N221">
         <v>104.76015</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O221" s="3" t="s">
+        <v>1494</v>
+      </c>
+      <c r="P221" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R221" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>833</v>
       </c>
@@ -13924,8 +17668,20 @@
       <c r="N222">
         <v>123.062428</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O222" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="P222" s="4">
+        <v>203205</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R222" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>836</v>
       </c>
@@ -13968,8 +17724,20 @@
       <c r="N223">
         <v>104.791476</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O223" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="P223" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R223" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>839</v>
       </c>
@@ -14012,8 +17780,20 @@
       <c r="N224">
         <v>125.127532</v>
       </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O224" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="P224" s="4">
+        <v>228008</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R224" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>843</v>
       </c>
@@ -14056,8 +17836,20 @@
       <c r="N225">
         <v>111.882268</v>
       </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O225" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="P225" s="4">
+        <v>1356056</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R225" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>847</v>
       </c>
@@ -14100,8 +17892,20 @@
       <c r="N226">
         <v>112.665565</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O226" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="P226" s="4">
+        <v>2692261</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R226" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>850</v>
       </c>
@@ -14144,8 +17948,20 @@
       <c r="N227">
         <v>105.21337800000001</v>
       </c>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O227" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="P227" s="4">
+        <v>1373771</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R227" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>854</v>
       </c>
@@ -14188,8 +18004,20 @@
       <c r="N228">
         <v>120.192222</v>
       </c>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O228" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="P228" s="4">
+        <v>468337</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R228" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>858</v>
       </c>
@@ -14232,8 +18060,20 @@
       <c r="N229">
         <v>110.819518</v>
       </c>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O229" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="P229" s="4">
+        <v>586166</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R229" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>862</v>
       </c>
@@ -14276,8 +18116,20 @@
       <c r="N230">
         <v>112.167683</v>
       </c>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O230" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="P230" s="4">
+        <v>159406</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R230" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>866</v>
       </c>
@@ -14320,8 +18172,20 @@
       <c r="N231">
         <v>120.314673</v>
       </c>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O231" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="P231" s="4">
+        <v>817363</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R231" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>870</v>
       </c>
@@ -14364,8 +18228,20 @@
       <c r="N232">
         <v>107.164843</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O232" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="P232" s="4">
+        <v>3172831</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R232" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>873</v>
       </c>
@@ -14408,8 +18284,20 @@
       <c r="N233">
         <v>112.767736</v>
       </c>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O233" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="P233" s="4">
+        <v>1982939</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R233" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>877</v>
       </c>
@@ -14452,8 +18340,20 @@
       <c r="N234">
         <v>112.652907</v>
       </c>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O234" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="P234" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R234" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>880</v>
       </c>
@@ -14496,8 +18396,20 @@
       <c r="N235">
         <v>110.39166400000001</v>
       </c>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O235" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="P235" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R235" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>884</v>
       </c>
@@ -14540,8 +18452,20 @@
       <c r="N236">
         <v>117.13990099999999</v>
       </c>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O236" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="P236" s="4">
+        <v>856361</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R236" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>887</v>
       </c>
@@ -14584,8 +18508,20 @@
       <c r="N237">
         <v>113.885851</v>
       </c>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O237" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="P237" s="4">
+        <v>302311</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R237" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>891</v>
       </c>
@@ -14628,8 +18564,20 @@
       <c r="N238">
         <v>109.347481</v>
       </c>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O238" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="P238" s="4">
+        <v>676096</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R238" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>894</v>
       </c>
@@ -14672,8 +18620,20 @@
       <c r="N239">
         <v>106.930753</v>
       </c>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O239" s="3" t="s">
+        <v>1512</v>
+      </c>
+      <c r="P239" s="4">
+        <v>361581</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R239" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>898</v>
       </c>
@@ -14716,8 +18676,20 @@
       <c r="N240">
         <v>116.117907</v>
       </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O240" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="P240" s="4">
+        <v>452812</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R240" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>902</v>
       </c>
@@ -14760,8 +18732,20 @@
       <c r="N241">
         <v>112.04934900000001</v>
       </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O241" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="P241" s="4">
+        <v>1249619</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R241" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>891</v>
       </c>
@@ -14804,8 +18788,20 @@
       <c r="N242">
         <v>109.347481</v>
       </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O242" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="P242" s="4">
+        <v>676096</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R242" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>905</v>
       </c>
@@ -14848,8 +18844,20 @@
       <c r="N243">
         <v>112.24469000000001</v>
       </c>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O243" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="P243" s="4">
+        <v>1364775</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R243" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>909</v>
       </c>
@@ -14892,8 +18900,20 @@
       <c r="N244">
         <v>112.67265999999999</v>
       </c>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O244" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="P244" s="4">
+        <v>1982939</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R244" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>912</v>
       </c>
@@ -14936,8 +18956,20 @@
       <c r="N245">
         <v>117.587605</v>
       </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O245" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="P245" s="4">
+        <v>246734</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R245" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>917</v>
       </c>
@@ -14980,8 +19012,20 @@
       <c r="N246">
         <v>107.908772</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O246" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="P246" s="4">
+        <v>2770531</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R246" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>921</v>
       </c>
@@ -15024,8 +19068,20 @@
       <c r="N247">
         <v>108.23177200000001</v>
       </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O247" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="P247" s="4">
+        <v>1345378</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R247" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>925</v>
       </c>
@@ -15068,8 +19124,20 @@
       <c r="N248">
         <v>106.630234</v>
       </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O248" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="P248" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R248" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>928</v>
       </c>
@@ -15112,8 +19180,20 @@
       <c r="N249">
         <v>112.61539500000001</v>
       </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O249" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="P249" s="4">
+        <v>1296688</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R249" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>931</v>
       </c>
@@ -15156,8 +19236,20 @@
       <c r="N250">
         <v>115.39859800000001</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O250" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="P250" s="4">
+        <v>220491</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R250" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>936</v>
       </c>
@@ -15200,8 +19292,20 @@
       <c r="N251">
         <v>113.933882</v>
       </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O251" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="P251" s="4">
+        <v>302311</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R251" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>940</v>
       </c>
@@ -15244,8 +19348,20 @@
       <c r="N252">
         <v>107.292559</v>
       </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O252" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="P252" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R252" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>943</v>
       </c>
@@ -15288,8 +19404,20 @@
       <c r="N253">
         <v>106.720572</v>
       </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O253" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="P253" s="4">
+        <v>1899515</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R253" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>947</v>
       </c>
@@ -15332,8 +19460,20 @@
       <c r="N254">
         <v>111.439922</v>
       </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O254" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="P254" s="4">
+        <v>901637</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R254" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>951</v>
       </c>
@@ -15376,8 +19516,20 @@
       <c r="N255">
         <v>109.65588700000001</v>
       </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O255" s="3" t="s">
+        <v>1527</v>
+      </c>
+      <c r="P255" s="4">
+        <v>1426832</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R255" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>955</v>
       </c>
@@ -15420,8 +19572,20 @@
       <c r="N256">
         <v>107.29899399999999</v>
       </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O256" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="P256" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R256" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>958</v>
       </c>
@@ -15464,8 +19628,20 @@
       <c r="N257">
         <v>123.590211</v>
       </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O257" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="P257" s="4">
+        <v>443349</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R257" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>963</v>
       </c>
@@ -15508,8 +19684,20 @@
       <c r="N258">
         <v>119.883326</v>
       </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O258" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="P258" s="4">
+        <v>382017</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R258" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>966</v>
       </c>
@@ -15552,8 +19740,20 @@
       <c r="N259">
         <v>107.766926</v>
       </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O259" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="P259" s="4">
+        <v>1624855</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R259" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>970</v>
       </c>
@@ -15596,8 +19796,20 @@
       <c r="N260">
         <v>106.621224</v>
       </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O260" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="P260" s="4">
+        <v>1899515</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R260" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>973</v>
       </c>
@@ -15640,8 +19852,20 @@
       <c r="N261">
         <v>96.126309000000006</v>
       </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O261" s="3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="P261" s="4">
+        <v>201720</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R261" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>977</v>
       </c>
@@ -15684,8 +19908,20 @@
       <c r="N262">
         <v>111.112225</v>
       </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O262" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="P262" s="4">
+        <v>599574</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R262" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>981</v>
       </c>
@@ -15728,8 +19964,20 @@
       <c r="N263">
         <v>112.038389</v>
       </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O263" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="P263" s="4">
+        <v>296792</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R263" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>984</v>
       </c>
@@ -15772,8 +20020,20 @@
       <c r="N264">
         <v>112.432158</v>
       </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O264" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="P264" s="4">
+        <v>141335</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R264" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>988</v>
       </c>
@@ -15816,8 +20076,20 @@
       <c r="N265">
         <v>107.140998</v>
       </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O265" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="P265" s="4">
+        <v>2516417</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R265" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>991</v>
       </c>
@@ -15860,8 +20132,20 @@
       <c r="N266">
         <v>106.841382</v>
       </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O266" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="P266" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R266" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>995</v>
       </c>
@@ -15904,8 +20188,20 @@
       <c r="N267">
         <v>106.92419200000001</v>
       </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O267" s="3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="P267" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q267" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R267" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>998</v>
       </c>
@@ -15948,8 +20244,20 @@
       <c r="N268">
         <v>107.596006</v>
       </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O268" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="P268" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q268" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R268" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1001</v>
       </c>
@@ -15992,8 +20300,20 @@
       <c r="N269">
         <v>101.41874799999999</v>
       </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O269" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="P269" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R269" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1004</v>
       </c>
@@ -16036,8 +20356,20 @@
       <c r="N270">
         <v>101.446726</v>
       </c>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O270" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="P270" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R270" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1008</v>
       </c>
@@ -16080,8 +20412,20 @@
       <c r="N271">
         <v>110.81621699999999</v>
       </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O271" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="P271" s="4">
+        <v>586166</v>
+      </c>
+      <c r="Q271" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R271" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1011</v>
       </c>
@@ -16124,8 +20468,20 @@
       <c r="N272">
         <v>106.94340800000001</v>
       </c>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O272" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="P272" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q272" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R272" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1014</v>
       </c>
@@ -16168,8 +20524,20 @@
       <c r="N273">
         <v>109.128843</v>
       </c>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O273" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="P273" s="4">
+        <v>291806</v>
+      </c>
+      <c r="Q273" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R273" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1018</v>
       </c>
@@ -16212,8 +20580,20 @@
       <c r="N274">
         <v>112.748824</v>
       </c>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O274" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="P274" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R274" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1021</v>
       </c>
@@ -16256,8 +20636,20 @@
       <c r="N275">
         <v>105.280238</v>
       </c>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O275" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="P275" s="4">
+        <v>1096935</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R275" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1024</v>
       </c>
@@ -16300,8 +20692,20 @@
       <c r="N276">
         <v>98.488361999999995</v>
       </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O276" s="3" t="s">
+        <v>1548</v>
+      </c>
+      <c r="P276" s="4">
+        <v>305977</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R276" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1028</v>
       </c>
@@ -16344,8 +20748,20 @@
       <c r="N277">
         <v>106.854455</v>
       </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O277" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="P277" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R277" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1031</v>
       </c>
@@ -16388,8 +20804,20 @@
       <c r="N278">
         <v>107.149914</v>
       </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O278" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="P278" s="4">
+        <v>3172831</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R278" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1034</v>
       </c>
@@ -16432,8 +20860,20 @@
       <c r="N279">
         <v>106.94340800000001</v>
       </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O279" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="P279" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R279" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1037</v>
       </c>
@@ -16476,8 +20916,20 @@
       <c r="N280">
         <v>109.02432</v>
       </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O280" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="P280" s="4">
+        <v>2022808</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R280" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1040</v>
       </c>
@@ -16520,8 +20972,20 @@
       <c r="N281">
         <v>116.897696</v>
       </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O281" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="P281" s="4">
+        <v>733397</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R281" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1043</v>
       </c>
@@ -16564,8 +21028,20 @@
       <c r="N282">
         <v>105.257766</v>
       </c>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O282" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="P282" s="4">
+        <v>1096935</v>
+      </c>
+      <c r="Q282" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R282" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1046</v>
       </c>
@@ -16608,8 +21084,20 @@
       <c r="N283">
         <v>108.969689</v>
       </c>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O283" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P283" s="4">
+        <v>242146</v>
+      </c>
+      <c r="Q283" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R283" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1049</v>
       </c>
@@ -16652,8 +21140,20 @@
       <c r="N284">
         <v>114.02211</v>
       </c>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O284" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="P284" s="4">
+        <v>678471</v>
+      </c>
+      <c r="Q284" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R284" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1053</v>
       </c>
@@ -16696,8 +21196,20 @@
       <c r="N285">
         <v>118.89269899999999</v>
       </c>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O285" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="P285" s="4">
+        <v>283282</v>
+      </c>
+      <c r="Q285" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R285" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1058</v>
       </c>
@@ -16740,8 +21252,20 @@
       <c r="N286">
         <v>112.240522</v>
       </c>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O286" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="P286" s="4">
+        <v>1364775</v>
+      </c>
+      <c r="Q286" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R286" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1061</v>
       </c>
@@ -16784,8 +21308,20 @@
       <c r="N287">
         <v>110.383214</v>
       </c>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O287" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="P287" s="4">
+        <v>1105415</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R287" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1064</v>
       </c>
@@ -16828,8 +21364,20 @@
       <c r="N288">
         <v>112.64920600000001</v>
       </c>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O288" s="3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="P288" s="4">
+        <v>1296688</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R288" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1067</v>
       </c>
@@ -16872,8 +21420,20 @@
       <c r="N289">
         <v>112.43944</v>
       </c>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O289" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="P289" s="4">
+        <v>141335</v>
+      </c>
+      <c r="Q289" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R289" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>0</v>
       </c>
@@ -16916,8 +21476,20 @@
       <c r="N290">
         <v>112.016654</v>
       </c>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O290" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="P290" s="4">
+        <v>296792</v>
+      </c>
+      <c r="Q290" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R290" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1072</v>
       </c>
@@ -16960,8 +21532,20 @@
       <c r="N291">
         <v>112.653008</v>
       </c>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O291" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="P291" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q291" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R291" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1075</v>
       </c>
@@ -17004,8 +21588,20 @@
       <c r="N292">
         <v>119.212132</v>
       </c>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O292" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="P292" s="4">
+        <v>491014</v>
+      </c>
+      <c r="Q292" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R292" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>0</v>
       </c>
@@ -17048,8 +21644,20 @@
       <c r="N293">
         <v>109.2401569</v>
       </c>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O293" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="P293" s="4">
+        <v>1849956</v>
+      </c>
+      <c r="Q293" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R293" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1082</v>
       </c>
@@ -17092,8 +21700,20 @@
       <c r="N294">
         <v>109.96825800000001</v>
       </c>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O294" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="P294" s="4">
+        <v>577770</v>
+      </c>
+      <c r="Q294" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R294" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1086</v>
       </c>
@@ -17136,8 +21756,20 @@
       <c r="N295">
         <v>103.628708</v>
       </c>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O295" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="P295" s="4">
+        <v>633649</v>
+      </c>
+      <c r="Q295" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R295" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1089</v>
       </c>
@@ -17180,8 +21812,20 @@
       <c r="N296">
         <v>101.438861</v>
       </c>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O296" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="P296" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q296" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R296" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1092</v>
       </c>
@@ -17224,8 +21868,20 @@
       <c r="N297">
         <v>101.435382</v>
       </c>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O297" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="P297" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q297" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R297" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1096</v>
       </c>
@@ -17268,8 +21924,20 @@
       <c r="N298">
         <v>110.81626900000001</v>
       </c>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O298" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="P298" s="4">
+        <v>586166</v>
+      </c>
+      <c r="Q298" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R298" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1099</v>
       </c>
@@ -17312,8 +21980,20 @@
       <c r="N299">
         <v>123.63088999999999</v>
       </c>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O299" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="P299" s="4">
+        <v>443349</v>
+      </c>
+      <c r="Q299" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R299" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1102</v>
       </c>
@@ -17356,8 +22036,20 @@
       <c r="N300">
         <v>110.459352</v>
       </c>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O300" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="P300" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q300" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R300" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1105</v>
       </c>
@@ -17400,8 +22092,20 @@
       <c r="N301">
         <v>109.04513900000001</v>
       </c>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O301" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="P301" s="4">
+        <v>2049622</v>
+      </c>
+      <c r="Q301" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R301" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1109</v>
       </c>
@@ -17444,8 +22148,20 @@
       <c r="N302">
         <v>124.303524</v>
       </c>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O302" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="P302" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q302" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R302" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1112</v>
       </c>
@@ -17488,8 +22204,20 @@
       <c r="N303">
         <v>104.782999</v>
       </c>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O303" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="P303" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q303" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R303" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1115</v>
       </c>
@@ -17532,8 +22260,20 @@
       <c r="N304">
         <v>106.676568</v>
       </c>
-    </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O304" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="P304" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q304" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R304" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1118</v>
       </c>
@@ -17576,8 +22316,20 @@
       <c r="N305">
         <v>98.659222</v>
       </c>
-    </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O305" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="P305" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q305" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R305" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1121</v>
       </c>
@@ -17620,8 +22372,20 @@
       <c r="N306">
         <v>106.708175</v>
       </c>
-    </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O306" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="P306" s="4">
+        <v>1899515</v>
+      </c>
+      <c r="Q306" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R306" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1124</v>
       </c>
@@ -17664,8 +22428,20 @@
       <c r="N307">
         <v>106.688096</v>
       </c>
-    </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O307" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="P307" s="4">
+        <v>1899515</v>
+      </c>
+      <c r="Q307" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R307" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1127</v>
       </c>
@@ -17708,8 +22484,20 @@
       <c r="N308">
         <v>105.302295</v>
       </c>
-    </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O308" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="P308" s="4">
+        <v>1096935</v>
+      </c>
+      <c r="Q308" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R308" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1130</v>
       </c>
@@ -17752,8 +22540,20 @@
       <c r="N309">
         <v>107.6343</v>
       </c>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O309" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="P309" s="4">
+        <v>3723181</v>
+      </c>
+      <c r="Q309" t="s">
+        <v>1392</v>
+      </c>
+      <c r="R309" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1134</v>
       </c>
@@ -17796,8 +22596,20 @@
       <c r="N310">
         <v>119.62249</v>
       </c>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O310" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="P310" s="4">
+        <v>158599</v>
+      </c>
+      <c r="Q310" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R310" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>1138</v>
       </c>
@@ -17840,8 +22652,20 @@
       <c r="N311">
         <v>106.574645</v>
       </c>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O311" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="P311" s="4">
+        <v>1899515</v>
+      </c>
+      <c r="Q311" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R311" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1141</v>
       </c>
@@ -17884,8 +22708,20 @@
       <c r="N312">
         <v>101.402602</v>
       </c>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O312" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="P312" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q312" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R312" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1144</v>
       </c>
@@ -17928,8 +22764,20 @@
       <c r="N313">
         <v>110.924075</v>
       </c>
-    </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O313" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="P313" s="4">
+        <v>1074475</v>
+      </c>
+      <c r="Q313" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R313" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1148</v>
       </c>
@@ -17972,8 +22820,20 @@
       <c r="N314">
         <v>99.160880000000006</v>
       </c>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O314" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="P314" s="4">
+        <v>178524</v>
+      </c>
+      <c r="Q314" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R314" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1152</v>
       </c>
@@ -18016,8 +22876,20 @@
       <c r="N315">
         <v>117.58619299999999</v>
       </c>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O315" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="P315" s="4">
+        <v>246734</v>
+      </c>
+      <c r="Q315" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R315" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>1155</v>
       </c>
@@ -18060,8 +22932,20 @@
       <c r="N316">
         <v>106.968514</v>
       </c>
-    </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O316" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="P316" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q316" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R316" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>1158</v>
       </c>
@@ -18104,8 +22988,20 @@
       <c r="N317">
         <v>106.975098</v>
       </c>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O317" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="P317" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q317" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R317" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1161</v>
       </c>
@@ -18148,8 +23044,20 @@
       <c r="N318">
         <v>111.491871</v>
       </c>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O318" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="P318" s="4">
+        <v>436351</v>
+      </c>
+      <c r="Q318" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R318" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>1165</v>
       </c>
@@ -18192,8 +23100,20 @@
       <c r="N319">
         <v>116.519181</v>
       </c>
-    </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O319" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="P319" s="4">
+        <v>1404343</v>
+      </c>
+      <c r="Q319" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R319" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>1169</v>
       </c>
@@ -18236,8 +23156,20 @@
       <c r="N320">
         <v>107.897812</v>
       </c>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O320" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="P320" s="4">
+        <v>2770531</v>
+      </c>
+      <c r="Q320" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R320" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>1172</v>
       </c>
@@ -18280,8 +23212,20 @@
       <c r="N321">
         <v>99.628338999999997</v>
       </c>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O321" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="P321" s="4">
+        <v>792179</v>
+      </c>
+      <c r="Q321" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R321" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>1176</v>
       </c>
@@ -18324,8 +23268,20 @@
       <c r="N322">
         <v>107.445504</v>
       </c>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O322" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="P322" s="4">
+        <v>1029561</v>
+      </c>
+      <c r="Q322" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R322" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>1180</v>
       </c>
@@ -18368,8 +23324,20 @@
       <c r="N323">
         <v>106.74329400000001</v>
       </c>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O323" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="P323" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q323" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R323" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>1183</v>
       </c>
@@ -18412,8 +23380,20 @@
       <c r="N324">
         <v>115.08147200000001</v>
       </c>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O324" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="P324" s="4">
+        <v>830236</v>
+      </c>
+      <c r="Q324" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R324" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1188</v>
       </c>
@@ -18456,8 +23436,20 @@
       <c r="N325">
         <v>105.261799</v>
       </c>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O325" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="P325" s="4">
+        <v>1096935</v>
+      </c>
+      <c r="Q325" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R325" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>1191</v>
       </c>
@@ -18500,8 +23492,20 @@
       <c r="N326">
         <v>119.876328</v>
       </c>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O326" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="P326" s="4">
+        <v>382017</v>
+      </c>
+      <c r="Q326" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R326" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1194</v>
       </c>
@@ -18544,8 +23548,20 @@
       <c r="N327">
         <v>120.369246</v>
       </c>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O327" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="P327" s="4">
+        <v>377580</v>
+      </c>
+      <c r="Q327" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R327" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>1198</v>
       </c>
@@ -18588,8 +23604,20 @@
       <c r="N328">
         <v>114.37392699999999</v>
       </c>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O328" s="3" t="s">
+        <v>1600</v>
+      </c>
+      <c r="P328" s="4">
+        <v>1769233</v>
+      </c>
+      <c r="Q328" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R328" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>1202</v>
       </c>
@@ -18632,8 +23660,20 @@
       <c r="N329">
         <v>108.747607</v>
       </c>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O329" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="P329" s="4">
+        <v>348911</v>
+      </c>
+      <c r="Q329" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R329" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>1205</v>
       </c>
@@ -18676,8 +23716,20 @@
       <c r="N330">
         <v>106.150015</v>
       </c>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O330" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="P330" s="4">
+        <v>232915</v>
+      </c>
+      <c r="Q330" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R330" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>1210</v>
       </c>
@@ -18720,8 +23772,20 @@
       <c r="N331">
         <v>107.145921</v>
       </c>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O331" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="P331" s="4">
+        <v>2516417</v>
+      </c>
+      <c r="Q331" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R331" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>1213</v>
       </c>
@@ -18764,8 +23828,20 @@
       <c r="N332">
         <v>120.193006</v>
       </c>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O332" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="P332" s="4">
+        <v>184296</v>
+      </c>
+      <c r="Q332" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R332" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1217</v>
       </c>
@@ -18808,8 +23884,20 @@
       <c r="N333">
         <v>107.918882</v>
       </c>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O333" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="P333" s="4">
+        <v>1197301</v>
+      </c>
+      <c r="Q333" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R333" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1221</v>
       </c>
@@ -18852,8 +23940,20 @@
       <c r="N334">
         <v>98.741460000000004</v>
       </c>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O334" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="P334" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q334" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R334" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1224</v>
       </c>
@@ -18896,8 +23996,20 @@
       <c r="N335">
         <v>98.449181999999993</v>
       </c>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O335" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="P335" s="4">
+        <v>1098660</v>
+      </c>
+      <c r="Q335" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R335" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1228</v>
       </c>
@@ -18940,8 +24052,20 @@
       <c r="N336">
         <v>107.55388499999999</v>
       </c>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O336" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P336" s="4">
+        <v>570829</v>
+      </c>
+      <c r="Q336" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R336" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1231</v>
       </c>
@@ -18984,8 +24108,20 @@
       <c r="N337">
         <v>106.828756</v>
       </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O337" s="3" t="s">
+        <v>1609</v>
+      </c>
+      <c r="P337" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q337" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R337" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1234</v>
       </c>
@@ -19028,8 +24164,20 @@
       <c r="N338">
         <v>99.838648000000006</v>
       </c>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O338" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="P338" s="4">
+        <v>506673</v>
+      </c>
+      <c r="Q338" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R338" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1238</v>
       </c>
@@ -19072,8 +24220,20 @@
       <c r="N339">
         <v>98.650711999999999</v>
       </c>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O339" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="P339" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q339" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R339" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="340" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1241</v>
       </c>
@@ -19116,8 +24276,20 @@
       <c r="N340">
         <v>119.888642</v>
       </c>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O340" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="P340" s="4">
+        <v>240664</v>
+      </c>
+      <c r="Q340" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R340" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1245</v>
       </c>
@@ -19160,8 +24332,20 @@
       <c r="N341">
         <v>107.569948</v>
       </c>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O341" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="P341" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q341" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R341" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="342" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1248</v>
       </c>
@@ -19204,8 +24388,20 @@
       <c r="N342">
         <v>117.15514</v>
       </c>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O342" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="P342" s="4">
+        <v>856361</v>
+      </c>
+      <c r="Q342" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R342" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="343" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>0</v>
       </c>
@@ -19248,9 +24444,21 @@
       <c r="N343">
         <v>124.92305279999999</v>
       </c>
+      <c r="O343" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="P343" s="4">
+        <v>478194</v>
+      </c>
+      <c r="Q343" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R343" t="s">
+        <v>1316</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N343" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/stores_complete.xlsx
+++ b/output/stores_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2B4802-FCF3-4FF3-8512-A20BE0989BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E338D9AD-760A-43FD-8493-9CA32B75B941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4335" uniqueCount="1616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4333" uniqueCount="1615">
   <si>
     <t>Store ID</t>
   </si>
@@ -3668,15 +3668,6 @@
     <t>KOTA PANGKAL PINANG</t>
   </si>
   <si>
-    <t>SQID00407</t>
-  </si>
-  <si>
-    <t>Xiaomi Authorized Store Av. Dr Muwardi Cianjur Indonesia</t>
-  </si>
-  <si>
-    <t>Jl. Dr. Muwardi No.37, Muka, Kec. Cianjur, Kabupaten Cianjur, Jawa Barat 43215</t>
-  </si>
-  <si>
     <t>SQID00415</t>
   </si>
   <si>
@@ -4847,9 +4838,6 @@
     <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Semabung%20Pangkal%20Pinang%20Indonesia%20Jl.%20Depati%20Hamzah%20No.88%2C%20Semabung%20Baru%2C%20Kec.%20Girimaya%2C%20Kota%20Pangkal%20Pinang%2C%20Kepulauan%20Bangka%20Belitung%2033684</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Dr%20Muwardi%20Cianjur%20Indonesia%20Jl.%20Dr.%20Muwardi%20No.37%2C%20Muka%2C%20Kec.%20Cianjur%2C%20Kabupaten%20Cianjur%2C%20Jawa%20Barat%2043215</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Manennungeng%20Palopo%20Indonesia%20Jl.%20Manennungeng%2C%20Batupasi%2C%20Kec.%20Wara%20Utara%2C%20Kota%20Palopo%2C%20Sulawesi%20Selatan%2091913</t>
   </si>
   <si>
@@ -4884,16 +4872,26 @@
   </si>
   <si>
     <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Paniki%20Manado%20Indonesia%20Jl.%20A.A.%20Maramis%20No.141%2C%20Paniki%20Bawah%2C%20Kec.%20Mapanget%2C%20Kota%20Manado%2C%20Sulawesi%20Utara%2095370</t>
+  </si>
+  <si>
+    <t>Xiaomi Authorized Store Av. Gajah Mada Jempong Mataram Indonesia</t>
+  </si>
+  <si>
+    <t>Jl. Gajah Mada No. 100, Jempong Baru, Kec. Sekarbela, Kota Mataram, Nusa Tenggara Barat 83116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Gajah%20Mada%20Jempong%20Mataram%20Indonesia%20Jl.%20Gajah%20Mada%20No.%20100%2C%20Jempong%20Baru%2C%20Kec.%20Sekarbela%2C%20Kota%20Mataram%2C%20Nusa%20Tenggara%20Barat%2083116</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -4938,7 +4936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4946,6 +4944,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -5255,6 +5255,8 @@
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5287,7 +5289,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -5302,16 +5304,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="R1" t="s">
         <v>1259</v>
-      </c>
-      <c r="P1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="R1" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -5343,7 +5345,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K2">
         <v>137</v>
@@ -5358,16 +5360,16 @@
         <v>106.90817</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="P2" s="4">
         <v>1876057</v>
       </c>
       <c r="Q2" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R2" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -5399,7 +5401,7 @@
         <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K3">
         <v>84</v>
@@ -5414,16 +5416,16 @@
         <v>107.001076</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="P3" s="4">
         <v>2496198</v>
       </c>
       <c r="Q3" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R3" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -5455,7 +5457,7 @@
         <v>21</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K4">
         <v>88</v>
@@ -5470,16 +5472,16 @@
         <v>106.82447999999999</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="P4" s="4">
         <v>5495373</v>
       </c>
       <c r="Q4" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R4" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -5511,7 +5513,7 @@
         <v>21</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K5">
         <v>103</v>
@@ -5526,16 +5528,16 @@
         <v>106.791349</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="P5" s="4">
         <v>2615945</v>
       </c>
       <c r="Q5" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R5" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -5567,7 +5569,7 @@
         <v>21</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K6">
         <v>86</v>
@@ -5582,16 +5584,16 @@
         <v>106.630724</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="P6" s="4">
         <v>3286420</v>
       </c>
       <c r="Q6" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R6" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -5623,7 +5625,7 @@
         <v>21</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K7">
         <v>75</v>
@@ -5638,16 +5640,16 @@
         <v>106.821789</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="P7" s="4">
         <v>1109489</v>
       </c>
       <c r="Q7" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R7" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -5679,7 +5681,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K8">
         <v>188</v>
@@ -5694,16 +5696,16 @@
         <v>107.608763</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="P8" s="4">
         <v>2555187</v>
       </c>
       <c r="Q8" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R8" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -5735,7 +5737,7 @@
         <v>21</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K9">
         <v>162</v>
@@ -5750,16 +5752,16 @@
         <v>106.80481</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="P9" s="4">
         <v>1122771</v>
       </c>
       <c r="Q9" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R9" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -5791,7 +5793,7 @@
         <v>21</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -5806,16 +5808,16 @@
         <v>112.67453399999999</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="P10" s="4">
         <v>3000075</v>
       </c>
       <c r="Q10" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R10" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -5847,7 +5849,7 @@
         <v>21</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K11">
         <v>76</v>
@@ -5862,16 +5864,16 @@
         <v>119.441374</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="P11" s="4">
         <v>1470262</v>
       </c>
       <c r="Q11" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R11" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -5903,7 +5905,7 @@
         <v>21</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K12">
         <v>62</v>
@@ -5918,16 +5920,16 @@
         <v>112.738867</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="P12" s="4">
         <v>3000075</v>
       </c>
       <c r="Q12" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R12" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -5959,7 +5961,7 @@
         <v>21</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K13">
         <v>63</v>
@@ -5974,16 +5976,16 @@
         <v>110.392461</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="P13" s="4">
         <v>1105415</v>
       </c>
       <c r="Q13" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R13" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -6015,7 +6017,7 @@
         <v>21</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K14">
         <v>53</v>
@@ -6030,16 +6032,16 @@
         <v>106.82740099999999</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="P14" s="4">
         <v>1927869</v>
       </c>
       <c r="Q14" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R14" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -6071,7 +6073,7 @@
         <v>21</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K15">
         <v>135</v>
@@ -6086,16 +6088,16 @@
         <v>106.72765</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="P15" s="4">
         <v>1404786</v>
       </c>
       <c r="Q15" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R15" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -6127,7 +6129,7 @@
         <v>21</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K16">
         <v>99</v>
@@ -6142,16 +6144,16 @@
         <v>106.79073</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="P16" s="4">
         <v>1876057</v>
       </c>
       <c r="Q16" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R16" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -6183,7 +6185,7 @@
         <v>21</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K17">
         <v>104</v>
@@ -6198,16 +6200,16 @@
         <v>106.783115</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="P17" s="4">
         <v>2408480</v>
       </c>
       <c r="Q17" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R17" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -6239,7 +6241,7 @@
         <v>21</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K18">
         <v>72</v>
@@ -6254,16 +6256,16 @@
         <v>106.73880699999999</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="P18" s="4">
         <v>2615945</v>
       </c>
       <c r="Q18" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R18" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -6295,7 +6297,7 @@
         <v>21</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K19">
         <v>64</v>
@@ -6310,16 +6312,16 @@
         <v>119.417417</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="P19" s="4">
         <v>1470262</v>
       </c>
       <c r="Q19" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R19" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -6351,7 +6353,7 @@
         <v>21</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K20">
         <v>95</v>
@@ -6366,16 +6368,16 @@
         <v>107.13300099999999</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="P20" s="4">
         <v>3172831</v>
       </c>
       <c r="Q20" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R20" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -6407,7 +6409,7 @@
         <v>21</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K21">
         <v>115</v>
@@ -6422,16 +6424,16 @@
         <v>112.77826899999999</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="P21" s="4">
         <v>3000075</v>
       </c>
       <c r="Q21" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R21" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -6463,7 +6465,7 @@
         <v>21</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -6478,16 +6480,16 @@
         <v>112.62235699999999</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="P22" s="4">
         <v>874660</v>
       </c>
       <c r="Q22" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R22" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -6519,7 +6521,7 @@
         <v>21</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K23">
         <v>51</v>
@@ -6534,16 +6536,16 @@
         <v>124.835188</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="P23" s="4">
         <v>478194</v>
       </c>
       <c r="Q23" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R23" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -6575,7 +6577,7 @@
         <v>21</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K24">
         <v>118</v>
@@ -6590,16 +6592,16 @@
         <v>107.591256</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="P24" s="4">
         <v>2555187</v>
       </c>
       <c r="Q24" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R24" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -6631,7 +6633,7 @@
         <v>21</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K25">
         <v>115</v>
@@ -6646,16 +6648,16 @@
         <v>98.674274999999994</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="P25" s="4">
         <v>2530492</v>
       </c>
       <c r="Q25" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R25" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -6687,7 +6689,7 @@
         <v>21</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K26">
         <v>82</v>
@@ -6702,16 +6704,16 @@
         <v>107.636404</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="P26" s="4">
         <v>2555187</v>
       </c>
       <c r="Q26" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R26" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -6743,7 +6745,7 @@
         <v>21</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K27">
         <v>116</v>
@@ -6758,16 +6760,16 @@
         <v>106.73313899999999</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="P27" s="4">
         <v>2615945</v>
       </c>
       <c r="Q27" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R27" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -6799,7 +6801,7 @@
         <v>21</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K28">
         <v>122</v>
@@ -6814,16 +6816,16 @@
         <v>106.979793</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="P28" s="4">
         <v>5495373</v>
       </c>
       <c r="Q28" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R28" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -6855,7 +6857,7 @@
         <v>21</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K29">
         <v>62</v>
@@ -6870,16 +6872,16 @@
         <v>117.115939</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="P29" s="4">
         <v>856361</v>
       </c>
       <c r="Q29" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R29" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -6911,7 +6913,7 @@
         <v>21</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K30">
         <v>101</v>
@@ -6926,16 +6928,16 @@
         <v>98.672222000000005</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="P30" s="4">
         <v>2530492</v>
       </c>
       <c r="Q30" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R30" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -6967,7 +6969,7 @@
         <v>21</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K31">
         <v>128</v>
@@ -6982,16 +6984,16 @@
         <v>106.64401700000001</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="P31" s="4">
         <v>3286420</v>
       </c>
       <c r="Q31" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R31" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -7023,7 +7025,7 @@
         <v>21</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K32">
         <v>45</v>
@@ -7038,16 +7040,16 @@
         <v>110.423447</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="P32" s="4">
         <v>1693034</v>
       </c>
       <c r="Q32" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R32" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
@@ -7079,7 +7081,7 @@
         <v>21</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K33">
         <v>125</v>
@@ -7094,16 +7096,16 @@
         <v>124.837932</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="P33" s="4">
         <v>478194</v>
       </c>
       <c r="Q33" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R33" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
@@ -7135,7 +7137,7 @@
         <v>21</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K34">
         <v>107</v>
@@ -7150,16 +7152,16 @@
         <v>107.27939499999999</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="P34" s="4">
         <v>2519882</v>
       </c>
       <c r="Q34" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R34" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
@@ -7191,7 +7193,7 @@
         <v>21</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K35">
         <v>48</v>
@@ -7206,16 +7208,16 @@
         <v>106.89216500000001</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="P35" s="4">
         <v>1876057</v>
       </c>
       <c r="Q35" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R35" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
@@ -7247,7 +7249,7 @@
         <v>21</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K36">
         <v>107</v>
@@ -7262,16 +7264,16 @@
         <v>110.39756800000001</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="P36" s="4">
         <v>1105415</v>
       </c>
       <c r="Q36" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R36" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
@@ -7303,7 +7305,7 @@
         <v>21</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K37">
         <v>76</v>
@@ -7318,16 +7320,16 @@
         <v>106.901945</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="P37" s="4">
         <v>1927869</v>
       </c>
       <c r="Q37" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R37" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
@@ -7359,7 +7361,7 @@
         <v>21</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -7374,16 +7376,16 @@
         <v>106.0642</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="P38" s="4">
         <v>464716</v>
       </c>
       <c r="Q38" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R38" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
@@ -7415,7 +7417,7 @@
         <v>21</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K39">
         <v>130</v>
@@ -7430,16 +7432,16 @@
         <v>108.552183</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="P39" s="4">
         <v>348911</v>
       </c>
       <c r="Q39" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R39" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
@@ -7471,7 +7473,7 @@
         <v>21</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K40">
         <v>64</v>
@@ -7486,16 +7488,16 @@
         <v>106.900447</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="P40" s="4">
         <v>3310145</v>
       </c>
       <c r="Q40" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R40" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
@@ -7527,7 +7529,7 @@
         <v>21</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K41">
         <v>69</v>
@@ -7542,16 +7544,16 @@
         <v>116.10522</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="P41" s="4">
         <v>452812</v>
       </c>
       <c r="Q41" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R41" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
@@ -7583,7 +7585,7 @@
         <v>21</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K42">
         <v>49</v>
@@ -7598,16 +7600,16 @@
         <v>110.41570900000001</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="P42" s="4">
         <v>1693034</v>
       </c>
       <c r="Q42" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R42" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
@@ -7639,7 +7641,7 @@
         <v>21</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K43">
         <v>79</v>
@@ -7654,16 +7656,16 @@
         <v>106.653631</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="P43" s="4">
         <v>1404786</v>
       </c>
       <c r="Q43" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R43" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
@@ -7695,7 +7697,7 @@
         <v>21</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K44">
         <v>87</v>
@@ -7707,16 +7709,16 @@
         <v>106.869567</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="P44" s="4">
         <v>3310145</v>
       </c>
       <c r="Q44" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R44" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
@@ -7748,7 +7750,7 @@
         <v>21</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K45">
         <v>95</v>
@@ -7763,16 +7765,16 @@
         <v>115.21697</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="P45" s="4">
         <v>660984</v>
       </c>
       <c r="Q45" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R45" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
@@ -7804,7 +7806,7 @@
         <v>21</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K46">
         <v>64</v>
@@ -7819,16 +7821,16 @@
         <v>110.41233699999999</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="P46" s="4">
         <v>1693034</v>
       </c>
       <c r="Q46" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R46" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
@@ -7860,7 +7862,7 @@
         <v>21</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K47">
         <v>93</v>
@@ -7875,16 +7877,16 @@
         <v>106.74499400000001</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="P47" s="4">
         <v>1927869</v>
       </c>
       <c r="Q47" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R47" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
@@ -7916,7 +7918,7 @@
         <v>21</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K48">
         <v>129</v>
@@ -7931,16 +7933,16 @@
         <v>109.345662</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="P48" s="4">
         <v>676096</v>
       </c>
       <c r="Q48" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R48" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -7972,7 +7974,7 @@
         <v>21</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K49">
         <v>68</v>
@@ -7987,16 +7989,16 @@
         <v>104.741816</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="P49" s="4">
         <v>1761461</v>
       </c>
       <c r="Q49" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R49" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
@@ -8028,7 +8030,7 @@
         <v>21</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K50">
         <v>106</v>
@@ -8043,16 +8045,16 @@
         <v>115.230413</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="P50" s="4">
         <v>660984</v>
       </c>
       <c r="Q50" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R50" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
@@ -8084,7 +8086,7 @@
         <v>21</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K51">
         <v>82</v>
@@ -8099,16 +8101,16 @@
         <v>112.734624</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="P51" s="4">
         <v>3000075</v>
       </c>
       <c r="Q51" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R51" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
@@ -8140,7 +8142,7 @@
         <v>21</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K52">
         <v>78</v>
@@ -8155,16 +8157,16 @@
         <v>109.23649500000001</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="P52" s="4">
         <v>1849956</v>
       </c>
       <c r="Q52" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R52" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
@@ -8196,7 +8198,7 @@
         <v>21</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K53">
         <v>96</v>
@@ -8211,16 +8213,16 @@
         <v>107.69852</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="P53" s="4">
         <v>2555187</v>
       </c>
       <c r="Q53" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R53" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
@@ -8252,7 +8254,7 @@
         <v>21</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K54">
         <v>72</v>
@@ -8267,16 +8269,16 @@
         <v>106.18141300000001</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="P54" s="4">
         <v>730530</v>
       </c>
       <c r="Q54" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R54" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
@@ -8308,7 +8310,7 @@
         <v>21</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K55">
         <v>92</v>
@@ -8323,16 +8325,16 @@
         <v>110.809951</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="P55" s="4">
         <v>586166</v>
       </c>
       <c r="Q55" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R55" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
@@ -8364,7 +8366,7 @@
         <v>21</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K56">
         <v>60</v>
@@ -8379,16 +8381,16 @@
         <v>106.82659</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="P56" s="4">
         <v>2408480</v>
       </c>
       <c r="Q56" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R56" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
@@ -8420,7 +8422,7 @@
         <v>21</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K57">
         <v>70</v>
@@ -8435,16 +8437,16 @@
         <v>114.600335</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="P57" s="4">
         <v>675916</v>
       </c>
       <c r="Q57" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R57" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
@@ -8476,7 +8478,7 @@
         <v>21</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K58">
         <v>140</v>
@@ -8491,16 +8493,16 @@
         <v>107.610801</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="P58" s="4">
         <v>2555187</v>
       </c>
       <c r="Q58" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R58" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
@@ -8532,7 +8534,7 @@
         <v>21</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K59">
         <v>73</v>
@@ -8547,16 +8549,16 @@
         <v>108.55003499999999</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="P59" s="4">
         <v>348911</v>
       </c>
       <c r="Q59" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R59" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
@@ -8588,7 +8590,7 @@
         <v>21</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K60">
         <v>90</v>
@@ -8603,16 +8605,16 @@
         <v>106.52486500000001</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="P60" s="4">
         <v>3286420</v>
       </c>
       <c r="Q60" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R60" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
@@ -8644,7 +8646,7 @@
         <v>21</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K61">
         <v>76</v>
@@ -8659,16 +8661,16 @@
         <v>106.839957</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="P61" s="4">
         <v>2408480</v>
       </c>
       <c r="Q61" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R61" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
@@ -8700,7 +8702,7 @@
         <v>21</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K62">
         <v>93</v>
@@ -8715,16 +8717,16 @@
         <v>110.362371</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="P62" s="4">
         <v>1105415</v>
       </c>
       <c r="Q62" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R62" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
@@ -8756,7 +8758,7 @@
         <v>21</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K63">
         <v>133</v>
@@ -8771,16 +8773,16 @@
         <v>106.74262899999999</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="P63" s="4">
         <v>1404786</v>
       </c>
       <c r="Q63" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R63" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
@@ -8812,7 +8814,7 @@
         <v>21</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K64">
         <v>90</v>
@@ -8827,16 +8829,16 @@
         <v>105.253226</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="P64" s="4">
         <v>1096935</v>
       </c>
       <c r="Q64" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R64" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
@@ -8868,7 +8870,7 @@
         <v>21</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K65">
         <v>99</v>
@@ -8883,16 +8885,16 @@
         <v>95.306488999999999</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="P65" s="4">
         <v>257315</v>
       </c>
       <c r="Q65" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R65" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
@@ -8924,7 +8926,7 @@
         <v>21</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K66">
         <v>64</v>
@@ -8939,16 +8941,16 @@
         <v>101.41777</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="P66" s="4">
         <v>1116142</v>
       </c>
       <c r="Q66" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R66" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
@@ -8980,7 +8982,7 @@
         <v>21</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -8995,16 +8997,16 @@
         <v>106.792402</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="P67" s="4">
         <v>2615945</v>
       </c>
       <c r="Q67" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R67" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.3">
@@ -9036,7 +9038,7 @@
         <v>21</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K68">
         <v>89</v>
@@ -9051,16 +9053,16 @@
         <v>110.224767</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="P68" s="4">
         <v>1324756</v>
       </c>
       <c r="Q68" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R68" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.3">
@@ -9092,7 +9094,7 @@
         <v>21</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K69">
         <v>80</v>
@@ -9107,16 +9109,16 @@
         <v>100.35557900000001</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="P69" s="4">
         <v>928539</v>
       </c>
       <c r="Q69" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R69" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.3">
@@ -9148,7 +9150,7 @@
         <v>21</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K70">
         <v>69</v>
@@ -9163,16 +9165,16 @@
         <v>112.01577899999999</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="P70" s="4">
         <v>296792</v>
       </c>
       <c r="Q70" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R70" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.3">
@@ -9204,7 +9206,7 @@
         <v>21</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K71">
         <v>66</v>
@@ -9219,16 +9221,16 @@
         <v>108.21763300000001</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="P71" s="4">
         <v>752545</v>
       </c>
       <c r="Q71" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R71" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
@@ -9260,7 +9262,7 @@
         <v>21</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -9275,16 +9277,16 @@
         <v>112.69844399999999</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="P72" s="4">
         <v>1982939</v>
       </c>
       <c r="Q72" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R72" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.3">
@@ -9316,7 +9318,7 @@
         <v>21</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K73">
         <v>92</v>
@@ -9331,16 +9333,16 @@
         <v>116.858486</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="P73" s="4">
         <v>733397</v>
       </c>
       <c r="Q73" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R73" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
@@ -9372,7 +9374,7 @@
         <v>21</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K74">
         <v>66</v>
@@ -9387,16 +9389,16 @@
         <v>115.182802</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="P74" s="4">
         <v>660984</v>
       </c>
       <c r="Q74" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R74" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
@@ -9428,7 +9430,7 @@
         <v>21</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K75">
         <v>64</v>
@@ -9443,16 +9445,16 @@
         <v>113.66279</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="P75" s="4">
         <v>2590289</v>
       </c>
       <c r="Q75" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R75" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
@@ -9484,7 +9486,7 @@
         <v>21</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K76">
         <v>70</v>
@@ -9499,16 +9501,16 @@
         <v>106.84590300000001</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="P76" s="4">
         <v>5495373</v>
       </c>
       <c r="Q76" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R76" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
@@ -9540,7 +9542,7 @@
         <v>21</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K77">
         <v>80</v>
@@ -9555,16 +9557,16 @@
         <v>106.9717</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="P77" s="4">
         <v>2496198</v>
       </c>
       <c r="Q77" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R77" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
@@ -9596,7 +9598,7 @@
         <v>21</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K78">
         <v>46</v>
@@ -9611,16 +9613,16 @@
         <v>107.292214</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="P78" s="4">
         <v>2519882</v>
       </c>
       <c r="Q78" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R78" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
@@ -9652,7 +9654,7 @@
         <v>21</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K79">
         <v>101</v>
@@ -9667,16 +9669,16 @@
         <v>106.82342</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="P79" s="4">
         <v>2408480</v>
       </c>
       <c r="Q79" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R79" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
@@ -9708,7 +9710,7 @@
         <v>21</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K80">
         <v>150</v>
@@ -9723,16 +9725,16 @@
         <v>112.601688</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="P80" s="4">
         <v>1296688</v>
       </c>
       <c r="Q80" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R80" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
@@ -9764,7 +9766,7 @@
         <v>21</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K81">
         <v>51</v>
@@ -9779,16 +9781,16 @@
         <v>107.586242</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="P81" s="4">
         <v>2555187</v>
       </c>
       <c r="Q81" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R81" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
@@ -9820,7 +9822,7 @@
         <v>21</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K82">
         <v>72</v>
@@ -9835,16 +9837,16 @@
         <v>102.267369</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="P82" s="4">
         <v>385511</v>
       </c>
       <c r="Q82" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R82" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
@@ -9876,7 +9878,7 @@
         <v>21</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K83">
         <v>84</v>
@@ -9891,16 +9893,16 @@
         <v>128.198103</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="P83" s="4">
         <v>354052</v>
       </c>
       <c r="Q83" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R83" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
@@ -9932,7 +9934,7 @@
         <v>21</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K84">
         <v>60</v>
@@ -9947,16 +9949,16 @@
         <v>119.554146</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="P84" s="4">
         <v>394615</v>
       </c>
       <c r="Q84" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R84" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
@@ -9988,7 +9990,7 @@
         <v>21</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K85">
         <v>57</v>
@@ -10003,16 +10005,16 @@
         <v>106.88909200000001</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="P85" s="4">
         <v>3310145</v>
       </c>
       <c r="Q85" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R85" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
@@ -10044,7 +10046,7 @@
         <v>21</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K86">
         <v>66</v>
@@ -10059,16 +10061,16 @@
         <v>110.432253</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="P86" s="4">
         <v>1693034</v>
       </c>
       <c r="Q86" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R86" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
@@ -10100,7 +10102,7 @@
         <v>21</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K87">
         <v>67</v>
@@ -10115,16 +10117,16 @@
         <v>106.818022</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="P87" s="4">
         <v>1109489</v>
       </c>
       <c r="Q87" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R87" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
@@ -10156,7 +10158,7 @@
         <v>21</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K88">
         <v>83</v>
@@ -10171,16 +10173,16 @@
         <v>104.79156399999999</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="P88" s="4">
         <v>844108</v>
       </c>
       <c r="Q88" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R88" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
@@ -10212,7 +10214,7 @@
         <v>21</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K89">
         <v>63</v>
@@ -10227,16 +10229,16 @@
         <v>117.154967</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="P89" s="4">
         <v>856361</v>
       </c>
       <c r="Q89" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R89" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.3">
@@ -10268,7 +10270,7 @@
         <v>21</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K90">
         <v>118</v>
@@ -10283,16 +10285,16 @@
         <v>106.982479</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="P90" s="4">
         <v>2496198</v>
       </c>
       <c r="Q90" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R90" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
@@ -10324,7 +10326,7 @@
         <v>21</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K91">
         <v>118</v>
@@ -10339,16 +10341,16 @@
         <v>98.626718999999994</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
       <c r="P91" s="4">
         <v>2530492</v>
       </c>
       <c r="Q91" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R91" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
@@ -10380,7 +10382,7 @@
         <v>21</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K92">
         <v>100</v>
@@ -10395,16 +10397,16 @@
         <v>98.663635999999997</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="P92" s="4">
         <v>2530492</v>
       </c>
       <c r="Q92" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R92" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.3">
@@ -10436,7 +10438,7 @@
         <v>21</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K93">
         <v>112</v>
@@ -10451,16 +10453,16 @@
         <v>106.993112</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="P93" s="4">
         <v>2496198</v>
       </c>
       <c r="Q93" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R93" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
@@ -10492,7 +10494,7 @@
         <v>21</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K94">
         <v>40</v>
@@ -10507,16 +10509,16 @@
         <v>112.443512</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="P94" s="4">
         <v>141335</v>
       </c>
       <c r="Q94" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R94" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
@@ -10548,7 +10550,7 @@
         <v>21</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K95">
         <v>124</v>
@@ -10563,16 +10565,16 @@
         <v>106.989428</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="P95" s="4">
         <v>2496198</v>
       </c>
       <c r="Q95" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R95" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
@@ -10604,7 +10606,7 @@
         <v>21</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K96">
         <v>104</v>
@@ -10619,16 +10621,16 @@
         <v>107.13134599999999</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="P96" s="4">
         <v>2516417</v>
       </c>
       <c r="Q96" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R96" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
@@ -10660,7 +10662,7 @@
         <v>21</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K97">
         <v>70</v>
@@ -10675,16 +10677,16 @@
         <v>110.816699</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="P97" s="4">
         <v>908228</v>
       </c>
       <c r="Q97" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R97" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.3">
@@ -10716,7 +10718,7 @@
         <v>21</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K98">
         <v>69</v>
@@ -10731,16 +10733,16 @@
         <v>112.749994</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="P98" s="4">
         <v>3000075</v>
       </c>
       <c r="Q98" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R98" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.3">
@@ -10772,7 +10774,7 @@
         <v>21</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K99">
         <v>58</v>
@@ -10787,16 +10789,16 @@
         <v>119.450033</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="P99" s="4">
         <v>1470262</v>
       </c>
       <c r="Q99" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R99" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.3">
@@ -10828,7 +10830,7 @@
         <v>21</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K100">
         <v>89</v>
@@ -10843,16 +10845,16 @@
         <v>112.72849100000001</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="P100" s="4">
         <v>3000075</v>
       </c>
       <c r="Q100" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R100" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.3">
@@ -10884,7 +10886,7 @@
         <v>21</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K101">
         <v>80</v>
@@ -10899,16 +10901,16 @@
         <v>115.18433899999999</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="P101" s="4">
         <v>526029</v>
       </c>
       <c r="Q101" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R101" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.3">
@@ -10940,7 +10942,7 @@
         <v>21</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K102">
         <v>60</v>
@@ -10955,16 +10957,16 @@
         <v>112.616159</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="P102" s="4">
         <v>1296688</v>
       </c>
       <c r="Q102" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R102" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.3">
@@ -10996,7 +10998,7 @@
         <v>21</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K103">
         <v>80</v>
@@ -11011,16 +11013,16 @@
         <v>114.84831</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="P103" s="4">
         <v>270346</v>
       </c>
       <c r="Q103" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R103" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.3">
@@ -11052,7 +11054,7 @@
         <v>21</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K104">
         <v>102</v>
@@ -11067,16 +11069,16 @@
         <v>104.738058</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="P104" s="4">
         <v>1761461</v>
       </c>
       <c r="Q104" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R104" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.3">
@@ -11108,7 +11110,7 @@
         <v>21</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K105">
         <v>60</v>
@@ -11123,16 +11125,16 @@
         <v>104.76113599999999</v>
       </c>
       <c r="O105" s="3" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="P105" s="4">
         <v>1761461</v>
       </c>
       <c r="Q105" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R105" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.3">
@@ -11164,7 +11166,7 @@
         <v>21</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K106">
         <v>62</v>
@@ -11179,16 +11181,16 @@
         <v>122.524231</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="P106" s="4">
         <v>347380</v>
       </c>
       <c r="Q106" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R106" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.3">
@@ -11220,7 +11222,7 @@
         <v>21</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K107">
         <v>120</v>
@@ -11235,16 +11237,16 @@
         <v>112.81139400000001</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="P107" s="4">
         <v>3000075</v>
       </c>
       <c r="Q107" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R107" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.3">
@@ -11276,7 +11278,7 @@
         <v>21</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K108">
         <v>77</v>
@@ -11291,16 +11293,16 @@
         <v>122.512057</v>
       </c>
       <c r="O108" s="3" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="P108" s="4">
         <v>347380</v>
       </c>
       <c r="Q108" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R108" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.3">
@@ -11332,7 +11334,7 @@
         <v>21</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K109">
         <v>80</v>
@@ -11347,16 +11349,16 @@
         <v>112.74863499999999</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="P109" s="4">
         <v>3000075</v>
       </c>
       <c r="Q109" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R109" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.3">
@@ -11388,7 +11390,7 @@
         <v>21</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="K110">
         <v>88</v>
@@ -11403,16 +11405,16 @@
         <v>106.874185</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="P110" s="4">
         <v>1109489</v>
       </c>
       <c r="Q110" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R110" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.3">
@@ -11444,7 +11446,7 @@
         <v>21</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K111">
         <v>80</v>
@@ -11459,16 +11461,16 @@
         <v>106.79934799999999</v>
       </c>
       <c r="O111" s="3" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="P111" s="4">
         <v>1122771</v>
       </c>
       <c r="Q111" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R111" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.3">
@@ -11500,7 +11502,7 @@
         <v>21</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K112">
         <v>59</v>
@@ -11515,16 +11517,16 @@
         <v>98.644181000000003</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="P112" s="4">
         <v>2530492</v>
       </c>
       <c r="Q112" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R112" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.3">
@@ -11556,7 +11558,7 @@
         <v>21</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K113">
         <v>60</v>
@@ -11571,16 +11573,16 @@
         <v>106.911119</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P113" s="4">
         <v>2496198</v>
       </c>
       <c r="Q113" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R113" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.3">
@@ -11612,7 +11614,7 @@
         <v>21</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K114">
         <v>80</v>
@@ -11627,16 +11629,16 @@
         <v>106.72872099999999</v>
       </c>
       <c r="O114" s="3" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="P114" s="4">
         <v>2615945</v>
       </c>
       <c r="Q114" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R114" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.3">
@@ -11668,7 +11670,7 @@
         <v>21</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="K115">
         <v>69</v>
@@ -11683,16 +11685,16 @@
         <v>106.817064</v>
       </c>
       <c r="O115" s="3" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="P115" s="4">
         <v>1122771</v>
       </c>
       <c r="Q115" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R115" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.3">
@@ -11724,7 +11726,7 @@
         <v>21</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="K116">
         <v>68</v>
@@ -11739,16 +11741,16 @@
         <v>124.837932</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P116" s="4">
         <v>478194</v>
       </c>
       <c r="Q116" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R116" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.3">
@@ -11780,7 +11782,7 @@
         <v>21</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K117">
         <v>86</v>
@@ -11795,16 +11797,16 @@
         <v>106.606495</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P117" s="4">
         <v>3286420</v>
       </c>
       <c r="Q117" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R117" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.3">
@@ -11836,7 +11838,7 @@
         <v>21</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="K118">
         <v>98</v>
@@ -11851,16 +11853,16 @@
         <v>106.843892</v>
       </c>
       <c r="O118" s="3" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="P118" s="4">
         <v>1109489</v>
       </c>
       <c r="Q118" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R118" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.3">
@@ -11892,7 +11894,7 @@
         <v>21</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K119">
         <v>117</v>
@@ -11907,16 +11909,16 @@
         <v>106.634049</v>
       </c>
       <c r="O119" s="3" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="P119" s="4">
         <v>1899515</v>
       </c>
       <c r="Q119" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R119" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.3">
@@ -11948,7 +11950,7 @@
         <v>21</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K120">
         <v>71</v>
@@ -11963,16 +11965,16 @@
         <v>112.74751999999999</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P120" s="4">
         <v>3000075</v>
       </c>
       <c r="Q120" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R120" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.3">
@@ -12004,7 +12006,7 @@
         <v>21</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="K121">
         <v>80</v>
@@ -12019,16 +12021,16 @@
         <v>106.69411700000001</v>
       </c>
       <c r="O121" s="3" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="P121" s="4">
         <v>2615945</v>
       </c>
       <c r="Q121" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R121" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.3">
@@ -12060,7 +12062,7 @@
         <v>21</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K122">
         <v>95</v>
@@ -12075,16 +12077,16 @@
         <v>123.062073</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P122" s="4">
         <v>203205</v>
       </c>
       <c r="Q122" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R122" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.3">
@@ -12116,7 +12118,7 @@
         <v>21</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K123">
         <v>68</v>
@@ -12131,16 +12133,16 @@
         <v>112.076255</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="P123" s="4">
         <v>1249619</v>
       </c>
       <c r="Q123" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R123" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.3">
@@ -12172,7 +12174,7 @@
         <v>21</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K124">
         <v>96</v>
@@ -12187,16 +12189,16 @@
         <v>113.924392</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="P124" s="4">
         <v>302311</v>
       </c>
       <c r="Q124" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R124" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.3">
@@ -12228,7 +12230,7 @@
         <v>21</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K125">
         <v>92</v>
@@ -12243,16 +12245,16 @@
         <v>119.8426</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="P125" s="4">
         <v>382017</v>
       </c>
       <c r="Q125" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R125" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.3">
@@ -12284,7 +12286,7 @@
         <v>21</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K126">
         <v>76</v>
@@ -12299,16 +12301,16 @@
         <v>106.959187</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="P126" s="4">
         <v>5495373</v>
       </c>
       <c r="Q126" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R126" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.3">
@@ -12340,7 +12342,7 @@
         <v>21</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K127">
         <v>69</v>
@@ -12355,16 +12357,16 @@
         <v>99.072187999999997</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="P127" s="4">
         <v>275189</v>
       </c>
       <c r="Q127" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R127" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.3">
@@ -12396,7 +12398,7 @@
         <v>21</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K128">
         <v>80</v>
@@ -12411,16 +12413,16 @@
         <v>108.33702</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="P128" s="4">
         <v>947166</v>
       </c>
       <c r="Q128" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R128" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.3">
@@ -12452,7 +12454,7 @@
         <v>21</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K129">
         <v>79</v>
@@ -12467,16 +12469,16 @@
         <v>106.925792</v>
       </c>
       <c r="O129" s="3" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="P129" s="4">
         <v>2496198</v>
       </c>
       <c r="Q129" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R129" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.3">
@@ -12508,7 +12510,7 @@
         <v>21</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K130">
         <v>98</v>
@@ -12523,16 +12525,16 @@
         <v>100.397521</v>
       </c>
       <c r="O130" s="3" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="P130" s="4">
         <v>928539</v>
       </c>
       <c r="Q130" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R130" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.3">
@@ -12564,7 +12566,7 @@
         <v>21</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K131">
         <v>74</v>
@@ -12579,16 +12581,16 @@
         <v>110.381372</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P131" s="4">
         <v>1693034</v>
       </c>
       <c r="Q131" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R131" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.3">
@@ -12620,7 +12622,7 @@
         <v>21</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K132">
         <v>66</v>
@@ -12635,16 +12637,16 @@
         <v>107.608931</v>
       </c>
       <c r="O132" s="3" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="P132" s="4">
         <v>2555187</v>
       </c>
       <c r="Q132" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R132" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.3">
@@ -12676,7 +12678,7 @@
         <v>21</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K133">
         <v>129</v>
@@ -12691,16 +12693,16 @@
         <v>106.842597</v>
       </c>
       <c r="O133" s="3" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P133" s="4">
         <v>2408480</v>
       </c>
       <c r="Q133" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R133" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.3">
@@ -12732,7 +12734,7 @@
         <v>21</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K134">
         <v>120.75</v>
@@ -12747,16 +12749,16 @@
         <v>106.840907</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P134" s="4">
         <v>5495373</v>
       </c>
       <c r="Q134" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R134" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.3">
@@ -12788,7 +12790,7 @@
         <v>21</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K135">
         <v>90</v>
@@ -12800,16 +12802,16 @@
         <v>119.39393099999999</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="P135" s="4">
         <v>1470262</v>
       </c>
       <c r="Q135" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R135" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.3">
@@ -12841,7 +12843,7 @@
         <v>21</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K136">
         <v>145.6</v>
@@ -12856,16 +12858,16 @@
         <v>110.420416</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="P136" s="4">
         <v>1693034</v>
       </c>
       <c r="Q136" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R136" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.3">
@@ -12897,7 +12899,7 @@
         <v>21</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K137">
         <v>172.02</v>
@@ -12912,16 +12914,16 @@
         <v>106.81286</v>
       </c>
       <c r="O137" s="3" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="P137" s="4">
         <v>2408480</v>
       </c>
       <c r="Q137" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R137" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
@@ -12953,7 +12955,7 @@
         <v>21</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K138">
         <v>105</v>
@@ -12968,16 +12970,16 @@
         <v>107.195449</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="P138" s="4">
         <v>3172831</v>
       </c>
       <c r="Q138" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R138" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
@@ -13009,7 +13011,7 @@
         <v>21</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K139">
         <v>77</v>
@@ -13024,16 +13026,16 @@
         <v>106.786618</v>
       </c>
       <c r="O139" s="3" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="P139" s="4">
         <v>2615945</v>
       </c>
       <c r="Q139" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R139" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.3">
@@ -13065,7 +13067,7 @@
         <v>21</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K140">
         <v>110.79</v>
@@ -13077,16 +13079,16 @@
         <v>106.89189399999999</v>
       </c>
       <c r="O140" s="3" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P140" s="4">
         <v>1876057</v>
       </c>
       <c r="Q140" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R140" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.3">
@@ -13118,7 +13120,7 @@
         <v>21</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K141">
         <v>112</v>
@@ -13133,16 +13135,16 @@
         <v>104.753834</v>
       </c>
       <c r="O141" s="3" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="P141" s="4">
         <v>1761461</v>
       </c>
       <c r="Q141" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R141" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.3">
@@ -13174,7 +13176,7 @@
         <v>21</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K142">
         <v>74</v>
@@ -13189,16 +13191,16 @@
         <v>109.369536</v>
       </c>
       <c r="O142" s="3" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="P142" s="4">
         <v>291750</v>
       </c>
       <c r="Q142" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R142" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.3">
@@ -13230,7 +13232,7 @@
         <v>21</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K143">
         <v>106.11</v>
@@ -13245,16 +13247,16 @@
         <v>112.720054</v>
       </c>
       <c r="O143" s="3" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="P143" s="4">
         <v>3000075</v>
       </c>
       <c r="Q143" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R143" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.3">
@@ -13286,7 +13288,7 @@
         <v>21</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K144">
         <v>432</v>
@@ -13301,16 +13303,16 @@
         <v>115.208021</v>
       </c>
       <c r="O144" s="3" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="P144" s="4">
         <v>660984</v>
       </c>
       <c r="Q144" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R144" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.3">
@@ -13342,7 +13344,7 @@
         <v>21</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K145">
         <v>222</v>
@@ -13357,16 +13359,16 @@
         <v>112.717679</v>
       </c>
       <c r="O145" s="3" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="P145" s="4">
         <v>1982939</v>
       </c>
       <c r="Q145" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R145" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.3">
@@ -13398,7 +13400,7 @@
         <v>21</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K146">
         <v>100</v>
@@ -13413,16 +13415,16 @@
         <v>112.666859</v>
       </c>
       <c r="O146" s="3" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="P146" s="4">
         <v>3000075</v>
       </c>
       <c r="Q146" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R146" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.3">
@@ -13454,7 +13456,7 @@
         <v>21</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K147">
         <v>60</v>
@@ -13469,16 +13471,16 @@
         <v>114.87306700000001</v>
       </c>
       <c r="O147" s="3" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="P147" s="4">
         <v>575113</v>
       </c>
       <c r="Q147" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R147" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.3">
@@ -13525,16 +13527,16 @@
         <v>98.678877999999997</v>
       </c>
       <c r="O148" s="3" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P148" s="4">
         <v>2530492</v>
       </c>
       <c r="Q148" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R148" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.3">
@@ -13566,7 +13568,7 @@
         <v>21</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K149">
         <v>112</v>
@@ -13581,16 +13583,16 @@
         <v>112.780812</v>
       </c>
       <c r="O149" s="3" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="P149" s="4">
         <v>3000075</v>
       </c>
       <c r="Q149" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R149" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.3">
@@ -13637,16 +13639,16 @@
         <v>109.651066</v>
       </c>
       <c r="O150" s="3" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="P150" s="4">
         <v>317534</v>
       </c>
       <c r="Q150" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R150" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.3">
@@ -13678,7 +13680,7 @@
         <v>21</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K151">
         <v>55</v>
@@ -13693,16 +13695,16 @@
         <v>113.722081</v>
       </c>
       <c r="O151" s="3" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="P151" s="4">
         <v>2590289</v>
       </c>
       <c r="Q151" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R151" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
@@ -13749,16 +13751,16 @@
         <v>100.396214</v>
       </c>
       <c r="O152" s="3" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="P152" s="4">
         <v>135489</v>
       </c>
       <c r="Q152" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R152" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.3">
@@ -13805,16 +13807,16 @@
         <v>100.354747</v>
       </c>
       <c r="O153" s="3" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="P153" s="4">
         <v>928539</v>
       </c>
       <c r="Q153" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R153" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.3">
@@ -13846,7 +13848,7 @@
         <v>21</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K154">
         <v>75</v>
@@ -13861,16 +13863,16 @@
         <v>116.844972</v>
       </c>
       <c r="O154" s="3" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="P154" s="4">
         <v>733397</v>
       </c>
       <c r="Q154" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R154" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.3">
@@ -13902,7 +13904,7 @@
         <v>21</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K155">
         <v>75</v>
@@ -13917,16 +13919,16 @@
         <v>108.981435</v>
       </c>
       <c r="O155" s="3" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="P155" s="4">
         <v>242146</v>
       </c>
       <c r="Q155" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R155" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.3">
@@ -13958,7 +13960,7 @@
         <v>21</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K156">
         <v>100</v>
@@ -13973,16 +13975,16 @@
         <v>109.306162</v>
       </c>
       <c r="O156" s="3" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="P156" s="4">
         <v>676096</v>
       </c>
       <c r="Q156" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R156" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.3">
@@ -14014,7 +14016,7 @@
         <v>21</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K157">
         <v>157</v>
@@ -14029,16 +14031,16 @@
         <v>111.898601</v>
       </c>
       <c r="O157" s="3" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="P157" s="4">
         <v>1132146</v>
       </c>
       <c r="Q157" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R157" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
@@ -14070,7 +14072,7 @@
         <v>21</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K158">
         <v>100</v>
@@ -14085,16 +14087,16 @@
         <v>112.01836400000001</v>
       </c>
       <c r="O158" s="3" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="P158" s="4">
         <v>296792</v>
       </c>
       <c r="Q158" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R158" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
@@ -14126,7 +14128,7 @@
         <v>21</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K159">
         <v>100</v>
@@ -14141,16 +14143,16 @@
         <v>119.887102</v>
       </c>
       <c r="O159" s="3" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="P159" s="4">
         <v>382017</v>
       </c>
       <c r="Q159" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R159" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.3">
@@ -14197,16 +14199,16 @@
         <v>104.76451400000001</v>
       </c>
       <c r="O160" s="3" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="P160" s="4">
         <v>1761461</v>
       </c>
       <c r="Q160" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R160" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.3">
@@ -14253,16 +14255,16 @@
         <v>98.708527000000004</v>
       </c>
       <c r="O161" s="3" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="P161" s="4">
         <v>2530492</v>
       </c>
       <c r="Q161" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R161" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.3">
@@ -14309,16 +14311,16 @@
         <v>103.59678</v>
       </c>
       <c r="O162" s="3" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="P162" s="4">
         <v>633649</v>
       </c>
       <c r="Q162" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R162" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.3">
@@ -14365,16 +14367,16 @@
         <v>95.330163999999996</v>
       </c>
       <c r="O163" s="3" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="P163" s="4">
         <v>257315</v>
       </c>
       <c r="Q163" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R163" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.3">
@@ -14406,7 +14408,7 @@
         <v>21</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K164">
         <v>378</v>
@@ -14421,16 +14423,16 @@
         <v>119.443811</v>
       </c>
       <c r="O164" s="3" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="P164" s="4">
         <v>1470262</v>
       </c>
       <c r="Q164" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R164" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.3">
@@ -14477,16 +14479,16 @@
         <v>107.623908</v>
       </c>
       <c r="O165" s="3" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="P165" s="4">
         <v>2555187</v>
       </c>
       <c r="Q165" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R165" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.3">
@@ -14533,16 +14535,16 @@
         <v>110.60007299999999</v>
       </c>
       <c r="O166" s="3" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="P166" s="4">
         <v>1099682</v>
       </c>
       <c r="Q166" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R166" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.3">
@@ -14589,16 +14591,16 @@
         <v>110.91150399999999</v>
       </c>
       <c r="O167" s="3" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="P167" s="4">
         <v>1507156</v>
       </c>
       <c r="Q167" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R167" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.3">
@@ -14645,16 +14647,16 @@
         <v>110.503196</v>
       </c>
       <c r="O168" s="3" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="P168" s="4">
         <v>200738</v>
       </c>
       <c r="Q168" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R168" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
@@ -14686,7 +14688,7 @@
         <v>21</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K169">
         <v>62</v>
@@ -14701,16 +14703,16 @@
         <v>115.321116</v>
       </c>
       <c r="O169" s="3" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="P169" s="4">
         <v>503546</v>
       </c>
       <c r="Q169" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R169" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
@@ -14742,7 +14744,7 @@
         <v>21</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K170">
         <v>73</v>
@@ -14757,16 +14759,16 @@
         <v>111.469902</v>
       </c>
       <c r="O170" s="3" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="P170" s="4">
         <v>973269</v>
       </c>
       <c r="Q170" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R170" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.3">
@@ -14798,7 +14800,7 @@
         <v>21</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K171">
         <v>142</v>
@@ -14813,16 +14815,16 @@
         <v>111.521343</v>
       </c>
       <c r="O171" s="3" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="P171" s="4">
         <v>201992</v>
       </c>
       <c r="Q171" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R171" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.3">
@@ -14854,7 +14856,7 @@
         <v>21</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K172">
         <v>95</v>
@@ -14869,16 +14871,16 @@
         <v>117.530023</v>
       </c>
       <c r="O172" s="3" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="P172" s="4">
         <v>427492</v>
       </c>
       <c r="Q172" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R172" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.3">
@@ -14910,7 +14912,7 @@
         <v>21</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K173">
         <v>72</v>
@@ -14925,16 +14927,16 @@
         <v>117.491473</v>
       </c>
       <c r="O173" s="3" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="P173" s="4">
         <v>187446</v>
       </c>
       <c r="Q173" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R173" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.3">
@@ -14981,16 +14983,16 @@
         <v>109.387243</v>
       </c>
       <c r="O174" s="3" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="P174" s="4">
         <v>1567045</v>
       </c>
       <c r="Q174" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R174" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.3">
@@ -15022,7 +15024,7 @@
         <v>21</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K175">
         <v>73</v>
@@ -15037,16 +15039,16 @@
         <v>112.608926</v>
       </c>
       <c r="O175" s="3" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="P175" s="4">
         <v>874660</v>
       </c>
       <c r="Q175" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R175" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.3">
@@ -15093,16 +15095,16 @@
         <v>105.247274</v>
       </c>
       <c r="O176" s="3" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="P176" s="4">
         <v>1096935</v>
       </c>
       <c r="Q176" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R176" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.3">
@@ -15149,16 +15151,16 @@
         <v>98.703643999999997</v>
       </c>
       <c r="O177" s="3" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="P177" s="4">
         <v>2016906</v>
       </c>
       <c r="Q177" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R177" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.3">
@@ -15190,7 +15192,7 @@
         <v>21</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K178">
         <v>119</v>
@@ -15205,16 +15207,16 @@
         <v>115.211603</v>
       </c>
       <c r="O178" s="3" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="P178" s="4">
         <v>660984</v>
       </c>
       <c r="Q178" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R178" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.3">
@@ -15246,7 +15248,7 @@
         <v>21</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K179">
         <v>74</v>
@@ -15261,16 +15263,16 @@
         <v>109.331602</v>
       </c>
       <c r="O179" s="3" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="P179" s="4">
         <v>676096</v>
       </c>
       <c r="Q179" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R179" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.3">
@@ -15302,7 +15304,7 @@
         <v>21</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K180">
         <v>80</v>
@@ -15317,16 +15319,16 @@
         <v>112.570826</v>
       </c>
       <c r="O180" s="3" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="P180" s="4">
         <v>2692261</v>
       </c>
       <c r="Q180" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R180" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.3">
@@ -15358,7 +15360,7 @@
         <v>21</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K181">
         <v>75</v>
@@ -15373,16 +15375,16 @@
         <v>119.40918000000001</v>
       </c>
       <c r="O181" s="3" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="P181" s="4">
         <v>1470262</v>
       </c>
       <c r="Q181" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R181" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.3">
@@ -15414,7 +15416,7 @@
         <v>21</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K182">
         <v>93</v>
@@ -15429,16 +15431,16 @@
         <v>124.861063</v>
       </c>
       <c r="O182" s="3" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="P182" s="4">
         <v>478194</v>
       </c>
       <c r="Q182" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R182" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.3">
@@ -15485,16 +15487,16 @@
         <v>97.144687000000005</v>
       </c>
       <c r="O183" s="3" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="P183" s="4">
         <v>193950</v>
       </c>
       <c r="Q183" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R183" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.3">
@@ -15541,16 +15543,16 @@
         <v>109.009351</v>
       </c>
       <c r="O184" s="3" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="P184" s="4">
         <v>2022808</v>
       </c>
       <c r="Q184" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R184" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.3">
@@ -15582,7 +15584,7 @@
         <v>21</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K185">
         <v>104</v>
@@ -15597,16 +15599,16 @@
         <v>119.48123200000001</v>
       </c>
       <c r="O185" s="3" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="P185" s="4">
         <v>1470262</v>
       </c>
       <c r="Q185" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R185" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.3">
@@ -15653,16 +15655,16 @@
         <v>111.029685</v>
       </c>
       <c r="O186" s="3" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="P186" s="4">
         <v>1012493</v>
       </c>
       <c r="Q186" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R186" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.3">
@@ -15709,16 +15711,16 @@
         <v>98.682354000000004</v>
       </c>
       <c r="O187" s="3" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="P187" s="4">
         <v>2530492</v>
       </c>
       <c r="Q187" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R187" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.3">
@@ -15750,7 +15752,7 @@
         <v>21</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K188">
         <v>100</v>
@@ -15765,16 +15767,16 @@
         <v>111.898078</v>
       </c>
       <c r="O188" s="3" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="P188" s="4">
         <v>1139616</v>
       </c>
       <c r="Q188" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R188" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.3">
@@ -15806,7 +15808,7 @@
         <v>21</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K189">
         <v>74</v>
@@ -15821,16 +15823,16 @@
         <v>116.00132600000001</v>
       </c>
       <c r="O189" s="3" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="P189" s="4">
         <v>343740</v>
       </c>
       <c r="Q189" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R189" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.3">
@@ -15862,7 +15864,7 @@
         <v>21</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K190">
         <v>60</v>
@@ -15877,16 +15879,16 @@
         <v>116.846875</v>
       </c>
       <c r="O190" s="3" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="P190" s="4">
         <v>733397</v>
       </c>
       <c r="Q190" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R190" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.3">
@@ -15918,7 +15920,7 @@
         <v>21</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K191">
         <v>67</v>
@@ -15933,16 +15935,16 @@
         <v>114.578221</v>
       </c>
       <c r="O191" s="3" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="P191" s="4">
         <v>675916</v>
       </c>
       <c r="Q191" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R191" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.3">
@@ -15989,16 +15991,16 @@
         <v>106.9164</v>
       </c>
       <c r="O192" s="3" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="P192" s="4">
         <v>1876057</v>
       </c>
       <c r="Q192" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R192" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.3">
@@ -16030,7 +16032,7 @@
         <v>21</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K193">
         <v>60</v>
@@ -16045,16 +16047,16 @@
         <v>114.602159</v>
       </c>
       <c r="O193" s="3" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="P193" s="4">
         <v>675916</v>
       </c>
       <c r="Q193" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R193" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.3">
@@ -16101,16 +16103,16 @@
         <v>110.82023700000001</v>
       </c>
       <c r="O194" s="3" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="P194" s="4">
         <v>586166</v>
       </c>
       <c r="Q194" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R194" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.3">
@@ -16142,7 +16144,7 @@
         <v>21</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K195">
         <v>120</v>
@@ -16157,16 +16159,16 @@
         <v>112.628643</v>
       </c>
       <c r="O195" s="3" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="P195" s="4">
         <v>874660</v>
       </c>
       <c r="Q195" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R195" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.3">
@@ -16198,7 +16200,7 @@
         <v>21</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K196">
         <v>117</v>
@@ -16213,16 +16215,16 @@
         <v>115.157217</v>
       </c>
       <c r="O196" s="3" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="P196" s="4">
         <v>526029</v>
       </c>
       <c r="Q196" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R196" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.3">
@@ -16269,16 +16271,16 @@
         <v>107.301137</v>
       </c>
       <c r="O197" s="3" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="P197" s="4">
         <v>2519882</v>
       </c>
       <c r="Q197" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R197" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.3">
@@ -16325,16 +16327,16 @@
         <v>108.21779100000001</v>
       </c>
       <c r="O198" s="3" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="P198" s="4">
         <v>752545</v>
       </c>
       <c r="Q198" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R198" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.3">
@@ -16366,7 +16368,7 @@
         <v>21</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K199">
         <v>100</v>
@@ -16381,16 +16383,16 @@
         <v>114.848354</v>
       </c>
       <c r="O199" s="3" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="P199" s="4">
         <v>270346</v>
       </c>
       <c r="Q199" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R199" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.3">
@@ -16422,7 +16424,7 @@
         <v>21</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K200">
         <v>175</v>
@@ -16437,16 +16439,16 @@
         <v>112.76169899999999</v>
       </c>
       <c r="O200" s="3" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="P200" s="4">
         <v>3000075</v>
       </c>
       <c r="Q200" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R200" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.3">
@@ -16493,16 +16495,16 @@
         <v>109.63630000000001</v>
       </c>
       <c r="O201" s="3" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="P201" s="4">
         <v>1008689</v>
       </c>
       <c r="Q201" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R201" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.3">
@@ -16549,16 +16551,16 @@
         <v>110.221926</v>
       </c>
       <c r="O202" s="3" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="P202" s="4">
         <v>128152</v>
       </c>
       <c r="Q202" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R202" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.3">
@@ -16590,7 +16592,7 @@
         <v>21</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K203">
         <v>60</v>
@@ -16605,16 +16607,16 @@
         <v>112.941255</v>
       </c>
       <c r="O203" s="3" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="P203" s="4">
         <v>433678</v>
       </c>
       <c r="Q203" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R203" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.3">
@@ -16661,16 +16663,16 @@
         <v>110.304295</v>
       </c>
       <c r="O204" s="3" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="P204" s="4">
         <v>1105415</v>
       </c>
       <c r="Q204" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R204" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.3">
@@ -16717,16 +16719,16 @@
         <v>115.242654</v>
       </c>
       <c r="O205" s="3" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="P205" s="4">
         <v>660984</v>
       </c>
       <c r="Q205" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R205" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.3">
@@ -16773,16 +16775,16 @@
         <v>109.34725400000001</v>
       </c>
       <c r="O206" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="P206" s="4">
         <v>676096</v>
       </c>
       <c r="Q206" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R206" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.3">
@@ -16814,7 +16816,7 @@
         <v>21</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K207">
         <v>80</v>
@@ -16829,16 +16831,16 @@
         <v>122.52200000000001</v>
       </c>
       <c r="O207" s="3" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="P207" s="4">
         <v>347380</v>
       </c>
       <c r="Q207" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R207" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.3">
@@ -16870,7 +16872,7 @@
         <v>21</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K208">
         <v>50</v>
@@ -16885,16 +16887,16 @@
         <v>119.79543</v>
       </c>
       <c r="O208" s="3" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="P208" s="4">
         <v>323430</v>
       </c>
       <c r="Q208" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R208" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.3">
@@ -16941,16 +16943,16 @@
         <v>105.257171</v>
       </c>
       <c r="O209" s="3" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="P209" s="4">
         <v>1096935</v>
       </c>
       <c r="Q209" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R209" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.3">
@@ -16997,16 +16999,16 @@
         <v>100.361576</v>
       </c>
       <c r="O210" s="3" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="P210" s="4">
         <v>928539</v>
       </c>
       <c r="Q210" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R210" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.3">
@@ -17053,16 +17055,16 @@
         <v>101.447146</v>
       </c>
       <c r="O211" s="3" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="P211" s="4">
         <v>1116142</v>
       </c>
       <c r="Q211" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R211" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.3">
@@ -17109,16 +17111,16 @@
         <v>112.621184</v>
       </c>
       <c r="O212" s="3" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="P212" s="4">
         <v>874660</v>
       </c>
       <c r="Q212" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R212" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.3">
@@ -17165,16 +17167,16 @@
         <v>107.583369</v>
       </c>
       <c r="O213" s="3" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="P213" s="4">
         <v>570829</v>
       </c>
       <c r="Q213" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R213" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.3">
@@ -17206,7 +17208,7 @@
         <v>21</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K214">
         <v>80</v>
@@ -17221,16 +17223,16 @@
         <v>112.897693</v>
       </c>
       <c r="O214" s="3" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="P214" s="4">
         <v>212403</v>
       </c>
       <c r="Q214" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R214" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.3">
@@ -17277,16 +17279,16 @@
         <v>104.768023</v>
       </c>
       <c r="O215" s="3" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="P215" s="4">
         <v>1761461</v>
       </c>
       <c r="Q215" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R215" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.3">
@@ -17333,16 +17335,16 @@
         <v>98.676056000000003</v>
       </c>
       <c r="O216" s="3" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="P216" s="4">
         <v>2530492</v>
       </c>
       <c r="Q216" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R216" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.3">
@@ -17389,16 +17391,16 @@
         <v>106.853514</v>
       </c>
       <c r="O217" s="3" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="P217" s="4">
         <v>1927869</v>
       </c>
       <c r="Q217" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R217" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.3">
@@ -17445,16 +17447,16 @@
         <v>108.542145</v>
       </c>
       <c r="O218" s="3" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="P218" s="4">
         <v>2420956</v>
       </c>
       <c r="Q218" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R218" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.3">
@@ -17501,16 +17503,16 @@
         <v>109.65213900000001</v>
       </c>
       <c r="O219" s="3" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="P219" s="4">
         <v>1008689</v>
       </c>
       <c r="Q219" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R219" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.3">
@@ -17542,7 +17544,7 @@
         <v>21</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K220">
         <v>110</v>
@@ -17557,16 +17559,16 @@
         <v>111.674758</v>
       </c>
       <c r="O220" s="3" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="P220" s="4">
         <v>282660</v>
       </c>
       <c r="Q220" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R220" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.3">
@@ -17613,16 +17615,16 @@
         <v>104.76015</v>
       </c>
       <c r="O221" s="3" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="P221" s="4">
         <v>1761461</v>
       </c>
       <c r="Q221" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R221" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.3">
@@ -17654,7 +17656,7 @@
         <v>21</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K222">
         <v>105</v>
@@ -17669,16 +17671,16 @@
         <v>123.062428</v>
       </c>
       <c r="O222" s="3" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="P222" s="4">
         <v>203205</v>
       </c>
       <c r="Q222" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R222" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.3">
@@ -17725,16 +17727,16 @@
         <v>104.791476</v>
       </c>
       <c r="O223" s="3" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="P223" s="4">
         <v>1761461</v>
       </c>
       <c r="Q223" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R223" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.3">
@@ -17766,7 +17768,7 @@
         <v>21</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K224">
         <v>82</v>
@@ -17781,16 +17783,16 @@
         <v>125.127532</v>
       </c>
       <c r="O224" s="3" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="P224" s="4">
         <v>228008</v>
       </c>
       <c r="Q224" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R224" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.3">
@@ -17837,16 +17839,16 @@
         <v>111.882268</v>
       </c>
       <c r="O225" s="3" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="P225" s="4">
         <v>1356056</v>
       </c>
       <c r="Q225" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R225" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.3">
@@ -17878,7 +17880,7 @@
         <v>21</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K226">
         <v>112</v>
@@ -17893,16 +17895,16 @@
         <v>112.665565</v>
       </c>
       <c r="O226" s="3" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="P226" s="4">
         <v>2692261</v>
       </c>
       <c r="Q226" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R226" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.3">
@@ -17949,16 +17951,16 @@
         <v>105.21337800000001</v>
       </c>
       <c r="O227" s="3" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="P227" s="4">
         <v>1373771</v>
       </c>
       <c r="Q227" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R227" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.3">
@@ -18005,16 +18007,16 @@
         <v>120.192222</v>
       </c>
       <c r="O228" s="3" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="P228" s="4">
         <v>468337</v>
       </c>
       <c r="Q228" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R228" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.3">
@@ -18061,16 +18063,16 @@
         <v>110.819518</v>
       </c>
       <c r="O229" s="3" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="P229" s="4">
         <v>586166</v>
       </c>
       <c r="Q229" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R229" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.3">
@@ -18102,7 +18104,7 @@
         <v>21</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K230">
         <v>70</v>
@@ -18117,16 +18119,16 @@
         <v>112.167683</v>
       </c>
       <c r="O230" s="3" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="P230" s="4">
         <v>159406</v>
       </c>
       <c r="Q230" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R230" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.3">
@@ -18173,16 +18175,16 @@
         <v>120.314673</v>
       </c>
       <c r="O231" s="3" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="P231" s="4">
         <v>817363</v>
       </c>
       <c r="Q231" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R231" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.3">
@@ -18229,16 +18231,16 @@
         <v>107.164843</v>
       </c>
       <c r="O232" s="3" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="P232" s="4">
         <v>3172831</v>
       </c>
       <c r="Q232" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R232" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.3">
@@ -18270,7 +18272,7 @@
         <v>21</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K233">
         <v>103</v>
@@ -18285,16 +18287,16 @@
         <v>112.767736</v>
       </c>
       <c r="O233" s="3" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="P233" s="4">
         <v>1982939</v>
       </c>
       <c r="Q233" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R233" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.3">
@@ -18326,7 +18328,7 @@
         <v>21</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K234">
         <v>81</v>
@@ -18341,16 +18343,16 @@
         <v>112.652907</v>
       </c>
       <c r="O234" s="3" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="P234" s="4">
         <v>3000075</v>
       </c>
       <c r="Q234" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R234" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.3">
@@ -18397,16 +18399,16 @@
         <v>110.39166400000001</v>
       </c>
       <c r="O235" s="3" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="P235" s="4">
         <v>1693034</v>
       </c>
       <c r="Q235" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R235" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.3">
@@ -18453,16 +18455,16 @@
         <v>117.13990099999999</v>
       </c>
       <c r="O236" s="3" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="P236" s="4">
         <v>856361</v>
       </c>
       <c r="Q236" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R236" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.3">
@@ -18509,16 +18511,16 @@
         <v>113.885851</v>
       </c>
       <c r="O237" s="3" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="P237" s="4">
         <v>302311</v>
       </c>
       <c r="Q237" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R237" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.3">
@@ -18550,7 +18552,7 @@
         <v>21</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K238">
         <v>87</v>
@@ -18565,16 +18567,16 @@
         <v>109.347481</v>
       </c>
       <c r="O238" s="3" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="P238" s="4">
         <v>676096</v>
       </c>
       <c r="Q238" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R238" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.3">
@@ -18621,16 +18623,16 @@
         <v>106.930753</v>
       </c>
       <c r="O239" s="3" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="P239" s="4">
         <v>361581</v>
       </c>
       <c r="Q239" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R239" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.3">
@@ -18662,7 +18664,7 @@
         <v>21</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K240">
         <v>97</v>
@@ -18677,16 +18679,16 @@
         <v>116.117907</v>
       </c>
       <c r="O240" s="3" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="P240" s="4">
         <v>452812</v>
       </c>
       <c r="Q240" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R240" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.3">
@@ -18733,16 +18735,16 @@
         <v>112.04934900000001</v>
       </c>
       <c r="O241" s="3" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="P241" s="4">
         <v>1249619</v>
       </c>
       <c r="Q241" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R241" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.3">
@@ -18774,7 +18776,7 @@
         <v>21</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K242">
         <v>87</v>
@@ -18789,16 +18791,16 @@
         <v>109.347481</v>
       </c>
       <c r="O242" s="3" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="P242" s="4">
         <v>676096</v>
       </c>
       <c r="Q242" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R242" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.3">
@@ -18845,16 +18847,16 @@
         <v>112.24469000000001</v>
       </c>
       <c r="O243" s="3" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="P243" s="4">
         <v>1364775</v>
       </c>
       <c r="Q243" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R243" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.3">
@@ -18886,7 +18888,7 @@
         <v>21</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K244">
         <v>99</v>
@@ -18901,16 +18903,16 @@
         <v>112.67265999999999</v>
       </c>
       <c r="O244" s="3" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="P244" s="4">
         <v>1982939</v>
       </c>
       <c r="Q244" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R244" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.3">
@@ -18942,7 +18944,7 @@
         <v>21</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K245">
         <v>130</v>
@@ -18957,16 +18959,16 @@
         <v>117.587605</v>
       </c>
       <c r="O245" s="3" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="P245" s="4">
         <v>246734</v>
       </c>
       <c r="Q245" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R245" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.3">
@@ -19013,16 +19015,16 @@
         <v>107.908772</v>
       </c>
       <c r="O246" s="3" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="P246" s="4">
         <v>2770531</v>
       </c>
       <c r="Q246" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R246" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.3">
@@ -19069,16 +19071,16 @@
         <v>108.23177200000001</v>
       </c>
       <c r="O247" s="3" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="P247" s="4">
         <v>1345378</v>
       </c>
       <c r="Q247" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R247" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.3">
@@ -19125,16 +19127,16 @@
         <v>106.630234</v>
       </c>
       <c r="O248" s="3" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="P248" s="4">
         <v>3286420</v>
       </c>
       <c r="Q248" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R248" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.3">
@@ -19166,7 +19168,7 @@
         <v>21</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K249">
         <v>74</v>
@@ -19181,16 +19183,16 @@
         <v>112.61539500000001</v>
       </c>
       <c r="O249" s="3" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="P249" s="4">
         <v>1296688</v>
       </c>
       <c r="Q249" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R249" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.3">
@@ -19237,16 +19239,16 @@
         <v>115.39859800000001</v>
       </c>
       <c r="O250" s="3" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="P250" s="4">
         <v>220491</v>
       </c>
       <c r="Q250" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R250" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.3">
@@ -19293,16 +19295,16 @@
         <v>113.933882</v>
       </c>
       <c r="O251" s="3" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="P251" s="4">
         <v>302311</v>
       </c>
       <c r="Q251" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R251" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.3">
@@ -19349,16 +19351,16 @@
         <v>107.292559</v>
       </c>
       <c r="O252" s="3" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="P252" s="4">
         <v>2519882</v>
       </c>
       <c r="Q252" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R252" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.3">
@@ -19390,7 +19392,7 @@
         <v>21</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K253">
         <v>111</v>
@@ -19405,16 +19407,16 @@
         <v>106.720572</v>
       </c>
       <c r="O253" s="3" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="P253" s="4">
         <v>1899515</v>
       </c>
       <c r="Q253" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R253" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.3">
@@ -19461,16 +19463,16 @@
         <v>111.439922</v>
       </c>
       <c r="O254" s="3" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="P254" s="4">
         <v>901637</v>
       </c>
       <c r="Q254" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R254" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.3">
@@ -19517,16 +19519,16 @@
         <v>109.65588700000001</v>
       </c>
       <c r="O255" s="3" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="P255" s="4">
         <v>1426832</v>
       </c>
       <c r="Q255" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R255" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.3">
@@ -19573,16 +19575,16 @@
         <v>107.29899399999999</v>
       </c>
       <c r="O256" s="3" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="P256" s="4">
         <v>2519882</v>
       </c>
       <c r="Q256" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R256" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.3">
@@ -19614,7 +19616,7 @@
         <v>21</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K257">
         <v>112</v>
@@ -19629,16 +19631,16 @@
         <v>123.590211</v>
       </c>
       <c r="O257" s="3" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="P257" s="4">
         <v>443349</v>
       </c>
       <c r="Q257" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R257" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.3">
@@ -19670,7 +19672,7 @@
         <v>21</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K258">
         <v>100</v>
@@ -19685,16 +19687,16 @@
         <v>119.883326</v>
       </c>
       <c r="O258" s="3" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="P258" s="4">
         <v>382017</v>
       </c>
       <c r="Q258" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R258" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.3">
@@ -19741,16 +19743,16 @@
         <v>107.766926</v>
       </c>
       <c r="O259" s="3" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="P259" s="4">
         <v>1624855</v>
       </c>
       <c r="Q259" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R259" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.3">
@@ -19797,16 +19799,16 @@
         <v>106.621224</v>
       </c>
       <c r="O260" s="3" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="P260" s="4">
         <v>1899515</v>
       </c>
       <c r="Q260" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R260" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.3">
@@ -19853,16 +19855,16 @@
         <v>96.126309000000006</v>
       </c>
       <c r="O261" s="3" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="P261" s="4">
         <v>201720</v>
       </c>
       <c r="Q261" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R261" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.3">
@@ -19909,16 +19911,16 @@
         <v>111.112225</v>
       </c>
       <c r="O262" s="3" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="P262" s="4">
         <v>599574</v>
       </c>
       <c r="Q262" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R262" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.3">
@@ -19965,16 +19967,16 @@
         <v>112.038389</v>
       </c>
       <c r="O263" s="3" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="P263" s="4">
         <v>296792</v>
       </c>
       <c r="Q263" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R263" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.3">
@@ -20021,16 +20023,16 @@
         <v>112.432158</v>
       </c>
       <c r="O264" s="3" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="P264" s="4">
         <v>141335</v>
       </c>
       <c r="Q264" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R264" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.3">
@@ -20077,16 +20079,16 @@
         <v>107.140998</v>
       </c>
       <c r="O265" s="3" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="P265" s="4">
         <v>2516417</v>
       </c>
       <c r="Q265" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R265" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.3">
@@ -20118,7 +20120,7 @@
         <v>994</v>
       </c>
       <c r="J266" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K266">
         <v>64.8</v>
@@ -20133,16 +20135,16 @@
         <v>106.841382</v>
       </c>
       <c r="O266" s="3" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="P266" s="4">
         <v>1109489</v>
       </c>
       <c r="Q266" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R266" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.3">
@@ -20174,7 +20176,7 @@
         <v>994</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K267">
         <v>64</v>
@@ -20189,16 +20191,16 @@
         <v>106.92419200000001</v>
       </c>
       <c r="O267" s="3" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="P267" s="4">
         <v>3310145</v>
       </c>
       <c r="Q267" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R267" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.3">
@@ -20230,7 +20232,7 @@
         <v>994</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K268">
         <v>53.76</v>
@@ -20245,16 +20247,16 @@
         <v>107.596006</v>
       </c>
       <c r="O268" s="3" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="P268" s="4">
         <v>2555187</v>
       </c>
       <c r="Q268" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R268" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.3">
@@ -20286,7 +20288,7 @@
         <v>994</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K269">
         <v>90.76</v>
@@ -20301,16 +20303,16 @@
         <v>101.41874799999999</v>
       </c>
       <c r="O269" s="3" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="P269" s="4">
         <v>1116142</v>
       </c>
       <c r="Q269" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R269" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.3">
@@ -20342,7 +20344,7 @@
         <v>994</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K270">
         <v>53.5</v>
@@ -20357,16 +20359,16 @@
         <v>101.446726</v>
       </c>
       <c r="O270" s="3" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="P270" s="4">
         <v>1116142</v>
       </c>
       <c r="Q270" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R270" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.3">
@@ -20398,7 +20400,7 @@
         <v>994</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K271">
         <v>64.25</v>
@@ -20413,16 +20415,16 @@
         <v>110.81621699999999</v>
       </c>
       <c r="O271" s="3" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="P271" s="4">
         <v>586166</v>
       </c>
       <c r="Q271" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R271" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.3">
@@ -20454,7 +20456,7 @@
         <v>994</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K272">
         <v>104.7</v>
@@ -20469,16 +20471,16 @@
         <v>106.94340800000001</v>
       </c>
       <c r="O272" s="3" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="P272" s="4">
         <v>3310145</v>
       </c>
       <c r="Q272" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R272" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.3">
@@ -20510,7 +20512,7 @@
         <v>994</v>
       </c>
       <c r="J273" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K273">
         <v>65.55</v>
@@ -20525,16 +20527,16 @@
         <v>109.128843</v>
       </c>
       <c r="O273" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="P273" s="4">
         <v>291806</v>
       </c>
       <c r="Q273" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R273" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="274" spans="1:18" x14ac:dyDescent="0.3">
@@ -20566,7 +20568,7 @@
         <v>994</v>
       </c>
       <c r="J274" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K274">
         <v>78.180000000000007</v>
@@ -20581,16 +20583,16 @@
         <v>112.748824</v>
       </c>
       <c r="O274" s="3" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="P274" s="4">
         <v>3000075</v>
       </c>
       <c r="Q274" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R274" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.3">
@@ -20622,7 +20624,7 @@
         <v>994</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K275">
         <v>52</v>
@@ -20637,16 +20639,16 @@
         <v>105.280238</v>
       </c>
       <c r="O275" s="3" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="P275" s="4">
         <v>1096935</v>
       </c>
       <c r="Q275" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R275" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.3">
@@ -20678,7 +20680,7 @@
         <v>994</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K276">
         <v>57.09</v>
@@ -20693,16 +20695,16 @@
         <v>98.488361999999995</v>
       </c>
       <c r="O276" s="3" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="P276" s="4">
         <v>305977</v>
       </c>
       <c r="Q276" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R276" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.3">
@@ -20734,7 +20736,7 @@
         <v>994</v>
       </c>
       <c r="J277" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="K277">
         <v>70</v>
@@ -20749,16 +20751,16 @@
         <v>106.854455</v>
       </c>
       <c r="O277" s="3" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="P277" s="4">
         <v>2408480</v>
       </c>
       <c r="Q277" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R277" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="278" spans="1:18" x14ac:dyDescent="0.3">
@@ -20790,7 +20792,7 @@
         <v>994</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="K278">
         <v>89.18</v>
@@ -20805,16 +20807,16 @@
         <v>107.149914</v>
       </c>
       <c r="O278" s="3" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="P278" s="4">
         <v>3172831</v>
       </c>
       <c r="Q278" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R278" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.3">
@@ -20846,7 +20848,7 @@
         <v>994</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="K279">
         <v>88.52</v>
@@ -20861,16 +20863,16 @@
         <v>106.94340800000001</v>
       </c>
       <c r="O279" s="3" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="P279" s="4">
         <v>3310145</v>
       </c>
       <c r="Q279" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R279" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.3">
@@ -20902,7 +20904,7 @@
         <v>994</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K280">
         <v>60</v>
@@ -20917,16 +20919,16 @@
         <v>109.02432</v>
       </c>
       <c r="O280" s="3" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="P280" s="4">
         <v>2022808</v>
       </c>
       <c r="Q280" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R280" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.3">
@@ -20958,7 +20960,7 @@
         <v>994</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K281">
         <v>102</v>
@@ -20973,16 +20975,16 @@
         <v>116.897696</v>
       </c>
       <c r="O281" s="3" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="P281" s="4">
         <v>733397</v>
       </c>
       <c r="Q281" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R281" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.3">
@@ -21014,7 +21016,7 @@
         <v>994</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="K282">
         <v>89.9</v>
@@ -21029,16 +21031,16 @@
         <v>105.257766</v>
       </c>
       <c r="O282" s="3" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="P282" s="4">
         <v>1096935</v>
       </c>
       <c r="Q282" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R282" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.3">
@@ -21070,7 +21072,7 @@
         <v>21</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K283">
         <v>87.37</v>
@@ -21085,16 +21087,16 @@
         <v>108.969689</v>
       </c>
       <c r="O283" s="3" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="P283" s="4">
         <v>242146</v>
       </c>
       <c r="Q283" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R283" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.3">
@@ -21123,10 +21125,10 @@
         <v>20</v>
       </c>
       <c r="I284" t="s">
-        <v>994</v>
+        <v>21</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K284">
         <v>136</v>
@@ -21141,16 +21143,16 @@
         <v>114.02211</v>
       </c>
       <c r="O284" s="3" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="P284" s="4">
         <v>678471</v>
       </c>
       <c r="Q284" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R284" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.3">
@@ -21182,7 +21184,7 @@
         <v>994</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="K285">
         <v>80</v>
@@ -21197,16 +21199,16 @@
         <v>118.89269899999999</v>
       </c>
       <c r="O285" s="3" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="P285" s="4">
         <v>283282</v>
       </c>
       <c r="Q285" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R285" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.3">
@@ -21253,16 +21255,16 @@
         <v>112.240522</v>
       </c>
       <c r="O286" s="3" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="P286" s="4">
         <v>1364775</v>
       </c>
       <c r="Q286" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R286" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.3">
@@ -21309,16 +21311,16 @@
         <v>110.383214</v>
       </c>
       <c r="O287" s="3" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="P287" s="4">
         <v>1105415</v>
       </c>
       <c r="Q287" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R287" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.3">
@@ -21365,16 +21367,16 @@
         <v>112.64920600000001</v>
       </c>
       <c r="O288" s="3" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="P288" s="4">
         <v>1296688</v>
       </c>
       <c r="Q288" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R288" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.3">
@@ -21421,16 +21423,16 @@
         <v>112.43944</v>
       </c>
       <c r="O289" s="3" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="P289" s="4">
         <v>141335</v>
       </c>
       <c r="Q289" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R289" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.3">
@@ -21477,16 +21479,16 @@
         <v>112.016654</v>
       </c>
       <c r="O290" s="3" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="P290" s="4">
         <v>296792</v>
       </c>
       <c r="Q290" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R290" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.3">
@@ -21533,16 +21535,16 @@
         <v>112.653008</v>
       </c>
       <c r="O291" s="3" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="P291" s="4">
         <v>874660</v>
       </c>
       <c r="Q291" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R291" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.3">
@@ -21589,16 +21591,16 @@
         <v>119.212132</v>
       </c>
       <c r="O292" s="3" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="P292" s="4">
         <v>491014</v>
       </c>
       <c r="Q292" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R292" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.3">
@@ -21645,16 +21647,16 @@
         <v>109.2401569</v>
       </c>
       <c r="O293" s="3" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="P293" s="4">
         <v>1849956</v>
       </c>
       <c r="Q293" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R293" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.3">
@@ -21701,16 +21703,16 @@
         <v>109.96825800000001</v>
       </c>
       <c r="O294" s="3" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="P294" s="4">
         <v>577770</v>
       </c>
       <c r="Q294" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R294" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.3">
@@ -21757,16 +21759,16 @@
         <v>103.628708</v>
       </c>
       <c r="O295" s="3" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="P295" s="4">
         <v>633649</v>
       </c>
       <c r="Q295" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R295" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.3">
@@ -21795,7 +21797,7 @@
         <v>549</v>
       </c>
       <c r="I296" t="s">
-        <v>994</v>
+        <v>21</v>
       </c>
       <c r="J296" s="1">
         <v>0</v>
@@ -21813,16 +21815,16 @@
         <v>101.438861</v>
       </c>
       <c r="O296" s="3" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="P296" s="4">
         <v>1116142</v>
       </c>
       <c r="Q296" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R296" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.3">
@@ -21869,16 +21871,16 @@
         <v>101.435382</v>
       </c>
       <c r="O297" s="3" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="P297" s="4">
         <v>1116142</v>
       </c>
       <c r="Q297" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R297" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.3">
@@ -21925,16 +21927,16 @@
         <v>110.81626900000001</v>
       </c>
       <c r="O298" s="3" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="P298" s="4">
         <v>586166</v>
       </c>
       <c r="Q298" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R298" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.3">
@@ -21981,16 +21983,16 @@
         <v>123.63088999999999</v>
       </c>
       <c r="O299" s="3" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="P299" s="4">
         <v>443349</v>
       </c>
       <c r="Q299" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R299" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.3">
@@ -22037,16 +22039,16 @@
         <v>110.459352</v>
       </c>
       <c r="O300" s="3" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="P300" s="4">
         <v>1693034</v>
       </c>
       <c r="Q300" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R300" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.3">
@@ -22093,16 +22095,16 @@
         <v>109.04513900000001</v>
       </c>
       <c r="O301" s="3" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="P301" s="4">
         <v>2049622</v>
       </c>
       <c r="Q301" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R301" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.3">
@@ -22149,16 +22151,16 @@
         <v>124.303524</v>
       </c>
       <c r="O302" s="3" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="P302" s="4">
         <v>2530492</v>
       </c>
       <c r="Q302" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R302" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.3">
@@ -22205,16 +22207,16 @@
         <v>104.782999</v>
       </c>
       <c r="O303" s="3" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="P303" s="4">
         <v>1761461</v>
       </c>
       <c r="Q303" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R303" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.3">
@@ -22261,16 +22263,16 @@
         <v>106.676568</v>
       </c>
       <c r="O304" s="3" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="P304" s="4">
         <v>1404786</v>
       </c>
       <c r="Q304" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R304" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.3">
@@ -22317,16 +22319,16 @@
         <v>98.659222</v>
       </c>
       <c r="O305" s="3" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="P305" s="4">
         <v>2530492</v>
       </c>
       <c r="Q305" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R305" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.3">
@@ -22373,16 +22375,16 @@
         <v>106.708175</v>
       </c>
       <c r="O306" s="3" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="P306" s="4">
         <v>1899515</v>
       </c>
       <c r="Q306" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R306" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.3">
@@ -22429,16 +22431,16 @@
         <v>106.688096</v>
       </c>
       <c r="O307" s="3" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="P307" s="4">
         <v>1899515</v>
       </c>
       <c r="Q307" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R307" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="308" spans="1:18" x14ac:dyDescent="0.3">
@@ -22485,16 +22487,16 @@
         <v>105.302295</v>
       </c>
       <c r="O308" s="3" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="P308" s="4">
         <v>1096935</v>
       </c>
       <c r="Q308" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R308" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="309" spans="1:18" x14ac:dyDescent="0.3">
@@ -22541,16 +22543,16 @@
         <v>107.6343</v>
       </c>
       <c r="O309" s="3" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="P309" s="4">
         <v>3723181</v>
       </c>
       <c r="Q309" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="R309" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="310" spans="1:18" x14ac:dyDescent="0.3">
@@ -22597,16 +22599,16 @@
         <v>119.62249</v>
       </c>
       <c r="O310" s="3" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="P310" s="4">
         <v>158599</v>
       </c>
       <c r="Q310" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R310" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.3">
@@ -22653,16 +22655,16 @@
         <v>106.574645</v>
       </c>
       <c r="O311" s="3" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="P311" s="4">
         <v>1899515</v>
       </c>
       <c r="Q311" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R311" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.3">
@@ -22709,16 +22711,16 @@
         <v>101.402602</v>
       </c>
       <c r="O312" s="3" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="P312" s="4">
         <v>1116142</v>
       </c>
       <c r="Q312" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R312" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="313" spans="1:18" x14ac:dyDescent="0.3">
@@ -22765,16 +22767,16 @@
         <v>110.924075</v>
       </c>
       <c r="O313" s="3" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="P313" s="4">
         <v>1074475</v>
       </c>
       <c r="Q313" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R313" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="314" spans="1:18" x14ac:dyDescent="0.3">
@@ -22821,16 +22823,16 @@
         <v>99.160880000000006</v>
       </c>
       <c r="O314" s="3" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="P314" s="4">
         <v>178524</v>
       </c>
       <c r="Q314" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R314" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="315" spans="1:18" x14ac:dyDescent="0.3">
@@ -22877,16 +22879,16 @@
         <v>117.58619299999999</v>
       </c>
       <c r="O315" s="3" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="P315" s="4">
         <v>246734</v>
       </c>
       <c r="Q315" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R315" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.3">
@@ -22933,16 +22935,16 @@
         <v>106.968514</v>
       </c>
       <c r="O316" s="3" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="P316" s="4">
         <v>2496198</v>
       </c>
       <c r="Q316" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R316" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="317" spans="1:18" x14ac:dyDescent="0.3">
@@ -22989,16 +22991,16 @@
         <v>106.975098</v>
       </c>
       <c r="O317" s="3" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="P317" s="4">
         <v>2496198</v>
       </c>
       <c r="Q317" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R317" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="318" spans="1:18" x14ac:dyDescent="0.3">
@@ -23045,16 +23047,16 @@
         <v>111.491871</v>
       </c>
       <c r="O318" s="3" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="P318" s="4">
         <v>436351</v>
       </c>
       <c r="Q318" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R318" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="319" spans="1:18" x14ac:dyDescent="0.3">
@@ -23101,16 +23103,16 @@
         <v>116.519181</v>
       </c>
       <c r="O319" s="3" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="P319" s="4">
         <v>1404343</v>
       </c>
       <c r="Q319" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R319" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="320" spans="1:18" x14ac:dyDescent="0.3">
@@ -23157,16 +23159,16 @@
         <v>107.897812</v>
       </c>
       <c r="O320" s="3" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="P320" s="4">
         <v>2770531</v>
       </c>
       <c r="Q320" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R320" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="321" spans="1:18" x14ac:dyDescent="0.3">
@@ -23213,16 +23215,16 @@
         <v>99.628338999999997</v>
       </c>
       <c r="O321" s="3" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="P321" s="4">
         <v>792179</v>
       </c>
       <c r="Q321" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R321" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="322" spans="1:18" x14ac:dyDescent="0.3">
@@ -23269,16 +23271,16 @@
         <v>107.445504</v>
       </c>
       <c r="O322" s="3" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="P322" s="4">
         <v>1029561</v>
       </c>
       <c r="Q322" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R322" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="323" spans="1:18" x14ac:dyDescent="0.3">
@@ -23325,16 +23327,16 @@
         <v>106.74329400000001</v>
       </c>
       <c r="O323" s="3" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="P323" s="4">
         <v>1927869</v>
       </c>
       <c r="Q323" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R323" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="324" spans="1:18" x14ac:dyDescent="0.3">
@@ -23381,16 +23383,16 @@
         <v>115.08147200000001</v>
       </c>
       <c r="O324" s="3" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="P324" s="4">
         <v>830236</v>
       </c>
       <c r="Q324" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R324" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.3">
@@ -23437,16 +23439,16 @@
         <v>105.261799</v>
       </c>
       <c r="O325" s="3" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="P325" s="4">
         <v>1096935</v>
       </c>
       <c r="Q325" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R325" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.3">
@@ -23493,16 +23495,16 @@
         <v>119.876328</v>
       </c>
       <c r="O326" s="3" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="P326" s="4">
         <v>382017</v>
       </c>
       <c r="Q326" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R326" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="327" spans="1:18" x14ac:dyDescent="0.3">
@@ -23549,16 +23551,16 @@
         <v>120.369246</v>
       </c>
       <c r="O327" s="3" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="P327" s="4">
         <v>377580</v>
       </c>
       <c r="Q327" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R327" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.3">
@@ -23605,16 +23607,16 @@
         <v>114.37392699999999</v>
       </c>
       <c r="O328" s="3" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="P328" s="4">
         <v>1769233</v>
       </c>
       <c r="Q328" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R328" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.3">
@@ -23661,16 +23663,16 @@
         <v>108.747607</v>
       </c>
       <c r="O329" s="3" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="P329" s="4">
         <v>348911</v>
       </c>
       <c r="Q329" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R329" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.3">
@@ -23717,16 +23719,16 @@
         <v>106.150015</v>
       </c>
       <c r="O330" s="3" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="P330" s="4">
         <v>232915</v>
       </c>
       <c r="Q330" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R330" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.3">
@@ -23740,16 +23742,16 @@
         <v>15</v>
       </c>
       <c r="D331" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E331" t="s">
         <v>1212</v>
       </c>
       <c r="F331" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="G331" t="s">
-        <v>385</v>
+        <v>1213</v>
       </c>
       <c r="H331" t="s">
         <v>549</v>
@@ -23761,51 +23763,51 @@
         <v>0</v>
       </c>
       <c r="K331">
-        <v>180</v>
+        <v>84.15</v>
       </c>
       <c r="L331">
-        <v>10416667</v>
+        <v>12083333</v>
       </c>
       <c r="M331">
-        <v>-6.8113070000000002</v>
+        <v>-2.9934639999999999</v>
       </c>
       <c r="N331">
-        <v>107.145921</v>
+        <v>120.193006</v>
       </c>
       <c r="O331" s="3" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="P331" s="4">
-        <v>2516417</v>
+        <v>184296</v>
       </c>
       <c r="Q331" t="s">
-        <v>1274</v>
+        <v>1312</v>
       </c>
       <c r="R331" t="s">
-        <v>1275</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B332" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C332" t="s">
         <v>15</v>
       </c>
       <c r="D332" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E332" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="F332" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G332" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H332" t="s">
         <v>549</v>
@@ -23817,51 +23819,51 @@
         <v>0</v>
       </c>
       <c r="K332">
-        <v>84.15</v>
+        <v>68</v>
       </c>
       <c r="L332">
-        <v>12083333</v>
+        <v>8333333</v>
       </c>
       <c r="M332">
-        <v>-2.9934639999999999</v>
+        <v>-6.8605150000000004</v>
       </c>
       <c r="N332">
-        <v>120.193006</v>
+        <v>107.918882</v>
       </c>
       <c r="O332" s="3" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="P332" s="4">
-        <v>184296</v>
+        <v>1197301</v>
       </c>
       <c r="Q332" t="s">
-        <v>1315</v>
+        <v>1271</v>
       </c>
       <c r="R332" t="s">
-        <v>1316</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B333" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C333" t="s">
         <v>15</v>
       </c>
       <c r="D333" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="E333" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="F333" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="G333" t="s">
-        <v>1220</v>
+        <v>120</v>
       </c>
       <c r="H333" t="s">
         <v>549</v>
@@ -23873,28 +23875,28 @@
         <v>0</v>
       </c>
       <c r="K333">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="L333">
-        <v>8333333</v>
+        <v>4583333</v>
       </c>
       <c r="M333">
-        <v>-6.8605150000000004</v>
+        <v>3.6130209999999998</v>
       </c>
       <c r="N333">
-        <v>107.918882</v>
+        <v>98.741460000000004</v>
       </c>
       <c r="O333" s="3" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="P333" s="4">
-        <v>1197301</v>
+        <v>2530492</v>
       </c>
       <c r="Q333" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R333" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.3">
@@ -23905,7 +23907,7 @@
         <v>1222</v>
       </c>
       <c r="C334" t="s">
-        <v>15</v>
+        <v>438</v>
       </c>
       <c r="D334" t="s">
         <v>117</v>
@@ -23917,7 +23919,7 @@
         <v>119</v>
       </c>
       <c r="G334" t="s">
-        <v>120</v>
+        <v>1224</v>
       </c>
       <c r="H334" t="s">
         <v>549</v>
@@ -23929,51 +23931,51 @@
         <v>0</v>
       </c>
       <c r="K334">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="L334">
-        <v>4583333</v>
+        <v>5000000</v>
       </c>
       <c r="M334">
-        <v>3.6130209999999998</v>
+        <v>3.7631670000000002</v>
       </c>
       <c r="N334">
-        <v>98.741460000000004</v>
+        <v>98.449181999999993</v>
       </c>
       <c r="O334" s="3" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="P334" s="4">
-        <v>2530492</v>
+        <v>1098660</v>
       </c>
       <c r="Q334" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R334" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B335" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C335" t="s">
-        <v>438</v>
+        <v>945</v>
       </c>
       <c r="D335" t="s">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="E335" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="F335" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="G335" t="s">
-        <v>1227</v>
+        <v>805</v>
       </c>
       <c r="H335" t="s">
         <v>549</v>
@@ -23985,28 +23987,28 @@
         <v>0</v>
       </c>
       <c r="K335">
-        <v>100</v>
+        <v>69.75</v>
       </c>
       <c r="L335">
-        <v>5000000</v>
+        <v>6166667</v>
       </c>
       <c r="M335">
-        <v>3.7631670000000002</v>
+        <v>-6.8986369999999999</v>
       </c>
       <c r="N335">
-        <v>98.449181999999993</v>
+        <v>107.55388499999999</v>
       </c>
       <c r="O335" s="3" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="P335" s="4">
-        <v>1098660</v>
+        <v>570829</v>
       </c>
       <c r="Q335" t="s">
-        <v>1274</v>
+        <v>1312</v>
       </c>
       <c r="R335" t="s">
-        <v>1275</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.3">
@@ -24017,19 +24019,19 @@
         <v>1229</v>
       </c>
       <c r="C336" t="s">
-        <v>945</v>
+        <v>15</v>
       </c>
       <c r="D336" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="E336" t="s">
         <v>1230</v>
       </c>
       <c r="F336" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G336" t="s">
-        <v>805</v>
+        <v>87</v>
       </c>
       <c r="H336" t="s">
         <v>549</v>
@@ -24041,28 +24043,28 @@
         <v>0</v>
       </c>
       <c r="K336">
-        <v>69.75</v>
+        <v>352</v>
       </c>
       <c r="L336">
-        <v>6166667</v>
+        <v>19166667</v>
       </c>
       <c r="M336">
-        <v>-6.8986369999999999</v>
+        <v>-6.3316720000000002</v>
       </c>
       <c r="N336">
-        <v>107.55388499999999</v>
+        <v>106.828756</v>
       </c>
       <c r="O336" s="3" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="P336" s="4">
-        <v>570829</v>
+        <v>2408480</v>
       </c>
       <c r="Q336" t="s">
-        <v>1315</v>
+        <v>1271</v>
       </c>
       <c r="R336" t="s">
-        <v>1316</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.3">
@@ -24076,16 +24078,16 @@
         <v>15</v>
       </c>
       <c r="D337" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="E337" t="s">
         <v>1233</v>
       </c>
       <c r="F337" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="G337" t="s">
-        <v>87</v>
+        <v>1234</v>
       </c>
       <c r="H337" t="s">
         <v>549</v>
@@ -24097,36 +24099,36 @@
         <v>0</v>
       </c>
       <c r="K337">
-        <v>352</v>
+        <v>121</v>
       </c>
       <c r="L337">
-        <v>19166667</v>
+        <v>12500000</v>
       </c>
       <c r="M337">
-        <v>-6.3316720000000002</v>
+        <v>2.0918670000000001</v>
       </c>
       <c r="N337">
-        <v>106.828756</v>
+        <v>99.838648000000006</v>
       </c>
       <c r="O337" s="3" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="P337" s="4">
-        <v>2408480</v>
+        <v>506673</v>
       </c>
       <c r="Q337" t="s">
-        <v>1274</v>
+        <v>1312</v>
       </c>
       <c r="R337" t="s">
-        <v>1275</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="338" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B338" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C338" t="s">
         <v>15</v>
@@ -24135,13 +24137,13 @@
         <v>117</v>
       </c>
       <c r="E338" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F338" t="s">
         <v>119</v>
       </c>
       <c r="G338" t="s">
-        <v>1237</v>
+        <v>120</v>
       </c>
       <c r="H338" t="s">
         <v>549</v>
@@ -24153,28 +24155,28 @@
         <v>0</v>
       </c>
       <c r="K338">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="L338">
-        <v>12500000</v>
+        <v>6666667</v>
       </c>
       <c r="M338">
-        <v>2.0918670000000001</v>
+        <v>3.5676420000000002</v>
       </c>
       <c r="N338">
-        <v>99.838648000000006</v>
+        <v>98.650711999999999</v>
       </c>
       <c r="O338" s="3" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="P338" s="4">
-        <v>506673</v>
+        <v>2530492</v>
       </c>
       <c r="Q338" t="s">
-        <v>1315</v>
+        <v>1271</v>
       </c>
       <c r="R338" t="s">
-        <v>1316</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.3">
@@ -24188,16 +24190,16 @@
         <v>15</v>
       </c>
       <c r="D339" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="E339" t="s">
         <v>1240</v>
       </c>
       <c r="F339" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="G339" t="s">
-        <v>120</v>
+        <v>1241</v>
       </c>
       <c r="H339" t="s">
         <v>549</v>
@@ -24209,51 +24211,51 @@
         <v>0</v>
       </c>
       <c r="K339">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L339">
-        <v>6666667</v>
+        <v>7500000</v>
       </c>
       <c r="M339">
-        <v>3.5676420000000002</v>
+        <v>-4.3561820000000004</v>
       </c>
       <c r="N339">
-        <v>98.650711999999999</v>
+        <v>119.888642</v>
       </c>
       <c r="O339" s="3" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="P339" s="4">
-        <v>2530492</v>
+        <v>240664</v>
       </c>
       <c r="Q339" t="s">
-        <v>1274</v>
+        <v>1312</v>
       </c>
       <c r="R339" t="s">
-        <v>1275</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="340" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B340" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="C340" t="s">
         <v>15</v>
       </c>
       <c r="D340" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E340" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F340" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G340" t="s">
-        <v>1244</v>
+        <v>48</v>
       </c>
       <c r="H340" t="s">
         <v>549</v>
@@ -24265,28 +24267,28 @@
         <v>0</v>
       </c>
       <c r="K340">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="L340">
-        <v>7500000</v>
+        <v>11350000</v>
       </c>
       <c r="M340">
-        <v>-4.3561820000000004</v>
+        <v>-6.919638</v>
       </c>
       <c r="N340">
-        <v>119.888642</v>
+        <v>107.569948</v>
       </c>
       <c r="O340" s="3" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="P340" s="4">
-        <v>240664</v>
+        <v>2555187</v>
       </c>
       <c r="Q340" t="s">
-        <v>1315</v>
+        <v>1271</v>
       </c>
       <c r="R340" t="s">
-        <v>1316</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.3">
@@ -24300,16 +24302,16 @@
         <v>15</v>
       </c>
       <c r="D341" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E341" t="s">
         <v>1247</v>
       </c>
       <c r="F341" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="G341" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="H341" t="s">
         <v>549</v>
@@ -24324,33 +24326,33 @@
         <v>71</v>
       </c>
       <c r="L341">
-        <v>11350000</v>
+        <v>16666667</v>
       </c>
       <c r="M341">
-        <v>-6.919638</v>
+        <v>-0.49393900000000002</v>
       </c>
       <c r="N341">
-        <v>107.569948</v>
+        <v>117.15514</v>
       </c>
       <c r="O341" s="3" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="P341" s="4">
-        <v>2555187</v>
+        <v>856361</v>
       </c>
       <c r="Q341" t="s">
-        <v>1274</v>
+        <v>1312</v>
       </c>
       <c r="R341" t="s">
-        <v>1275</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A342" t="s">
+      <c r="A342">
+        <v>0</v>
+      </c>
+      <c r="B342" t="s">
         <v>1248</v>
-      </c>
-      <c r="B342" t="s">
-        <v>1249</v>
       </c>
       <c r="C342" t="s">
         <v>15</v>
@@ -24359,13 +24361,13 @@
         <v>61</v>
       </c>
       <c r="E342" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F342" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="G342" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="H342" t="s">
         <v>549</v>
@@ -24377,28 +24379,28 @@
         <v>0</v>
       </c>
       <c r="K342">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L342">
-        <v>16666667</v>
+        <v>7500000</v>
       </c>
       <c r="M342">
-        <v>-0.49393900000000002</v>
+        <v>1.5285683000000001</v>
       </c>
       <c r="N342">
-        <v>117.15514</v>
+        <v>124.92305279999999</v>
       </c>
       <c r="O342" s="3" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="P342" s="4">
-        <v>856361</v>
+        <v>478194</v>
       </c>
       <c r="Q342" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R342" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.3">
@@ -24406,25 +24408,22 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>1251</v>
+        <v>1612</v>
       </c>
       <c r="C343" t="s">
         <v>15</v>
       </c>
       <c r="D343" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E343" t="s">
-        <v>1252</v>
+        <v>1613</v>
       </c>
       <c r="F343" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="G343" t="s">
-        <v>110</v>
-      </c>
-      <c r="H343" t="s">
-        <v>549</v>
+        <v>179</v>
       </c>
       <c r="I343" t="s">
         <v>994</v>
@@ -24433,28 +24432,28 @@
         <v>0</v>
       </c>
       <c r="K343">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L343">
-        <v>7500000</v>
-      </c>
-      <c r="M343">
-        <v>1.5285683000000001</v>
+        <v>3334000</v>
+      </c>
+      <c r="M343" s="6">
+        <v>-8.6146250000000002</v>
       </c>
       <c r="N343">
-        <v>124.92305279999999</v>
-      </c>
-      <c r="O343" s="3" t="s">
-        <v>1615</v>
-      </c>
-      <c r="P343" s="4">
-        <v>478194</v>
+        <v>116.09873</v>
+      </c>
+      <c r="O343" t="s">
+        <v>1614</v>
+      </c>
+      <c r="P343" s="5">
+        <v>452812</v>
       </c>
       <c r="Q343" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="R343" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
   </sheetData>

--- a/output/stores_complete.xlsx
+++ b/output/stores_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6B556F-87AC-4B3A-9481-8C16E0F68601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601681B9-FA88-40E1-A20A-7DF18FF13BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4909,25 +4909,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="23"/>
-      </right>
-      <top style="thin">
-        <color indexed="23"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="23"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -4965,7 +4952,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4976,16 +4963,17 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5317,8 +5305,8 @@
     <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="255.77734375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.109375" bestFit="1" customWidth="1"/>
@@ -21089,10 +21077,10 @@
       <c r="L282">
         <v>6250000</v>
       </c>
-      <c r="M282" s="9">
+      <c r="M282" s="8">
         <v>-7.7657980000000002</v>
       </c>
-      <c r="N282" s="8">
+      <c r="N282" s="12">
         <v>112.189042</v>
       </c>
       <c r="O282" s="3" t="s">
@@ -21313,11 +21301,11 @@
       <c r="L286">
         <v>10500000</v>
       </c>
-      <c r="M286">
-        <v>-7.8333089999999999</v>
-      </c>
-      <c r="N286">
-        <v>112.016654</v>
+      <c r="M286" s="7">
+        <v>-7.7648576</v>
+      </c>
+      <c r="N286" s="11">
+        <v>112.1865755</v>
       </c>
       <c r="O286" s="3" t="s">
         <v>1533</v>
@@ -24245,7 +24233,7 @@
       </c>
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A339" s="10" t="s">
+      <c r="A339" s="9" t="s">
         <v>1596</v>
       </c>
       <c r="B339" t="s">
@@ -24281,10 +24269,10 @@
       <c r="L339">
         <v>10000000</v>
       </c>
-      <c r="M339" s="11">
+      <c r="M339" s="10">
         <v>-7.7794319999999999</v>
       </c>
-      <c r="N339" s="11">
+      <c r="N339" s="10">
         <v>110.338553</v>
       </c>
       <c r="O339" s="3" t="s">

--- a/output/stores_complete.xlsx
+++ b/output/stores_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601681B9-FA88-40E1-A20A-7DF18FF13BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6735EA95-EF88-44C5-A075-07AD92F3E8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$339</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$337</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4287" uniqueCount="1602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4264" uniqueCount="1595">
   <si>
     <t>Store ID</t>
   </si>
@@ -3656,15 +3656,6 @@
     <t>Jl. Mahar Martanegara No.22, Cigugur Tengah, Kec. Cimahi Tengah, Kota Cimahi, Jawa Barat 40522</t>
   </si>
   <si>
-    <t>SQID00424</t>
-  </si>
-  <si>
-    <t>Xiaomi Authorized Store Av. Jeruk Raya Jagakarsa Jakarta Indonesia</t>
-  </si>
-  <si>
-    <t>Jl. Jeruk Raya No.164, RT.13/RW.1, Jagakarsa, Kec. Jagakarsa, Kota Jakarta Selatan, Daerah Khusus Ibukota Jakarta 12620</t>
-  </si>
-  <si>
     <t>SQID00423</t>
   </si>
   <si>
@@ -3716,12 +3707,6 @@
     <t>Jl. Kyai Haji Ahmad Dahlan, Sungai Pinang Luar, Kec. Samarinda Kota, Kota Samarinda, Kalimantan Timur 75242</t>
   </si>
   <si>
-    <t>Xiaomi Authorized Store Av. Paniki Manado Indonesia</t>
-  </si>
-  <si>
-    <t>Jl. A.A. Maramis No.141, Paniki Bawah, Kec. Mapanget, Kota Manado, Sulawesi Utara 95370</t>
-  </si>
-  <si>
     <t>Grade</t>
   </si>
   <si>
@@ -4772,9 +4757,6 @@
     <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Cimindi%20Cimahi%20Indonesia%20Jl.%20Mahar%20Martanegara%20No.22%2C%20Cigugur%20Tengah%2C%20Kec.%20Cimahi%20Tengah%2C%20Kota%20Cimahi%2C%20Jawa%20Barat%2040522</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Jeruk%20Raya%20Jagakarsa%20Jakarta%20Indonesia%20Jl.%20Jeruk%20Raya%20No.164%2C%20RT.13/RW.1%2C%20Jagakarsa%2C%20Kec.%20Jagakarsa%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2012620</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20A%20Yani%20Rantau%20Prapat%20Indonesia%20Jl.%20Jend.%20Ahmad%20Yani%20No.50D%2C%20Bakaran%20Batu%2C%20Kec.%20Rantau%20Sel.%2C%20Kab.%20Labuhanbatu%2C%20Sumatera%20Utara%2021411</t>
   </si>
   <si>
@@ -4788,9 +4770,6 @@
   </si>
   <si>
     <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Ahmad%20Dahlan%20Samarinda%20Indonesia%20Jl.%20Kyai%20Haji%20Ahmad%20Dahlan%2C%20Sungai%20Pinang%20Luar%2C%20Kec.%20Samarinda%20Kota%2C%20Kota%20Samarinda%2C%20Kalimantan%20Timur%2075242</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Paniki%20Manado%20Indonesia%20Jl.%20A.A.%20Maramis%20No.141%2C%20Paniki%20Bawah%2C%20Kec.%20Mapanget%2C%20Kota%20Manado%2C%20Sulawesi%20Utara%2095370</t>
   </si>
   <si>
     <t>Xiaomi Authorized Store Av. Gajah Mada Jempong Mataram Indonesia</t>
@@ -5290,7 +5269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R339"/>
+  <dimension ref="A1:R337"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -5342,7 +5321,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -5357,16 +5336,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="P1" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="Q1" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="R1" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -5398,7 +5377,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K2">
         <v>137</v>
@@ -5413,16 +5392,16 @@
         <v>106.90817</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="P2" s="4">
         <v>1876057</v>
       </c>
       <c r="Q2" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R2" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -5454,7 +5433,7 @@
         <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K3">
         <v>84</v>
@@ -5469,16 +5448,16 @@
         <v>107.001076</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="P3" s="4">
         <v>2496198</v>
       </c>
       <c r="Q3" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R3" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -5510,7 +5489,7 @@
         <v>21</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K4">
         <v>88</v>
@@ -5525,16 +5504,16 @@
         <v>106.82447999999999</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="P4" s="4">
         <v>5495373</v>
       </c>
       <c r="Q4" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R4" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -5566,7 +5545,7 @@
         <v>21</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K5">
         <v>103</v>
@@ -5581,16 +5560,16 @@
         <v>106.791349</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="P5" s="4">
         <v>2615945</v>
       </c>
       <c r="Q5" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R5" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -5622,7 +5601,7 @@
         <v>21</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K6">
         <v>86</v>
@@ -5637,16 +5616,16 @@
         <v>106.630724</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="P6" s="4">
         <v>3286420</v>
       </c>
       <c r="Q6" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R6" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -5678,7 +5657,7 @@
         <v>21</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K7">
         <v>75</v>
@@ -5693,16 +5672,16 @@
         <v>106.821789</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="P7" s="4">
         <v>1109489</v>
       </c>
       <c r="Q7" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R7" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -5734,7 +5713,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K8">
         <v>188</v>
@@ -5749,16 +5728,16 @@
         <v>107.608763</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="P8" s="4">
         <v>2555187</v>
       </c>
       <c r="Q8" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R8" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -5790,7 +5769,7 @@
         <v>21</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K9">
         <v>162</v>
@@ -5805,16 +5784,16 @@
         <v>106.80481</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="P9" s="4">
         <v>1122771</v>
       </c>
       <c r="Q9" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R9" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -5846,7 +5825,7 @@
         <v>21</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -5861,16 +5840,16 @@
         <v>112.67453399999999</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="P10" s="4">
         <v>3000075</v>
       </c>
       <c r="Q10" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R10" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -5902,7 +5881,7 @@
         <v>21</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K11">
         <v>76</v>
@@ -5917,16 +5896,16 @@
         <v>119.441374</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="P11" s="4">
         <v>1470262</v>
       </c>
       <c r="Q11" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R11" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -5958,7 +5937,7 @@
         <v>21</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K12">
         <v>62</v>
@@ -5973,16 +5952,16 @@
         <v>112.738867</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="P12" s="4">
         <v>3000075</v>
       </c>
       <c r="Q12" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R12" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -6014,7 +5993,7 @@
         <v>21</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K13">
         <v>63</v>
@@ -6029,16 +6008,16 @@
         <v>110.392461</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="P13" s="4">
         <v>1105415</v>
       </c>
       <c r="Q13" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R13" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -6070,7 +6049,7 @@
         <v>21</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K14">
         <v>53</v>
@@ -6085,16 +6064,16 @@
         <v>106.82740099999999</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="P14" s="4">
         <v>1927869</v>
       </c>
       <c r="Q14" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R14" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -6126,7 +6105,7 @@
         <v>21</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K15">
         <v>135</v>
@@ -6141,16 +6120,16 @@
         <v>106.72765</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="P15" s="4">
         <v>1404786</v>
       </c>
       <c r="Q15" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R15" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -6182,7 +6161,7 @@
         <v>21</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K16">
         <v>99</v>
@@ -6197,16 +6176,16 @@
         <v>106.79073</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="P16" s="4">
         <v>1876057</v>
       </c>
       <c r="Q16" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R16" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -6238,7 +6217,7 @@
         <v>21</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K17">
         <v>104</v>
@@ -6253,16 +6232,16 @@
         <v>106.783115</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="P17" s="4">
         <v>2408480</v>
       </c>
       <c r="Q17" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R17" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -6294,7 +6273,7 @@
         <v>21</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K18">
         <v>72</v>
@@ -6309,16 +6288,16 @@
         <v>106.73880699999999</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="P18" s="4">
         <v>2615945</v>
       </c>
       <c r="Q18" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R18" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -6350,7 +6329,7 @@
         <v>21</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K19">
         <v>64</v>
@@ -6365,16 +6344,16 @@
         <v>119.417417</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="P19" s="4">
         <v>1470262</v>
       </c>
       <c r="Q19" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R19" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -6406,7 +6385,7 @@
         <v>21</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K20">
         <v>95</v>
@@ -6421,16 +6400,16 @@
         <v>107.13300099999999</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="P20" s="4">
         <v>3172831</v>
       </c>
       <c r="Q20" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R20" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -6462,7 +6441,7 @@
         <v>21</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K21">
         <v>115</v>
@@ -6477,16 +6456,16 @@
         <v>112.77826899999999</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
       <c r="P21" s="4">
         <v>3000075</v>
       </c>
       <c r="Q21" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R21" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -6518,7 +6497,7 @@
         <v>21</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -6533,16 +6512,16 @@
         <v>112.62235699999999</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>1264</v>
+        <v>1259</v>
       </c>
       <c r="P22" s="4">
         <v>874660</v>
       </c>
       <c r="Q22" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R22" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -6574,7 +6553,7 @@
         <v>21</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K23">
         <v>51</v>
@@ -6589,16 +6568,16 @@
         <v>124.835188</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="P23" s="4">
         <v>478194</v>
       </c>
       <c r="Q23" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R23" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -6630,7 +6609,7 @@
         <v>21</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K24">
         <v>118</v>
@@ -6645,16 +6624,16 @@
         <v>107.591256</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="P24" s="4">
         <v>2555187</v>
       </c>
       <c r="Q24" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R24" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -6686,7 +6665,7 @@
         <v>21</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K25">
         <v>115</v>
@@ -6701,16 +6680,16 @@
         <v>98.674274999999994</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="P25" s="4">
         <v>2530492</v>
       </c>
       <c r="Q25" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R25" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -6742,7 +6721,7 @@
         <v>21</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K26">
         <v>82</v>
@@ -6757,16 +6736,16 @@
         <v>107.636404</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="P26" s="4">
         <v>2555187</v>
       </c>
       <c r="Q26" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R26" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -6798,7 +6777,7 @@
         <v>21</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K27">
         <v>116</v>
@@ -6813,16 +6792,16 @@
         <v>106.73313899999999</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="P27" s="4">
         <v>2615945</v>
       </c>
       <c r="Q27" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R27" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -6854,7 +6833,7 @@
         <v>21</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K28">
         <v>122</v>
@@ -6869,16 +6848,16 @@
         <v>106.979793</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="P28" s="4">
         <v>5495373</v>
       </c>
       <c r="Q28" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R28" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -6910,7 +6889,7 @@
         <v>21</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K29">
         <v>62</v>
@@ -6925,16 +6904,16 @@
         <v>117.115939</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="P29" s="4">
         <v>856361</v>
       </c>
       <c r="Q29" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R29" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -6966,7 +6945,7 @@
         <v>21</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K30">
         <v>101</v>
@@ -6981,16 +6960,16 @@
         <v>98.672222000000005</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="P30" s="4">
         <v>2530492</v>
       </c>
       <c r="Q30" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R30" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -7022,7 +7001,7 @@
         <v>21</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K31">
         <v>128</v>
@@ -7037,16 +7016,16 @@
         <v>106.64401700000001</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="P31" s="4">
         <v>3286420</v>
       </c>
       <c r="Q31" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R31" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -7078,7 +7057,7 @@
         <v>21</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K32">
         <v>45</v>
@@ -7093,16 +7072,16 @@
         <v>110.423447</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="P32" s="4">
         <v>1693034</v>
       </c>
       <c r="Q32" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R32" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
@@ -7134,7 +7113,7 @@
         <v>21</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K33">
         <v>125</v>
@@ -7149,16 +7128,16 @@
         <v>124.837932</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="P33" s="4">
         <v>478194</v>
       </c>
       <c r="Q33" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R33" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
@@ -7190,7 +7169,7 @@
         <v>21</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K34">
         <v>107</v>
@@ -7205,16 +7184,16 @@
         <v>107.27939499999999</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="P34" s="4">
         <v>2519882</v>
       </c>
       <c r="Q34" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R34" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
@@ -7246,7 +7225,7 @@
         <v>21</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K35">
         <v>48</v>
@@ -7261,16 +7240,16 @@
         <v>106.89216500000001</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="P35" s="4">
         <v>1876057</v>
       </c>
       <c r="Q35" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R35" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
@@ -7302,7 +7281,7 @@
         <v>21</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K36">
         <v>107</v>
@@ -7317,16 +7296,16 @@
         <v>110.39756800000001</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="P36" s="4">
         <v>1105415</v>
       </c>
       <c r="Q36" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R36" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
@@ -7358,7 +7337,7 @@
         <v>21</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K37">
         <v>76</v>
@@ -7373,16 +7352,16 @@
         <v>106.901945</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="P37" s="4">
         <v>1927869</v>
       </c>
       <c r="Q37" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R37" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
@@ -7414,7 +7393,7 @@
         <v>21</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -7429,16 +7408,16 @@
         <v>106.0642</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="P38" s="4">
         <v>464716</v>
       </c>
       <c r="Q38" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R38" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
@@ -7470,7 +7449,7 @@
         <v>21</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K39">
         <v>130</v>
@@ -7485,16 +7464,16 @@
         <v>108.552183</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="P39" s="4">
         <v>348911</v>
       </c>
       <c r="Q39" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R39" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
@@ -7526,7 +7505,7 @@
         <v>21</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K40">
         <v>64</v>
@@ -7541,16 +7520,16 @@
         <v>106.900447</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="P40" s="4">
         <v>3310145</v>
       </c>
       <c r="Q40" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R40" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
@@ -7582,7 +7561,7 @@
         <v>21</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K41">
         <v>69</v>
@@ -7597,16 +7576,16 @@
         <v>116.10522</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="P41" s="4">
         <v>452812</v>
       </c>
       <c r="Q41" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R41" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
@@ -7638,7 +7617,7 @@
         <v>21</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K42">
         <v>49</v>
@@ -7653,16 +7632,16 @@
         <v>110.41570900000001</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="P42" s="4">
         <v>1693034</v>
       </c>
       <c r="Q42" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R42" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
@@ -7694,7 +7673,7 @@
         <v>21</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K43">
         <v>79</v>
@@ -7709,16 +7688,16 @@
         <v>106.653631</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="P43" s="4">
         <v>1404786</v>
       </c>
       <c r="Q43" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R43" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
@@ -7750,7 +7729,7 @@
         <v>21</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K44">
         <v>87</v>
@@ -7762,16 +7741,16 @@
         <v>106.869567</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="P44" s="4">
         <v>3310145</v>
       </c>
       <c r="Q44" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R44" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
@@ -7803,7 +7782,7 @@
         <v>21</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K45">
         <v>95</v>
@@ -7818,16 +7797,16 @@
         <v>115.21697</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="P45" s="4">
         <v>660984</v>
       </c>
       <c r="Q45" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R45" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
@@ -7859,7 +7838,7 @@
         <v>21</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K46">
         <v>64</v>
@@ -7874,16 +7853,16 @@
         <v>110.41233699999999</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="P46" s="4">
         <v>1693034</v>
       </c>
       <c r="Q46" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R46" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
@@ -7915,7 +7894,7 @@
         <v>21</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K47">
         <v>93</v>
@@ -7930,16 +7909,16 @@
         <v>106.74499400000001</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="P47" s="4">
         <v>1927869</v>
       </c>
       <c r="Q47" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R47" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
@@ -7971,7 +7950,7 @@
         <v>21</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K48">
         <v>129</v>
@@ -7986,16 +7965,16 @@
         <v>109.345662</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="P48" s="4">
         <v>676096</v>
       </c>
       <c r="Q48" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R48" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -8027,7 +8006,7 @@
         <v>21</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K49">
         <v>68</v>
@@ -8042,16 +8021,16 @@
         <v>104.741816</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="P49" s="4">
         <v>1761461</v>
       </c>
       <c r="Q49" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R49" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
@@ -8083,7 +8062,7 @@
         <v>21</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K50">
         <v>106</v>
@@ -8098,16 +8077,16 @@
         <v>115.230413</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="P50" s="4">
         <v>660984</v>
       </c>
       <c r="Q50" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R50" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
@@ -8139,7 +8118,7 @@
         <v>21</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K51">
         <v>82</v>
@@ -8154,16 +8133,16 @@
         <v>112.734624</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="P51" s="4">
         <v>3000075</v>
       </c>
       <c r="Q51" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R51" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
@@ -8195,7 +8174,7 @@
         <v>21</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K52">
         <v>78</v>
@@ -8210,16 +8189,16 @@
         <v>109.23649500000001</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="P52" s="4">
         <v>1849956</v>
       </c>
       <c r="Q52" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R52" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
@@ -8251,7 +8230,7 @@
         <v>21</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K53">
         <v>96</v>
@@ -8266,16 +8245,16 @@
         <v>107.69852</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="P53" s="4">
         <v>2555187</v>
       </c>
       <c r="Q53" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R53" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
@@ -8307,7 +8286,7 @@
         <v>21</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K54">
         <v>72</v>
@@ -8322,16 +8301,16 @@
         <v>106.18141300000001</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="P54" s="4">
         <v>730530</v>
       </c>
       <c r="Q54" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R54" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
@@ -8363,7 +8342,7 @@
         <v>21</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K55">
         <v>92</v>
@@ -8378,16 +8357,16 @@
         <v>110.809951</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="P55" s="4">
         <v>586166</v>
       </c>
       <c r="Q55" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R55" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
@@ -8419,7 +8398,7 @@
         <v>21</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K56">
         <v>60</v>
@@ -8434,16 +8413,16 @@
         <v>106.82659</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="P56" s="4">
         <v>2408480</v>
       </c>
       <c r="Q56" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R56" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
@@ -8475,7 +8454,7 @@
         <v>21</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K57">
         <v>70</v>
@@ -8490,16 +8469,16 @@
         <v>114.600335</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="P57" s="4">
         <v>675916</v>
       </c>
       <c r="Q57" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R57" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
@@ -8531,7 +8510,7 @@
         <v>21</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K58">
         <v>140</v>
@@ -8546,16 +8525,16 @@
         <v>107.610801</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="P58" s="4">
         <v>2555187</v>
       </c>
       <c r="Q58" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R58" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
@@ -8587,7 +8566,7 @@
         <v>21</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K59">
         <v>73</v>
@@ -8602,16 +8581,16 @@
         <v>108.55003499999999</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="P59" s="4">
         <v>348911</v>
       </c>
       <c r="Q59" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R59" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
@@ -8643,7 +8622,7 @@
         <v>21</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K60">
         <v>90</v>
@@ -8658,16 +8637,16 @@
         <v>106.52486500000001</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="P60" s="4">
         <v>3286420</v>
       </c>
       <c r="Q60" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R60" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
@@ -8699,7 +8678,7 @@
         <v>21</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K61">
         <v>76</v>
@@ -8714,16 +8693,16 @@
         <v>106.839957</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="P61" s="4">
         <v>2408480</v>
       </c>
       <c r="Q61" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R61" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
@@ -8755,7 +8734,7 @@
         <v>21</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K62">
         <v>93</v>
@@ -8770,16 +8749,16 @@
         <v>110.362371</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="P62" s="4">
         <v>1105415</v>
       </c>
       <c r="Q62" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R62" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
@@ -8811,7 +8790,7 @@
         <v>21</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K63">
         <v>133</v>
@@ -8826,16 +8805,16 @@
         <v>106.74262899999999</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="P63" s="4">
         <v>1404786</v>
       </c>
       <c r="Q63" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R63" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
@@ -8867,7 +8846,7 @@
         <v>21</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K64">
         <v>90</v>
@@ -8882,16 +8861,16 @@
         <v>105.253226</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="P64" s="4">
         <v>1096935</v>
       </c>
       <c r="Q64" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R64" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
@@ -8923,7 +8902,7 @@
         <v>21</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K65">
         <v>99</v>
@@ -8938,16 +8917,16 @@
         <v>95.306488999999999</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="P65" s="4">
         <v>257315</v>
       </c>
       <c r="Q65" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R65" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
@@ -8979,7 +8958,7 @@
         <v>21</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K66">
         <v>64</v>
@@ -8994,16 +8973,16 @@
         <v>101.41777</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="P66" s="4">
         <v>1116142</v>
       </c>
       <c r="Q66" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R66" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
@@ -9035,7 +9014,7 @@
         <v>21</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -9050,16 +9029,16 @@
         <v>106.792402</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="P67" s="4">
         <v>2615945</v>
       </c>
       <c r="Q67" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R67" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.3">
@@ -9091,7 +9070,7 @@
         <v>21</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K68">
         <v>89</v>
@@ -9106,16 +9085,16 @@
         <v>110.224767</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="P68" s="4">
         <v>1324756</v>
       </c>
       <c r="Q68" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R68" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.3">
@@ -9147,7 +9126,7 @@
         <v>21</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K69">
         <v>80</v>
@@ -9162,16 +9141,16 @@
         <v>100.35557900000001</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="P69" s="4">
         <v>928539</v>
       </c>
       <c r="Q69" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R69" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.3">
@@ -9203,7 +9182,7 @@
         <v>21</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K70">
         <v>69</v>
@@ -9218,16 +9197,16 @@
         <v>112.01577899999999</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="P70" s="4">
         <v>296792</v>
       </c>
       <c r="Q70" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R70" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.3">
@@ -9259,7 +9238,7 @@
         <v>21</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K71">
         <v>66</v>
@@ -9274,16 +9253,16 @@
         <v>108.21763300000001</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="P71" s="4">
         <v>752545</v>
       </c>
       <c r="Q71" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R71" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
@@ -9315,7 +9294,7 @@
         <v>21</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -9330,16 +9309,16 @@
         <v>112.69844399999999</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="P72" s="4">
         <v>1982939</v>
       </c>
       <c r="Q72" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R72" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.3">
@@ -9371,7 +9350,7 @@
         <v>21</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K73">
         <v>92</v>
@@ -9386,16 +9365,16 @@
         <v>116.858486</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="P73" s="4">
         <v>733397</v>
       </c>
       <c r="Q73" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R73" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
@@ -9427,7 +9406,7 @@
         <v>21</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K74">
         <v>66</v>
@@ -9442,16 +9421,16 @@
         <v>115.182802</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="P74" s="4">
         <v>660984</v>
       </c>
       <c r="Q74" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R74" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
@@ -9483,7 +9462,7 @@
         <v>21</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K75">
         <v>64</v>
@@ -9498,16 +9477,16 @@
         <v>113.66279</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="P75" s="4">
         <v>2590289</v>
       </c>
       <c r="Q75" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R75" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
@@ -9539,7 +9518,7 @@
         <v>21</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K76">
         <v>70</v>
@@ -9554,16 +9533,16 @@
         <v>106.84590300000001</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="P76" s="4">
         <v>5495373</v>
       </c>
       <c r="Q76" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R76" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
@@ -9595,7 +9574,7 @@
         <v>21</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K77">
         <v>80</v>
@@ -9610,16 +9589,16 @@
         <v>106.9717</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="P77" s="4">
         <v>2496198</v>
       </c>
       <c r="Q77" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R77" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
@@ -9651,7 +9630,7 @@
         <v>21</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K78">
         <v>46</v>
@@ -9666,16 +9645,16 @@
         <v>107.292214</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="P78" s="4">
         <v>2519882</v>
       </c>
       <c r="Q78" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R78" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
@@ -9707,7 +9686,7 @@
         <v>21</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K79">
         <v>101</v>
@@ -9722,16 +9701,16 @@
         <v>106.82342</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="P79" s="4">
         <v>2408480</v>
       </c>
       <c r="Q79" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R79" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
@@ -9763,7 +9742,7 @@
         <v>21</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K80">
         <v>150</v>
@@ -9778,16 +9757,16 @@
         <v>112.601688</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="P80" s="4">
         <v>1296688</v>
       </c>
       <c r="Q80" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R80" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
@@ -9819,7 +9798,7 @@
         <v>21</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K81">
         <v>51</v>
@@ -9834,16 +9813,16 @@
         <v>107.586242</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="P81" s="4">
         <v>2555187</v>
       </c>
       <c r="Q81" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R81" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
@@ -9875,7 +9854,7 @@
         <v>21</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K82">
         <v>72</v>
@@ -9890,16 +9869,16 @@
         <v>102.267369</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="P82" s="4">
         <v>385511</v>
       </c>
       <c r="Q82" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R82" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
@@ -9931,7 +9910,7 @@
         <v>21</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K83">
         <v>84</v>
@@ -9946,16 +9925,16 @@
         <v>128.198103</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="P83" s="4">
         <v>354052</v>
       </c>
       <c r="Q83" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R83" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
@@ -9987,7 +9966,7 @@
         <v>21</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K84">
         <v>60</v>
@@ -10002,16 +9981,16 @@
         <v>119.554146</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="P84" s="4">
         <v>394615</v>
       </c>
       <c r="Q84" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R84" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
@@ -10043,7 +10022,7 @@
         <v>21</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K85">
         <v>57</v>
@@ -10058,16 +10037,16 @@
         <v>106.88909200000001</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="P85" s="4">
         <v>3310145</v>
       </c>
       <c r="Q85" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R85" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
@@ -10099,7 +10078,7 @@
         <v>21</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K86">
         <v>66</v>
@@ -10114,16 +10093,16 @@
         <v>110.432253</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="P86" s="4">
         <v>1693034</v>
       </c>
       <c r="Q86" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R86" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
@@ -10155,7 +10134,7 @@
         <v>21</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K87">
         <v>67</v>
@@ -10170,16 +10149,16 @@
         <v>106.818022</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="P87" s="4">
         <v>1109489</v>
       </c>
       <c r="Q87" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R87" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
@@ -10211,7 +10190,7 @@
         <v>21</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K88">
         <v>83</v>
@@ -10226,16 +10205,16 @@
         <v>104.79156399999999</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="P88" s="4">
         <v>844108</v>
       </c>
       <c r="Q88" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R88" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
@@ -10267,7 +10246,7 @@
         <v>21</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K89">
         <v>63</v>
@@ -10282,16 +10261,16 @@
         <v>117.154967</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="P89" s="4">
         <v>856361</v>
       </c>
       <c r="Q89" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R89" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.3">
@@ -10323,7 +10302,7 @@
         <v>21</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K90">
         <v>118</v>
@@ -10338,16 +10317,16 @@
         <v>106.982479</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="P90" s="4">
         <v>2496198</v>
       </c>
       <c r="Q90" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R90" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
@@ -10379,7 +10358,7 @@
         <v>21</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K91">
         <v>118</v>
@@ -10394,16 +10373,16 @@
         <v>98.626718999999994</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="P91" s="4">
         <v>2530492</v>
       </c>
       <c r="Q91" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R91" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
@@ -10435,7 +10414,7 @@
         <v>21</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K92">
         <v>100</v>
@@ -10450,16 +10429,16 @@
         <v>98.663635999999997</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="P92" s="4">
         <v>2530492</v>
       </c>
       <c r="Q92" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R92" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.3">
@@ -10491,7 +10470,7 @@
         <v>21</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K93">
         <v>112</v>
@@ -10506,16 +10485,16 @@
         <v>106.993112</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="P93" s="4">
         <v>2496198</v>
       </c>
       <c r="Q93" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R93" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
@@ -10547,7 +10526,7 @@
         <v>21</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K94">
         <v>40</v>
@@ -10562,16 +10541,16 @@
         <v>112.443512</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="P94" s="4">
         <v>141335</v>
       </c>
       <c r="Q94" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R94" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
@@ -10603,7 +10582,7 @@
         <v>21</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K95">
         <v>124</v>
@@ -10618,16 +10597,16 @@
         <v>106.989428</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="P95" s="4">
         <v>2496198</v>
       </c>
       <c r="Q95" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R95" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
@@ -10659,7 +10638,7 @@
         <v>21</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K96">
         <v>104</v>
@@ -10674,16 +10653,16 @@
         <v>107.13134599999999</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="P96" s="4">
         <v>2516417</v>
       </c>
       <c r="Q96" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R96" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
@@ -10715,7 +10694,7 @@
         <v>21</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K97">
         <v>70</v>
@@ -10730,16 +10709,16 @@
         <v>110.816699</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="P97" s="4">
         <v>908228</v>
       </c>
       <c r="Q97" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R97" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.3">
@@ -10771,7 +10750,7 @@
         <v>21</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K98">
         <v>69</v>
@@ -10786,16 +10765,16 @@
         <v>112.749994</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="P98" s="4">
         <v>3000075</v>
       </c>
       <c r="Q98" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R98" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.3">
@@ -10827,7 +10806,7 @@
         <v>21</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K99">
         <v>58</v>
@@ -10842,16 +10821,16 @@
         <v>119.450033</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="P99" s="4">
         <v>1470262</v>
       </c>
       <c r="Q99" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R99" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.3">
@@ -10883,7 +10862,7 @@
         <v>21</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K100">
         <v>89</v>
@@ -10898,16 +10877,16 @@
         <v>112.72849100000001</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="P100" s="4">
         <v>3000075</v>
       </c>
       <c r="Q100" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R100" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.3">
@@ -10939,7 +10918,7 @@
         <v>21</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K101">
         <v>80</v>
@@ -10954,16 +10933,16 @@
         <v>115.18433899999999</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="P101" s="4">
         <v>526029</v>
       </c>
       <c r="Q101" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R101" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.3">
@@ -10995,7 +10974,7 @@
         <v>21</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K102">
         <v>60</v>
@@ -11010,16 +10989,16 @@
         <v>112.616159</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="P102" s="4">
         <v>1296688</v>
       </c>
       <c r="Q102" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R102" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.3">
@@ -11051,7 +11030,7 @@
         <v>21</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K103">
         <v>80</v>
@@ -11066,16 +11045,16 @@
         <v>114.84831</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="P103" s="4">
         <v>270346</v>
       </c>
       <c r="Q103" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R103" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.3">
@@ -11107,7 +11086,7 @@
         <v>21</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K104">
         <v>102</v>
@@ -11122,16 +11101,16 @@
         <v>104.738058</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="P104" s="4">
         <v>1761461</v>
       </c>
       <c r="Q104" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R104" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.3">
@@ -11163,7 +11142,7 @@
         <v>21</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K105">
         <v>60</v>
@@ -11178,16 +11157,16 @@
         <v>104.76113599999999</v>
       </c>
       <c r="O105" s="3" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="P105" s="4">
         <v>1761461</v>
       </c>
       <c r="Q105" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R105" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.3">
@@ -11219,7 +11198,7 @@
         <v>21</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K106">
         <v>62</v>
@@ -11234,16 +11213,16 @@
         <v>122.524231</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="P106" s="4">
         <v>347380</v>
       </c>
       <c r="Q106" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R106" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.3">
@@ -11275,7 +11254,7 @@
         <v>21</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K107">
         <v>120</v>
@@ -11290,16 +11269,16 @@
         <v>112.81139400000001</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="P107" s="4">
         <v>3000075</v>
       </c>
       <c r="Q107" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R107" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.3">
@@ -11331,7 +11310,7 @@
         <v>21</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K108">
         <v>77</v>
@@ -11346,16 +11325,16 @@
         <v>122.512057</v>
       </c>
       <c r="O108" s="3" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="P108" s="4">
         <v>347380</v>
       </c>
       <c r="Q108" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R108" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.3">
@@ -11387,7 +11366,7 @@
         <v>21</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K109">
         <v>80</v>
@@ -11402,16 +11381,16 @@
         <v>112.74863499999999</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="P109" s="4">
         <v>3000075</v>
       </c>
       <c r="Q109" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R109" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.3">
@@ -11443,7 +11422,7 @@
         <v>21</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="K110">
         <v>88</v>
@@ -11458,16 +11437,16 @@
         <v>106.874185</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="P110" s="4">
         <v>1109489</v>
       </c>
       <c r="Q110" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R110" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.3">
@@ -11499,7 +11478,7 @@
         <v>21</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K111">
         <v>80</v>
@@ -11514,16 +11493,16 @@
         <v>106.79934799999999</v>
       </c>
       <c r="O111" s="3" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="P111" s="4">
         <v>1122771</v>
       </c>
       <c r="Q111" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R111" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.3">
@@ -11555,7 +11534,7 @@
         <v>21</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K112">
         <v>59</v>
@@ -11570,16 +11549,16 @@
         <v>98.644181000000003</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="P112" s="4">
         <v>2530492</v>
       </c>
       <c r="Q112" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R112" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.3">
@@ -11611,7 +11590,7 @@
         <v>21</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K113">
         <v>60</v>
@@ -11626,16 +11605,16 @@
         <v>106.911119</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="P113" s="4">
         <v>2496198</v>
       </c>
       <c r="Q113" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R113" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.3">
@@ -11667,7 +11646,7 @@
         <v>21</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K114">
         <v>80</v>
@@ -11682,16 +11661,16 @@
         <v>106.72872099999999</v>
       </c>
       <c r="O114" s="3" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="P114" s="4">
         <v>2615945</v>
       </c>
       <c r="Q114" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R114" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.3">
@@ -11723,7 +11702,7 @@
         <v>21</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="K115">
         <v>69</v>
@@ -11738,16 +11717,16 @@
         <v>106.817064</v>
       </c>
       <c r="O115" s="3" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="P115" s="4">
         <v>1122771</v>
       </c>
       <c r="Q115" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R115" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.3">
@@ -11779,7 +11758,7 @@
         <v>21</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="K116">
         <v>68</v>
@@ -11794,16 +11773,16 @@
         <v>124.837932</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="P116" s="4">
         <v>478194</v>
       </c>
       <c r="Q116" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R116" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.3">
@@ -11835,7 +11814,7 @@
         <v>21</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K117">
         <v>86</v>
@@ -11850,16 +11829,16 @@
         <v>106.606495</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="P117" s="4">
         <v>3286420</v>
       </c>
       <c r="Q117" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R117" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.3">
@@ -11891,7 +11870,7 @@
         <v>21</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="K118">
         <v>98</v>
@@ -11906,16 +11885,16 @@
         <v>106.843892</v>
       </c>
       <c r="O118" s="3" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="P118" s="4">
         <v>1109489</v>
       </c>
       <c r="Q118" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R118" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.3">
@@ -11947,7 +11926,7 @@
         <v>21</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K119">
         <v>117</v>
@@ -11962,16 +11941,16 @@
         <v>106.634049</v>
       </c>
       <c r="O119" s="3" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="P119" s="4">
         <v>1899515</v>
       </c>
       <c r="Q119" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R119" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.3">
@@ -12003,7 +11982,7 @@
         <v>21</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K120">
         <v>71</v>
@@ -12018,16 +11997,16 @@
         <v>112.74751999999999</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="P120" s="4">
         <v>3000075</v>
       </c>
       <c r="Q120" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R120" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.3">
@@ -12059,7 +12038,7 @@
         <v>21</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="K121">
         <v>80</v>
@@ -12074,16 +12053,16 @@
         <v>106.69411700000001</v>
       </c>
       <c r="O121" s="3" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="P121" s="4">
         <v>2615945</v>
       </c>
       <c r="Q121" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R121" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.3">
@@ -12115,7 +12094,7 @@
         <v>21</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K122">
         <v>95</v>
@@ -12130,16 +12109,16 @@
         <v>123.062073</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="P122" s="4">
         <v>203205</v>
       </c>
       <c r="Q122" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R122" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.3">
@@ -12171,7 +12150,7 @@
         <v>21</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K123">
         <v>68</v>
@@ -12186,16 +12165,16 @@
         <v>112.076255</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="P123" s="4">
         <v>1249619</v>
       </c>
       <c r="Q123" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R123" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.3">
@@ -12227,7 +12206,7 @@
         <v>21</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K124">
         <v>96</v>
@@ -12242,16 +12221,16 @@
         <v>113.924392</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="P124" s="4">
         <v>302311</v>
       </c>
       <c r="Q124" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R124" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.3">
@@ -12283,7 +12262,7 @@
         <v>21</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K125">
         <v>92</v>
@@ -12298,16 +12277,16 @@
         <v>119.8426</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="P125" s="4">
         <v>382017</v>
       </c>
       <c r="Q125" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R125" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.3">
@@ -12339,7 +12318,7 @@
         <v>21</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K126">
         <v>76</v>
@@ -12354,16 +12333,16 @@
         <v>106.959187</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="P126" s="4">
         <v>5495373</v>
       </c>
       <c r="Q126" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R126" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.3">
@@ -12395,7 +12374,7 @@
         <v>21</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K127">
         <v>69</v>
@@ -12410,16 +12389,16 @@
         <v>99.072187999999997</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="P127" s="4">
         <v>275189</v>
       </c>
       <c r="Q127" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R127" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.3">
@@ -12451,7 +12430,7 @@
         <v>21</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K128">
         <v>80</v>
@@ -12466,16 +12445,16 @@
         <v>108.33702</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="P128" s="4">
         <v>947166</v>
       </c>
       <c r="Q128" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R128" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.3">
@@ -12507,7 +12486,7 @@
         <v>21</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K129">
         <v>79</v>
@@ -12522,16 +12501,16 @@
         <v>106.925792</v>
       </c>
       <c r="O129" s="3" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="P129" s="4">
         <v>2496198</v>
       </c>
       <c r="Q129" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R129" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.3">
@@ -12563,7 +12542,7 @@
         <v>21</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K130">
         <v>98</v>
@@ -12578,16 +12557,16 @@
         <v>100.397521</v>
       </c>
       <c r="O130" s="3" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="P130" s="4">
         <v>928539</v>
       </c>
       <c r="Q130" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R130" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.3">
@@ -12619,7 +12598,7 @@
         <v>21</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K131">
         <v>74</v>
@@ -12634,16 +12613,16 @@
         <v>110.381372</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="P131" s="4">
         <v>1693034</v>
       </c>
       <c r="Q131" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R131" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.3">
@@ -12675,7 +12654,7 @@
         <v>21</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K132">
         <v>66</v>
@@ -12690,16 +12669,16 @@
         <v>107.608931</v>
       </c>
       <c r="O132" s="3" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="P132" s="4">
         <v>2555187</v>
       </c>
       <c r="Q132" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R132" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.3">
@@ -12731,7 +12710,7 @@
         <v>21</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K133">
         <v>129</v>
@@ -12746,16 +12725,16 @@
         <v>106.842597</v>
       </c>
       <c r="O133" s="3" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="P133" s="4">
         <v>2408480</v>
       </c>
       <c r="Q133" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R133" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.3">
@@ -12787,7 +12766,7 @@
         <v>21</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K134">
         <v>120.75</v>
@@ -12802,16 +12781,16 @@
         <v>106.840907</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="P134" s="4">
         <v>5495373</v>
       </c>
       <c r="Q134" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R134" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.3">
@@ -12843,7 +12822,7 @@
         <v>21</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K135">
         <v>90</v>
@@ -12855,16 +12834,16 @@
         <v>119.39393099999999</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="P135" s="4">
         <v>1470262</v>
       </c>
       <c r="Q135" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R135" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.3">
@@ -12896,7 +12875,7 @@
         <v>21</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K136">
         <v>145.6</v>
@@ -12911,16 +12890,16 @@
         <v>110.420416</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="P136" s="4">
         <v>1693034</v>
       </c>
       <c r="Q136" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R136" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.3">
@@ -12952,7 +12931,7 @@
         <v>21</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K137">
         <v>172.02</v>
@@ -12967,16 +12946,16 @@
         <v>106.81286</v>
       </c>
       <c r="O137" s="3" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="P137" s="4">
         <v>2408480</v>
       </c>
       <c r="Q137" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R137" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
@@ -13008,7 +12987,7 @@
         <v>21</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K138">
         <v>105</v>
@@ -13023,16 +13002,16 @@
         <v>107.195449</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="P138" s="4">
         <v>3172831</v>
       </c>
       <c r="Q138" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R138" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
@@ -13064,7 +13043,7 @@
         <v>21</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K139">
         <v>77</v>
@@ -13079,16 +13058,16 @@
         <v>106.786618</v>
       </c>
       <c r="O139" s="3" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="P139" s="4">
         <v>2615945</v>
       </c>
       <c r="Q139" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R139" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.3">
@@ -13120,7 +13099,7 @@
         <v>21</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K140">
         <v>110.79</v>
@@ -13132,16 +13111,16 @@
         <v>106.89189399999999</v>
       </c>
       <c r="O140" s="3" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="P140" s="4">
         <v>1876057</v>
       </c>
       <c r="Q140" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R140" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.3">
@@ -13173,7 +13152,7 @@
         <v>21</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K141">
         <v>112</v>
@@ -13188,16 +13167,16 @@
         <v>104.753834</v>
       </c>
       <c r="O141" s="3" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="P141" s="4">
         <v>1761461</v>
       </c>
       <c r="Q141" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R141" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.3">
@@ -13229,7 +13208,7 @@
         <v>21</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K142">
         <v>74</v>
@@ -13244,16 +13223,16 @@
         <v>109.369536</v>
       </c>
       <c r="O142" s="3" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="P142" s="4">
         <v>291750</v>
       </c>
       <c r="Q142" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R142" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.3">
@@ -13285,7 +13264,7 @@
         <v>21</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K143">
         <v>106.11</v>
@@ -13300,16 +13279,16 @@
         <v>112.720054</v>
       </c>
       <c r="O143" s="3" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="P143" s="4">
         <v>3000075</v>
       </c>
       <c r="Q143" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R143" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.3">
@@ -13341,7 +13320,7 @@
         <v>21</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K144">
         <v>432</v>
@@ -13356,16 +13335,16 @@
         <v>115.208021</v>
       </c>
       <c r="O144" s="3" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="P144" s="4">
         <v>660984</v>
       </c>
       <c r="Q144" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R144" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.3">
@@ -13397,7 +13376,7 @@
         <v>21</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K145">
         <v>222</v>
@@ -13412,16 +13391,16 @@
         <v>112.717679</v>
       </c>
       <c r="O145" s="3" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="P145" s="4">
         <v>1982939</v>
       </c>
       <c r="Q145" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R145" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.3">
@@ -13453,7 +13432,7 @@
         <v>21</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K146">
         <v>100</v>
@@ -13468,16 +13447,16 @@
         <v>112.666859</v>
       </c>
       <c r="O146" s="3" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="P146" s="4">
         <v>3000075</v>
       </c>
       <c r="Q146" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R146" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.3">
@@ -13509,7 +13488,7 @@
         <v>21</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K147">
         <v>60</v>
@@ -13524,16 +13503,16 @@
         <v>114.87306700000001</v>
       </c>
       <c r="O147" s="3" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="P147" s="4">
         <v>575113</v>
       </c>
       <c r="Q147" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R147" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.3">
@@ -13580,16 +13559,16 @@
         <v>98.678877999999997</v>
       </c>
       <c r="O148" s="3" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="P148" s="4">
         <v>2530492</v>
       </c>
       <c r="Q148" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R148" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.3">
@@ -13621,7 +13600,7 @@
         <v>21</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K149">
         <v>112</v>
@@ -13636,16 +13615,16 @@
         <v>112.780812</v>
       </c>
       <c r="O149" s="3" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="P149" s="4">
         <v>3000075</v>
       </c>
       <c r="Q149" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R149" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.3">
@@ -13692,16 +13671,16 @@
         <v>109.651066</v>
       </c>
       <c r="O150" s="3" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="P150" s="4">
         <v>317534</v>
       </c>
       <c r="Q150" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R150" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.3">
@@ -13733,7 +13712,7 @@
         <v>21</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K151">
         <v>55</v>
@@ -13748,16 +13727,16 @@
         <v>113.722081</v>
       </c>
       <c r="O151" s="3" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="P151" s="4">
         <v>2590289</v>
       </c>
       <c r="Q151" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R151" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
@@ -13804,16 +13783,16 @@
         <v>100.396214</v>
       </c>
       <c r="O152" s="3" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="P152" s="4">
         <v>135489</v>
       </c>
       <c r="Q152" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R152" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.3">
@@ -13860,16 +13839,16 @@
         <v>100.354747</v>
       </c>
       <c r="O153" s="3" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="P153" s="4">
         <v>928539</v>
       </c>
       <c r="Q153" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R153" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.3">
@@ -13901,7 +13880,7 @@
         <v>21</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K154">
         <v>75</v>
@@ -13916,16 +13895,16 @@
         <v>116.844972</v>
       </c>
       <c r="O154" s="3" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="P154" s="4">
         <v>733397</v>
       </c>
       <c r="Q154" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R154" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.3">
@@ -13957,7 +13936,7 @@
         <v>21</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K155">
         <v>75</v>
@@ -13972,16 +13951,16 @@
         <v>108.981435</v>
       </c>
       <c r="O155" s="3" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="P155" s="4">
         <v>242146</v>
       </c>
       <c r="Q155" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R155" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.3">
@@ -14013,7 +13992,7 @@
         <v>21</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K156">
         <v>100</v>
@@ -14028,16 +14007,16 @@
         <v>109.306162</v>
       </c>
       <c r="O156" s="3" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="P156" s="4">
         <v>676096</v>
       </c>
       <c r="Q156" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R156" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.3">
@@ -14069,7 +14048,7 @@
         <v>21</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K157">
         <v>157</v>
@@ -14084,16 +14063,16 @@
         <v>111.898601</v>
       </c>
       <c r="O157" s="3" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="P157" s="4">
         <v>1132146</v>
       </c>
       <c r="Q157" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R157" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
@@ -14125,7 +14104,7 @@
         <v>21</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K158">
         <v>100</v>
@@ -14140,16 +14119,16 @@
         <v>112.01836400000001</v>
       </c>
       <c r="O158" s="3" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="P158" s="4">
         <v>296792</v>
       </c>
       <c r="Q158" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R158" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
@@ -14181,7 +14160,7 @@
         <v>21</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K159">
         <v>100</v>
@@ -14196,16 +14175,16 @@
         <v>119.887102</v>
       </c>
       <c r="O159" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="P159" s="4">
         <v>382017</v>
       </c>
       <c r="Q159" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R159" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.3">
@@ -14252,16 +14231,16 @@
         <v>104.76451400000001</v>
       </c>
       <c r="O160" s="3" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="P160" s="4">
         <v>1761461</v>
       </c>
       <c r="Q160" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R160" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.3">
@@ -14308,16 +14287,16 @@
         <v>98.708527000000004</v>
       </c>
       <c r="O161" s="3" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="P161" s="4">
         <v>2530492</v>
       </c>
       <c r="Q161" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R161" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.3">
@@ -14364,16 +14343,16 @@
         <v>103.59678</v>
       </c>
       <c r="O162" s="3" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="P162" s="4">
         <v>633649</v>
       </c>
       <c r="Q162" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R162" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.3">
@@ -14420,16 +14399,16 @@
         <v>95.330163999999996</v>
       </c>
       <c r="O163" s="3" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="P163" s="4">
         <v>257315</v>
       </c>
       <c r="Q163" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R163" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.3">
@@ -14461,7 +14440,7 @@
         <v>21</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K164">
         <v>378</v>
@@ -14476,16 +14455,16 @@
         <v>119.443811</v>
       </c>
       <c r="O164" s="3" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="P164" s="4">
         <v>1470262</v>
       </c>
       <c r="Q164" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R164" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.3">
@@ -14532,16 +14511,16 @@
         <v>107.623908</v>
       </c>
       <c r="O165" s="3" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="P165" s="4">
         <v>2555187</v>
       </c>
       <c r="Q165" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R165" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.3">
@@ -14573,7 +14552,7 @@
         <v>21</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K166">
         <v>62</v>
@@ -14588,16 +14567,16 @@
         <v>115.321116</v>
       </c>
       <c r="O166" s="3" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="P166" s="4">
         <v>503546</v>
       </c>
       <c r="Q166" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R166" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.3">
@@ -14629,7 +14608,7 @@
         <v>21</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K167">
         <v>73</v>
@@ -14644,16 +14623,16 @@
         <v>111.469902</v>
       </c>
       <c r="O167" s="3" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="P167" s="4">
         <v>973269</v>
       </c>
       <c r="Q167" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R167" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.3">
@@ -14685,7 +14664,7 @@
         <v>21</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K168">
         <v>142</v>
@@ -14700,16 +14679,16 @@
         <v>111.521343</v>
       </c>
       <c r="O168" s="3" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="P168" s="4">
         <v>201992</v>
       </c>
       <c r="Q168" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R168" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
@@ -14741,7 +14720,7 @@
         <v>21</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K169">
         <v>95</v>
@@ -14756,16 +14735,16 @@
         <v>117.530023</v>
       </c>
       <c r="O169" s="3" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="P169" s="4">
         <v>427492</v>
       </c>
       <c r="Q169" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R169" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
@@ -14797,7 +14776,7 @@
         <v>21</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K170">
         <v>72</v>
@@ -14812,16 +14791,16 @@
         <v>117.491473</v>
       </c>
       <c r="O170" s="3" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="P170" s="4">
         <v>187446</v>
       </c>
       <c r="Q170" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R170" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.3">
@@ -14868,16 +14847,16 @@
         <v>109.387243</v>
       </c>
       <c r="O171" s="3" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="P171" s="4">
         <v>1567045</v>
       </c>
       <c r="Q171" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R171" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.3">
@@ -14909,7 +14888,7 @@
         <v>21</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K172">
         <v>73</v>
@@ -14924,16 +14903,16 @@
         <v>112.608926</v>
       </c>
       <c r="O172" s="3" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="P172" s="4">
         <v>874660</v>
       </c>
       <c r="Q172" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R172" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.3">
@@ -14980,16 +14959,16 @@
         <v>105.247274</v>
       </c>
       <c r="O173" s="3" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="P173" s="4">
         <v>1096935</v>
       </c>
       <c r="Q173" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R173" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.3">
@@ -15036,16 +15015,16 @@
         <v>98.703643999999997</v>
       </c>
       <c r="O174" s="3" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="P174" s="4">
         <v>2016906</v>
       </c>
       <c r="Q174" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R174" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.3">
@@ -15077,7 +15056,7 @@
         <v>21</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="K175">
         <v>119</v>
@@ -15092,16 +15071,16 @@
         <v>115.211603</v>
       </c>
       <c r="O175" s="3" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="P175" s="4">
         <v>660984</v>
       </c>
       <c r="Q175" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R175" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.3">
@@ -15133,7 +15112,7 @@
         <v>21</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K176">
         <v>74</v>
@@ -15148,16 +15127,16 @@
         <v>109.331602</v>
       </c>
       <c r="O176" s="3" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="P176" s="4">
         <v>676096</v>
       </c>
       <c r="Q176" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R176" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.3">
@@ -15189,7 +15168,7 @@
         <v>21</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K177">
         <v>80</v>
@@ -15204,16 +15183,16 @@
         <v>112.570826</v>
       </c>
       <c r="O177" s="3" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="P177" s="4">
         <v>2692261</v>
       </c>
       <c r="Q177" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R177" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.3">
@@ -15245,7 +15224,7 @@
         <v>21</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K178">
         <v>75</v>
@@ -15260,16 +15239,16 @@
         <v>119.40918000000001</v>
       </c>
       <c r="O178" s="3" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="P178" s="4">
         <v>1470262</v>
       </c>
       <c r="Q178" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R178" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.3">
@@ -15301,7 +15280,7 @@
         <v>21</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K179">
         <v>93</v>
@@ -15316,16 +15295,16 @@
         <v>124.861063</v>
       </c>
       <c r="O179" s="3" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="P179" s="4">
         <v>478194</v>
       </c>
       <c r="Q179" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R179" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.3">
@@ -15372,16 +15351,16 @@
         <v>97.144687000000005</v>
       </c>
       <c r="O180" s="3" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="P180" s="4">
         <v>193950</v>
       </c>
       <c r="Q180" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R180" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.3">
@@ -15428,16 +15407,16 @@
         <v>109.009351</v>
       </c>
       <c r="O181" s="3" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="P181" s="4">
         <v>2022808</v>
       </c>
       <c r="Q181" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R181" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.3">
@@ -15469,7 +15448,7 @@
         <v>21</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K182">
         <v>104</v>
@@ -15484,16 +15463,16 @@
         <v>119.48123200000001</v>
       </c>
       <c r="O182" s="3" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="P182" s="4">
         <v>1470262</v>
       </c>
       <c r="Q182" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R182" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.3">
@@ -15540,16 +15519,16 @@
         <v>111.029685</v>
       </c>
       <c r="O183" s="3" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="P183" s="4">
         <v>1012493</v>
       </c>
       <c r="Q183" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R183" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.3">
@@ -15596,16 +15575,16 @@
         <v>98.682354000000004</v>
       </c>
       <c r="O184" s="3" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="P184" s="4">
         <v>2530492</v>
       </c>
       <c r="Q184" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R184" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.3">
@@ -15637,7 +15616,7 @@
         <v>21</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K185">
         <v>100</v>
@@ -15652,16 +15631,16 @@
         <v>111.898078</v>
       </c>
       <c r="O185" s="3" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="P185" s="4">
         <v>1139616</v>
       </c>
       <c r="Q185" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R185" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.3">
@@ -15693,7 +15672,7 @@
         <v>21</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K186">
         <v>74</v>
@@ -15708,16 +15687,16 @@
         <v>116.00132600000001</v>
       </c>
       <c r="O186" s="3" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="P186" s="4">
         <v>343740</v>
       </c>
       <c r="Q186" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R186" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.3">
@@ -15749,7 +15728,7 @@
         <v>21</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K187">
         <v>60</v>
@@ -15764,16 +15743,16 @@
         <v>116.846875</v>
       </c>
       <c r="O187" s="3" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="P187" s="4">
         <v>733397</v>
       </c>
       <c r="Q187" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R187" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.3">
@@ -15805,7 +15784,7 @@
         <v>21</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K188">
         <v>67</v>
@@ -15820,16 +15799,16 @@
         <v>114.578221</v>
       </c>
       <c r="O188" s="3" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="P188" s="4">
         <v>675916</v>
       </c>
       <c r="Q188" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R188" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.3">
@@ -15876,16 +15855,16 @@
         <v>106.9164</v>
       </c>
       <c r="O189" s="3" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="P189" s="4">
         <v>1876057</v>
       </c>
       <c r="Q189" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R189" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.3">
@@ -15917,7 +15896,7 @@
         <v>21</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K190">
         <v>60</v>
@@ -15932,16 +15911,16 @@
         <v>114.602159</v>
       </c>
       <c r="O190" s="3" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="P190" s="4">
         <v>675916</v>
       </c>
       <c r="Q190" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R190" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.3">
@@ -15988,16 +15967,16 @@
         <v>110.82023700000001</v>
       </c>
       <c r="O191" s="3" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="P191" s="4">
         <v>586166</v>
       </c>
       <c r="Q191" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R191" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.3">
@@ -16029,7 +16008,7 @@
         <v>21</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K192">
         <v>120</v>
@@ -16044,16 +16023,16 @@
         <v>112.628643</v>
       </c>
       <c r="O192" s="3" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="P192" s="4">
         <v>874660</v>
       </c>
       <c r="Q192" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R192" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.3">
@@ -16085,7 +16064,7 @@
         <v>21</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K193">
         <v>117</v>
@@ -16100,16 +16079,16 @@
         <v>115.157217</v>
       </c>
       <c r="O193" s="3" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="P193" s="4">
         <v>526029</v>
       </c>
       <c r="Q193" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R193" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.3">
@@ -16156,16 +16135,16 @@
         <v>107.301137</v>
       </c>
       <c r="O194" s="3" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="P194" s="4">
         <v>2519882</v>
       </c>
       <c r="Q194" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R194" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.3">
@@ -16212,16 +16191,16 @@
         <v>108.21779100000001</v>
       </c>
       <c r="O195" s="3" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="P195" s="4">
         <v>752545</v>
       </c>
       <c r="Q195" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R195" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.3">
@@ -16253,7 +16232,7 @@
         <v>21</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K196">
         <v>100</v>
@@ -16268,16 +16247,16 @@
         <v>114.848354</v>
       </c>
       <c r="O196" s="3" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="P196" s="4">
         <v>270346</v>
       </c>
       <c r="Q196" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R196" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.3">
@@ -16309,7 +16288,7 @@
         <v>21</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K197">
         <v>175</v>
@@ -16324,16 +16303,16 @@
         <v>112.76169899999999</v>
       </c>
       <c r="O197" s="3" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="P197" s="4">
         <v>3000075</v>
       </c>
       <c r="Q197" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R197" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.3">
@@ -16380,16 +16359,16 @@
         <v>109.63630000000001</v>
       </c>
       <c r="O198" s="3" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="P198" s="4">
         <v>1008689</v>
       </c>
       <c r="Q198" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R198" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.3">
@@ -16436,16 +16415,16 @@
         <v>110.221926</v>
       </c>
       <c r="O199" s="3" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="P199" s="4">
         <v>128152</v>
       </c>
       <c r="Q199" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R199" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.3">
@@ -16477,7 +16456,7 @@
         <v>21</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K200">
         <v>60</v>
@@ -16492,16 +16471,16 @@
         <v>112.941255</v>
       </c>
       <c r="O200" s="3" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="P200" s="4">
         <v>433678</v>
       </c>
       <c r="Q200" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R200" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.3">
@@ -16548,16 +16527,16 @@
         <v>110.304295</v>
       </c>
       <c r="O201" s="3" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="P201" s="4">
         <v>1105415</v>
       </c>
       <c r="Q201" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R201" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.3">
@@ -16604,16 +16583,16 @@
         <v>115.242654</v>
       </c>
       <c r="O202" s="3" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="P202" s="4">
         <v>660984</v>
       </c>
       <c r="Q202" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R202" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.3">
@@ -16660,16 +16639,16 @@
         <v>109.34725400000001</v>
       </c>
       <c r="O203" s="3" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="P203" s="4">
         <v>676096</v>
       </c>
       <c r="Q203" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R203" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.3">
@@ -16701,7 +16680,7 @@
         <v>21</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K204">
         <v>80</v>
@@ -16716,16 +16695,16 @@
         <v>122.52200000000001</v>
       </c>
       <c r="O204" s="3" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="P204" s="4">
         <v>347380</v>
       </c>
       <c r="Q204" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R204" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.3">
@@ -16757,7 +16736,7 @@
         <v>21</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K205">
         <v>50</v>
@@ -16772,16 +16751,16 @@
         <v>119.79543</v>
       </c>
       <c r="O205" s="3" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="P205" s="4">
         <v>323430</v>
       </c>
       <c r="Q205" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R205" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.3">
@@ -16828,16 +16807,16 @@
         <v>105.257171</v>
       </c>
       <c r="O206" s="3" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="P206" s="4">
         <v>1096935</v>
       </c>
       <c r="Q206" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R206" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.3">
@@ -16884,16 +16863,16 @@
         <v>100.361576</v>
       </c>
       <c r="O207" s="3" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="P207" s="4">
         <v>928539</v>
       </c>
       <c r="Q207" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R207" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.3">
@@ -16940,16 +16919,16 @@
         <v>101.447146</v>
       </c>
       <c r="O208" s="3" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="P208" s="4">
         <v>1116142</v>
       </c>
       <c r="Q208" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R208" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.3">
@@ -16996,16 +16975,16 @@
         <v>112.621184</v>
       </c>
       <c r="O209" s="3" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="P209" s="4">
         <v>874660</v>
       </c>
       <c r="Q209" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R209" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.3">
@@ -17052,16 +17031,16 @@
         <v>107.583369</v>
       </c>
       <c r="O210" s="3" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="P210" s="4">
         <v>570829</v>
       </c>
       <c r="Q210" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R210" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.3">
@@ -17093,7 +17072,7 @@
         <v>21</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K211">
         <v>80</v>
@@ -17108,16 +17087,16 @@
         <v>112.897693</v>
       </c>
       <c r="O211" s="3" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
       <c r="P211" s="4">
         <v>212403</v>
       </c>
       <c r="Q211" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R211" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.3">
@@ -17164,16 +17143,16 @@
         <v>104.768023</v>
       </c>
       <c r="O212" s="3" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="P212" s="4">
         <v>1761461</v>
       </c>
       <c r="Q212" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R212" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.3">
@@ -17220,16 +17199,16 @@
         <v>98.676056000000003</v>
       </c>
       <c r="O213" s="3" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="P213" s="4">
         <v>2530492</v>
       </c>
       <c r="Q213" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R213" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.3">
@@ -17276,16 +17255,16 @@
         <v>106.853514</v>
       </c>
       <c r="O214" s="3" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="P214" s="4">
         <v>1927869</v>
       </c>
       <c r="Q214" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R214" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.3">
@@ -17332,16 +17311,16 @@
         <v>108.542145</v>
       </c>
       <c r="O215" s="3" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="P215" s="4">
         <v>2420956</v>
       </c>
       <c r="Q215" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R215" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.3">
@@ -17388,16 +17367,16 @@
         <v>109.65213900000001</v>
       </c>
       <c r="O216" s="3" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="P216" s="4">
         <v>1008689</v>
       </c>
       <c r="Q216" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R216" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.3">
@@ -17429,7 +17408,7 @@
         <v>21</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K217">
         <v>110</v>
@@ -17444,16 +17423,16 @@
         <v>111.674758</v>
       </c>
       <c r="O217" s="3" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="P217" s="4">
         <v>282660</v>
       </c>
       <c r="Q217" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R217" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.3">
@@ -17500,16 +17479,16 @@
         <v>104.76015</v>
       </c>
       <c r="O218" s="3" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="P218" s="4">
         <v>1761461</v>
       </c>
       <c r="Q218" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R218" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.3">
@@ -17541,7 +17520,7 @@
         <v>21</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K219">
         <v>105</v>
@@ -17556,16 +17535,16 @@
         <v>123.062428</v>
       </c>
       <c r="O219" s="3" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="P219" s="4">
         <v>203205</v>
       </c>
       <c r="Q219" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R219" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.3">
@@ -17612,16 +17591,16 @@
         <v>104.791476</v>
       </c>
       <c r="O220" s="3" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="P220" s="4">
         <v>1761461</v>
       </c>
       <c r="Q220" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R220" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.3">
@@ -17653,7 +17632,7 @@
         <v>21</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K221">
         <v>82</v>
@@ -17668,16 +17647,16 @@
         <v>125.127532</v>
       </c>
       <c r="O221" s="3" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="P221" s="4">
         <v>228008</v>
       </c>
       <c r="Q221" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R221" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.3">
@@ -17724,16 +17703,16 @@
         <v>111.882268</v>
       </c>
       <c r="O222" s="3" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="P222" s="4">
         <v>1356056</v>
       </c>
       <c r="Q222" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R222" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.3">
@@ -17765,7 +17744,7 @@
         <v>21</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K223">
         <v>112</v>
@@ -17780,16 +17759,16 @@
         <v>112.665565</v>
       </c>
       <c r="O223" s="3" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="P223" s="4">
         <v>2692261</v>
       </c>
       <c r="Q223" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R223" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.3">
@@ -17836,16 +17815,16 @@
         <v>105.21337800000001</v>
       </c>
       <c r="O224" s="3" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="P224" s="4">
         <v>1373771</v>
       </c>
       <c r="Q224" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R224" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.3">
@@ -17892,16 +17871,16 @@
         <v>120.192222</v>
       </c>
       <c r="O225" s="3" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="P225" s="4">
         <v>468337</v>
       </c>
       <c r="Q225" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R225" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.3">
@@ -17948,16 +17927,16 @@
         <v>110.819518</v>
       </c>
       <c r="O226" s="3" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="P226" s="4">
         <v>586166</v>
       </c>
       <c r="Q226" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R226" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.3">
@@ -17989,7 +17968,7 @@
         <v>21</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K227">
         <v>70</v>
@@ -18004,16 +17983,16 @@
         <v>112.167683</v>
       </c>
       <c r="O227" s="3" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="P227" s="4">
         <v>159406</v>
       </c>
       <c r="Q227" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R227" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.3">
@@ -18060,16 +18039,16 @@
         <v>120.314673</v>
       </c>
       <c r="O228" s="3" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="P228" s="4">
         <v>817363</v>
       </c>
       <c r="Q228" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R228" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.3">
@@ -18116,16 +18095,16 @@
         <v>107.164843</v>
       </c>
       <c r="O229" s="3" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="P229" s="4">
         <v>3172831</v>
       </c>
       <c r="Q229" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R229" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.3">
@@ -18157,7 +18136,7 @@
         <v>21</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K230">
         <v>103</v>
@@ -18172,16 +18151,16 @@
         <v>112.767736</v>
       </c>
       <c r="O230" s="3" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="P230" s="4">
         <v>1982939</v>
       </c>
       <c r="Q230" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R230" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.3">
@@ -18213,7 +18192,7 @@
         <v>21</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K231">
         <v>81</v>
@@ -18228,16 +18207,16 @@
         <v>112.652907</v>
       </c>
       <c r="O231" s="3" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="P231" s="4">
         <v>3000075</v>
       </c>
       <c r="Q231" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R231" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.3">
@@ -18284,16 +18263,16 @@
         <v>110.39166400000001</v>
       </c>
       <c r="O232" s="3" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="P232" s="4">
         <v>1693034</v>
       </c>
       <c r="Q232" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R232" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.3">
@@ -18340,16 +18319,16 @@
         <v>117.13990099999999</v>
       </c>
       <c r="O233" s="3" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="P233" s="4">
         <v>856361</v>
       </c>
       <c r="Q233" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R233" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.3">
@@ -18396,16 +18375,16 @@
         <v>113.885851</v>
       </c>
       <c r="O234" s="3" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="P234" s="4">
         <v>302311</v>
       </c>
       <c r="Q234" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R234" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.3">
@@ -18437,7 +18416,7 @@
         <v>21</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K235">
         <v>87</v>
@@ -18452,16 +18431,16 @@
         <v>109.347481</v>
       </c>
       <c r="O235" s="3" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="P235" s="4">
         <v>676096</v>
       </c>
       <c r="Q235" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R235" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.3">
@@ -18508,16 +18487,16 @@
         <v>106.930753</v>
       </c>
       <c r="O236" s="3" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="P236" s="4">
         <v>361581</v>
       </c>
       <c r="Q236" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R236" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.3">
@@ -18549,7 +18528,7 @@
         <v>21</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K237">
         <v>97</v>
@@ -18564,16 +18543,16 @@
         <v>116.117907</v>
       </c>
       <c r="O237" s="3" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="P237" s="4">
         <v>452812</v>
       </c>
       <c r="Q237" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R237" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.3">
@@ -18620,16 +18599,16 @@
         <v>112.04934900000001</v>
       </c>
       <c r="O238" s="3" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="P238" s="4">
         <v>1249619</v>
       </c>
       <c r="Q238" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R238" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.3">
@@ -18676,16 +18655,16 @@
         <v>112.24469000000001</v>
       </c>
       <c r="O239" s="3" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="P239" s="4">
         <v>1364775</v>
       </c>
       <c r="Q239" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R239" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.3">
@@ -18717,7 +18696,7 @@
         <v>21</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K240">
         <v>99</v>
@@ -18732,16 +18711,16 @@
         <v>112.67265999999999</v>
       </c>
       <c r="O240" s="3" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="P240" s="4">
         <v>1982939</v>
       </c>
       <c r="Q240" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R240" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.3">
@@ -18773,7 +18752,7 @@
         <v>21</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K241">
         <v>130</v>
@@ -18788,16 +18767,16 @@
         <v>117.587605</v>
       </c>
       <c r="O241" s="3" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="P241" s="4">
         <v>246734</v>
       </c>
       <c r="Q241" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R241" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.3">
@@ -18844,16 +18823,16 @@
         <v>107.908772</v>
       </c>
       <c r="O242" s="3" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="P242" s="4">
         <v>2770531</v>
       </c>
       <c r="Q242" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R242" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.3">
@@ -18900,16 +18879,16 @@
         <v>108.23177200000001</v>
       </c>
       <c r="O243" s="3" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="P243" s="4">
         <v>1345378</v>
       </c>
       <c r="Q243" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R243" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.3">
@@ -18956,16 +18935,16 @@
         <v>106.630234</v>
       </c>
       <c r="O244" s="3" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="P244" s="4">
         <v>3286420</v>
       </c>
       <c r="Q244" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R244" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.3">
@@ -18997,7 +18976,7 @@
         <v>21</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K245">
         <v>74</v>
@@ -19012,16 +18991,16 @@
         <v>112.61539500000001</v>
       </c>
       <c r="O245" s="3" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="P245" s="4">
         <v>1296688</v>
       </c>
       <c r="Q245" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R245" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.3">
@@ -19068,16 +19047,16 @@
         <v>115.39859800000001</v>
       </c>
       <c r="O246" s="3" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="P246" s="4">
         <v>220491</v>
       </c>
       <c r="Q246" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R246" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.3">
@@ -19124,16 +19103,16 @@
         <v>113.933882</v>
       </c>
       <c r="O247" s="3" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="P247" s="4">
         <v>302311</v>
       </c>
       <c r="Q247" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R247" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.3">
@@ -19180,16 +19159,16 @@
         <v>107.292559</v>
       </c>
       <c r="O248" s="3" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="P248" s="4">
         <v>2519882</v>
       </c>
       <c r="Q248" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R248" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.3">
@@ -19221,7 +19200,7 @@
         <v>21</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K249">
         <v>111</v>
@@ -19236,16 +19215,16 @@
         <v>106.720572</v>
       </c>
       <c r="O249" s="3" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="P249" s="4">
         <v>1899515</v>
       </c>
       <c r="Q249" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R249" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.3">
@@ -19292,16 +19271,16 @@
         <v>111.439922</v>
       </c>
       <c r="O250" s="3" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="P250" s="4">
         <v>901637</v>
       </c>
       <c r="Q250" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R250" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.3">
@@ -19348,16 +19327,16 @@
         <v>109.65588700000001</v>
       </c>
       <c r="O251" s="3" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="P251" s="4">
         <v>1426832</v>
       </c>
       <c r="Q251" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R251" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.3">
@@ -19404,16 +19383,16 @@
         <v>107.29899399999999</v>
       </c>
       <c r="O252" s="3" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="P252" s="4">
         <v>2519882</v>
       </c>
       <c r="Q252" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R252" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.3">
@@ -19445,7 +19424,7 @@
         <v>21</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K253">
         <v>112</v>
@@ -19460,16 +19439,16 @@
         <v>123.590211</v>
       </c>
       <c r="O253" s="3" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="P253" s="4">
         <v>443349</v>
       </c>
       <c r="Q253" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R253" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.3">
@@ -19501,7 +19480,7 @@
         <v>21</v>
       </c>
       <c r="J254" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K254">
         <v>100</v>
@@ -19516,16 +19495,16 @@
         <v>119.883326</v>
       </c>
       <c r="O254" s="3" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="P254" s="4">
         <v>382017</v>
       </c>
       <c r="Q254" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R254" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.3">
@@ -19572,16 +19551,16 @@
         <v>107.766926</v>
       </c>
       <c r="O255" s="3" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="P255" s="4">
         <v>1624855</v>
       </c>
       <c r="Q255" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R255" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.3">
@@ -19628,16 +19607,16 @@
         <v>106.621224</v>
       </c>
       <c r="O256" s="3" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="P256" s="4">
         <v>1899515</v>
       </c>
       <c r="Q256" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R256" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.3">
@@ -19684,16 +19663,16 @@
         <v>96.126309000000006</v>
       </c>
       <c r="O257" s="3" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="P257" s="4">
         <v>201720</v>
       </c>
       <c r="Q257" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R257" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.3">
@@ -19740,16 +19719,16 @@
         <v>111.112225</v>
       </c>
       <c r="O258" s="3" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="P258" s="4">
         <v>599574</v>
       </c>
       <c r="Q258" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R258" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.3">
@@ -19796,16 +19775,16 @@
         <v>112.038389</v>
       </c>
       <c r="O259" s="3" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="P259" s="4">
         <v>296792</v>
       </c>
       <c r="Q259" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R259" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.3">
@@ -19852,16 +19831,16 @@
         <v>112.432158</v>
       </c>
       <c r="O260" s="3" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="P260" s="4">
         <v>141335</v>
       </c>
       <c r="Q260" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R260" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.3">
@@ -19908,16 +19887,16 @@
         <v>107.140998</v>
       </c>
       <c r="O261" s="3" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="P261" s="4">
         <v>2516417</v>
       </c>
       <c r="Q261" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R261" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.3">
@@ -19949,7 +19928,7 @@
         <v>981</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K262">
         <v>64.8</v>
@@ -19964,24 +19943,24 @@
         <v>106.841382</v>
       </c>
       <c r="O262" s="3" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="P262" s="4">
         <v>1109489</v>
       </c>
       <c r="Q262" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R262" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
       <c r="B263" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="C263" t="s">
         <v>15</v>
@@ -20005,7 +19984,7 @@
         <v>981</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K263">
         <v>60</v>
@@ -20020,16 +19999,16 @@
         <v>106.92419200000001</v>
       </c>
       <c r="O263" s="3" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="P263" s="4">
         <v>3310145</v>
       </c>
       <c r="Q263" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R263" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.3">
@@ -20061,7 +20040,7 @@
         <v>981</v>
       </c>
       <c r="J264" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K264">
         <v>53.76</v>
@@ -20076,16 +20055,16 @@
         <v>107.596006</v>
       </c>
       <c r="O264" s="3" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="P264" s="4">
         <v>2555187</v>
       </c>
       <c r="Q264" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R264" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.3">
@@ -20117,7 +20096,7 @@
         <v>981</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K265">
         <v>90.76</v>
@@ -20132,16 +20111,16 @@
         <v>101.41874799999999</v>
       </c>
       <c r="O265" s="3" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="P265" s="4">
         <v>1116142</v>
       </c>
       <c r="Q265" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R265" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.3">
@@ -20173,7 +20152,7 @@
         <v>981</v>
       </c>
       <c r="J266" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K266">
         <v>53.5</v>
@@ -20188,16 +20167,16 @@
         <v>101.446726</v>
       </c>
       <c r="O266" s="3" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="P266" s="4">
         <v>1116142</v>
       </c>
       <c r="Q266" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R266" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.3">
@@ -20229,7 +20208,7 @@
         <v>981</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K267">
         <v>64.25</v>
@@ -20244,16 +20223,16 @@
         <v>110.81621699999999</v>
       </c>
       <c r="O267" s="3" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="P267" s="4">
         <v>586166</v>
       </c>
       <c r="Q267" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R267" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.3">
@@ -20285,7 +20264,7 @@
         <v>981</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K268">
         <v>104.7</v>
@@ -20300,16 +20279,16 @@
         <v>106.94340800000001</v>
       </c>
       <c r="O268" s="3" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="P268" s="4">
         <v>3310145</v>
       </c>
       <c r="Q268" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R268" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.3">
@@ -20341,7 +20320,7 @@
         <v>981</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K269">
         <v>65.55</v>
@@ -20356,16 +20335,16 @@
         <v>109.128843</v>
       </c>
       <c r="O269" s="3" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="P269" s="4">
         <v>291806</v>
       </c>
       <c r="Q269" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R269" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.3">
@@ -20397,7 +20376,7 @@
         <v>981</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K270">
         <v>78.180000000000007</v>
@@ -20412,16 +20391,16 @@
         <v>112.748824</v>
       </c>
       <c r="O270" s="3" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="P270" s="4">
         <v>3000075</v>
       </c>
       <c r="Q270" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R270" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.3">
@@ -20453,7 +20432,7 @@
         <v>981</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K271">
         <v>52</v>
@@ -20468,16 +20447,16 @@
         <v>105.280238</v>
       </c>
       <c r="O271" s="3" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="P271" s="4">
         <v>1096935</v>
       </c>
       <c r="Q271" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R271" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.3">
@@ -20509,7 +20488,7 @@
         <v>981</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K272">
         <v>57.09</v>
@@ -20524,16 +20503,16 @@
         <v>98.488361999999995</v>
       </c>
       <c r="O272" s="3" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="P272" s="4">
         <v>305977</v>
       </c>
       <c r="Q272" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R272" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.3">
@@ -20565,7 +20544,7 @@
         <v>981</v>
       </c>
       <c r="J273" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="K273">
         <v>70</v>
@@ -20580,16 +20559,16 @@
         <v>106.854455</v>
       </c>
       <c r="O273" s="3" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="P273" s="4">
         <v>2408480</v>
       </c>
       <c r="Q273" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R273" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="274" spans="1:18" x14ac:dyDescent="0.3">
@@ -20621,7 +20600,7 @@
         <v>981</v>
       </c>
       <c r="J274" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="K274">
         <v>89.18</v>
@@ -20636,16 +20615,16 @@
         <v>107.149914</v>
       </c>
       <c r="O274" s="3" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="P274" s="4">
         <v>3172831</v>
       </c>
       <c r="Q274" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R274" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.3">
@@ -20677,7 +20656,7 @@
         <v>981</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="K275">
         <v>88.52</v>
@@ -20692,16 +20671,16 @@
         <v>106.94340800000001</v>
       </c>
       <c r="O275" s="3" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="P275" s="4">
         <v>3310145</v>
       </c>
       <c r="Q275" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="R275" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.3">
@@ -20733,7 +20712,7 @@
         <v>981</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K276">
         <v>60</v>
@@ -20748,16 +20727,16 @@
         <v>109.02432</v>
       </c>
       <c r="O276" s="3" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="P276" s="4">
         <v>2022808</v>
       </c>
       <c r="Q276" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R276" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.3">
@@ -20789,7 +20768,7 @@
         <v>981</v>
       </c>
       <c r="J277" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K277">
         <v>102</v>
@@ -20804,16 +20783,16 @@
         <v>116.897696</v>
       </c>
       <c r="O277" s="3" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="P277" s="4">
         <v>733397</v>
       </c>
       <c r="Q277" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R277" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="278" spans="1:18" x14ac:dyDescent="0.3">
@@ -20845,7 +20824,7 @@
         <v>981</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="K278">
         <v>89.9</v>
@@ -20860,16 +20839,16 @@
         <v>105.257766</v>
       </c>
       <c r="O278" s="3" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="P278" s="4">
         <v>1096935</v>
       </c>
       <c r="Q278" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R278" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.3">
@@ -20901,7 +20880,7 @@
         <v>21</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K279">
         <v>87.37</v>
@@ -20916,16 +20895,16 @@
         <v>108.969689</v>
       </c>
       <c r="O279" s="3" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="P279" s="4">
         <v>242146</v>
       </c>
       <c r="Q279" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R279" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.3">
@@ -20957,7 +20936,7 @@
         <v>21</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K280">
         <v>136</v>
@@ -20972,16 +20951,16 @@
         <v>114.02211</v>
       </c>
       <c r="O280" s="3" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="P280" s="4">
         <v>678471</v>
       </c>
       <c r="Q280" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R280" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.3">
@@ -21013,7 +20992,7 @@
         <v>981</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="K281">
         <v>80</v>
@@ -21028,24 +21007,24 @@
         <v>118.89269899999999</v>
       </c>
       <c r="O281" s="3" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="P281" s="4">
         <v>283282</v>
       </c>
       <c r="Q281" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="R281" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="B282" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="C282" t="s">
         <v>555</v>
@@ -21054,13 +21033,13 @@
         <v>55</v>
       </c>
       <c r="E282" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="F282" t="s">
         <v>57</v>
       </c>
       <c r="G282" t="s">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="H282" t="s">
         <v>549</v>
@@ -21084,16 +21063,16 @@
         <v>112.189042</v>
       </c>
       <c r="O282" s="3" t="s">
-        <v>1595</v>
+        <v>1588</v>
       </c>
       <c r="P282" s="4">
         <v>1679042</v>
       </c>
       <c r="Q282" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R282" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.3">
@@ -21140,16 +21119,16 @@
         <v>110.383214</v>
       </c>
       <c r="O283" s="3" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="P283" s="4">
         <v>1105415</v>
       </c>
       <c r="Q283" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R283" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.3">
@@ -21196,16 +21175,16 @@
         <v>112.64920600000001</v>
       </c>
       <c r="O284" s="3" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="P284" s="4">
         <v>1296688</v>
       </c>
       <c r="Q284" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R284" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.3">
@@ -21252,16 +21231,16 @@
         <v>112.43944</v>
       </c>
       <c r="O285" s="3" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="P285" s="4">
         <v>141335</v>
       </c>
       <c r="Q285" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R285" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.3">
@@ -21308,16 +21287,16 @@
         <v>112.1865755</v>
       </c>
       <c r="O286" s="3" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="P286" s="4">
         <v>296792</v>
       </c>
       <c r="Q286" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R286" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.3">
@@ -21364,16 +21343,16 @@
         <v>112.653008</v>
       </c>
       <c r="O287" s="3" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="P287" s="4">
         <v>874660</v>
       </c>
       <c r="Q287" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R287" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.3">
@@ -21420,24 +21399,24 @@
         <v>119.212132</v>
       </c>
       <c r="O288" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="P288" s="4">
         <v>491014</v>
       </c>
       <c r="Q288" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R288" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="B289" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="C289" t="s">
         <v>1061</v>
@@ -21476,16 +21455,16 @@
         <v>109.2401569</v>
       </c>
       <c r="O289" s="3" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="P289" s="4">
         <v>1849956</v>
       </c>
       <c r="Q289" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R289" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.3">
@@ -21532,16 +21511,16 @@
         <v>109.96825800000001</v>
       </c>
       <c r="O290" s="3" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="P290" s="4">
         <v>577770</v>
       </c>
       <c r="Q290" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R290" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.3">
@@ -21588,16 +21567,16 @@
         <v>103.628708</v>
       </c>
       <c r="O291" s="3" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="P291" s="4">
         <v>633649</v>
       </c>
       <c r="Q291" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R291" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.3">
@@ -21644,16 +21623,16 @@
         <v>101.438861</v>
       </c>
       <c r="O292" s="3" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="P292" s="4">
         <v>1116142</v>
       </c>
       <c r="Q292" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R292" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.3">
@@ -21700,16 +21679,16 @@
         <v>101.435382</v>
       </c>
       <c r="O293" s="3" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="P293" s="4">
         <v>1116142</v>
       </c>
       <c r="Q293" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R293" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.3">
@@ -21756,16 +21735,16 @@
         <v>110.81626900000001</v>
       </c>
       <c r="O294" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="P294" s="4">
         <v>586166</v>
       </c>
       <c r="Q294" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R294" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.3">
@@ -21812,16 +21791,16 @@
         <v>123.63088999999999</v>
       </c>
       <c r="O295" s="3" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="P295" s="4">
         <v>443349</v>
       </c>
       <c r="Q295" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R295" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.3">
@@ -21868,16 +21847,16 @@
         <v>110.459352</v>
       </c>
       <c r="O296" s="3" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="P296" s="4">
         <v>1693034</v>
       </c>
       <c r="Q296" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R296" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.3">
@@ -21924,16 +21903,16 @@
         <v>109.04513900000001</v>
       </c>
       <c r="O297" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="P297" s="4">
         <v>2049622</v>
       </c>
       <c r="Q297" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R297" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.3">
@@ -21980,16 +21959,16 @@
         <v>124.303524</v>
       </c>
       <c r="O298" s="3" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="P298" s="4">
         <v>2530492</v>
       </c>
       <c r="Q298" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R298" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.3">
@@ -22036,16 +22015,16 @@
         <v>104.782999</v>
       </c>
       <c r="O299" s="3" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="P299" s="4">
         <v>1761461</v>
       </c>
       <c r="Q299" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R299" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.3">
@@ -22092,16 +22071,16 @@
         <v>106.676568</v>
       </c>
       <c r="O300" s="3" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="P300" s="4">
         <v>1404786</v>
       </c>
       <c r="Q300" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R300" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.3">
@@ -22148,16 +22127,16 @@
         <v>98.659222</v>
       </c>
       <c r="O301" s="3" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="P301" s="4">
         <v>2530492</v>
       </c>
       <c r="Q301" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R301" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.3">
@@ -22204,16 +22183,16 @@
         <v>106.708175</v>
       </c>
       <c r="O302" s="3" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="P302" s="4">
         <v>1899515</v>
       </c>
       <c r="Q302" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="R302" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.3">
@@ -22260,16 +22239,16 @@
         <v>106.688096</v>
       </c>
       <c r="O303" s="3" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="P303" s="4">
         <v>1899515</v>
       </c>
       <c r="Q303" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R303" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.3">
@@ -22316,16 +22295,16 @@
         <v>105.302295</v>
       </c>
       <c r="O304" s="3" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="P304" s="4">
         <v>1096935</v>
       </c>
       <c r="Q304" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R304" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.3">
@@ -22372,16 +22351,16 @@
         <v>107.6343</v>
       </c>
       <c r="O305" s="3" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="P305" s="4">
         <v>3723181</v>
       </c>
       <c r="Q305" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="R305" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.3">
@@ -22428,16 +22407,16 @@
         <v>119.62249</v>
       </c>
       <c r="O306" s="3" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="P306" s="4">
         <v>158599</v>
       </c>
       <c r="Q306" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R306" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.3">
@@ -22484,16 +22463,16 @@
         <v>106.574645</v>
       </c>
       <c r="O307" s="3" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="P307" s="4">
         <v>1899515</v>
       </c>
       <c r="Q307" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R307" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="308" spans="1:18" x14ac:dyDescent="0.3">
@@ -22540,16 +22519,16 @@
         <v>101.402602</v>
       </c>
       <c r="O308" s="3" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="P308" s="4">
         <v>1116142</v>
       </c>
       <c r="Q308" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R308" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="309" spans="1:18" x14ac:dyDescent="0.3">
@@ -22596,16 +22575,16 @@
         <v>110.924075</v>
       </c>
       <c r="O309" s="3" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="P309" s="4">
         <v>1074475</v>
       </c>
       <c r="Q309" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R309" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="310" spans="1:18" x14ac:dyDescent="0.3">
@@ -22652,16 +22631,16 @@
         <v>99.160880000000006</v>
       </c>
       <c r="O310" s="3" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
       <c r="P310" s="4">
         <v>178524</v>
       </c>
       <c r="Q310" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R310" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.3">
@@ -22708,16 +22687,16 @@
         <v>117.58619299999999</v>
       </c>
       <c r="O311" s="3" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="P311" s="4">
         <v>246734</v>
       </c>
       <c r="Q311" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R311" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.3">
@@ -22764,16 +22743,16 @@
         <v>106.968514</v>
       </c>
       <c r="O312" s="3" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="P312" s="4">
         <v>2496198</v>
       </c>
       <c r="Q312" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R312" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="313" spans="1:18" x14ac:dyDescent="0.3">
@@ -22820,16 +22799,16 @@
         <v>111.491871</v>
       </c>
       <c r="O313" s="3" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="P313" s="4">
         <v>436351</v>
       </c>
       <c r="Q313" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R313" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="314" spans="1:18" x14ac:dyDescent="0.3">
@@ -22876,16 +22855,16 @@
         <v>116.519181</v>
       </c>
       <c r="O314" s="3" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="P314" s="4">
         <v>1404343</v>
       </c>
       <c r="Q314" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R314" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="315" spans="1:18" x14ac:dyDescent="0.3">
@@ -22932,16 +22911,16 @@
         <v>107.897812</v>
       </c>
       <c r="O315" s="3" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="P315" s="4">
         <v>2770531</v>
       </c>
       <c r="Q315" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R315" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.3">
@@ -22988,16 +22967,16 @@
         <v>99.628338999999997</v>
       </c>
       <c r="O316" s="3" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="P316" s="4">
         <v>792179</v>
       </c>
       <c r="Q316" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R316" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="317" spans="1:18" x14ac:dyDescent="0.3">
@@ -23044,16 +23023,16 @@
         <v>107.445504</v>
       </c>
       <c r="O317" s="3" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="P317" s="4">
         <v>1029561</v>
       </c>
       <c r="Q317" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R317" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="318" spans="1:18" x14ac:dyDescent="0.3">
@@ -23100,16 +23079,16 @@
         <v>106.74329400000001</v>
       </c>
       <c r="O318" s="3" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="P318" s="4">
         <v>1927869</v>
       </c>
       <c r="Q318" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R318" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="319" spans="1:18" x14ac:dyDescent="0.3">
@@ -23156,16 +23135,16 @@
         <v>115.08147200000001</v>
       </c>
       <c r="O319" s="3" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="P319" s="4">
         <v>830236</v>
       </c>
       <c r="Q319" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R319" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="320" spans="1:18" x14ac:dyDescent="0.3">
@@ -23212,16 +23191,16 @@
         <v>105.261799</v>
       </c>
       <c r="O320" s="3" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="P320" s="4">
         <v>1096935</v>
       </c>
       <c r="Q320" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R320" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="321" spans="1:18" x14ac:dyDescent="0.3">
@@ -23268,16 +23247,16 @@
         <v>119.876328</v>
       </c>
       <c r="O321" s="3" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="P321" s="4">
         <v>382017</v>
       </c>
       <c r="Q321" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R321" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="322" spans="1:18" x14ac:dyDescent="0.3">
@@ -23324,16 +23303,16 @@
         <v>120.369246</v>
       </c>
       <c r="O322" s="3" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="P322" s="4">
         <v>377580</v>
       </c>
       <c r="Q322" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R322" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="323" spans="1:18" x14ac:dyDescent="0.3">
@@ -23380,16 +23359,16 @@
         <v>114.37392699999999</v>
       </c>
       <c r="O323" s="3" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="P323" s="4">
         <v>1769233</v>
       </c>
       <c r="Q323" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R323" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="324" spans="1:18" x14ac:dyDescent="0.3">
@@ -23436,16 +23415,16 @@
         <v>108.747607</v>
       </c>
       <c r="O324" s="3" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="P324" s="4">
         <v>348911</v>
       </c>
       <c r="Q324" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R324" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.3">
@@ -23492,16 +23471,16 @@
         <v>106.150015</v>
       </c>
       <c r="O325" s="3" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="P325" s="4">
         <v>232915</v>
       </c>
       <c r="Q325" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R325" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.3">
@@ -23548,16 +23527,16 @@
         <v>120.193006</v>
       </c>
       <c r="O326" s="3" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="P326" s="4">
         <v>184296</v>
       </c>
       <c r="Q326" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R326" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="327" spans="1:18" x14ac:dyDescent="0.3">
@@ -23604,16 +23583,16 @@
         <v>107.918882</v>
       </c>
       <c r="O327" s="3" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
       <c r="P327" s="4">
         <v>1197301</v>
       </c>
       <c r="Q327" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R327" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.3">
@@ -23660,16 +23639,16 @@
         <v>98.741460000000004</v>
       </c>
       <c r="O328" s="3" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="P328" s="4">
         <v>2530492</v>
       </c>
       <c r="Q328" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R328" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.3">
@@ -23716,16 +23695,16 @@
         <v>98.449181999999993</v>
       </c>
       <c r="O329" s="3" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="P329" s="4">
         <v>1098660</v>
       </c>
       <c r="Q329" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="R329" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.3">
@@ -23772,16 +23751,16 @@
         <v>107.55388499999999</v>
       </c>
       <c r="O330" s="3" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="P330" s="4">
         <v>570829</v>
       </c>
       <c r="Q330" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="R330" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.3">
@@ -23795,16 +23774,16 @@
         <v>15</v>
       </c>
       <c r="D331" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="E331" t="s">
         <v>1208</v>
       </c>
       <c r="F331" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="G331" t="s">
-        <v>87</v>
+        <v>1209</v>
       </c>
       <c r="H331" t="s">
         <v>549</v>
@@ -23816,36 +23795,36 @@
         <v>0</v>
       </c>
       <c r="K331">
-        <v>352</v>
+        <v>121</v>
       </c>
       <c r="L331">
-        <v>19166667</v>
+        <v>12500000</v>
       </c>
       <c r="M331">
-        <v>-6.3316720000000002</v>
+        <v>2.0918670000000001</v>
       </c>
       <c r="N331">
-        <v>106.828756</v>
+        <v>99.838648000000006</v>
       </c>
       <c r="O331" s="3" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="P331" s="4">
-        <v>2408480</v>
+        <v>506673</v>
       </c>
       <c r="Q331" t="s">
-        <v>1249</v>
+        <v>1285</v>
       </c>
       <c r="R331" t="s">
-        <v>1250</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B332" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C332" t="s">
         <v>15</v>
@@ -23854,13 +23833,13 @@
         <v>117</v>
       </c>
       <c r="E332" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F332" t="s">
         <v>119</v>
       </c>
       <c r="G332" t="s">
-        <v>1212</v>
+        <v>120</v>
       </c>
       <c r="H332" t="s">
         <v>549</v>
@@ -23872,28 +23851,28 @@
         <v>0</v>
       </c>
       <c r="K332">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="L332">
-        <v>12500000</v>
+        <v>6666667</v>
       </c>
       <c r="M332">
-        <v>2.0918670000000001</v>
+        <v>3.5676420000000002</v>
       </c>
       <c r="N332">
-        <v>99.838648000000006</v>
+        <v>98.650711999999999</v>
       </c>
       <c r="O332" s="3" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="P332" s="4">
-        <v>506673</v>
+        <v>2530492</v>
       </c>
       <c r="Q332" t="s">
-        <v>1290</v>
+        <v>1244</v>
       </c>
       <c r="R332" t="s">
-        <v>1291</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.3">
@@ -23907,16 +23886,16 @@
         <v>15</v>
       </c>
       <c r="D333" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="E333" t="s">
         <v>1215</v>
       </c>
       <c r="F333" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="G333" t="s">
-        <v>120</v>
+        <v>1216</v>
       </c>
       <c r="H333" t="s">
         <v>549</v>
@@ -23928,51 +23907,51 @@
         <v>0</v>
       </c>
       <c r="K333">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L333">
-        <v>6666667</v>
+        <v>7500000</v>
       </c>
       <c r="M333">
-        <v>3.5676420000000002</v>
+        <v>-4.3561820000000004</v>
       </c>
       <c r="N333">
-        <v>98.650711999999999</v>
+        <v>119.888642</v>
       </c>
       <c r="O333" s="3" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="P333" s="4">
-        <v>2530492</v>
+        <v>240664</v>
       </c>
       <c r="Q333" t="s">
-        <v>1249</v>
+        <v>1285</v>
       </c>
       <c r="R333" t="s">
-        <v>1250</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B334" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C334" t="s">
         <v>15</v>
       </c>
       <c r="D334" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E334" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="F334" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G334" t="s">
-        <v>1219</v>
+        <v>48</v>
       </c>
       <c r="H334" t="s">
         <v>549</v>
@@ -23984,28 +23963,28 @@
         <v>0</v>
       </c>
       <c r="K334">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="L334">
-        <v>7500000</v>
+        <v>11350000</v>
       </c>
       <c r="M334">
-        <v>-4.3561820000000004</v>
+        <v>-6.919638</v>
       </c>
       <c r="N334">
-        <v>119.888642</v>
+        <v>107.569948</v>
       </c>
       <c r="O334" s="3" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="P334" s="4">
-        <v>240664</v>
+        <v>2555187</v>
       </c>
       <c r="Q334" t="s">
-        <v>1290</v>
+        <v>1244</v>
       </c>
       <c r="R334" t="s">
-        <v>1291</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.3">
@@ -24019,16 +23998,16 @@
         <v>15</v>
       </c>
       <c r="D335" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E335" t="s">
         <v>1222</v>
       </c>
       <c r="F335" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="G335" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="H335" t="s">
         <v>549</v>
@@ -24043,48 +24022,48 @@
         <v>71</v>
       </c>
       <c r="L335">
-        <v>11350000</v>
+        <v>16666667</v>
       </c>
       <c r="M335">
-        <v>-6.919638</v>
+        <v>-0.49393900000000002</v>
       </c>
       <c r="N335">
-        <v>107.569948</v>
+        <v>117.15514</v>
       </c>
       <c r="O335" s="3" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="P335" s="4">
-        <v>2555187</v>
+        <v>856361</v>
       </c>
       <c r="Q335" t="s">
-        <v>1249</v>
+        <v>1285</v>
       </c>
       <c r="R335" t="s">
-        <v>1250</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>1223</v>
+        <v>1593</v>
       </c>
       <c r="B336" t="s">
-        <v>1224</v>
+        <v>1578</v>
       </c>
       <c r="C336" t="s">
         <v>15</v>
       </c>
       <c r="D336" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E336" t="s">
-        <v>1225</v>
+        <v>1579</v>
       </c>
       <c r="F336" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="G336" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="H336" t="s">
         <v>549</v>
@@ -24096,200 +24075,88 @@
         <v>0</v>
       </c>
       <c r="K336">
+        <v>72</v>
+      </c>
+      <c r="L336">
+        <v>3334000</v>
+      </c>
+      <c r="M336" s="6">
+        <v>-8.6146250000000002</v>
+      </c>
+      <c r="N336">
+        <v>116.09873</v>
+      </c>
+      <c r="O336" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="P336" s="5">
+        <v>452812</v>
+      </c>
+      <c r="Q336" t="s">
+        <v>1285</v>
+      </c>
+      <c r="R336" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A337" s="9" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B337" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C337" t="s">
+        <v>753</v>
+      </c>
+      <c r="D337" t="s">
+        <v>46</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F337" t="s">
         <v>71</v>
       </c>
-      <c r="L336">
-        <v>16666667</v>
-      </c>
-      <c r="M336">
-        <v>-0.49393900000000002</v>
-      </c>
-      <c r="N336">
-        <v>117.15514</v>
-      </c>
-      <c r="O336" s="3" t="s">
-        <v>1583</v>
-      </c>
-      <c r="P336" s="4">
-        <v>856361</v>
-      </c>
-      <c r="Q336" t="s">
-        <v>1290</v>
-      </c>
-      <c r="R336" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A337">
-        <v>0</v>
-      </c>
-      <c r="B337" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C337" t="s">
-        <v>15</v>
-      </c>
-      <c r="D337" t="s">
-        <v>61</v>
-      </c>
-      <c r="E337" t="s">
-        <v>1227</v>
-      </c>
-      <c r="F337" t="s">
-        <v>109</v>
-      </c>
       <c r="G337" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="H337" t="s">
         <v>549</v>
       </c>
       <c r="I337" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J337" s="1">
         <v>0</v>
       </c>
       <c r="K337">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L337">
-        <v>7500000</v>
-      </c>
-      <c r="M337">
-        <v>1.5285683000000001</v>
-      </c>
-      <c r="N337">
-        <v>124.92305279999999</v>
+        <v>10000000</v>
+      </c>
+      <c r="M337" s="10">
+        <v>-7.7794319999999999</v>
+      </c>
+      <c r="N337" s="10">
+        <v>110.338553</v>
       </c>
       <c r="O337" s="3" t="s">
-        <v>1584</v>
+        <v>1594</v>
       </c>
       <c r="P337" s="4">
-        <v>478194</v>
+        <v>1105415</v>
       </c>
       <c r="Q337" t="s">
-        <v>1290</v>
+        <v>1244</v>
       </c>
       <c r="R337" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A338" t="s">
-        <v>1600</v>
-      </c>
-      <c r="B338" t="s">
-        <v>1585</v>
-      </c>
-      <c r="C338" t="s">
-        <v>15</v>
-      </c>
-      <c r="D338" t="s">
-        <v>55</v>
-      </c>
-      <c r="E338" t="s">
-        <v>1586</v>
-      </c>
-      <c r="F338" t="s">
-        <v>178</v>
-      </c>
-      <c r="G338" t="s">
-        <v>179</v>
-      </c>
-      <c r="H338" t="s">
-        <v>549</v>
-      </c>
-      <c r="I338" t="s">
-        <v>981</v>
-      </c>
-      <c r="J338" s="1">
-        <v>0</v>
-      </c>
-      <c r="K338">
-        <v>72</v>
-      </c>
-      <c r="L338">
-        <v>3334000</v>
-      </c>
-      <c r="M338" s="6">
-        <v>-8.6146250000000002</v>
-      </c>
-      <c r="N338">
-        <v>116.09873</v>
-      </c>
-      <c r="O338" s="3" t="s">
-        <v>1587</v>
-      </c>
-      <c r="P338" s="5">
-        <v>452812</v>
-      </c>
-      <c r="Q338" t="s">
-        <v>1290</v>
-      </c>
-      <c r="R338" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A339" s="9" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B339" t="s">
-        <v>1597</v>
-      </c>
-      <c r="C339" t="s">
-        <v>753</v>
-      </c>
-      <c r="D339" t="s">
-        <v>46</v>
-      </c>
-      <c r="E339" t="s">
-        <v>1598</v>
-      </c>
-      <c r="F339" t="s">
-        <v>71</v>
-      </c>
-      <c r="G339" t="s">
-        <v>72</v>
-      </c>
-      <c r="H339" t="s">
-        <v>549</v>
-      </c>
-      <c r="I339" t="s">
-        <v>21</v>
-      </c>
-      <c r="J339" s="1">
-        <v>0</v>
-      </c>
-      <c r="K339">
-        <v>64</v>
-      </c>
-      <c r="L339">
-        <v>10000000</v>
-      </c>
-      <c r="M339" s="10">
-        <v>-7.7794319999999999</v>
-      </c>
-      <c r="N339" s="10">
-        <v>110.338553</v>
-      </c>
-      <c r="O339" s="3" t="s">
-        <v>1601</v>
-      </c>
-      <c r="P339" s="4">
-        <v>1105415</v>
-      </c>
-      <c r="Q339" t="s">
-        <v>1249</v>
-      </c>
-      <c r="R339" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R339" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R337" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/output/stores_complete.xlsx
+++ b/output/stores_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6735EA95-EF88-44C5-A075-07AD92F3E8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29574A51-98E0-4CB6-8448-3F0990F2CA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5276,7 +5276,7 @@
     <col min="2" max="2" width="71.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="179.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="122.77734375" customWidth="1"/>
     <col min="6" max="6" width="33.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -20037,7 +20037,7 @@
         <v>20</v>
       </c>
       <c r="I264" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>1225</v>
@@ -20989,7 +20989,7 @@
         <v>20</v>
       </c>
       <c r="I281" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J281" s="1" t="s">
         <v>1227</v>
@@ -21381,7 +21381,7 @@
         <v>549</v>
       </c>
       <c r="I288" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J288" s="1">
         <v>0</v>
@@ -21493,7 +21493,7 @@
         <v>549</v>
       </c>
       <c r="I290" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J290" s="1">
         <v>0</v>
@@ -21549,7 +21549,7 @@
         <v>549</v>
       </c>
       <c r="I291" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J291" s="1">
         <v>0</v>
@@ -21661,7 +21661,7 @@
         <v>549</v>
       </c>
       <c r="I293" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J293" s="1">
         <v>0</v>
@@ -21773,7 +21773,7 @@
         <v>549</v>
       </c>
       <c r="I295" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J295" s="1">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>549</v>
       </c>
       <c r="I296" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J296" s="1">
         <v>0</v>
@@ -21885,7 +21885,7 @@
         <v>549</v>
       </c>
       <c r="I297" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J297" s="1">
         <v>0</v>
@@ -21997,7 +21997,7 @@
         <v>549</v>
       </c>
       <c r="I299" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J299" s="1">
         <v>0</v>
@@ -22109,7 +22109,7 @@
         <v>549</v>
       </c>
       <c r="I301" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J301" s="1">
         <v>0</v>
@@ -22333,7 +22333,7 @@
         <v>549</v>
       </c>
       <c r="I305" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J305" s="1">
         <v>0</v>
@@ -22389,7 +22389,7 @@
         <v>549</v>
       </c>
       <c r="I306" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J306" s="1">
         <v>0</v>
@@ -23117,7 +23117,7 @@
         <v>549</v>
       </c>
       <c r="I319" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J319" s="1">
         <v>0</v>
@@ -23677,7 +23677,7 @@
         <v>549</v>
       </c>
       <c r="I329" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J329" s="1">
         <v>0</v>
@@ -23733,7 +23733,7 @@
         <v>549</v>
       </c>
       <c r="I330" t="s">
-        <v>981</v>
+        <v>21</v>
       </c>
       <c r="J330" s="1">
         <v>0</v>

--- a/output/stores_complete.xlsx
+++ b/output/stores_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DBF7B2-B72E-4501-B4C3-AA52AD3291DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA41DF1-A15A-41A7-A0B0-409CD0407424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4286" uniqueCount="1601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4308" uniqueCount="1609">
   <si>
     <t>Store ID</t>
   </si>
@@ -4839,6 +4839,30 @@
   </si>
   <si>
     <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20MP.%20Mangkunegara%20Palembang%20Indonesia%20Jl.%20MP.%20Mangkunegara%2C%208%20Ilir%2C%20Kec.%20Ilir%20Tim.%20II%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030961</t>
+  </si>
+  <si>
+    <t>Xiaomi Authorized Store Av. Panglima Sudirman Batu Indonesia</t>
+  </si>
+  <si>
+    <t>Xiaomi Authorized Store Av. Dr. Ir. Soekarno Tabanan Bali Indonesia</t>
+  </si>
+  <si>
+    <t>Jl. Panglima Sudirman No.12, Ngaglik, Kec. Batu, Kota Batu, Jawa Timur 65311</t>
+  </si>
+  <si>
+    <t>Jl. Dr. Ir. Soekarno, Delod Peken No.99 , Kec. Tabanan, Kabupaten Tabanan, Bali 82121</t>
+  </si>
+  <si>
+    <t>KOTA BATU</t>
+  </si>
+  <si>
+    <t>KABUPATEN TABANAN</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Panglima%20Sudirman%20Batu%20Indonesia%20Jl.%20Panglima%20Sudirman%20No.12%2C%20Ngaglik%2C%20Kec.%20Batu%2C%20Kota%20Batu%2C%20Jawa%20Timur%2065311</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Xiaomi%20Authorized%20Store%20Av.%20Dr.%20Ir.%20Soekarno%20Tabanan%20Bali%20Indonesia%20Jl.%20Dr.%20Ir.%20Soekarno%2C%20Delod%20Peken%20No.99%2C%20Kec.%20Tabanan%2C%20Kabupaten%20Tabanan%2C%20Bali%2082121</t>
   </si>
 </sst>
 </file>
@@ -4852,7 +4876,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4884,6 +4908,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -4928,7 +4959,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4953,6 +4984,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -5267,7 +5302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R339"/>
+  <dimension ref="A1:R341"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -24265,6 +24300,118 @@
         <v>1243</v>
       </c>
     </row>
+    <row r="340" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A340">
+        <v>0</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C340" t="s">
+        <v>677</v>
+      </c>
+      <c r="D340" t="s">
+        <v>55</v>
+      </c>
+      <c r="E340" s="14" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F340" t="s">
+        <v>57</v>
+      </c>
+      <c r="G340" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H340" t="s">
+        <v>549</v>
+      </c>
+      <c r="I340" t="s">
+        <v>981</v>
+      </c>
+      <c r="J340" s="1">
+        <v>0</v>
+      </c>
+      <c r="K340">
+        <v>90</v>
+      </c>
+      <c r="L340">
+        <v>7500000</v>
+      </c>
+      <c r="M340" s="15">
+        <v>-7.8697400999999996</v>
+      </c>
+      <c r="N340" s="15">
+        <v>112.523565</v>
+      </c>
+      <c r="O340" t="s">
+        <v>1607</v>
+      </c>
+      <c r="P340" s="3">
+        <v>219840</v>
+      </c>
+      <c r="Q340" t="s">
+        <v>1242</v>
+      </c>
+      <c r="R340" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A341">
+        <v>0</v>
+      </c>
+      <c r="B341" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C341" t="s">
+        <v>670</v>
+      </c>
+      <c r="D341" t="s">
+        <v>55</v>
+      </c>
+      <c r="E341" s="14" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F341" t="s">
+        <v>192</v>
+      </c>
+      <c r="G341" t="s">
+        <v>1606</v>
+      </c>
+      <c r="H341" t="s">
+        <v>549</v>
+      </c>
+      <c r="I341" t="s">
+        <v>981</v>
+      </c>
+      <c r="J341" s="1">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>143</v>
+      </c>
+      <c r="L341">
+        <v>10000000</v>
+      </c>
+      <c r="M341" s="15">
+        <v>-8.5508150000000001</v>
+      </c>
+      <c r="N341" s="15">
+        <v>115.125559</v>
+      </c>
+      <c r="O341" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P341" s="3">
+        <v>471335</v>
+      </c>
+      <c r="Q341" t="s">
+        <v>1242</v>
+      </c>
+      <c r="R341" t="s">
+        <v>1243</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R339" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B1:B1048576">
